--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -543,10 +543,10 @@
         <v>76</v>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L2" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
@@ -601,13 +601,13 @@
         <v>87</v>
       </c>
       <c r="J3" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -662,22 +662,22 @@
         <v>61</v>
       </c>
       <c r="J4" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L4" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>15</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>21</v>
@@ -723,28 +723,28 @@
         <v>56</v>
       </c>
       <c r="J5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -781,28 +781,28 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J6" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M6" t="n">
         <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O6" t="n">
         <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J7" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M7" t="n">
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O7" t="n">
         <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -903,28 +903,28 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J8" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
         <v>14</v>
       </c>
       <c r="O8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -970,19 +970,19 @@
         <v>89</v>
       </c>
       <c r="K9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
         <v>9</v>
@@ -1028,19 +1028,19 @@
         <v>86</v>
       </c>
       <c r="J10" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M10" t="n">
         <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
@@ -1089,16 +1089,16 @@
         <v>80</v>
       </c>
       <c r="J11" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L11" t="n">
         <v>36</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
         <v>7</v>
@@ -1107,7 +1107,7 @@
         <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1147,31 +1147,31 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="N12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O12" t="n">
-        <v>5</v>
-      </c>
       <c r="P12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="13">
@@ -1211,13 +1211,13 @@
         <v>68</v>
       </c>
       <c r="J13" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K13" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M13" t="n">
         <v>3</v>
@@ -1226,10 +1226,10 @@
         <v>6</v>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1275,25 +1275,25 @@
         <v>82</v>
       </c>
       <c r="K14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L14" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>8</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
         <v>11</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="15">
@@ -1330,16 +1330,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J15" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M15" t="n">
         <v>2</v>
@@ -1391,28 +1391,28 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J16" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K16" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L16" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1452,31 +1452,31 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J17" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L17" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M17" t="n">
         <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O17" t="n">
         <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="18">
@@ -1513,28 +1513,28 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J18" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L18" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1574,16 +1574,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J19" t="n">
         <v>92</v>
       </c>
       <c r="K19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L19" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M19" t="n">
         <v>6</v>
@@ -1638,28 +1638,28 @@
         <v>68</v>
       </c>
       <c r="J20" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K20" t="n">
         <v>23</v>
       </c>
       <c r="L20" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P20" t="n">
         <v>17</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="21">
@@ -1699,13 +1699,13 @@
         <v>71</v>
       </c>
       <c r="J21" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M21" t="n">
         <v>8</v>
@@ -1717,7 +1717,7 @@
         <v>11</v>
       </c>
       <c r="P21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -1757,16 +1757,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J22" t="n">
         <v>95</v>
       </c>
       <c r="K22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L22" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M22" t="n">
         <v>2</v>
@@ -1778,7 +1778,7 @@
         <v>7</v>
       </c>
       <c r="P22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -1821,25 +1821,25 @@
         <v>84</v>
       </c>
       <c r="J23" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -1879,16 +1879,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J24" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L24" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M24" t="n">
         <v>2</v>
@@ -1897,13 +1897,13 @@
         <v>6</v>
       </c>
       <c r="O24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J25" t="n">
         <v>98</v>
@@ -1949,22 +1949,22 @@
         <v>17</v>
       </c>
       <c r="L25" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
         <v>9</v>
       </c>
       <c r="O25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P25" t="n">
         <v>16</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="26">
@@ -2001,16 +2001,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J26" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L26" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M26" t="n">
         <v>2</v>
@@ -2019,10 +2019,10 @@
         <v>6</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P26" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2068,22 +2068,22 @@
         <v>95</v>
       </c>
       <c r="K27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L27" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M27" t="n">
         <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O27" t="n">
         <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2123,28 +2123,28 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J28" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L28" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M28" t="n">
         <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O28" t="n">
         <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2190,22 +2190,22 @@
         <v>81</v>
       </c>
       <c r="K29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L29" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>8</v>
+      </c>
+      <c r="O29" t="n">
         <v>3</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
-      </c>
-      <c r="O29" t="n">
-        <v>5</v>
-      </c>
-      <c r="P29" t="n">
-        <v>16</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2245,28 +2245,28 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J30" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L30" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O30" t="n">
         <v>7</v>
       </c>
       <c r="P30" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2306,25 +2306,25 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J31" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L31" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
       <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="n">
         <v>5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>6</v>
       </c>
       <c r="P31" t="n">
         <v>13</v>
@@ -2370,13 +2370,13 @@
         <v>57</v>
       </c>
       <c r="J32" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K32" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L32" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M32" t="n">
         <v>2</v>
@@ -2385,7 +2385,7 @@
         <v>8</v>
       </c>
       <c r="O32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P32" t="n">
         <v>18</v>
@@ -2431,28 +2431,28 @@
         <v>54</v>
       </c>
       <c r="J33" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K33" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L33" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
         <v>13</v>
       </c>
       <c r="O33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P33" t="n">
         <v>17</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="34">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J34" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K34" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L34" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M34" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" t="n">
         <v>3</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>8</v>
-      </c>
-      <c r="O34" t="n">
-        <v>5</v>
       </c>
       <c r="P34" t="n">
         <v>13</v>
@@ -2553,28 +2553,28 @@
         <v>59</v>
       </c>
       <c r="J35" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K35" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L35" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M35" t="n">
         <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="36">
@@ -2617,25 +2617,25 @@
         <v>81</v>
       </c>
       <c r="K36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L36" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M36" t="n">
         <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O36" t="n">
         <v>5</v>
       </c>
       <c r="P36" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="37">
@@ -2672,28 +2672,28 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J37" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L37" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M37" t="n">
+        <v>2</v>
+      </c>
+      <c r="N37" t="n">
+        <v>14</v>
+      </c>
+      <c r="O37" t="n">
         <v>3</v>
       </c>
-      <c r="N37" t="n">
-        <v>16</v>
-      </c>
-      <c r="O37" t="n">
-        <v>5</v>
-      </c>
       <c r="P37" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -2733,28 +2733,28 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J38" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L38" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P38" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -2797,25 +2797,25 @@
         <v>74</v>
       </c>
       <c r="J39" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K39" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L39" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M39" t="n">
         <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P39" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -2916,28 +2916,28 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J41" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K41" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L41" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O41" t="n">
         <v>5</v>
       </c>
       <c r="P41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -2980,25 +2980,25 @@
         <v>52</v>
       </c>
       <c r="J42" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K42" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L42" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M42" t="n">
         <v>2</v>
       </c>
       <c r="N42" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3038,28 +3038,28 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J43" t="n">
         <v>95</v>
       </c>
       <c r="K43" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L43" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M43" t="n">
         <v>5</v>
       </c>
       <c r="N43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O43" t="n">
         <v>7</v>
       </c>
       <c r="P43" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3102,25 +3102,25 @@
         <v>61</v>
       </c>
       <c r="J44" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K44" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L44" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M44" t="n">
         <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P44" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -3163,22 +3163,22 @@
         <v>71</v>
       </c>
       <c r="J45" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K45" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L45" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
         <v>15</v>
       </c>
       <c r="O45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P45" t="n">
         <v>21</v>
@@ -3221,16 +3221,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J46" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K46" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L46" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
@@ -3239,13 +3239,13 @@
         <v>6</v>
       </c>
       <c r="O46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P46" t="n">
         <v>16</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="47">
@@ -3282,31 +3282,31 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J47" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K47" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L47" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3343,16 +3343,16 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J48" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L48" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M48" t="n">
         <v>3</v>
@@ -3364,7 +3364,7 @@
         <v>6</v>
       </c>
       <c r="P48" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -3404,28 +3404,28 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J49" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K49" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L49" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="M49" t="n">
         <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -3465,28 +3465,28 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J50" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K50" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L50" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="M50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -3526,28 +3526,28 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J51" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K51" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L51" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M51" t="n">
         <v>3</v>
       </c>
       <c r="N51" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O51" t="n">
         <v>6</v>
       </c>
       <c r="P51" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -3587,31 +3587,31 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J52" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K52" t="n">
         <v>17</v>
       </c>
       <c r="L52" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
         <v>7</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P52" t="n">
         <v>9</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="53">
@@ -3651,7 +3651,7 @@
         <v>79</v>
       </c>
       <c r="J53" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K53" t="n">
         <v>18</v>
@@ -3660,13 +3660,13 @@
         <v>36</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N53" t="n">
+        <v>10</v>
+      </c>
+      <c r="O53" t="n">
         <v>7</v>
-      </c>
-      <c r="O53" t="n">
-        <v>8</v>
       </c>
       <c r="P53" t="n">
         <v>17</v>
@@ -3715,22 +3715,22 @@
         <v>110</v>
       </c>
       <c r="K54" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L54" t="n">
         <v>36</v>
       </c>
       <c r="M54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N54" t="n">
+        <v>15</v>
+      </c>
+      <c r="O54" t="n">
         <v>6</v>
       </c>
-      <c r="O54" t="n">
-        <v>5</v>
-      </c>
       <c r="P54" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -3773,25 +3773,25 @@
         <v>75</v>
       </c>
       <c r="J55" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L55" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
         <v>11</v>
       </c>
       <c r="O55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P55" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -3840,7 +3840,7 @@
         <v>24</v>
       </c>
       <c r="L56" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M56" t="n">
         <v>2</v>
@@ -3892,28 +3892,28 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J57" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K57" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L57" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="M57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N57" t="n">
         <v>8</v>
       </c>
       <c r="O57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P57" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -3953,31 +3953,31 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J58" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K58" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L58" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M58" t="n">
         <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="59">
@@ -4014,28 +4014,28 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J59" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K59" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L59" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M59" t="n">
         <v>2</v>
       </c>
       <c r="N59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O59" t="n">
         <v>5</v>
       </c>
       <c r="P59" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4075,28 +4075,28 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J60" t="n">
         <v>92</v>
       </c>
       <c r="K60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L60" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M60" t="n">
         <v>5</v>
       </c>
       <c r="N60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O60" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P60" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -4136,16 +4136,16 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J61" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K61" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L61" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M61" t="n">
         <v>2</v>
@@ -4154,10 +4154,10 @@
         <v>9</v>
       </c>
       <c r="O61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -4197,31 +4197,31 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J62" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K62" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L62" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P62" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="63">
@@ -4261,10 +4261,10 @@
         <v>86</v>
       </c>
       <c r="J63" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K63" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L63" t="n">
         <v>37</v>
@@ -4276,10 +4276,10 @@
         <v>9</v>
       </c>
       <c r="O63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P63" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -4319,19 +4319,19 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J64" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K64" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L64" t="n">
         <v>43</v>
       </c>
       <c r="M64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N64" t="n">
         <v>6</v>
@@ -4383,28 +4383,28 @@
         <v>61</v>
       </c>
       <c r="J65" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K65" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L65" t="n">
         <v>60</v>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O65" t="n">
         <v>5</v>
       </c>
       <c r="P65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="66">
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J66" t="n">
         <v>92</v>
@@ -4450,19 +4450,19 @@
         <v>21</v>
       </c>
       <c r="L66" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M66" t="n">
         <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O66" t="n">
         <v>7</v>
       </c>
       <c r="P66" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -4502,28 +4502,28 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J67" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K67" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L67" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M67" t="n">
         <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P67" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -4563,16 +4563,16 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J68" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K68" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L68" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M68" t="n">
         <v>5</v>
@@ -4581,13 +4581,13 @@
         <v>9</v>
       </c>
       <c r="O68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P68" t="n">
         <v>14</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="69">
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J69" t="n">
         <v>100</v>
@@ -4633,10 +4633,10 @@
         <v>16</v>
       </c>
       <c r="L69" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N69" t="n">
         <v>9</v>
@@ -4648,7 +4648,7 @@
         <v>21</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="70">
@@ -4685,16 +4685,16 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J70" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K70" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L70" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M70" t="n">
         <v>5</v>
@@ -4703,13 +4703,13 @@
         <v>11</v>
       </c>
       <c r="O70" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P70" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="71">
@@ -4746,25 +4746,25 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J71" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K71" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L71" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M71" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N71" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O71" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P71" t="n">
         <v>25</v>
@@ -4810,28 +4810,28 @@
         <v>67</v>
       </c>
       <c r="J72" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K72" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L72" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N72" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="73">
@@ -4868,31 +4868,31 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J73" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K73" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L73" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N73" t="n">
         <v>13</v>
       </c>
       <c r="O73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P73" t="n">
         <v>17</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="74">
@@ -4932,28 +4932,28 @@
         <v>56</v>
       </c>
       <c r="J74" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K74" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L74" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="M74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N74" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P74" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="75">
@@ -4993,25 +4993,25 @@
         <v>65</v>
       </c>
       <c r="J75" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L75" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M75" t="n">
         <v>2</v>
       </c>
       <c r="N75" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O75" t="n">
         <v>3</v>
       </c>
       <c r="P75" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -5051,31 +5051,31 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J76" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K76" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L76" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M76" t="n">
         <v>2</v>
       </c>
       <c r="N76" t="n">
+        <v>6</v>
+      </c>
+      <c r="O76" t="n">
         <v>7</v>
       </c>
-      <c r="O76" t="n">
-        <v>5</v>
-      </c>
       <c r="P76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="77">
@@ -5112,31 +5112,31 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J77" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K77" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L77" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O77" t="n">
         <v>3</v>
       </c>
       <c r="P77" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="78">
@@ -5173,28 +5173,28 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="J78" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K78" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L78" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="M78" t="n">
         <v>3</v>
       </c>
       <c r="N78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O78" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P78" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -5237,25 +5237,25 @@
         <v>54</v>
       </c>
       <c r="J79" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K79" t="n">
         <v>21</v>
       </c>
       <c r="L79" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N79" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P79" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -5301,22 +5301,22 @@
         <v>82</v>
       </c>
       <c r="K80" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L80" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P80" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         <v>86</v>
       </c>
       <c r="K81" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L81" t="n">
         <v>72</v>
@@ -5380,7 +5380,7 @@
         <v>17</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -5417,25 +5417,25 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J82" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K82" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L82" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N82" t="n">
         <v>6</v>
       </c>
       <c r="O82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P82" t="n">
         <v>16</v>
@@ -5478,25 +5478,25 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J83" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K83" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L83" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M83" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N83" t="n">
         <v>10</v>
       </c>
       <c r="O83" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P83" t="n">
         <v>14</v>
@@ -5539,28 +5539,28 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J84" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K84" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L84" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="M84" t="n">
         <v>8</v>
       </c>
       <c r="N84" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O84" t="n">
         <v>11</v>
       </c>
       <c r="P84" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -5603,13 +5603,13 @@
         <v>57</v>
       </c>
       <c r="J85" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K85" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L85" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M85" t="n">
         <v>2</v>
@@ -5618,7 +5618,7 @@
         <v>7</v>
       </c>
       <c r="O85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P85" t="n">
         <v>14</v>
@@ -5661,31 +5661,31 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J86" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K86" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L86" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N86" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O86" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P86" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5722,16 +5722,16 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J87" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K87" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L87" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M87" t="n">
         <v>3</v>
@@ -5746,7 +5746,7 @@
         <v>19</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="88">
@@ -5783,28 +5783,28 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J88" t="n">
         <v>88</v>
       </c>
       <c r="K88" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L88" t="n">
         <v>49</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N88" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P88" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -5847,25 +5847,25 @@
         <v>88</v>
       </c>
       <c r="J89" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K89" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L89" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N89" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O89" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P89" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -5905,31 +5905,31 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J90" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K90" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L90" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M90" t="n">
         <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P90" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="91">
@@ -5969,28 +5969,28 @@
         <v>68</v>
       </c>
       <c r="J91" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K91" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L91" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M91" t="n">
         <v>5</v>
       </c>
       <c r="N91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O91" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P91" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="92">
@@ -6036,19 +6036,19 @@
         <v>16</v>
       </c>
       <c r="L92" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -6088,28 +6088,28 @@
         </is>
       </c>
       <c r="I93" t="n">
+        <v>58</v>
+      </c>
+      <c r="J93" t="n">
+        <v>85</v>
+      </c>
+      <c r="K93" t="n">
+        <v>25</v>
+      </c>
+      <c r="L93" t="n">
         <v>59</v>
       </c>
-      <c r="J93" t="n">
-        <v>84</v>
-      </c>
-      <c r="K93" t="n">
-        <v>24</v>
-      </c>
-      <c r="L93" t="n">
-        <v>58</v>
-      </c>
       <c r="M93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O93" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -6149,13 +6149,13 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J94" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K94" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L94" t="n">
         <v>37</v>
@@ -6164,10 +6164,10 @@
         <v>6</v>
       </c>
       <c r="N94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O94" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P94" t="n">
         <v>24</v>
@@ -6213,13 +6213,13 @@
         <v>73</v>
       </c>
       <c r="J95" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K95" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L95" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M95" t="n">
         <v>2</v>
@@ -6228,7 +6228,7 @@
         <v>6</v>
       </c>
       <c r="O95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P95" t="n">
         <v>17</v>
@@ -6274,25 +6274,25 @@
         <v>71</v>
       </c>
       <c r="J96" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K96" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L96" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N96" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P96" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -6335,25 +6335,25 @@
         <v>61</v>
       </c>
       <c r="J97" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K97" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L97" t="n">
         <v>55</v>
       </c>
       <c r="M97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O97" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P97" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -6396,22 +6396,22 @@
         <v>85</v>
       </c>
       <c r="J98" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K98" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L98" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M98" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N98" t="n">
         <v>13</v>
       </c>
       <c r="O98" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P98" t="n">
         <v>16</v>
@@ -6457,13 +6457,13 @@
         <v>61</v>
       </c>
       <c r="J99" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K99" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L99" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M99" t="n">
         <v>2</v>
@@ -6475,7 +6475,7 @@
         <v>5</v>
       </c>
       <c r="P99" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -6518,10 +6518,10 @@
         <v>72</v>
       </c>
       <c r="J100" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K100" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L100" t="n">
         <v>38</v>
@@ -6533,10 +6533,10 @@
         <v>8</v>
       </c>
       <c r="O100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P100" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -6576,28 +6576,28 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J101" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K101" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L101" t="n">
         <v>44</v>
       </c>
       <c r="M101" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N101" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O101" t="n">
         <v>7</v>
       </c>
       <c r="P101" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -6640,25 +6640,25 @@
         <v>59</v>
       </c>
       <c r="J102" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K102" t="n">
         <v>19</v>
       </c>
       <c r="L102" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="M102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N102" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O102" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P102" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -6698,31 +6698,31 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J103" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K103" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L103" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M103" t="n">
         <v>3</v>
       </c>
       <c r="N103" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O103" t="n">
         <v>6</v>
       </c>
       <c r="P103" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="104">
@@ -6762,22 +6762,22 @@
         <v>82</v>
       </c>
       <c r="J104" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K104" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L104" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M104" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N104" t="n">
         <v>11</v>
       </c>
       <c r="O104" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P104" t="n">
         <v>24</v>
@@ -6823,13 +6823,13 @@
         <v>73</v>
       </c>
       <c r="J105" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K105" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L105" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M105" t="n">
         <v>6</v>
@@ -6838,7 +6838,7 @@
         <v>14</v>
       </c>
       <c r="O105" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P105" t="n">
         <v>23</v>
@@ -6881,28 +6881,28 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J106" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K106" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L106" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M106" t="n">
         <v>2</v>
       </c>
       <c r="N106" t="n">
+        <v>6</v>
+      </c>
+      <c r="O106" t="n">
         <v>7</v>
       </c>
-      <c r="O106" t="n">
-        <v>5</v>
-      </c>
       <c r="P106" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -6945,25 +6945,25 @@
         <v>68</v>
       </c>
       <c r="J107" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K107" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L107" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N107" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O107" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P107" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -7006,28 +7006,28 @@
         <v>60</v>
       </c>
       <c r="J108" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K108" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L108" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M108" t="n">
         <v>3</v>
       </c>
       <c r="N108" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O108" t="n">
         <v>5</v>
       </c>
       <c r="P108" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="109">
@@ -7073,22 +7073,22 @@
         <v>22</v>
       </c>
       <c r="L109" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N109" t="n">
         <v>9</v>
       </c>
       <c r="O109" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P109" t="n">
         <v>13</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="110">
@@ -7128,25 +7128,25 @@
         <v>81</v>
       </c>
       <c r="J110" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K110" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L110" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M110" t="n">
         <v>3</v>
       </c>
       <c r="N110" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P110" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -7189,25 +7189,25 @@
         <v>68</v>
       </c>
       <c r="J111" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K111" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L111" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N111" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O111" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P111" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -7247,31 +7247,31 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J112" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K112" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L112" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N112" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O112" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P112" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="113">
@@ -7308,31 +7308,31 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J113" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K113" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L113" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="M113" t="n">
         <v>2</v>
       </c>
       <c r="N113" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O113" t="n">
         <v>5</v>
       </c>
       <c r="P113" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="114">
@@ -7369,28 +7369,28 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J114" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K114" t="n">
         <v>19</v>
       </c>
       <c r="L114" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M114" t="n">
         <v>2</v>
       </c>
       <c r="N114" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P114" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -7430,28 +7430,28 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J115" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K115" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L115" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N115" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O115" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P115" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q115" t="n">
         <v>0.02</v>
@@ -7497,22 +7497,22 @@
         <v>93</v>
       </c>
       <c r="K116" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L116" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M116" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N116" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O116" t="n">
         <v>8</v>
       </c>
       <c r="P116" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -7558,25 +7558,25 @@
         <v>85</v>
       </c>
       <c r="K117" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L117" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M117" t="n">
         <v>2</v>
       </c>
       <c r="N117" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O117" t="n">
         <v>3</v>
       </c>
       <c r="P117" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -7619,19 +7619,19 @@
         <v>80</v>
       </c>
       <c r="K118" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L118" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M118" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N118" t="n">
         <v>10</v>
       </c>
       <c r="O118" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P118" t="n">
         <v>15</v>
@@ -7674,25 +7674,25 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J119" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K119" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L119" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="M119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P119" t="n">
         <v>8</v>
@@ -7735,13 +7735,13 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J120" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K120" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L120" t="n">
         <v>69</v>
@@ -7750,16 +7750,16 @@
         <v>1</v>
       </c>
       <c r="N120" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O120" t="n">
         <v>1</v>
       </c>
       <c r="P120" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="121">
@@ -7805,19 +7805,19 @@
         <v>28</v>
       </c>
       <c r="L121" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M121" t="n">
         <v>3</v>
       </c>
       <c r="N121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P121" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -7857,16 +7857,16 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J122" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K122" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L122" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M122" t="n">
         <v>2</v>
@@ -7878,7 +7878,7 @@
         <v>6</v>
       </c>
       <c r="P122" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -7918,7 +7918,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J123" t="n">
         <v>106</v>
@@ -7927,16 +7927,16 @@
         <v>17</v>
       </c>
       <c r="L123" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M123" t="n">
         <v>2</v>
       </c>
       <c r="N123" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O123" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P123" t="n">
         <v>15</v>
@@ -7979,16 +7979,16 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J124" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K124" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L124" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M124" t="n">
         <v>2</v>
@@ -8000,7 +8000,7 @@
         <v>7</v>
       </c>
       <c r="P124" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J125" t="n">
         <v>107</v>
@@ -8049,19 +8049,19 @@
         <v>13</v>
       </c>
       <c r="L125" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N125" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O125" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P125" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -8107,22 +8107,22 @@
         <v>90</v>
       </c>
       <c r="K126" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L126" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M126" t="n">
         <v>2</v>
       </c>
       <c r="N126" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O126" t="n">
         <v>3</v>
       </c>
       <c r="P126" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J127" t="n">
         <v>98</v>
       </c>
       <c r="K127" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L127" t="n">
         <v>58</v>
@@ -8229,19 +8229,19 @@
         <v>85</v>
       </c>
       <c r="K128" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L128" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N128" t="n">
         <v>13</v>
       </c>
       <c r="O128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P128" t="n">
         <v>17</v>
@@ -8287,13 +8287,13 @@
         <v>74</v>
       </c>
       <c r="J129" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K129" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L129" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M129" t="n">
         <v>3</v>
@@ -8302,13 +8302,13 @@
         <v>7</v>
       </c>
       <c r="O129" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P129" t="n">
         <v>17</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="130">
@@ -8348,28 +8348,28 @@
         <v>66</v>
       </c>
       <c r="J130" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K130" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L130" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N130" t="n">
         <v>8</v>
       </c>
       <c r="O130" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P130" t="n">
         <v>15</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="131">
@@ -8409,25 +8409,25 @@
         <v>81</v>
       </c>
       <c r="J131" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K131" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L131" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M131" t="n">
         <v>2</v>
       </c>
       <c r="N131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O131" t="n">
         <v>6</v>
       </c>
       <c r="P131" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q131" t="n">
         <v>0</v>
@@ -8467,7 +8467,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J132" t="n">
         <v>97</v>
@@ -8476,19 +8476,19 @@
         <v>14</v>
       </c>
       <c r="L132" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M132" t="n">
         <v>2</v>
       </c>
       <c r="N132" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O132" t="n">
         <v>3</v>
       </c>
       <c r="P132" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q132" t="n">
         <v>0</v>
@@ -8528,28 +8528,28 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J133" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K133" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L133" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N133" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P133" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
@@ -8592,28 +8592,28 @@
         <v>57</v>
       </c>
       <c r="J134" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K134" t="n">
         <v>27</v>
       </c>
       <c r="L134" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N134" t="n">
         <v>14</v>
       </c>
       <c r="O134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P134" t="n">
         <v>19</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -8650,31 +8650,31 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J135" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K135" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L135" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M135" t="n">
         <v>3</v>
       </c>
       <c r="N135" t="n">
+        <v>10</v>
+      </c>
+      <c r="O135" t="n">
         <v>7</v>
       </c>
-      <c r="O135" t="n">
-        <v>8</v>
-      </c>
       <c r="P135" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="136">
@@ -8711,25 +8711,25 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J136" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K136" t="n">
         <v>22</v>
       </c>
       <c r="L136" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="M136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N136" t="n">
         <v>10</v>
       </c>
       <c r="O136" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P136" t="n">
         <v>15</v>
@@ -8772,28 +8772,28 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J137" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K137" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L137" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="M137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N137" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O137" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P137" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q137" t="n">
         <v>0</v>
@@ -8833,28 +8833,28 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J138" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K138" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L138" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M138" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N138" t="n">
         <v>9</v>
       </c>
       <c r="O138" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P138" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
@@ -8894,28 +8894,28 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J139" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K139" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L139" t="n">
         <v>71</v>
       </c>
       <c r="M139" t="n">
+        <v>2</v>
+      </c>
+      <c r="N139" t="n">
+        <v>14</v>
+      </c>
+      <c r="O139" t="n">
         <v>3</v>
       </c>
-      <c r="N139" t="n">
-        <v>16</v>
-      </c>
-      <c r="O139" t="n">
-        <v>5</v>
-      </c>
       <c r="P139" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
@@ -8955,16 +8955,16 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J140" t="n">
         <v>80</v>
       </c>
       <c r="K140" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L140" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M140" t="n">
         <v>5</v>
@@ -8973,13 +8973,13 @@
         <v>10</v>
       </c>
       <c r="O140" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P140" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="141">
@@ -9016,31 +9016,31 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J141" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K141" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L141" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N141" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O141" t="n">
         <v>8</v>
       </c>
       <c r="P141" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="142">
@@ -9083,7 +9083,7 @@
         <v>90</v>
       </c>
       <c r="K142" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L142" t="n">
         <v>56</v>
@@ -9092,13 +9092,13 @@
         <v>5</v>
       </c>
       <c r="N142" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O142" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P142" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q142" t="n">
         <v>0</v>
@@ -9141,28 +9141,28 @@
         <v>58</v>
       </c>
       <c r="J143" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K143" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L143" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M143" t="n">
         <v>2</v>
       </c>
       <c r="N143" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O143" t="n">
         <v>3</v>
       </c>
       <c r="P143" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="144">
@@ -9208,22 +9208,22 @@
         <v>23</v>
       </c>
       <c r="L144" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M144" t="n">
         <v>1</v>
       </c>
       <c r="N144" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O144" t="n">
         <v>1</v>
       </c>
       <c r="P144" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="145">
@@ -9266,25 +9266,25 @@
         <v>106</v>
       </c>
       <c r="K145" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L145" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M145" t="n">
         <v>2</v>
       </c>
       <c r="N145" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O145" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P145" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="146">
@@ -9327,25 +9327,25 @@
         <v>92</v>
       </c>
       <c r="K146" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L146" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M146" t="n">
+        <v>3</v>
+      </c>
+      <c r="N146" t="n">
+        <v>10</v>
+      </c>
+      <c r="O146" t="n">
         <v>5</v>
       </c>
-      <c r="N146" t="n">
-        <v>11</v>
-      </c>
-      <c r="O146" t="n">
-        <v>7</v>
-      </c>
       <c r="P146" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="147">
@@ -9388,10 +9388,10 @@
         <v>92</v>
       </c>
       <c r="K147" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L147" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M147" t="n">
         <v>6</v>
@@ -9400,10 +9400,10 @@
         <v>8</v>
       </c>
       <c r="O147" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P147" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q147" t="n">
         <v>0</v>
@@ -9449,25 +9449,25 @@
         <v>83</v>
       </c>
       <c r="K148" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L148" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N148" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P148" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="149">
@@ -9504,22 +9504,22 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J149" t="n">
         <v>92</v>
       </c>
       <c r="K149" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L149" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M149" t="n">
         <v>3</v>
       </c>
       <c r="N149" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O149" t="n">
         <v>7</v>
@@ -9565,28 +9565,28 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J150" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K150" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L150" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="M150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P150" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q150" t="n">
         <v>0</v>
@@ -9629,22 +9629,22 @@
         <v>77</v>
       </c>
       <c r="J151" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K151" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L151" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M151" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N151" t="n">
         <v>15</v>
       </c>
       <c r="O151" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P151" t="n">
         <v>31</v>
@@ -9690,13 +9690,13 @@
         <v>83</v>
       </c>
       <c r="J152" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K152" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L152" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M152" t="n">
         <v>1</v>
@@ -9748,31 +9748,31 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J153" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K153" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L153" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N153" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O153" t="n">
         <v>5</v>
       </c>
       <c r="P153" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="154">
@@ -9809,28 +9809,28 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J154" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K154" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L154" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="M154" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N154" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O154" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P154" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q154" t="n">
         <v>0</v>
@@ -9870,28 +9870,28 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J155" t="n">
         <v>77</v>
       </c>
       <c r="K155" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L155" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M155" t="n">
         <v>2</v>
       </c>
       <c r="N155" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O155" t="n">
         <v>3</v>
       </c>
       <c r="P155" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q155" t="n">
         <v>0.05</v>
@@ -9931,31 +9931,31 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J156" t="n">
         <v>86</v>
       </c>
       <c r="K156" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L156" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N156" t="n">
+        <v>13</v>
+      </c>
+      <c r="O156" t="n">
+        <v>1</v>
+      </c>
+      <c r="P156" t="n">
         <v>17</v>
       </c>
-      <c r="O156" t="n">
-        <v>3</v>
-      </c>
-      <c r="P156" t="n">
-        <v>24</v>
-      </c>
       <c r="Q156" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -9995,13 +9995,13 @@
         <v>57</v>
       </c>
       <c r="J157" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K157" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L157" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M157" t="n">
         <v>2</v>
@@ -10062,19 +10062,19 @@
         <v>18</v>
       </c>
       <c r="L158" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M158" t="n">
+        <v>2</v>
+      </c>
+      <c r="N158" t="n">
+        <v>14</v>
+      </c>
+      <c r="O158" t="n">
         <v>3</v>
       </c>
-      <c r="N158" t="n">
-        <v>15</v>
-      </c>
-      <c r="O158" t="n">
-        <v>5</v>
-      </c>
       <c r="P158" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q158" t="n">
         <v>0</v>

--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q158"/>
+  <dimension ref="A1:T158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +499,22 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>peak_wind_gust_time</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>solar_radiation_max</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>daily_precipitation_total</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>snow_flag</t>
         </is>
       </c>
     </row>
@@ -528,7 +543,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -560,8 +575,17 @@
       <c r="P2" t="n">
         <v>16</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>962</v>
+      </c>
+      <c r="S2" t="n">
         <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -589,7 +613,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -621,8 +645,17 @@
       <c r="P3" t="n">
         <v>22</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>929</v>
+      </c>
+      <c r="S3" t="n">
         <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -650,7 +683,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -682,8 +715,17 @@
       <c r="P4" t="n">
         <v>21</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>814</v>
+      </c>
+      <c r="S4" t="n">
         <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -711,7 +753,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -743,8 +785,17 @@
       <c r="P5" t="n">
         <v>11</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>759</v>
+      </c>
+      <c r="S5" t="n">
         <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -772,7 +823,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -804,8 +855,17 @@
       <c r="P6" t="n">
         <v>25</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>891</v>
+      </c>
+      <c r="S6" t="n">
         <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -833,7 +893,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -865,8 +925,17 @@
       <c r="P7" t="n">
         <v>16</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>810</v>
+      </c>
+      <c r="S7" t="n">
         <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -894,7 +963,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -926,8 +995,17 @@
       <c r="P8" t="n">
         <v>23</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>979</v>
+      </c>
+      <c r="S8" t="n">
         <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -955,7 +1033,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -987,8 +1065,17 @@
       <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>982</v>
+      </c>
+      <c r="S9" t="n">
         <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1016,7 +1103,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1048,8 +1135,17 @@
       <c r="P10" t="n">
         <v>17</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>909</v>
+      </c>
+      <c r="S10" t="n">
         <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1077,7 +1173,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1109,8 +1205,17 @@
       <c r="P11" t="n">
         <v>16</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>967</v>
+      </c>
+      <c r="S11" t="n">
         <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1138,7 +1243,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1170,8 +1275,17 @@
       <c r="P12" t="n">
         <v>13</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>871</v>
+      </c>
+      <c r="S12" t="n">
         <v>0.02</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1199,7 +1313,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1231,8 +1345,17 @@
       <c r="P13" t="n">
         <v>21</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>945</v>
+      </c>
+      <c r="S13" t="n">
         <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1260,7 +1383,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1292,8 +1415,17 @@
       <c r="P14" t="n">
         <v>11</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>898</v>
+      </c>
+      <c r="S14" t="n">
         <v>0.02</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1321,7 +1453,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1353,8 +1485,17 @@
       <c r="P15" t="n">
         <v>13</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>966</v>
+      </c>
+      <c r="S15" t="n">
         <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1382,7 +1523,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1414,8 +1555,17 @@
       <c r="P16" t="n">
         <v>17</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>819</v>
+      </c>
+      <c r="S16" t="n">
         <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1443,7 +1593,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1475,8 +1625,17 @@
       <c r="P17" t="n">
         <v>15</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>784</v>
+      </c>
+      <c r="S17" t="n">
         <v>0.01</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1504,7 +1663,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1536,8 +1695,17 @@
       <c r="P18" t="n">
         <v>22</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="n">
+        <v>856</v>
+      </c>
+      <c r="S18" t="n">
         <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1565,7 +1733,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1597,8 +1765,21 @@
       <c r="P19" t="n">
         <v>22</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1/4/1 17:00 LMT</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>991</v>
+      </c>
+      <c r="S19" t="n">
         <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1626,7 +1807,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1658,8 +1839,17 @@
       <c r="P20" t="n">
         <v>17</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>952</v>
+      </c>
+      <c r="S20" t="n">
         <v>0.02</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1687,7 +1877,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1719,8 +1909,17 @@
       <c r="P21" t="n">
         <v>22</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="n">
+        <v>973</v>
+      </c>
+      <c r="S21" t="n">
         <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1748,7 +1947,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1780,8 +1979,17 @@
       <c r="P22" t="n">
         <v>16</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="n">
+        <v>966</v>
+      </c>
+      <c r="S22" t="n">
         <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1809,7 +2017,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1841,8 +2049,17 @@
       <c r="P23" t="n">
         <v>26</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="n">
+        <v>892</v>
+      </c>
+      <c r="S23" t="n">
         <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1870,7 +2087,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1902,8 +2119,17 @@
       <c r="P24" t="n">
         <v>13</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>771</v>
+      </c>
+      <c r="S24" t="n">
         <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1931,7 +2157,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1963,8 +2189,17 @@
       <c r="P25" t="n">
         <v>16</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>968</v>
+      </c>
+      <c r="S25" t="n">
         <v>0.03</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1992,7 +2227,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2024,8 +2259,17 @@
       <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="n">
+        <v>825</v>
+      </c>
+      <c r="S26" t="n">
         <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -2053,7 +2297,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2085,8 +2329,17 @@
       <c r="P27" t="n">
         <v>17</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>982</v>
+      </c>
+      <c r="S27" t="n">
         <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -2114,7 +2367,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2146,8 +2399,17 @@
       <c r="P28" t="n">
         <v>21</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="n">
+        <v>939</v>
+      </c>
+      <c r="S28" t="n">
         <v>0</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2175,7 +2437,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2207,8 +2469,17 @@
       <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>708</v>
+      </c>
+      <c r="S29" t="n">
         <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2236,7 +2507,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2268,8 +2539,17 @@
       <c r="P30" t="n">
         <v>23</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="n">
+        <v>886</v>
+      </c>
+      <c r="S30" t="n">
         <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2297,7 +2577,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2329,8 +2609,17 @@
       <c r="P31" t="n">
         <v>13</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="n">
+        <v>953</v>
+      </c>
+      <c r="S31" t="n">
         <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2358,7 +2647,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2390,8 +2679,17 @@
       <c r="P32" t="n">
         <v>18</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="n">
+        <v>904</v>
+      </c>
+      <c r="S32" t="n">
         <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2419,7 +2717,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2451,8 +2749,17 @@
       <c r="P33" t="n">
         <v>17</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="n">
+        <v>717</v>
+      </c>
+      <c r="S33" t="n">
         <v>0.08</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2480,7 +2787,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2512,8 +2819,17 @@
       <c r="P34" t="n">
         <v>13</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="n">
+        <v>763</v>
+      </c>
+      <c r="S34" t="n">
         <v>0.02</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2541,7 +2857,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2573,8 +2889,17 @@
       <c r="P35" t="n">
         <v>16</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="n">
+        <v>851</v>
+      </c>
+      <c r="S35" t="n">
         <v>0.03</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2602,7 +2927,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2634,8 +2959,17 @@
       <c r="P36" t="n">
         <v>15</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="n">
+        <v>728</v>
+      </c>
+      <c r="S36" t="n">
         <v>0.06</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -2663,7 +2997,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2695,8 +3029,17 @@
       <c r="P37" t="n">
         <v>19</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>814</v>
+      </c>
+      <c r="S37" t="n">
         <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -2724,7 +3067,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2756,8 +3099,17 @@
       <c r="P38" t="n">
         <v>24</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="n">
+        <v>904</v>
+      </c>
+      <c r="S38" t="n">
         <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2785,7 +3137,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2817,8 +3169,17 @@
       <c r="P39" t="n">
         <v>21</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="n">
+        <v>992</v>
+      </c>
+      <c r="S39" t="n">
         <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -2846,7 +3207,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2878,8 +3239,17 @@
       <c r="P40" t="n">
         <v>15</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>892</v>
+      </c>
+      <c r="S40" t="n">
         <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -2907,7 +3277,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2939,8 +3309,17 @@
       <c r="P41" t="n">
         <v>16</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="n">
+        <v>822</v>
+      </c>
+      <c r="S41" t="n">
         <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -2968,7 +3347,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3000,8 +3379,17 @@
       <c r="P42" t="n">
         <v>17</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>846</v>
+      </c>
+      <c r="S42" t="n">
         <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -3029,7 +3417,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3061,8 +3449,17 @@
       <c r="P43" t="n">
         <v>19</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="n">
+        <v>955</v>
+      </c>
+      <c r="S43" t="n">
         <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -3090,7 +3487,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3122,8 +3519,17 @@
       <c r="P44" t="n">
         <v>18</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="n">
+        <v>800</v>
+      </c>
+      <c r="S44" t="n">
         <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -3151,7 +3557,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3183,8 +3589,17 @@
       <c r="P45" t="n">
         <v>21</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="n">
+        <v>952</v>
+      </c>
+      <c r="S45" t="n">
         <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -3212,7 +3627,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3244,8 +3659,17 @@
       <c r="P46" t="n">
         <v>16</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>963</v>
+      </c>
+      <c r="S46" t="n">
         <v>0.03</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -3273,7 +3697,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3305,8 +3729,17 @@
       <c r="P47" t="n">
         <v>15</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="n">
+        <v>658</v>
+      </c>
+      <c r="S47" t="n">
         <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -3334,7 +3767,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3366,8 +3799,17 @@
       <c r="P48" t="n">
         <v>22</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>939</v>
+      </c>
+      <c r="S48" t="n">
         <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -3395,7 +3837,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3427,8 +3869,17 @@
       <c r="P49" t="n">
         <v>17</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="n">
+        <v>688</v>
+      </c>
+      <c r="S49" t="n">
         <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3456,7 +3907,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3488,8 +3939,17 @@
       <c r="P50" t="n">
         <v>17</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="n">
+        <v>789</v>
+      </c>
+      <c r="S50" t="n">
         <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -3517,7 +3977,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3549,8 +4009,17 @@
       <c r="P51" t="n">
         <v>24</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="n">
+        <v>929</v>
+      </c>
+      <c r="S51" t="n">
         <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -3578,7 +4047,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3610,8 +4079,17 @@
       <c r="P52" t="n">
         <v>9</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="n">
+        <v>987</v>
+      </c>
+      <c r="S52" t="n">
         <v>0.01</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -3639,7 +4117,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3671,8 +4149,17 @@
       <c r="P53" t="n">
         <v>17</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="n">
+        <v>940</v>
+      </c>
+      <c r="S53" t="n">
         <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -3700,7 +4187,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3732,8 +4219,17 @@
       <c r="P54" t="n">
         <v>24</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="n">
+        <v>743</v>
+      </c>
+      <c r="S54" t="n">
         <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -3761,7 +4257,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3793,8 +4289,17 @@
       <c r="P55" t="n">
         <v>16</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="n">
+        <v>899</v>
+      </c>
+      <c r="S55" t="n">
         <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -3822,7 +4327,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3854,8 +4359,17 @@
       <c r="P56" t="n">
         <v>13</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="n">
+        <v>865</v>
+      </c>
+      <c r="S56" t="n">
         <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -3883,7 +4397,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3915,8 +4429,17 @@
       <c r="P57" t="n">
         <v>17</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="n">
+        <v>686</v>
+      </c>
+      <c r="S57" t="n">
         <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -3944,7 +4467,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3976,8 +4499,17 @@
       <c r="P58" t="n">
         <v>11</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="n">
+        <v>656</v>
+      </c>
+      <c r="S58" t="n">
         <v>0.05</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -4005,7 +4537,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4037,8 +4569,17 @@
       <c r="P59" t="n">
         <v>22</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>910</v>
+      </c>
+      <c r="S59" t="n">
         <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -4066,7 +4607,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4098,8 +4639,17 @@
       <c r="P60" t="n">
         <v>24</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="n">
+        <v>978</v>
+      </c>
+      <c r="S60" t="n">
         <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -4127,7 +4677,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4159,8 +4709,17 @@
       <c r="P61" t="n">
         <v>14</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="n">
+        <v>996</v>
+      </c>
+      <c r="S61" t="n">
         <v>0</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -4188,7 +4747,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4220,8 +4779,17 @@
       <c r="P62" t="n">
         <v>17</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="n">
+        <v>693</v>
+      </c>
+      <c r="S62" t="n">
         <v>0.02</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -4249,7 +4817,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4281,8 +4849,17 @@
       <c r="P63" t="n">
         <v>21</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="n">
+        <v>892</v>
+      </c>
+      <c r="S63" t="n">
         <v>0</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -4310,7 +4887,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4342,8 +4919,17 @@
       <c r="P64" t="n">
         <v>13</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="n">
+        <v>996</v>
+      </c>
+      <c r="S64" t="n">
         <v>0</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -4371,7 +4957,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4403,8 +4989,17 @@
       <c r="P65" t="n">
         <v>15</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="n">
+        <v>716</v>
+      </c>
+      <c r="S65" t="n">
         <v>0.03</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -4432,7 +5027,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4464,8 +5059,17 @@
       <c r="P66" t="n">
         <v>18</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="n">
+        <v>955</v>
+      </c>
+      <c r="S66" t="n">
         <v>0</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4493,7 +5097,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4525,8 +5129,17 @@
       <c r="P67" t="n">
         <v>24</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="n">
+        <v>839</v>
+      </c>
+      <c r="S67" t="n">
         <v>0</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -4554,7 +5167,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4586,8 +5199,17 @@
       <c r="P68" t="n">
         <v>14</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="n">
+        <v>930</v>
+      </c>
+      <c r="S68" t="n">
         <v>0.11</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -4615,7 +5237,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4647,8 +5269,17 @@
       <c r="P69" t="n">
         <v>21</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="n">
+        <v>965</v>
+      </c>
+      <c r="S69" t="n">
         <v>0.01</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -4676,7 +5307,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4708,8 +5339,17 @@
       <c r="P70" t="n">
         <v>23</v>
       </c>
-      <c r="Q70" t="n">
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="n">
+        <v>858</v>
+      </c>
+      <c r="S70" t="n">
         <v>0.04</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -4737,7 +5377,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4769,8 +5409,17 @@
       <c r="P71" t="n">
         <v>25</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="n">
+        <v>930</v>
+      </c>
+      <c r="S71" t="n">
         <v>0</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -4798,7 +5447,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4830,8 +5479,17 @@
       <c r="P72" t="n">
         <v>16</v>
       </c>
-      <c r="Q72" t="n">
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="n">
+        <v>764</v>
+      </c>
+      <c r="S72" t="n">
         <v>0.04</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -4859,7 +5517,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4891,8 +5549,17 @@
       <c r="P73" t="n">
         <v>17</v>
       </c>
-      <c r="Q73" t="n">
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="n">
+        <v>675</v>
+      </c>
+      <c r="S73" t="n">
         <v>0.03</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -4920,7 +5587,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4952,8 +5619,17 @@
       <c r="P74" t="n">
         <v>16</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="n">
+        <v>808</v>
+      </c>
+      <c r="S74" t="n">
         <v>0.01</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -4981,7 +5657,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5013,8 +5689,17 @@
       <c r="P75" t="n">
         <v>16</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="n">
+        <v>898</v>
+      </c>
+      <c r="S75" t="n">
         <v>0</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -5042,7 +5727,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5074,8 +5759,17 @@
       <c r="P76" t="n">
         <v>11</v>
       </c>
-      <c r="Q76" t="n">
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="n">
+        <v>710</v>
+      </c>
+      <c r="S76" t="n">
         <v>0.03</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -5103,7 +5797,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5135,8 +5829,17 @@
       <c r="P77" t="n">
         <v>13</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="n">
+        <v>906</v>
+      </c>
+      <c r="S77" t="n">
         <v>0.02</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -5164,7 +5867,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5196,8 +5899,17 @@
       <c r="P78" t="n">
         <v>15</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="n">
+        <v>871</v>
+      </c>
+      <c r="S78" t="n">
         <v>0</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -5225,7 +5937,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5257,8 +5969,17 @@
       <c r="P79" t="n">
         <v>16</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="n">
+        <v>818</v>
+      </c>
+      <c r="S79" t="n">
         <v>0</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -5286,7 +6007,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5318,8 +6039,17 @@
       <c r="P80" t="n">
         <v>11</v>
       </c>
-      <c r="Q80" t="n">
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="n">
+        <v>916</v>
+      </c>
+      <c r="S80" t="n">
         <v>0</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -5347,7 +6077,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5379,8 +6109,17 @@
       <c r="P81" t="n">
         <v>17</v>
       </c>
-      <c r="Q81" t="n">
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="n">
+        <v>910</v>
+      </c>
+      <c r="S81" t="n">
         <v>0</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -5408,7 +6147,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5440,8 +6179,17 @@
       <c r="P82" t="n">
         <v>16</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="n">
+        <v>922</v>
+      </c>
+      <c r="S82" t="n">
         <v>0</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -5469,7 +6217,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5501,8 +6249,17 @@
       <c r="P83" t="n">
         <v>14</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="n">
+        <v>978</v>
+      </c>
+      <c r="S83" t="n">
         <v>0</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -5530,7 +6287,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5562,8 +6319,17 @@
       <c r="P84" t="n">
         <v>19</v>
       </c>
-      <c r="Q84" t="n">
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="n">
+        <v>901</v>
+      </c>
+      <c r="S84" t="n">
         <v>0</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -5591,7 +6357,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5623,8 +6389,17 @@
       <c r="P85" t="n">
         <v>14</v>
       </c>
-      <c r="Q85" t="n">
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="n">
+        <v>929</v>
+      </c>
+      <c r="S85" t="n">
         <v>0</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -5652,7 +6427,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5684,8 +6459,17 @@
       <c r="P86" t="n">
         <v>13</v>
       </c>
-      <c r="Q86" t="n">
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="n">
+        <v>740</v>
+      </c>
+      <c r="S86" t="n">
         <v>0</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -5713,7 +6497,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5745,8 +6529,17 @@
       <c r="P87" t="n">
         <v>19</v>
       </c>
-      <c r="Q87" t="n">
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="n">
+        <v>853</v>
+      </c>
+      <c r="S87" t="n">
         <v>0.01</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -5774,7 +6567,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5806,8 +6599,17 @@
       <c r="P88" t="n">
         <v>13</v>
       </c>
-      <c r="Q88" t="n">
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="n">
+        <v>815</v>
+      </c>
+      <c r="S88" t="n">
         <v>0</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -5835,7 +6637,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5867,8 +6669,17 @@
       <c r="P89" t="n">
         <v>24</v>
       </c>
-      <c r="Q89" t="n">
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="n">
+        <v>906</v>
+      </c>
+      <c r="S89" t="n">
         <v>0</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -5896,7 +6707,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5928,8 +6739,17 @@
       <c r="P90" t="n">
         <v>14</v>
       </c>
-      <c r="Q90" t="n">
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="n">
+        <v>624</v>
+      </c>
+      <c r="S90" t="n">
         <v>0.03</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -5957,7 +6777,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5989,8 +6809,17 @@
       <c r="P91" t="n">
         <v>17</v>
       </c>
-      <c r="Q91" t="n">
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="n">
+        <v>809</v>
+      </c>
+      <c r="S91" t="n">
         <v>0.01</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -6018,7 +6847,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6050,8 +6879,17 @@
       <c r="P92" t="n">
         <v>16</v>
       </c>
-      <c r="Q92" t="n">
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="n">
+        <v>976</v>
+      </c>
+      <c r="S92" t="n">
         <v>0</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -6079,7 +6917,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6111,8 +6949,17 @@
       <c r="P93" t="n">
         <v>10</v>
       </c>
-      <c r="Q93" t="n">
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="n">
+        <v>715</v>
+      </c>
+      <c r="S93" t="n">
         <v>0</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -6140,7 +6987,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6172,8 +7019,17 @@
       <c r="P94" t="n">
         <v>24</v>
       </c>
-      <c r="Q94" t="n">
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="n">
+        <v>915</v>
+      </c>
+      <c r="S94" t="n">
         <v>0</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -6201,7 +7057,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6233,8 +7089,17 @@
       <c r="P95" t="n">
         <v>17</v>
       </c>
-      <c r="Q95" t="n">
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="n">
+        <v>978</v>
+      </c>
+      <c r="S95" t="n">
         <v>0</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -6262,7 +7127,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6294,8 +7159,17 @@
       <c r="P96" t="n">
         <v>24</v>
       </c>
-      <c r="Q96" t="n">
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="n">
+        <v>733</v>
+      </c>
+      <c r="S96" t="n">
         <v>0</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -6323,7 +7197,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6355,8 +7229,17 @@
       <c r="P97" t="n">
         <v>15</v>
       </c>
-      <c r="Q97" t="n">
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="n">
+        <v>724</v>
+      </c>
+      <c r="S97" t="n">
         <v>0</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -6384,7 +7267,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6416,8 +7299,17 @@
       <c r="P98" t="n">
         <v>16</v>
       </c>
-      <c r="Q98" t="n">
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="n">
+        <v>916</v>
+      </c>
+      <c r="S98" t="n">
         <v>0</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -6445,7 +7337,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6477,8 +7369,17 @@
       <c r="P99" t="n">
         <v>19</v>
       </c>
-      <c r="Q99" t="n">
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="n">
+        <v>903</v>
+      </c>
+      <c r="S99" t="n">
         <v>0</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -6506,7 +7407,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6538,8 +7439,17 @@
       <c r="P100" t="n">
         <v>15</v>
       </c>
-      <c r="Q100" t="n">
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="n">
+        <v>982</v>
+      </c>
+      <c r="S100" t="n">
         <v>0</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -6567,7 +7477,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6599,8 +7509,17 @@
       <c r="P101" t="n">
         <v>14</v>
       </c>
-      <c r="Q101" t="n">
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="n">
+        <v>791</v>
+      </c>
+      <c r="S101" t="n">
         <v>0</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -6628,7 +7547,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6660,8 +7579,17 @@
       <c r="P102" t="n">
         <v>15</v>
       </c>
-      <c r="Q102" t="n">
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="n">
+        <v>969</v>
+      </c>
+      <c r="S102" t="n">
         <v>0</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -6689,7 +7617,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6721,8 +7649,17 @@
       <c r="P103" t="n">
         <v>25</v>
       </c>
-      <c r="Q103" t="n">
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="n">
+        <v>902</v>
+      </c>
+      <c r="S103" t="n">
         <v>0.02</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -6750,7 +7687,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6782,8 +7719,17 @@
       <c r="P104" t="n">
         <v>24</v>
       </c>
-      <c r="Q104" t="n">
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="n">
+        <v>934</v>
+      </c>
+      <c r="S104" t="n">
         <v>0</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -6811,7 +7757,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6843,8 +7789,17 @@
       <c r="P105" t="n">
         <v>23</v>
       </c>
-      <c r="Q105" t="n">
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="n">
+        <v>962</v>
+      </c>
+      <c r="S105" t="n">
         <v>0</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -6872,7 +7827,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6904,8 +7859,17 @@
       <c r="P106" t="n">
         <v>16</v>
       </c>
-      <c r="Q106" t="n">
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="n">
+        <v>805</v>
+      </c>
+      <c r="S106" t="n">
         <v>0</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -6933,7 +7897,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6965,8 +7929,17 @@
       <c r="P107" t="n">
         <v>14</v>
       </c>
-      <c r="Q107" t="n">
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="n">
+        <v>870</v>
+      </c>
+      <c r="S107" t="n">
         <v>0</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -6994,7 +7967,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7026,8 +7999,17 @@
       <c r="P108" t="n">
         <v>21</v>
       </c>
-      <c r="Q108" t="n">
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="n">
+        <v>948</v>
+      </c>
+      <c r="S108" t="n">
         <v>0.04</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -7055,7 +8037,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7087,8 +8069,17 @@
       <c r="P109" t="n">
         <v>13</v>
       </c>
-      <c r="Q109" t="n">
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="n">
+        <v>916</v>
+      </c>
+      <c r="S109" t="n">
         <v>0.02</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -7116,7 +8107,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7148,8 +8139,17 @@
       <c r="P110" t="n">
         <v>13</v>
       </c>
-      <c r="Q110" t="n">
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="n">
+        <v>918</v>
+      </c>
+      <c r="S110" t="n">
         <v>0</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -7177,7 +8177,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7209,8 +8209,17 @@
       <c r="P111" t="n">
         <v>14</v>
       </c>
-      <c r="Q111" t="n">
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="n">
+        <v>800</v>
+      </c>
+      <c r="S111" t="n">
         <v>0</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -7238,7 +8247,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7270,8 +8279,17 @@
       <c r="P112" t="n">
         <v>14</v>
       </c>
-      <c r="Q112" t="n">
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="n">
+        <v>866</v>
+      </c>
+      <c r="S112" t="n">
         <v>0.04</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -7299,7 +8317,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7331,8 +8349,17 @@
       <c r="P113" t="n">
         <v>13</v>
       </c>
-      <c r="Q113" t="n">
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="n">
+        <v>756</v>
+      </c>
+      <c r="S113" t="n">
         <v>0.04</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -7360,7 +8387,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7392,8 +8419,17 @@
       <c r="P114" t="n">
         <v>13</v>
       </c>
-      <c r="Q114" t="n">
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="n">
+        <v>890</v>
+      </c>
+      <c r="S114" t="n">
         <v>0</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -7421,7 +8457,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7453,8 +8489,17 @@
       <c r="P115" t="n">
         <v>11</v>
       </c>
-      <c r="Q115" t="n">
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="n">
+        <v>813</v>
+      </c>
+      <c r="S115" t="n">
         <v>0.02</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -7482,7 +8527,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7514,8 +8559,17 @@
       <c r="P116" t="n">
         <v>18</v>
       </c>
-      <c r="Q116" t="n">
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="n">
+        <v>968</v>
+      </c>
+      <c r="S116" t="n">
         <v>0</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -7543,7 +8597,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7575,8 +8629,17 @@
       <c r="P117" t="n">
         <v>19</v>
       </c>
-      <c r="Q117" t="n">
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="n">
+        <v>906</v>
+      </c>
+      <c r="S117" t="n">
         <v>0</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -7604,7 +8667,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7636,8 +8699,17 @@
       <c r="P118" t="n">
         <v>15</v>
       </c>
-      <c r="Q118" t="n">
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="n">
+        <v>979</v>
+      </c>
+      <c r="S118" t="n">
         <v>0</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -7665,7 +8737,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7697,8 +8769,17 @@
       <c r="P119" t="n">
         <v>8</v>
       </c>
-      <c r="Q119" t="n">
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="n">
+        <v>827</v>
+      </c>
+      <c r="S119" t="n">
         <v>0</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -7726,7 +8807,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7758,8 +8839,17 @@
       <c r="P120" t="n">
         <v>17</v>
       </c>
-      <c r="Q120" t="n">
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="n">
+        <v>836</v>
+      </c>
+      <c r="S120" t="n">
         <v>0.01</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -7787,7 +8877,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7819,8 +8909,17 @@
       <c r="P121" t="n">
         <v>14</v>
       </c>
-      <c r="Q121" t="n">
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="n">
+        <v>924</v>
+      </c>
+      <c r="S121" t="n">
         <v>0</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -7848,7 +8947,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7880,8 +8979,17 @@
       <c r="P122" t="n">
         <v>15</v>
       </c>
-      <c r="Q122" t="n">
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="n">
+        <v>997</v>
+      </c>
+      <c r="S122" t="n">
         <v>0</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -7909,7 +9017,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7941,8 +9049,17 @@
       <c r="P123" t="n">
         <v>15</v>
       </c>
-      <c r="Q123" t="n">
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="n">
+        <v>942</v>
+      </c>
+      <c r="S123" t="n">
         <v>0</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -7970,7 +9087,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8002,8 +9119,17 @@
       <c r="P124" t="n">
         <v>16</v>
       </c>
-      <c r="Q124" t="n">
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="n">
+        <v>990</v>
+      </c>
+      <c r="S124" t="n">
         <v>0</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -8031,7 +9157,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8063,8 +9189,17 @@
       <c r="P125" t="n">
         <v>23</v>
       </c>
-      <c r="Q125" t="n">
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="n">
+        <v>958</v>
+      </c>
+      <c r="S125" t="n">
         <v>0</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -8092,7 +9227,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8124,8 +9259,17 @@
       <c r="P126" t="n">
         <v>16</v>
       </c>
-      <c r="Q126" t="n">
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="n">
+        <v>966</v>
+      </c>
+      <c r="S126" t="n">
         <v>0</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -8153,7 +9297,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8185,8 +9329,17 @@
       <c r="P127" t="n">
         <v>15</v>
       </c>
-      <c r="Q127" t="n">
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="n">
+        <v>955</v>
+      </c>
+      <c r="S127" t="n">
         <v>0</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -8214,7 +9367,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8246,8 +9399,17 @@
       <c r="P128" t="n">
         <v>17</v>
       </c>
-      <c r="Q128" t="n">
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="n">
+        <v>894</v>
+      </c>
+      <c r="S128" t="n">
         <v>0</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -8275,7 +9437,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8307,8 +9469,17 @@
       <c r="P129" t="n">
         <v>17</v>
       </c>
-      <c r="Q129" t="n">
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="n">
+        <v>918</v>
+      </c>
+      <c r="S129" t="n">
         <v>0.03</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -8336,7 +9507,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8368,8 +9539,17 @@
       <c r="P130" t="n">
         <v>15</v>
       </c>
-      <c r="Q130" t="n">
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="n">
+        <v>960</v>
+      </c>
+      <c r="S130" t="n">
         <v>0.04</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -8397,7 +9577,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8429,8 +9609,17 @@
       <c r="P131" t="n">
         <v>17</v>
       </c>
-      <c r="Q131" t="n">
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="n">
+        <v>908</v>
+      </c>
+      <c r="S131" t="n">
         <v>0</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -8458,7 +9647,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8490,8 +9679,17 @@
       <c r="P132" t="n">
         <v>15</v>
       </c>
-      <c r="Q132" t="n">
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="n">
+        <v>969</v>
+      </c>
+      <c r="S132" t="n">
         <v>0</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -8519,7 +9717,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8551,8 +9749,17 @@
       <c r="P133" t="n">
         <v>14</v>
       </c>
-      <c r="Q133" t="n">
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="n">
+        <v>812</v>
+      </c>
+      <c r="S133" t="n">
         <v>0</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -8580,7 +9787,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8612,8 +9819,17 @@
       <c r="P134" t="n">
         <v>19</v>
       </c>
-      <c r="Q134" t="n">
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="n">
+        <v>705</v>
+      </c>
+      <c r="S134" t="n">
         <v>0</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -8641,7 +9857,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8673,8 +9889,17 @@
       <c r="P135" t="n">
         <v>18</v>
       </c>
-      <c r="Q135" t="n">
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="n">
+        <v>931</v>
+      </c>
+      <c r="S135" t="n">
         <v>0.02</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -8702,7 +9927,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8734,8 +9959,17 @@
       <c r="P136" t="n">
         <v>15</v>
       </c>
-      <c r="Q136" t="n">
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="n">
+        <v>744</v>
+      </c>
+      <c r="S136" t="n">
         <v>0</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -8763,7 +9997,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8795,8 +10029,17 @@
       <c r="P137" t="n">
         <v>15</v>
       </c>
-      <c r="Q137" t="n">
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="n">
+        <v>881</v>
+      </c>
+      <c r="S137" t="n">
         <v>0</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -8824,7 +10067,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8856,8 +10099,17 @@
       <c r="P138" t="n">
         <v>22</v>
       </c>
-      <c r="Q138" t="n">
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="n">
+        <v>934</v>
+      </c>
+      <c r="S138" t="n">
         <v>0</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -8885,7 +10137,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8917,8 +10169,17 @@
       <c r="P139" t="n">
         <v>19</v>
       </c>
-      <c r="Q139" t="n">
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="n">
+        <v>871</v>
+      </c>
+      <c r="S139" t="n">
         <v>0</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -8946,7 +10207,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8978,8 +10239,17 @@
       <c r="P140" t="n">
         <v>16</v>
       </c>
-      <c r="Q140" t="n">
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="n">
+        <v>917</v>
+      </c>
+      <c r="S140" t="n">
         <v>0.03</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -9007,7 +10277,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9039,8 +10309,17 @@
       <c r="P141" t="n">
         <v>19</v>
       </c>
-      <c r="Q141" t="n">
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="n">
+        <v>872</v>
+      </c>
+      <c r="S141" t="n">
         <v>0.02</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -9068,7 +10347,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9100,8 +10379,17 @@
       <c r="P142" t="n">
         <v>19</v>
       </c>
-      <c r="Q142" t="n">
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="n">
+        <v>916</v>
+      </c>
+      <c r="S142" t="n">
         <v>0</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -9129,7 +10417,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9161,8 +10449,17 @@
       <c r="P143" t="n">
         <v>19</v>
       </c>
-      <c r="Q143" t="n">
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="n">
+        <v>819</v>
+      </c>
+      <c r="S143" t="n">
         <v>0.06</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -9190,7 +10487,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9222,8 +10519,17 @@
       <c r="P144" t="n">
         <v>15</v>
       </c>
-      <c r="Q144" t="n">
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="n">
+        <v>872</v>
+      </c>
+      <c r="S144" t="n">
         <v>0.01</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -9251,7 +10557,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9283,8 +10589,17 @@
       <c r="P145" t="n">
         <v>23</v>
       </c>
-      <c r="Q145" t="n">
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="n">
+        <v>883</v>
+      </c>
+      <c r="S145" t="n">
         <v>0.04</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -9312,7 +10627,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9344,8 +10659,17 @@
       <c r="P146" t="n">
         <v>15</v>
       </c>
-      <c r="Q146" t="n">
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="n">
+        <v>886</v>
+      </c>
+      <c r="S146" t="n">
         <v>0.14</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -9373,7 +10697,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9405,8 +10729,21 @@
       <c r="P147" t="n">
         <v>15</v>
       </c>
-      <c r="Q147" t="n">
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>1/6/1 17:00 LMT</t>
+        </is>
+      </c>
+      <c r="R147" t="n">
+        <v>975</v>
+      </c>
+      <c r="S147" t="n">
         <v>0</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -9434,7 +10771,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9466,8 +10803,17 @@
       <c r="P148" t="n">
         <v>16</v>
       </c>
-      <c r="Q148" t="n">
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="n">
+        <v>887</v>
+      </c>
+      <c r="S148" t="n">
         <v>0.01</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -9495,7 +10841,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9527,8 +10873,17 @@
       <c r="P149" t="n">
         <v>24</v>
       </c>
-      <c r="Q149" t="n">
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="n">
+        <v>804</v>
+      </c>
+      <c r="S149" t="n">
         <v>0</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -9556,7 +10911,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9588,8 +10943,17 @@
       <c r="P150" t="n">
         <v>11</v>
       </c>
-      <c r="Q150" t="n">
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="n">
+        <v>829</v>
+      </c>
+      <c r="S150" t="n">
         <v>0</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -9617,7 +10981,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9649,8 +11013,17 @@
       <c r="P151" t="n">
         <v>31</v>
       </c>
-      <c r="Q151" t="n">
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="n">
+        <v>939</v>
+      </c>
+      <c r="S151" t="n">
         <v>0</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -9678,7 +11051,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9710,8 +11083,17 @@
       <c r="P152" t="n">
         <v>23</v>
       </c>
-      <c r="Q152" t="n">
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="n">
+        <v>884</v>
+      </c>
+      <c r="S152" t="n">
         <v>0</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -9739,7 +11121,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9771,8 +11153,17 @@
       <c r="P153" t="n">
         <v>13</v>
       </c>
-      <c r="Q153" t="n">
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="n">
+        <v>744</v>
+      </c>
+      <c r="S153" t="n">
         <v>0.04</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -9800,7 +11191,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9832,8 +11223,17 @@
       <c r="P154" t="n">
         <v>17</v>
       </c>
-      <c r="Q154" t="n">
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="n">
+        <v>735</v>
+      </c>
+      <c r="S154" t="n">
         <v>0</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -9861,7 +11261,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9893,8 +11293,17 @@
       <c r="P155" t="n">
         <v>15</v>
       </c>
-      <c r="Q155" t="n">
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="n">
+        <v>775</v>
+      </c>
+      <c r="S155" t="n">
         <v>0.05</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -9922,7 +11331,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9954,8 +11363,17 @@
       <c r="P156" t="n">
         <v>17</v>
       </c>
-      <c r="Q156" t="n">
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="n">
+        <v>716</v>
+      </c>
+      <c r="S156" t="n">
         <v>0.07000000000000001</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -9983,7 +11401,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10015,8 +11433,17 @@
       <c r="P157" t="n">
         <v>18</v>
       </c>
-      <c r="Q157" t="n">
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="n">
+        <v>880</v>
+      </c>
+      <c r="S157" t="n">
         <v>0</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -10044,7 +11471,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>8/22/2026</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10076,8 +11503,17 @@
       <c r="P158" t="n">
         <v>19</v>
       </c>
-      <c r="Q158" t="n">
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="n">
+        <v>882</v>
+      </c>
+      <c r="S158" t="n">
         <v>0</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -552,32 +552,32 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>962</v>
+        <v>822</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -613,7 +613,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -622,32 +622,32 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J3" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="K3" t="n">
+        <v>22</v>
+      </c>
+      <c r="L3" t="n">
+        <v>52</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>7</v>
+      </c>
+      <c r="P3" t="n">
         <v>16</v>
-      </c>
-      <c r="L3" t="n">
-        <v>35</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>11</v>
-      </c>
-      <c r="O3" t="n">
-        <v>5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>22</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>929</v>
+        <v>837</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -683,7 +683,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -692,32 +692,32 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J4" t="n">
         <v>90</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L4" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>814</v>
+        <v>782</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -768,26 +768,26 @@
         <v>80</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P5" t="n">
         <v>11</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -832,32 +832,32 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="J6" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="M6" t="n">
         <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>891</v>
+        <v>849</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -905,32 +905,36 @@
         <v>56</v>
       </c>
       <c r="J7" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8</v>
+      </c>
+      <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>11</v>
       </c>
-      <c r="O7" t="n">
-        <v>5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1/3/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R7" t="n">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -963,7 +967,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -975,29 +979,29 @@
         <v>75</v>
       </c>
       <c r="J8" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K8" t="n">
         <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M8" t="n">
         <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>979</v>
+        <v>849</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1033,7 +1037,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1045,29 +1049,29 @@
         <v>54</v>
       </c>
       <c r="J9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L9" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
         <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
         <v>9</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>982</v>
+        <v>803</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1103,7 +1107,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1112,32 +1116,32 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J10" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L10" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="M10" t="n">
         <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>909</v>
+        <v>853</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1173,7 +1177,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1182,32 +1186,32 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J11" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
         <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>967</v>
+        <v>868</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1243,7 +1247,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1255,32 +1259,36 @@
         <v>59</v>
       </c>
       <c r="J12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L12" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1/3/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R12" t="n">
-        <v>871</v>
+        <v>802</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1313,7 +1321,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1325,29 +1333,29 @@
         <v>68</v>
       </c>
       <c r="J13" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K13" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L13" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>10</v>
       </c>
       <c r="P13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>945</v>
+        <v>832</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1383,7 +1391,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1398,29 +1406,29 @@
         <v>82</v>
       </c>
       <c r="K14" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L14" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>898</v>
+        <v>668</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1453,7 +1461,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1471,23 +1479,23 @@
         <v>13</v>
       </c>
       <c r="L15" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>966</v>
+        <v>883</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1523,7 +1531,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1532,32 +1540,32 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J16" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K16" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L16" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>819</v>
+        <v>702</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1593,7 +1601,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1605,32 +1613,32 @@
         <v>57</v>
       </c>
       <c r="J17" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K17" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M17" t="n">
         <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O17" t="n">
         <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>784</v>
+        <v>774</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1663,7 +1671,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1675,29 +1683,29 @@
         <v>65</v>
       </c>
       <c r="J18" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L18" t="n">
         <v>43</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P18" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>856</v>
+        <v>695</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1733,7 +1741,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1745,33 +1753,29 @@
         <v>68</v>
       </c>
       <c r="J19" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K19" t="n">
         <v>16</v>
       </c>
       <c r="L19" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O19" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>1/4/1 17:00 LMT</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>991</v>
+        <v>782</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -1807,7 +1811,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1816,35 +1820,35 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J20" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K20" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P20" t="n">
         <v>17</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>952</v>
+        <v>799</v>
       </c>
       <c r="S20" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1877,7 +1881,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1889,29 +1893,29 @@
         <v>71</v>
       </c>
       <c r="J21" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L21" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M21" t="n">
         <v>8</v>
       </c>
       <c r="N21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>973</v>
+        <v>870</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -1947,7 +1951,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1956,32 +1960,32 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J22" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L22" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O22" t="n">
         <v>7</v>
       </c>
       <c r="P22" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>966</v>
+        <v>875</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2017,7 +2021,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2029,29 +2033,29 @@
         <v>84</v>
       </c>
       <c r="J23" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K23" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L23" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>892</v>
+        <v>859</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2087,7 +2091,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2096,35 +2100,35 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J24" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K24" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L24" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
         <v>6</v>
       </c>
       <c r="P24" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
-        <v>771</v>
+        <v>811</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2157,7 +2161,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2166,35 +2170,35 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J25" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K25" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L25" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
+        <v>11</v>
+      </c>
+      <c r="O25" t="n">
         <v>9</v>
       </c>
-      <c r="O25" t="n">
-        <v>7</v>
-      </c>
       <c r="P25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
-        <v>968</v>
+        <v>846</v>
       </c>
       <c r="S25" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2227,7 +2231,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2236,32 +2240,32 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J26" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L26" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>825</v>
+        <v>688</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2297,7 +2301,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2309,29 +2313,29 @@
         <v>67</v>
       </c>
       <c r="J27" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K27" t="n">
         <v>14</v>
       </c>
       <c r="L27" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
+        <v>9</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
         <v>13</v>
-      </c>
-      <c r="O27" t="n">
-        <v>5</v>
-      </c>
-      <c r="P27" t="n">
-        <v>17</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>982</v>
+        <v>868</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2367,7 +2371,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2376,32 +2380,36 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J28" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K28" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L28" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P28" t="n">
         <v>21</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1/2/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R28" t="n">
-        <v>939</v>
+        <v>870</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2437,7 +2445,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2446,35 +2454,39 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J29" t="n">
         <v>81</v>
       </c>
       <c r="K29" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L29" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
         <v>8</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1/3/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R29" t="n">
-        <v>708</v>
+        <v>814</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2507,7 +2519,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2516,32 +2528,32 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J30" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K30" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L30" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O30" t="n">
         <v>7</v>
       </c>
       <c r="P30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>886</v>
+        <v>776</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2577,7 +2589,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2586,32 +2598,32 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J31" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K31" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L31" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P31" t="n">
         <v>13</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>953</v>
+        <v>823</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -2647,7 +2659,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2659,29 +2671,29 @@
         <v>57</v>
       </c>
       <c r="J32" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L32" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M32" t="n">
         <v>2</v>
       </c>
       <c r="N32" t="n">
+        <v>6</v>
+      </c>
+      <c r="O32" t="n">
         <v>8</v>
       </c>
-      <c r="O32" t="n">
-        <v>6</v>
-      </c>
       <c r="P32" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="n">
-        <v>904</v>
+        <v>814</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -2717,7 +2729,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2729,32 +2741,32 @@
         <v>54</v>
       </c>
       <c r="J33" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K33" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L33" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N33" t="n">
+        <v>9</v>
+      </c>
+      <c r="O33" t="n">
+        <v>8</v>
+      </c>
+      <c r="P33" t="n">
         <v>13</v>
-      </c>
-      <c r="O33" t="n">
-        <v>7</v>
-      </c>
-      <c r="P33" t="n">
-        <v>17</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="S33" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2787,7 +2799,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2796,35 +2808,35 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J34" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K34" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L34" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="M34" t="n">
         <v>2</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P34" t="n">
         <v>13</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="n">
-        <v>763</v>
+        <v>724</v>
       </c>
       <c r="S34" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -2857,7 +2869,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2866,16 +2878,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J35" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K35" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L35" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M35" t="n">
         <v>2</v>
@@ -2891,10 +2903,10 @@
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="n">
-        <v>851</v>
+        <v>839</v>
       </c>
       <c r="S35" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -2927,7 +2939,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2939,32 +2951,32 @@
         <v>57</v>
       </c>
       <c r="J36" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K36" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L36" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P36" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
-        <v>728</v>
+        <v>779</v>
       </c>
       <c r="S36" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -2997,7 +3009,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3006,32 +3018,32 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J37" t="n">
         <v>84</v>
       </c>
       <c r="K37" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L37" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M37" t="n">
         <v>2</v>
       </c>
       <c r="N37" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="n">
-        <v>814</v>
+        <v>751</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3067,7 +3079,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3076,32 +3088,32 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="J38" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K38" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L38" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="M38" t="n">
         <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
-        <v>904</v>
+        <v>869</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3137,7 +3149,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3149,29 +3161,29 @@
         <v>74</v>
       </c>
       <c r="J39" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K39" t="n">
         <v>14</v>
       </c>
       <c r="L39" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="M39" t="n">
         <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
         <v>7</v>
       </c>
       <c r="P39" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
-        <v>992</v>
+        <v>895</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3207,7 +3219,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3216,32 +3228,32 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J40" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K40" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L40" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P40" t="n">
         <v>15</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="n">
-        <v>892</v>
+        <v>824</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3277,7 +3289,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3286,32 +3298,32 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J41" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K41" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L41" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M41" t="n">
         <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O41" t="n">
         <v>5</v>
       </c>
       <c r="P41" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
-        <v>822</v>
+        <v>602</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -3347,7 +3359,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3356,32 +3368,32 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J42" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K42" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L42" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="M42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="n">
-        <v>846</v>
+        <v>775</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3417,7 +3429,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3426,32 +3438,32 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J43" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K43" t="n">
         <v>14</v>
       </c>
       <c r="L43" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N43" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P43" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="n">
-        <v>955</v>
+        <v>827</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3487,7 +3499,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3496,32 +3508,32 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J44" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K44" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L44" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O44" t="n">
         <v>7</v>
       </c>
       <c r="P44" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="n">
-        <v>800</v>
+        <v>735</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -3557,7 +3569,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3569,29 +3581,29 @@
         <v>71</v>
       </c>
       <c r="J45" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L45" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N45" t="n">
+        <v>10</v>
+      </c>
+      <c r="O45" t="n">
+        <v>7</v>
+      </c>
+      <c r="P45" t="n">
         <v>15</v>
-      </c>
-      <c r="O45" t="n">
-        <v>5</v>
-      </c>
-      <c r="P45" t="n">
-        <v>21</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
-        <v>952</v>
+        <v>863</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -3627,7 +3639,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3636,35 +3648,35 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J46" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K46" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L46" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
       </c>
       <c r="N46" t="n">
+        <v>7</v>
+      </c>
+      <c r="O46" t="n">
         <v>6</v>
       </c>
-      <c r="O46" t="n">
-        <v>5</v>
-      </c>
       <c r="P46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="n">
-        <v>963</v>
+        <v>824</v>
       </c>
       <c r="S46" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -3697,7 +3709,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3709,32 +3721,32 @@
         <v>56</v>
       </c>
       <c r="J47" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K47" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L47" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P47" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="n">
-        <v>658</v>
+        <v>694</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -3767,7 +3779,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3776,32 +3788,32 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J48" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K48" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L48" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O48" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P48" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="n">
-        <v>939</v>
+        <v>880</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -3837,7 +3849,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3846,13 +3858,13 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J49" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K49" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L49" t="n">
         <v>39</v>
@@ -3861,20 +3873,20 @@
         <v>3</v>
       </c>
       <c r="N49" t="n">
+        <v>6</v>
+      </c>
+      <c r="O49" t="n">
         <v>8</v>
       </c>
-      <c r="O49" t="n">
-        <v>7</v>
-      </c>
       <c r="P49" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="n">
-        <v>688</v>
+        <v>604</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -3907,7 +3919,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3919,32 +3931,32 @@
         <v>66</v>
       </c>
       <c r="J50" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K50" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L50" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P50" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="n">
-        <v>789</v>
+        <v>744</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -3977,7 +3989,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3986,32 +3998,32 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="J51" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K51" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L51" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O51" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P51" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="n">
-        <v>929</v>
+        <v>880</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -4047,7 +4059,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4059,32 +4071,32 @@
         <v>56</v>
       </c>
       <c r="J52" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L52" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
         <v>7</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P52" t="n">
         <v>9</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="n">
-        <v>987</v>
+        <v>801</v>
       </c>
       <c r="S52" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -4117,7 +4129,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4126,32 +4138,32 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J53" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K53" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L53" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N53" t="n">
+        <v>8</v>
+      </c>
+      <c r="O53" t="n">
         <v>10</v>
       </c>
-      <c r="O53" t="n">
-        <v>7</v>
-      </c>
       <c r="P53" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="n">
-        <v>940</v>
+        <v>843</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -4187,7 +4199,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4196,32 +4208,32 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J54" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K54" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L54" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>9</v>
+      </c>
+      <c r="O54" t="n">
         <v>2</v>
       </c>
-      <c r="N54" t="n">
-        <v>15</v>
-      </c>
-      <c r="O54" t="n">
-        <v>6</v>
-      </c>
       <c r="P54" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="n">
-        <v>743</v>
+        <v>822</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -4257,7 +4269,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4266,32 +4278,32 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J55" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K55" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L55" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="M55" t="n">
         <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O55" t="n">
         <v>5</v>
       </c>
       <c r="P55" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="n">
-        <v>899</v>
+        <v>784</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -4327,7 +4339,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4342,26 +4354,26 @@
         <v>82</v>
       </c>
       <c r="K56" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L56" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="M56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P56" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="n">
-        <v>865</v>
+        <v>716</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -4397,7 +4409,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4406,35 +4418,35 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J57" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K57" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L57" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="M57" t="n">
         <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P57" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="n">
-        <v>686</v>
+        <v>711</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -4467,7 +4479,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4482,10 +4494,10 @@
         <v>79</v>
       </c>
       <c r="K58" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L58" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M58" t="n">
         <v>2</v>
@@ -4497,14 +4509,14 @@
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="n">
-        <v>656</v>
+        <v>699</v>
       </c>
       <c r="S58" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -4537,7 +4549,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4546,32 +4558,32 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J59" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K59" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L59" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M59" t="n">
         <v>2</v>
       </c>
       <c r="N59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P59" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="n">
-        <v>910</v>
+        <v>657</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -4607,7 +4619,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4622,26 +4634,26 @@
         <v>92</v>
       </c>
       <c r="K60" t="n">
+        <v>16</v>
+      </c>
+      <c r="L60" t="n">
+        <v>37</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3</v>
+      </c>
+      <c r="N60" t="n">
         <v>15</v>
       </c>
-      <c r="L60" t="n">
-        <v>41</v>
-      </c>
-      <c r="M60" t="n">
-        <v>5</v>
-      </c>
-      <c r="N60" t="n">
-        <v>16</v>
-      </c>
       <c r="O60" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P60" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="n">
-        <v>978</v>
+        <v>894</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -4677,7 +4689,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4686,32 +4698,32 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J61" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K61" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L61" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="M61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P61" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="n">
-        <v>996</v>
+        <v>910</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -4747,7 +4759,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4756,35 +4768,35 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J62" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K62" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L62" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O62" t="n">
         <v>3</v>
       </c>
       <c r="P62" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="n">
-        <v>693</v>
+        <v>625</v>
       </c>
       <c r="S62" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -4817,7 +4829,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4829,29 +4841,29 @@
         <v>86</v>
       </c>
       <c r="J63" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="K63" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L63" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="n">
-        <v>892</v>
+        <v>805</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -4887,7 +4899,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4896,16 +4908,16 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J64" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K64" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L64" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
@@ -4914,14 +4926,14 @@
         <v>6</v>
       </c>
       <c r="O64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P64" t="n">
         <v>13</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="n">
-        <v>996</v>
+        <v>826</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -4957,7 +4969,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4966,35 +4978,35 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J65" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K65" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L65" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M65" t="n">
         <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O65" t="n">
         <v>5</v>
       </c>
       <c r="P65" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="n">
-        <v>716</v>
+        <v>743</v>
       </c>
       <c r="S65" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -5027,7 +5039,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5036,32 +5048,32 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J66" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K66" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L66" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M66" t="n">
         <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="n">
-        <v>955</v>
+        <v>758</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5097,7 +5109,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5106,13 +5118,13 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J67" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K67" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L67" t="n">
         <v>56</v>
@@ -5121,17 +5133,17 @@
         <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O67" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P67" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="n">
-        <v>839</v>
+        <v>868</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -5167,7 +5179,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5176,16 +5188,16 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J68" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K68" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="L68" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M68" t="n">
         <v>5</v>
@@ -5194,17 +5206,17 @@
         <v>9</v>
       </c>
       <c r="O68" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P68" t="n">
         <v>14</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="n">
-        <v>930</v>
+        <v>816</v>
       </c>
       <c r="S68" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5237,7 +5249,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5246,35 +5258,35 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J69" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K69" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L69" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="M69" t="n">
         <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O69" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P69" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="n">
-        <v>965</v>
+        <v>861</v>
       </c>
       <c r="S69" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -5307,7 +5319,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5316,35 +5328,35 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J70" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K70" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L70" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P70" t="n">
         <v>23</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="n">
-        <v>858</v>
+        <v>747</v>
       </c>
       <c r="S70" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -5377,7 +5389,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5389,32 +5401,32 @@
         <v>68</v>
       </c>
       <c r="J71" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K71" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L71" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M71" t="n">
         <v>7</v>
       </c>
       <c r="N71" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O71" t="n">
         <v>13</v>
       </c>
       <c r="P71" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="n">
-        <v>930</v>
+        <v>828</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -5447,7 +5459,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5456,32 +5468,32 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J72" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K72" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L72" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="M72" t="n">
         <v>1</v>
       </c>
       <c r="N72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="n">
-        <v>764</v>
+        <v>822</v>
       </c>
       <c r="S72" t="n">
         <v>0.04</v>
@@ -5517,7 +5529,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5535,26 +5547,30 @@
         <v>22</v>
       </c>
       <c r="L73" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="M73" t="n">
         <v>2</v>
       </c>
       <c r="N73" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O73" t="n">
         <v>3</v>
       </c>
       <c r="P73" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q73" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1/3/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R73" t="n">
-        <v>675</v>
+        <v>523</v>
       </c>
       <c r="S73" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5587,7 +5603,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5596,16 +5612,16 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J74" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K74" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L74" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="M74" t="n">
         <v>5</v>
@@ -5621,10 +5637,10 @@
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="n">
-        <v>808</v>
+        <v>645</v>
       </c>
       <c r="S74" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -5657,7 +5673,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5672,26 +5688,26 @@
         <v>93</v>
       </c>
       <c r="K75" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L75" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M75" t="n">
         <v>2</v>
       </c>
       <c r="N75" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O75" t="n">
         <v>3</v>
       </c>
       <c r="P75" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
-        <v>898</v>
+        <v>826</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -5727,7 +5743,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5739,29 +5755,29 @@
         <v>58</v>
       </c>
       <c r="J76" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K76" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L76" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M76" t="n">
         <v>2</v>
       </c>
       <c r="N76" t="n">
+        <v>5</v>
+      </c>
+      <c r="O76" t="n">
         <v>6</v>
       </c>
-      <c r="O76" t="n">
-        <v>7</v>
-      </c>
       <c r="P76" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="n">
-        <v>710</v>
+        <v>752</v>
       </c>
       <c r="S76" t="n">
         <v>0.03</v>
@@ -5797,7 +5813,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5806,35 +5822,35 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J77" t="n">
         <v>89</v>
       </c>
       <c r="K77" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L77" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N77" t="n">
         <v>6</v>
       </c>
       <c r="O77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P77" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="n">
-        <v>906</v>
+        <v>785</v>
       </c>
       <c r="S77" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -5867,7 +5883,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5876,35 +5892,35 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J78" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K78" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L78" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M78" t="n">
         <v>3</v>
       </c>
       <c r="N78" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P78" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="n">
-        <v>871</v>
+        <v>625</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -5937,7 +5953,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5952,10 +5968,10 @@
         <v>87</v>
       </c>
       <c r="K79" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L79" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="M79" t="n">
         <v>2</v>
@@ -5971,7 +5987,7 @@
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="n">
-        <v>818</v>
+        <v>790</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -6007,7 +6023,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6016,32 +6032,32 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J80" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K80" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L80" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M80" t="n">
         <v>3</v>
       </c>
       <c r="N80" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O80" t="n">
         <v>5</v>
       </c>
       <c r="P80" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="n">
-        <v>916</v>
+        <v>782</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -6077,7 +6093,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6086,32 +6102,32 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J81" t="n">
         <v>86</v>
       </c>
       <c r="K81" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L81" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N81" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P81" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="n">
-        <v>910</v>
+        <v>745</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -6147,7 +6163,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6156,32 +6172,32 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J82" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K82" t="n">
         <v>16</v>
       </c>
       <c r="L82" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="M82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N82" t="n">
         <v>6</v>
       </c>
       <c r="O82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P82" t="n">
         <v>16</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="n">
-        <v>922</v>
+        <v>767</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -6217,7 +6233,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6229,29 +6245,29 @@
         <v>69</v>
       </c>
       <c r="J83" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K83" t="n">
         <v>13</v>
       </c>
       <c r="L83" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N83" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P83" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="n">
-        <v>978</v>
+        <v>877</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -6287,7 +6303,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6305,23 +6321,27 @@
         <v>12</v>
       </c>
       <c r="L84" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M84" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N84" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O84" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P84" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q84" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1/7/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R84" t="n">
-        <v>901</v>
+        <v>858</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -6357,7 +6377,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6369,16 +6389,16 @@
         <v>57</v>
       </c>
       <c r="J85" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K85" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L85" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="M85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N85" t="n">
         <v>7</v>
@@ -6387,11 +6407,11 @@
         <v>6</v>
       </c>
       <c r="P85" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="n">
-        <v>929</v>
+        <v>824</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -6427,7 +6447,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6436,35 +6456,39 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J86" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K86" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L86" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="M86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O86" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P86" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q86" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1/3/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R86" t="n">
-        <v>740</v>
+        <v>827</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -6497,7 +6521,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6506,35 +6530,35 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J87" t="n">
         <v>95</v>
       </c>
       <c r="K87" t="n">
+        <v>17</v>
+      </c>
+      <c r="L87" t="n">
+        <v>72</v>
+      </c>
+      <c r="M87" t="n">
+        <v>6</v>
+      </c>
+      <c r="N87" t="n">
         <v>18</v>
       </c>
-      <c r="L87" t="n">
-        <v>65</v>
-      </c>
-      <c r="M87" t="n">
-        <v>3</v>
-      </c>
-      <c r="N87" t="n">
-        <v>14</v>
-      </c>
       <c r="O87" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P87" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="n">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="S87" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -6567,7 +6591,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6576,32 +6600,32 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J88" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K88" t="n">
         <v>20</v>
       </c>
       <c r="L88" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="M88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N88" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P88" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="n">
-        <v>815</v>
+        <v>779</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -6637,7 +6661,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6646,32 +6670,32 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J89" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K89" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L89" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="M89" t="n">
         <v>3</v>
       </c>
       <c r="N89" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P89" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="n">
-        <v>906</v>
+        <v>783</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -6707,7 +6731,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6716,35 +6740,35 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J90" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K90" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L90" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="M90" t="n">
         <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O90" t="n">
         <v>3</v>
       </c>
       <c r="P90" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="n">
-        <v>624</v>
+        <v>552</v>
       </c>
       <c r="S90" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -6777,7 +6801,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6786,35 +6810,35 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J91" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K91" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="L91" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="M91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N91" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O91" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P91" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="n">
-        <v>809</v>
+        <v>776</v>
       </c>
       <c r="S91" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -6847,7 +6871,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6859,29 +6883,29 @@
         <v>62</v>
       </c>
       <c r="J92" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K92" t="n">
         <v>16</v>
       </c>
       <c r="L92" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="M92" t="n">
+        <v>2</v>
+      </c>
+      <c r="N92" t="n">
+        <v>7</v>
+      </c>
+      <c r="O92" t="n">
         <v>3</v>
       </c>
-      <c r="N92" t="n">
-        <v>11</v>
-      </c>
-      <c r="O92" t="n">
-        <v>5</v>
-      </c>
       <c r="P92" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="n">
-        <v>976</v>
+        <v>801</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -6917,7 +6941,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6926,32 +6950,32 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J93" t="n">
         <v>85</v>
       </c>
       <c r="K93" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L93" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M93" t="n">
         <v>1</v>
       </c>
       <c r="N93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P93" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="n">
-        <v>715</v>
+        <v>749</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -6987,7 +7011,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6999,32 +7023,32 @@
         <v>64</v>
       </c>
       <c r="J94" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K94" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L94" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N94" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O94" t="n">
         <v>11</v>
       </c>
       <c r="P94" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
-        <v>915</v>
+        <v>861</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -7057,7 +7081,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7066,32 +7090,32 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J95" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K95" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L95" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="M95" t="n">
         <v>2</v>
       </c>
       <c r="N95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P95" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="n">
-        <v>978</v>
+        <v>879</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -7127,7 +7151,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7136,32 +7160,32 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J96" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K96" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L96" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="M96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N96" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="n">
-        <v>733</v>
+        <v>843</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -7197,7 +7221,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7209,29 +7233,29 @@
         <v>61</v>
       </c>
       <c r="J97" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K97" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L97" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N97" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O97" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="n">
-        <v>724</v>
+        <v>690</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -7267,7 +7291,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7279,29 +7303,33 @@
         <v>85</v>
       </c>
       <c r="J98" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K98" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L98" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M98" t="n">
         <v>6</v>
       </c>
       <c r="N98" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P98" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q98" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1/1/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R98" t="n">
-        <v>916</v>
+        <v>792</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -7337,7 +7365,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7346,35 +7374,35 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J99" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K99" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L99" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M99" t="n">
         <v>2</v>
       </c>
       <c r="N99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O99" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P99" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="n">
-        <v>903</v>
+        <v>857</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -7407,7 +7435,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7416,32 +7444,32 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J100" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K100" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L100" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N100" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O100" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P100" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="n">
-        <v>982</v>
+        <v>898</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -7477,7 +7505,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7486,32 +7514,32 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J101" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K101" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L101" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M101" t="n">
         <v>2</v>
       </c>
       <c r="N101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O101" t="n">
         <v>7</v>
       </c>
       <c r="P101" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="n">
-        <v>791</v>
+        <v>728</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -7547,7 +7575,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7556,32 +7584,32 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J102" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K102" t="n">
         <v>19</v>
       </c>
       <c r="L102" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="M102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N102" t="n">
         <v>10</v>
       </c>
       <c r="O102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P102" t="n">
         <v>15</v>
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="n">
-        <v>969</v>
+        <v>800</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -7617,7 +7645,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7626,35 +7654,35 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J103" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="K103" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L103" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="M103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N103" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O103" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P103" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="n">
-        <v>902</v>
+        <v>769</v>
       </c>
       <c r="S103" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -7687,7 +7715,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7696,32 +7724,32 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J104" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K104" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L104" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M104" t="n">
         <v>6</v>
       </c>
       <c r="N104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O104" t="n">
         <v>11</v>
       </c>
       <c r="P104" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="n">
-        <v>934</v>
+        <v>767</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -7757,7 +7785,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7769,29 +7797,29 @@
         <v>73</v>
       </c>
       <c r="J105" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K105" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L105" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M105" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N105" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O105" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P105" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="n">
-        <v>962</v>
+        <v>870</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -7827,7 +7855,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7836,35 +7864,35 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J106" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K106" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L106" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O106" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P106" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="n">
-        <v>805</v>
+        <v>688</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -7897,7 +7925,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7906,7 +7934,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J107" t="n">
         <v>95</v>
@@ -7915,23 +7943,23 @@
         <v>22</v>
       </c>
       <c r="L107" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="M107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N107" t="n">
         <v>6</v>
       </c>
       <c r="O107" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P107" t="n">
         <v>14</v>
       </c>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="n">
-        <v>870</v>
+        <v>702</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -7967,7 +7995,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7976,35 +8004,35 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J108" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K108" t="n">
         <v>20</v>
       </c>
       <c r="L108" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M108" t="n">
         <v>3</v>
       </c>
       <c r="N108" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O108" t="n">
         <v>5</v>
       </c>
       <c r="P108" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="n">
-        <v>948</v>
+        <v>803</v>
       </c>
       <c r="S108" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -8037,7 +8065,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8046,35 +8074,35 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J109" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K109" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L109" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M109" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N109" t="n">
         <v>9</v>
       </c>
       <c r="O109" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P109" t="n">
         <v>13</v>
       </c>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="n">
-        <v>916</v>
+        <v>763</v>
       </c>
       <c r="S109" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -8107,7 +8135,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8119,29 +8147,29 @@
         <v>81</v>
       </c>
       <c r="J110" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K110" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="L110" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="M110" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" t="n">
+        <v>8</v>
+      </c>
+      <c r="O110" t="n">
         <v>3</v>
       </c>
-      <c r="N110" t="n">
-        <v>7</v>
-      </c>
-      <c r="O110" t="n">
-        <v>5</v>
-      </c>
       <c r="P110" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="n">
-        <v>918</v>
+        <v>862</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -8177,7 +8205,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8186,16 +8214,16 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J111" t="n">
         <v>94</v>
       </c>
       <c r="K111" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L111" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="M111" t="n">
         <v>2</v>
@@ -8204,14 +8232,14 @@
         <v>6</v>
       </c>
       <c r="O111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P111" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="n">
-        <v>800</v>
+        <v>745</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -8247,7 +8275,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8256,35 +8284,35 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J112" t="n">
         <v>89</v>
       </c>
       <c r="K112" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L112" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N112" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P112" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="n">
-        <v>866</v>
+        <v>776</v>
       </c>
       <c r="S112" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -8317,7 +8345,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8326,35 +8354,35 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J113" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K113" t="n">
         <v>24</v>
       </c>
       <c r="L113" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M113" t="n">
         <v>2</v>
       </c>
       <c r="N113" t="n">
+        <v>5</v>
+      </c>
+      <c r="O113" t="n">
         <v>6</v>
       </c>
-      <c r="O113" t="n">
-        <v>5</v>
-      </c>
       <c r="P113" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="n">
-        <v>756</v>
+        <v>722</v>
       </c>
       <c r="S113" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -8387,7 +8415,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8396,32 +8424,32 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J114" t="n">
         <v>95</v>
       </c>
       <c r="K114" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L114" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N114" t="n">
         <v>5</v>
       </c>
       <c r="O114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P114" t="n">
         <v>13</v>
       </c>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="n">
-        <v>890</v>
+        <v>855</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -8457,7 +8485,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8466,32 +8494,32 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J115" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K115" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L115" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O115" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P115" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="n">
-        <v>813</v>
+        <v>692</v>
       </c>
       <c r="S115" t="n">
         <v>0.02</v>
@@ -8527,7 +8555,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8536,32 +8564,32 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J116" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K116" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L116" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N116" t="n">
+        <v>9</v>
+      </c>
+      <c r="O116" t="n">
         <v>13</v>
       </c>
-      <c r="O116" t="n">
-        <v>8</v>
-      </c>
       <c r="P116" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="n">
-        <v>968</v>
+        <v>860</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -8597,7 +8625,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8609,29 +8637,29 @@
         <v>55</v>
       </c>
       <c r="J117" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K117" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L117" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="M117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N117" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P117" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="n">
-        <v>906</v>
+        <v>747</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -8667,7 +8695,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8676,32 +8704,32 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J118" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K118" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L118" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="M118" t="n">
+        <v>3</v>
+      </c>
+      <c r="N118" t="n">
+        <v>9</v>
+      </c>
+      <c r="O118" t="n">
         <v>5</v>
       </c>
-      <c r="N118" t="n">
-        <v>10</v>
-      </c>
-      <c r="O118" t="n">
-        <v>7</v>
-      </c>
       <c r="P118" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="n">
-        <v>979</v>
+        <v>811</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -8737,7 +8765,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8746,32 +8774,32 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J119" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K119" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L119" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O119" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="n">
-        <v>827</v>
+        <v>838</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -8807,7 +8835,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8816,7 +8844,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J120" t="n">
         <v>93</v>
@@ -8828,23 +8856,23 @@
         <v>69</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N120" t="n">
         <v>13</v>
       </c>
       <c r="O120" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P120" t="n">
         <v>17</v>
       </c>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="n">
-        <v>836</v>
+        <v>799</v>
       </c>
       <c r="S120" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -8877,7 +8905,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8886,19 +8914,19 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J121" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K121" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L121" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="M121" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N121" t="n">
         <v>9</v>
@@ -8911,7 +8939,7 @@
       </c>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="n">
-        <v>924</v>
+        <v>781</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -8947,7 +8975,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8956,16 +8984,16 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J122" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K122" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L122" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="M122" t="n">
         <v>2</v>
@@ -8977,11 +9005,11 @@
         <v>6</v>
       </c>
       <c r="P122" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="n">
-        <v>997</v>
+        <v>769</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -9017,7 +9045,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9026,32 +9054,32 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J123" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K123" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L123" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="M123" t="n">
         <v>2</v>
       </c>
       <c r="N123" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O123" t="n">
         <v>5</v>
       </c>
       <c r="P123" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="n">
-        <v>942</v>
+        <v>851</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -9087,7 +9115,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9099,29 +9127,29 @@
         <v>70</v>
       </c>
       <c r="J124" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K124" t="n">
         <v>15</v>
       </c>
       <c r="L124" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M124" t="n">
         <v>2</v>
       </c>
       <c r="N124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O124" t="n">
         <v>7</v>
       </c>
       <c r="P124" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="n">
-        <v>990</v>
+        <v>898</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -9157,7 +9185,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9166,32 +9194,32 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J125" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K125" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L125" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M125" t="n">
         <v>2</v>
       </c>
       <c r="N125" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O125" t="n">
         <v>6</v>
       </c>
       <c r="P125" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="n">
-        <v>958</v>
+        <v>844</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -9227,7 +9255,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9236,32 +9264,32 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J126" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K126" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L126" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M126" t="n">
         <v>2</v>
       </c>
       <c r="N126" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O126" t="n">
         <v>3</v>
       </c>
       <c r="P126" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="n">
-        <v>966</v>
+        <v>821</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -9297,7 +9325,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9306,32 +9334,32 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J127" t="n">
         <v>98</v>
       </c>
       <c r="K127" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L127" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N127" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P127" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="n">
-        <v>955</v>
+        <v>842</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -9367,7 +9395,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9379,29 +9407,29 @@
         <v>56</v>
       </c>
       <c r="J128" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K128" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L128" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="M128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N128" t="n">
+        <v>9</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1</v>
+      </c>
+      <c r="P128" t="n">
         <v>13</v>
-      </c>
-      <c r="O128" t="n">
-        <v>5</v>
-      </c>
-      <c r="P128" t="n">
-        <v>17</v>
       </c>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="n">
-        <v>894</v>
+        <v>833</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -9437,7 +9465,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9446,35 +9474,35 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J129" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K129" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L129" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="M129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N129" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O129" t="n">
         <v>6</v>
       </c>
       <c r="P129" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="n">
-        <v>918</v>
+        <v>893</v>
       </c>
       <c r="S129" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -9507,7 +9535,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -9516,35 +9544,35 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J130" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K130" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="L130" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M130" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N130" t="n">
         <v>8</v>
       </c>
       <c r="O130" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P130" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="n">
-        <v>960</v>
+        <v>765</v>
       </c>
       <c r="S130" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -9577,7 +9605,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -9586,32 +9614,32 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J131" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K131" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L131" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="M131" t="n">
         <v>2</v>
       </c>
       <c r="N131" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O131" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P131" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="n">
-        <v>908</v>
+        <v>885</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -9647,7 +9675,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9665,23 +9693,23 @@
         <v>14</v>
       </c>
       <c r="L132" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="M132" t="n">
         <v>2</v>
       </c>
       <c r="N132" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O132" t="n">
         <v>3</v>
       </c>
       <c r="P132" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="n">
-        <v>969</v>
+        <v>867</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -9717,7 +9745,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -9726,32 +9754,32 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J133" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K133" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L133" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M133" t="n">
         <v>1</v>
       </c>
       <c r="N133" t="n">
+        <v>3</v>
+      </c>
+      <c r="O133" t="n">
         <v>5</v>
       </c>
-      <c r="O133" t="n">
-        <v>3</v>
-      </c>
       <c r="P133" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="n">
-        <v>812</v>
+        <v>696</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -9787,7 +9815,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9802,10 +9830,10 @@
         <v>80</v>
       </c>
       <c r="K134" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L134" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="M134" t="n">
         <v>2</v>
@@ -9821,10 +9849,10 @@
       </c>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="n">
-        <v>705</v>
+        <v>622</v>
       </c>
       <c r="S134" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -9857,7 +9885,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9866,35 +9894,35 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J135" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K135" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L135" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N135" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O135" t="n">
         <v>7</v>
       </c>
       <c r="P135" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="n">
-        <v>931</v>
+        <v>826</v>
       </c>
       <c r="S135" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -9927,7 +9955,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9936,32 +9964,32 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J136" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K136" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L136" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N136" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P136" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="n">
-        <v>744</v>
+        <v>798</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -9997,7 +10025,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10006,32 +10034,32 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J137" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K137" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L137" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M137" t="n">
         <v>5</v>
       </c>
       <c r="N137" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O137" t="n">
         <v>8</v>
       </c>
       <c r="P137" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="n">
-        <v>881</v>
+        <v>716</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -10067,7 +10095,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10076,32 +10104,32 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J138" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K138" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L138" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="M138" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N138" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O138" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P138" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="n">
-        <v>934</v>
+        <v>831</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -10137,7 +10165,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10146,32 +10174,32 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J139" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K139" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L139" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="M139" t="n">
         <v>2</v>
       </c>
       <c r="N139" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O139" t="n">
         <v>3</v>
       </c>
       <c r="P139" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="n">
-        <v>871</v>
+        <v>740</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -10207,7 +10235,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10225,26 +10253,26 @@
         <v>22</v>
       </c>
       <c r="L140" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M140" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N140" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O140" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P140" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="n">
-        <v>917</v>
+        <v>856</v>
       </c>
       <c r="S140" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -10277,7 +10305,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10286,35 +10314,35 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J141" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K141" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L141" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="M141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N141" t="n">
         <v>9</v>
       </c>
       <c r="O141" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P141" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="n">
-        <v>872</v>
+        <v>741</v>
       </c>
       <c r="S141" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -10347,7 +10375,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -10356,32 +10384,32 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J142" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K142" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L142" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M142" t="n">
         <v>5</v>
       </c>
       <c r="N142" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O142" t="n">
         <v>9</v>
       </c>
       <c r="P142" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="n">
-        <v>916</v>
+        <v>857</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -10417,7 +10445,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10426,35 +10454,35 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J143" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K143" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L143" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M143" t="n">
         <v>2</v>
       </c>
       <c r="N143" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O143" t="n">
         <v>3</v>
       </c>
       <c r="P143" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="n">
-        <v>819</v>
+        <v>807</v>
       </c>
       <c r="S143" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -10487,7 +10515,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10496,35 +10524,35 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J144" t="n">
         <v>82</v>
       </c>
       <c r="K144" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L144" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N144" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O144" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P144" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="n">
-        <v>872</v>
+        <v>798</v>
       </c>
       <c r="S144" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -10557,7 +10585,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -10566,35 +10594,35 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J145" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K145" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L145" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M145" t="n">
         <v>2</v>
       </c>
       <c r="N145" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O145" t="n">
         <v>6</v>
       </c>
       <c r="P145" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="n">
-        <v>883</v>
+        <v>845</v>
       </c>
       <c r="S145" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -10627,7 +10655,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10636,35 +10664,35 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J146" t="n">
         <v>92</v>
       </c>
       <c r="K146" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L146" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="M146" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N146" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O146" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P146" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="n">
-        <v>886</v>
+        <v>793</v>
       </c>
       <c r="S146" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -10697,7 +10725,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -10709,33 +10737,29 @@
         <v>67</v>
       </c>
       <c r="J147" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K147" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L147" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="M147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N147" t="n">
         <v>8</v>
       </c>
       <c r="O147" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P147" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>1/6/1 17:00 LMT</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="Q147" t="inlineStr"/>
       <c r="R147" t="n">
-        <v>975</v>
+        <v>814</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -10771,7 +10795,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10780,35 +10804,35 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J148" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K148" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L148" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N148" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P148" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="n">
-        <v>887</v>
+        <v>854</v>
       </c>
       <c r="S148" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -10841,7 +10865,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10850,32 +10874,32 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J149" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K149" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L149" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M149" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N149" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O149" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P149" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="n">
-        <v>804</v>
+        <v>845</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -10911,7 +10935,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10923,32 +10947,32 @@
         <v>53</v>
       </c>
       <c r="J150" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K150" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L150" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P150" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="n">
-        <v>829</v>
+        <v>704</v>
       </c>
       <c r="S150" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -10981,7 +11005,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10993,29 +11017,29 @@
         <v>77</v>
       </c>
       <c r="J151" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K151" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L151" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M151" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N151" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O151" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P151" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="n">
-        <v>939</v>
+        <v>744</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -11051,7 +11075,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11060,32 +11084,32 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J152" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K152" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L152" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N152" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P152" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="n">
-        <v>884</v>
+        <v>854</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -11121,7 +11145,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11130,35 +11154,35 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J153" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K153" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L153" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="M153" t="n">
         <v>2</v>
       </c>
       <c r="N153" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O153" t="n">
         <v>5</v>
       </c>
       <c r="P153" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="n">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="S153" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -11191,7 +11215,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11200,35 +11224,35 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J154" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K154" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L154" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M154" t="n">
         <v>5</v>
       </c>
       <c r="N154" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O154" t="n">
         <v>9</v>
       </c>
       <c r="P154" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="n">
-        <v>735</v>
+        <v>553</v>
       </c>
       <c r="S154" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -11261,7 +11285,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11276,29 +11300,29 @@
         <v>77</v>
       </c>
       <c r="K155" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L155" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M155" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N155" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O155" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P155" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="n">
-        <v>775</v>
+        <v>646</v>
       </c>
       <c r="S155" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -11331,7 +11355,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11340,35 +11364,35 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J156" t="n">
         <v>86</v>
       </c>
       <c r="K156" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L156" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M156" t="n">
         <v>1</v>
       </c>
       <c r="N156" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O156" t="n">
         <v>1</v>
       </c>
       <c r="P156" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="n">
-        <v>716</v>
+        <v>810</v>
       </c>
       <c r="S156" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -11401,7 +11425,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11410,35 +11434,35 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J157" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="K157" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="L157" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="M157" t="n">
         <v>2</v>
       </c>
       <c r="N157" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O157" t="n">
         <v>6</v>
       </c>
       <c r="P157" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="n">
-        <v>880</v>
+        <v>806</v>
       </c>
       <c r="S157" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -11471,7 +11495,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>8/22/2026</t>
+          <t>8/23/2026</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11480,7 +11504,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J158" t="n">
         <v>91</v>
@@ -11489,23 +11513,23 @@
         <v>18</v>
       </c>
       <c r="L158" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M158" t="n">
         <v>2</v>
       </c>
       <c r="N158" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O158" t="n">
         <v>3</v>
       </c>
       <c r="P158" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="n">
-        <v>882</v>
+        <v>781</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>

--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J2" t="n">
         <v>77</v>
@@ -561,23 +561,23 @@
         <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="M2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" t="n">
-        <v>13</v>
-      </c>
-      <c r="O2" t="n">
-        <v>7</v>
-      </c>
       <c r="P2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>822</v>
+        <v>782</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -625,13 +625,13 @@
         <v>86</v>
       </c>
       <c r="J3" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M3" t="n">
         <v>2</v>
@@ -643,11 +643,11 @@
         <v>7</v>
       </c>
       <c r="P3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>837</v>
+        <v>866</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -698,26 +698,26 @@
         <v>90</v>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>782</v>
+        <v>886</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -768,7 +768,7 @@
         <v>80</v>
       </c>
       <c r="K5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5" t="n">
         <v>62</v>
@@ -780,14 +780,14 @@
         <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>762</v>
+        <v>886</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -832,22 +832,22 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J6" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M6" t="n">
         <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
         <v>7</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>849</v>
+        <v>927</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -902,39 +902,35 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J7" t="n">
         <v>79</v>
       </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1/3/1 17:00 LMT</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>797</v>
+        <v>773</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -976,32 +972,32 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K8" t="n">
         <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M8" t="n">
         <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>849</v>
+        <v>950</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1046,7 +1042,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J9" t="n">
         <v>90</v>
@@ -1055,23 +1051,23 @@
         <v>18</v>
       </c>
       <c r="L9" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>803</v>
+        <v>922</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1116,16 +1112,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J10" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L10" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="M10" t="n">
         <v>3</v>
@@ -1137,11 +1133,11 @@
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>853</v>
+        <v>914</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1192,26 +1188,26 @@
         <v>104</v>
       </c>
       <c r="K11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P11" t="n">
         <v>19</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>868</v>
+        <v>827</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1256,36 +1252,32 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J12" t="n">
         <v>94</v>
       </c>
       <c r="K12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>11</v>
+      </c>
+      <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>5</v>
-      </c>
       <c r="P12" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1/3/1 17:00 LMT</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>802</v>
+        <v>930</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1333,10 +1325,10 @@
         <v>68</v>
       </c>
       <c r="J13" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L13" t="n">
         <v>36</v>
@@ -1355,7 +1347,7 @@
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>832</v>
+        <v>898</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1400,35 +1392,35 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J14" t="n">
         <v>82</v>
       </c>
       <c r="K14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L14" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8</v>
+      </c>
+      <c r="O14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" t="n">
-        <v>9</v>
-      </c>
-      <c r="O14" t="n">
-        <v>5</v>
-      </c>
       <c r="P14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>668</v>
+        <v>732</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1470,7 +1462,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J15" t="n">
         <v>100</v>
@@ -1479,23 +1471,23 @@
         <v>13</v>
       </c>
       <c r="L15" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>883</v>
+        <v>937</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1540,19 +1532,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J16" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K16" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L16" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
         <v>9</v>
@@ -1565,7 +1557,7 @@
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>702</v>
+        <v>815</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1616,26 +1608,26 @@
         <v>83</v>
       </c>
       <c r="K17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L17" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>14</v>
+      </c>
+      <c r="O17" t="n">
         <v>3</v>
       </c>
-      <c r="N17" t="n">
-        <v>11</v>
-      </c>
-      <c r="O17" t="n">
-        <v>5</v>
-      </c>
       <c r="P17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1680,32 +1672,32 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J18" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
         <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
         <v>18</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>695</v>
+        <v>764</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1750,13 +1742,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J19" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L19" t="n">
         <v>36</v>
@@ -1765,17 +1757,17 @@
         <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
         <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>782</v>
+        <v>804</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -1826,13 +1818,13 @@
         <v>92</v>
       </c>
       <c r="K20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L20" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
         <v>9</v>
@@ -1841,14 +1833,14 @@
         <v>8</v>
       </c>
       <c r="P20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>799</v>
+        <v>923</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1890,32 +1882,36 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J21" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L21" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P21" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1/1/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R21" t="n">
-        <v>870</v>
+        <v>976</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -1966,26 +1962,26 @@
         <v>94</v>
       </c>
       <c r="K22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L22" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O22" t="n">
         <v>7</v>
       </c>
       <c r="P22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>875</v>
+        <v>941</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2030,16 +2026,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J23" t="n">
         <v>105</v>
       </c>
       <c r="K23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L23" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
@@ -2055,7 +2051,7 @@
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>859</v>
+        <v>911</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2100,35 +2096,35 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J24" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L24" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>7</v>
       </c>
       <c r="O24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
         <v>811</v>
       </c>
       <c r="S24" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2170,32 +2166,32 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J25" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K25" t="n">
         <v>24</v>
       </c>
       <c r="L25" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="M25" t="n">
         <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O25" t="n">
         <v>9</v>
       </c>
       <c r="P25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2240,32 +2236,32 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J26" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K26" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L26" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>688</v>
+        <v>896</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2310,32 +2306,32 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J27" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L27" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
+        <v>7</v>
+      </c>
+      <c r="O27" t="n">
+        <v>5</v>
+      </c>
+      <c r="P27" t="n">
         <v>9</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>13</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>868</v>
+        <v>972</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2380,22 +2376,22 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J28" t="n">
         <v>110</v>
       </c>
       <c r="K28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L28" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O28" t="n">
         <v>8</v>
@@ -2403,13 +2399,9 @@
       <c r="P28" t="n">
         <v>21</v>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>1/2/1 17:00 LMT</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
-        <v>870</v>
+        <v>913</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2454,39 +2446,35 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J29" t="n">
         <v>81</v>
       </c>
       <c r="K29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L29" t="n">
         <v>77</v>
       </c>
       <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>9</v>
+      </c>
+      <c r="O29" t="n">
         <v>3</v>
       </c>
-      <c r="N29" t="n">
-        <v>8</v>
-      </c>
-      <c r="O29" t="n">
-        <v>5</v>
-      </c>
       <c r="P29" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>1/3/1 17:00 LMT</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>814</v>
+        <v>654</v>
       </c>
       <c r="S29" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2528,32 +2516,32 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J30" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K30" t="n">
         <v>28</v>
       </c>
       <c r="L30" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O30" t="n">
         <v>7</v>
       </c>
       <c r="P30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>776</v>
+        <v>932</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2598,16 +2586,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J31" t="n">
         <v>75</v>
       </c>
       <c r="K31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L31" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M31" t="n">
         <v>2</v>
@@ -2619,11 +2607,11 @@
         <v>9</v>
       </c>
       <c r="P31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>823</v>
+        <v>646</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -2668,32 +2656,32 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J32" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K32" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L32" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M32" t="n">
         <v>2</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="n">
-        <v>814</v>
+        <v>910</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -2738,35 +2726,35 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J33" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L33" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="M33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P33" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>725</v>
+        <v>786</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2808,16 +2796,16 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J34" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K34" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L34" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="M34" t="n">
         <v>2</v>
@@ -2826,17 +2814,17 @@
         <v>5</v>
       </c>
       <c r="O34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P34" t="n">
         <v>13</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="n">
-        <v>724</v>
+        <v>791</v>
       </c>
       <c r="S34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -2878,32 +2866,32 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J35" t="n">
         <v>90</v>
       </c>
       <c r="K35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L35" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M35" t="n">
         <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="n">
-        <v>839</v>
+        <v>897</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -2948,35 +2936,35 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J36" t="n">
         <v>82</v>
       </c>
       <c r="K36" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L36" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
         <v>9</v>
       </c>
       <c r="O36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P36" t="n">
         <v>13</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
-        <v>779</v>
+        <v>717</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3021,29 +3009,29 @@
         <v>57</v>
       </c>
       <c r="J37" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K37" t="n">
         <v>15</v>
       </c>
       <c r="L37" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M37" t="n">
         <v>2</v>
       </c>
       <c r="N37" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="n">
-        <v>751</v>
+        <v>833</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3088,22 +3076,22 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J38" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K38" t="n">
         <v>26</v>
       </c>
       <c r="L38" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O38" t="n">
         <v>6</v>
@@ -3113,7 +3101,7 @@
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
-        <v>869</v>
+        <v>926</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3158,32 +3146,32 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J39" t="n">
         <v>96</v>
       </c>
       <c r="K39" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L39" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
         <v>6</v>
       </c>
       <c r="O39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P39" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
-        <v>895</v>
+        <v>989</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3237,23 +3225,23 @@
         <v>20</v>
       </c>
       <c r="L40" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M40" t="n">
         <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="n">
-        <v>824</v>
+        <v>764</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3301,13 +3289,13 @@
         <v>54</v>
       </c>
       <c r="J41" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K41" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L41" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M41" t="n">
         <v>2</v>
@@ -3319,14 +3307,14 @@
         <v>5</v>
       </c>
       <c r="P41" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
-        <v>602</v>
+        <v>797</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -3374,26 +3362,26 @@
         <v>91</v>
       </c>
       <c r="K42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L42" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="M42" t="n">
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="n">
-        <v>775</v>
+        <v>877</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3438,32 +3426,36 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J43" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K43" t="n">
         <v>14</v>
       </c>
       <c r="L43" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O43" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P43" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q43" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1/3/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R43" t="n">
-        <v>827</v>
+        <v>895</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3508,32 +3500,32 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J44" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K44" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L44" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
         <v>7</v>
       </c>
       <c r="O44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="n">
-        <v>735</v>
+        <v>842</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -3581,29 +3573,29 @@
         <v>71</v>
       </c>
       <c r="J45" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L45" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M45" t="n">
         <v>5</v>
       </c>
       <c r="N45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O45" t="n">
         <v>7</v>
       </c>
       <c r="P45" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
-        <v>863</v>
+        <v>967</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -3648,16 +3640,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J46" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K46" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L46" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
@@ -3673,7 +3665,7 @@
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="n">
-        <v>824</v>
+        <v>922</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -3718,16 +3710,16 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J47" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K47" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L47" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -3743,10 +3735,10 @@
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="n">
-        <v>694</v>
+        <v>775</v>
       </c>
       <c r="S47" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -3788,32 +3780,32 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J48" t="n">
         <v>108</v>
       </c>
       <c r="K48" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L48" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
         <v>10</v>
       </c>
       <c r="O48" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="n">
-        <v>880</v>
+        <v>925</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -3858,35 +3850,35 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J49" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K49" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L49" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
         <v>6</v>
       </c>
       <c r="O49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P49" t="n">
         <v>14</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="n">
-        <v>604</v>
+        <v>653</v>
       </c>
       <c r="S49" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -3928,16 +3920,16 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J50" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K50" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L50" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M50" t="n">
         <v>2</v>
@@ -3946,17 +3938,17 @@
         <v>8</v>
       </c>
       <c r="O50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P50" t="n">
         <v>13</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="n">
-        <v>744</v>
+        <v>764</v>
       </c>
       <c r="S50" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -3998,22 +3990,22 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J51" t="n">
         <v>108</v>
       </c>
       <c r="K51" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L51" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="M51" t="n">
         <v>6</v>
       </c>
       <c r="N51" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O51" t="n">
         <v>9</v>
@@ -4023,7 +4015,7 @@
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="n">
-        <v>880</v>
+        <v>931</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -4074,26 +4066,26 @@
         <v>94</v>
       </c>
       <c r="K52" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L52" t="n">
         <v>72</v>
       </c>
       <c r="M52" t="n">
+        <v>2</v>
+      </c>
+      <c r="N52" t="n">
+        <v>8</v>
+      </c>
+      <c r="O52" t="n">
         <v>3</v>
       </c>
-      <c r="N52" t="n">
-        <v>7</v>
-      </c>
-      <c r="O52" t="n">
-        <v>5</v>
-      </c>
       <c r="P52" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="n">
-        <v>801</v>
+        <v>948</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -4138,16 +4130,16 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J53" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K53" t="n">
         <v>22</v>
       </c>
       <c r="L53" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M53" t="n">
         <v>5</v>
@@ -4156,17 +4148,17 @@
         <v>8</v>
       </c>
       <c r="O53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P53" t="n">
         <v>19</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="n">
-        <v>843</v>
+        <v>905</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4211,29 +4203,29 @@
         <v>85</v>
       </c>
       <c r="J54" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L54" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M54" t="n">
         <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O54" t="n">
         <v>2</v>
       </c>
       <c r="P54" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="n">
-        <v>822</v>
+        <v>870</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -4278,35 +4270,35 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J55" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K55" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L55" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O55" t="n">
         <v>5</v>
       </c>
       <c r="P55" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="n">
-        <v>784</v>
+        <v>895</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -4354,26 +4346,26 @@
         <v>82</v>
       </c>
       <c r="K56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L56" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N56" t="n">
+        <v>7</v>
+      </c>
+      <c r="O56" t="n">
         <v>3</v>
       </c>
-      <c r="N56" t="n">
-        <v>8</v>
-      </c>
-      <c r="O56" t="n">
-        <v>5</v>
-      </c>
       <c r="P56" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="n">
-        <v>716</v>
+        <v>756</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -4418,16 +4410,16 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J57" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K57" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L57" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="M57" t="n">
         <v>1</v>
@@ -4436,17 +4428,17 @@
         <v>6</v>
       </c>
       <c r="O57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P57" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="n">
-        <v>711</v>
+        <v>783</v>
       </c>
       <c r="S57" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -4491,13 +4483,13 @@
         <v>56</v>
       </c>
       <c r="J58" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K58" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L58" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M58" t="n">
         <v>2</v>
@@ -4509,11 +4501,11 @@
         <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="n">
-        <v>699</v>
+        <v>745</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -4561,13 +4553,13 @@
         <v>68</v>
       </c>
       <c r="J59" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K59" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L59" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M59" t="n">
         <v>2</v>
@@ -4583,10 +4575,10 @@
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="n">
-        <v>657</v>
+        <v>840</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -4634,10 +4626,10 @@
         <v>92</v>
       </c>
       <c r="K60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L60" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M60" t="n">
         <v>3</v>
@@ -4646,14 +4638,14 @@
         <v>15</v>
       </c>
       <c r="O60" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P60" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="n">
-        <v>894</v>
+        <v>865</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -4698,32 +4690,32 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J61" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K61" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L61" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M61" t="n">
         <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P61" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="n">
-        <v>910</v>
+        <v>973</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -4768,35 +4760,35 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J62" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K62" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L62" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O62" t="n">
         <v>3</v>
       </c>
       <c r="P62" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="n">
-        <v>625</v>
+        <v>673</v>
       </c>
       <c r="S62" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -4844,26 +4836,26 @@
         <v>112</v>
       </c>
       <c r="K63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L63" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M63" t="n">
         <v>2</v>
       </c>
       <c r="N63" t="n">
+        <v>7</v>
+      </c>
+      <c r="O63" t="n">
         <v>6</v>
       </c>
-      <c r="O63" t="n">
-        <v>5</v>
-      </c>
       <c r="P63" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="n">
-        <v>805</v>
+        <v>872</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -4908,16 +4900,16 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J64" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K64" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L64" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
@@ -4933,10 +4925,10 @@
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="n">
-        <v>826</v>
+        <v>948</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -4978,16 +4970,16 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J65" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K65" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L65" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M65" t="n">
         <v>1</v>
@@ -4999,11 +4991,11 @@
         <v>5</v>
       </c>
       <c r="P65" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="n">
-        <v>743</v>
+        <v>849</v>
       </c>
       <c r="S65" t="n">
         <v>0.02</v>
@@ -5048,10 +5040,10 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J66" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K66" t="n">
         <v>23</v>
@@ -5063,17 +5055,17 @@
         <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="n">
-        <v>758</v>
+        <v>917</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5121,29 +5113,29 @@
         <v>62</v>
       </c>
       <c r="J67" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K67" t="n">
         <v>17</v>
       </c>
       <c r="L67" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O67" t="n">
         <v>6</v>
       </c>
       <c r="P67" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="n">
-        <v>868</v>
+        <v>847</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -5194,10 +5186,10 @@
         <v>84</v>
       </c>
       <c r="K68" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L68" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M68" t="n">
         <v>5</v>
@@ -5206,17 +5198,17 @@
         <v>9</v>
       </c>
       <c r="O68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P68" t="n">
         <v>14</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="n">
-        <v>816</v>
+        <v>877</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5264,26 +5256,26 @@
         <v>98</v>
       </c>
       <c r="K69" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L69" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M69" t="n">
         <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="n">
-        <v>861</v>
+        <v>876</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -5328,32 +5320,32 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J70" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K70" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L70" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N70" t="n">
         <v>13</v>
       </c>
       <c r="O70" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P70" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="n">
-        <v>747</v>
+        <v>850</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -5398,16 +5390,16 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J71" t="n">
         <v>91</v>
       </c>
       <c r="K71" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L71" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M71" t="n">
         <v>7</v>
@@ -5416,17 +5408,17 @@
         <v>10</v>
       </c>
       <c r="O71" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P71" t="n">
         <v>23</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="n">
-        <v>828</v>
+        <v>904</v>
       </c>
       <c r="S71" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -5468,16 +5460,16 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J72" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K72" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L72" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M72" t="n">
         <v>1</v>
@@ -5486,17 +5478,17 @@
         <v>5</v>
       </c>
       <c r="O72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P72" t="n">
         <v>15</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="n">
-        <v>822</v>
+        <v>875</v>
       </c>
       <c r="S72" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -5541,36 +5533,32 @@
         <v>55</v>
       </c>
       <c r="J73" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L73" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="M73" t="n">
         <v>2</v>
       </c>
       <c r="N73" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O73" t="n">
         <v>3</v>
       </c>
       <c r="P73" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>1/3/1 17:00 LMT</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="n">
-        <v>523</v>
+        <v>714</v>
       </c>
       <c r="S73" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5612,32 +5600,32 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J74" t="n">
         <v>86</v>
       </c>
       <c r="K74" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L74" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="M74" t="n">
+        <v>3</v>
+      </c>
+      <c r="N74" t="n">
+        <v>13</v>
+      </c>
+      <c r="O74" t="n">
         <v>5</v>
       </c>
-      <c r="N74" t="n">
-        <v>11</v>
-      </c>
-      <c r="O74" t="n">
-        <v>7</v>
-      </c>
       <c r="P74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="n">
-        <v>645</v>
+        <v>677</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -5685,32 +5673,32 @@
         <v>65</v>
       </c>
       <c r="J75" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K75" t="n">
         <v>15</v>
       </c>
       <c r="L75" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M75" t="n">
         <v>2</v>
       </c>
       <c r="N75" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O75" t="n">
         <v>3</v>
       </c>
       <c r="P75" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
-        <v>826</v>
+        <v>912</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -5758,10 +5746,10 @@
         <v>83</v>
       </c>
       <c r="K76" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L76" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M76" t="n">
         <v>2</v>
@@ -5770,17 +5758,17 @@
         <v>5</v>
       </c>
       <c r="O76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P76" t="n">
         <v>13</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="n">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="S76" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -5822,32 +5810,32 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J77" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L77" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N77" t="n">
+        <v>7</v>
+      </c>
+      <c r="O77" t="n">
         <v>6</v>
-      </c>
-      <c r="O77" t="n">
-        <v>5</v>
       </c>
       <c r="P77" t="n">
         <v>11</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="n">
-        <v>785</v>
+        <v>921</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -5892,35 +5880,35 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J78" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K78" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L78" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N78" t="n">
         <v>7</v>
       </c>
       <c r="O78" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P78" t="n">
         <v>11</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="n">
-        <v>625</v>
+        <v>816</v>
       </c>
       <c r="S78" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -5962,35 +5950,35 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J79" t="n">
         <v>87</v>
       </c>
       <c r="K79" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L79" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N79" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P79" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="n">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -6032,32 +6020,32 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J80" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K80" t="n">
         <v>21</v>
       </c>
       <c r="L80" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M80" t="n">
         <v>3</v>
       </c>
       <c r="N80" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O80" t="n">
         <v>5</v>
       </c>
       <c r="P80" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="n">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -6108,29 +6096,29 @@
         <v>86</v>
       </c>
       <c r="K81" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L81" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M81" t="n">
         <v>1</v>
       </c>
       <c r="N81" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O81" t="n">
         <v>1</v>
       </c>
       <c r="P81" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="n">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -6172,30 +6160,34 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J82" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K82" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L82" t="n">
         <v>48</v>
       </c>
       <c r="M82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O82" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P82" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q82" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1/3/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R82" t="n">
         <v>767</v>
       </c>
@@ -6242,13 +6234,13 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J83" t="n">
         <v>101</v>
       </c>
       <c r="K83" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L83" t="n">
         <v>38</v>
@@ -6257,17 +6249,17 @@
         <v>5</v>
       </c>
       <c r="N83" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O83" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P83" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="n">
-        <v>877</v>
+        <v>985</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -6315,33 +6307,33 @@
         <v>72</v>
       </c>
       <c r="J84" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K84" t="n">
         <v>12</v>
       </c>
       <c r="L84" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N84" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P84" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>1/7/1 17:00 LMT</t>
+          <t>1/5/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R84" t="n">
-        <v>858</v>
+        <v>948</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -6389,16 +6381,16 @@
         <v>57</v>
       </c>
       <c r="J85" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K85" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L85" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N85" t="n">
         <v>7</v>
@@ -6407,11 +6399,11 @@
         <v>6</v>
       </c>
       <c r="P85" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="n">
-        <v>824</v>
+        <v>966</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -6456,39 +6448,35 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J86" t="n">
         <v>74</v>
       </c>
       <c r="K86" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L86" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="M86" t="n">
         <v>2</v>
       </c>
       <c r="N86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O86" t="n">
         <v>3</v>
       </c>
       <c r="P86" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>1/3/1 17:00 LMT</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="n">
-        <v>827</v>
+        <v>929</v>
       </c>
       <c r="S86" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -6530,35 +6518,35 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J87" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K87" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L87" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="M87" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N87" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O87" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="n">
-        <v>859</v>
+        <v>956</v>
       </c>
       <c r="S87" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -6600,32 +6588,32 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J88" t="n">
         <v>89</v>
       </c>
       <c r="K88" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L88" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M88" t="n">
+        <v>2</v>
+      </c>
+      <c r="N88" t="n">
+        <v>7</v>
+      </c>
+      <c r="O88" t="n">
         <v>3</v>
       </c>
-      <c r="N88" t="n">
-        <v>11</v>
-      </c>
-      <c r="O88" t="n">
-        <v>5</v>
-      </c>
       <c r="P88" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="n">
-        <v>779</v>
+        <v>852</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -6670,22 +6658,22 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J89" t="n">
         <v>108</v>
       </c>
       <c r="K89" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L89" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="M89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O89" t="n">
         <v>7</v>
@@ -6695,7 +6683,7 @@
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="n">
-        <v>783</v>
+        <v>926</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -6740,16 +6728,16 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J90" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K90" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L90" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="M90" t="n">
         <v>1</v>
@@ -6761,14 +6749,14 @@
         <v>3</v>
       </c>
       <c r="P90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="n">
-        <v>552</v>
+        <v>689</v>
       </c>
       <c r="S90" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -6813,13 +6801,13 @@
         <v>67</v>
       </c>
       <c r="J91" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K91" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L91" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M91" t="n">
         <v>3</v>
@@ -6831,14 +6819,14 @@
         <v>7</v>
       </c>
       <c r="P91" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="n">
-        <v>776</v>
+        <v>712</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -6880,16 +6868,16 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J92" t="n">
         <v>92</v>
       </c>
       <c r="K92" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L92" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M92" t="n">
         <v>2</v>
@@ -6905,7 +6893,7 @@
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="n">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -6953,10 +6941,10 @@
         <v>57</v>
       </c>
       <c r="J93" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K93" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L93" t="n">
         <v>60</v>
@@ -6975,7 +6963,7 @@
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="n">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -7026,10 +7014,10 @@
         <v>79</v>
       </c>
       <c r="K94" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L94" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M94" t="n">
         <v>5</v>
@@ -7038,17 +7026,17 @@
         <v>8</v>
       </c>
       <c r="O94" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P94" t="n">
         <v>21</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
-        <v>861</v>
+        <v>875</v>
       </c>
       <c r="S94" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -7090,7 +7078,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J95" t="n">
         <v>96</v>
@@ -7099,13 +7087,13 @@
         <v>22</v>
       </c>
       <c r="L95" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="M95" t="n">
         <v>2</v>
       </c>
       <c r="N95" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O95" t="n">
         <v>7</v>
@@ -7115,7 +7103,7 @@
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="n">
-        <v>879</v>
+        <v>868</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -7166,26 +7154,26 @@
         <v>92</v>
       </c>
       <c r="K96" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L96" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N96" t="n">
         <v>10</v>
       </c>
       <c r="O96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P96" t="n">
         <v>18</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="n">
-        <v>843</v>
+        <v>907</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -7230,35 +7218,35 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J97" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K97" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L97" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N97" t="n">
         <v>7</v>
       </c>
       <c r="O97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P97" t="n">
         <v>10</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="n">
-        <v>690</v>
+        <v>735</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -7309,19 +7297,19 @@
         <v>15</v>
       </c>
       <c r="L98" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M98" t="n">
         <v>6</v>
       </c>
       <c r="N98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O98" t="n">
         <v>9</v>
       </c>
       <c r="P98" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -7329,7 +7317,7 @@
         </is>
       </c>
       <c r="R98" t="n">
-        <v>792</v>
+        <v>905</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -7374,7 +7362,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J99" t="n">
         <v>84</v>
@@ -7386,7 +7374,7 @@
         <v>54</v>
       </c>
       <c r="M99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N99" t="n">
         <v>6</v>
@@ -7399,7 +7387,7 @@
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="n">
-        <v>857</v>
+        <v>876</v>
       </c>
       <c r="S99" t="n">
         <v>0.02</v>
@@ -7444,32 +7432,32 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J100" t="n">
         <v>99</v>
       </c>
       <c r="K100" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L100" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M100" t="n">
         <v>5</v>
       </c>
       <c r="N100" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O100" t="n">
         <v>9</v>
       </c>
       <c r="P100" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="n">
-        <v>898</v>
+        <v>839</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -7514,19 +7502,19 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J101" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K101" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L101" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N101" t="n">
         <v>5</v>
@@ -7539,7 +7527,7 @@
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="n">
-        <v>728</v>
+        <v>834</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -7584,32 +7572,32 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J102" t="n">
         <v>89</v>
       </c>
       <c r="K102" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L102" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="M102" t="n">
         <v>2</v>
       </c>
       <c r="N102" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O102" t="n">
         <v>3</v>
       </c>
       <c r="P102" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="n">
-        <v>800</v>
+        <v>811</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -7654,32 +7642,32 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J103" t="n">
         <v>107</v>
       </c>
       <c r="K103" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L103" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M103" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N103" t="n">
         <v>11</v>
       </c>
       <c r="O103" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P103" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="n">
-        <v>769</v>
+        <v>831</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -7724,19 +7712,19 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J104" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K104" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L104" t="n">
         <v>27</v>
       </c>
       <c r="M104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N104" t="n">
         <v>10</v>
@@ -7749,7 +7737,7 @@
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="n">
-        <v>767</v>
+        <v>922</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -7794,10 +7782,10 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J105" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K105" t="n">
         <v>15</v>
@@ -7806,20 +7794,20 @@
         <v>45</v>
       </c>
       <c r="M105" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N105" t="n">
         <v>15</v>
       </c>
       <c r="O105" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P105" t="n">
         <v>24</v>
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="n">
-        <v>870</v>
+        <v>970</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -7864,35 +7852,35 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J106" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K106" t="n">
         <v>23</v>
       </c>
       <c r="L106" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N106" t="n">
         <v>5</v>
       </c>
       <c r="O106" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P106" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="n">
-        <v>688</v>
+        <v>731</v>
       </c>
       <c r="S106" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -7934,32 +7922,32 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J107" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K107" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L107" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P107" t="n">
         <v>14</v>
       </c>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="n">
-        <v>702</v>
+        <v>825</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -8010,26 +7998,26 @@
         <v>85</v>
       </c>
       <c r="K108" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L108" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M108" t="n">
         <v>3</v>
       </c>
       <c r="N108" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O108" t="n">
         <v>5</v>
       </c>
       <c r="P108" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="n">
-        <v>803</v>
+        <v>606</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -8074,32 +8062,32 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J109" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K109" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L109" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M109" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N109" t="n">
         <v>9</v>
       </c>
       <c r="O109" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P109" t="n">
         <v>13</v>
       </c>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="n">
-        <v>763</v>
+        <v>835</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -8144,32 +8132,32 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J110" t="n">
         <v>101</v>
       </c>
       <c r="K110" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L110" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="M110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N110" t="n">
         <v>8</v>
       </c>
       <c r="O110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P110" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="n">
-        <v>862</v>
+        <v>898</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -8214,32 +8202,32 @@
         </is>
       </c>
       <c r="I111" t="n">
+        <v>62</v>
+      </c>
+      <c r="J111" t="n">
+        <v>92</v>
+      </c>
+      <c r="K111" t="n">
+        <v>26</v>
+      </c>
+      <c r="L111" t="n">
         <v>65</v>
-      </c>
-      <c r="J111" t="n">
-        <v>94</v>
-      </c>
-      <c r="K111" t="n">
-        <v>22</v>
-      </c>
-      <c r="L111" t="n">
-        <v>58</v>
       </c>
       <c r="M111" t="n">
         <v>2</v>
       </c>
       <c r="N111" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O111" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P111" t="n">
         <v>13</v>
       </c>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="n">
-        <v>745</v>
+        <v>823</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -8284,35 +8272,35 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J112" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K112" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L112" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M112" t="n">
         <v>2</v>
       </c>
       <c r="N112" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O112" t="n">
         <v>5</v>
       </c>
       <c r="P112" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="n">
-        <v>776</v>
+        <v>873</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -8354,16 +8342,16 @@
         </is>
       </c>
       <c r="I113" t="n">
+        <v>58</v>
+      </c>
+      <c r="J113" t="n">
+        <v>79</v>
+      </c>
+      <c r="K113" t="n">
+        <v>26</v>
+      </c>
+      <c r="L113" t="n">
         <v>60</v>
-      </c>
-      <c r="J113" t="n">
-        <v>80</v>
-      </c>
-      <c r="K113" t="n">
-        <v>24</v>
-      </c>
-      <c r="L113" t="n">
-        <v>54</v>
       </c>
       <c r="M113" t="n">
         <v>2</v>
@@ -8375,14 +8363,14 @@
         <v>6</v>
       </c>
       <c r="P113" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="n">
-        <v>722</v>
+        <v>759</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -8424,16 +8412,16 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J114" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K114" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L114" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="M114" t="n">
         <v>1</v>
@@ -8445,11 +8433,11 @@
         <v>3</v>
       </c>
       <c r="P114" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="n">
-        <v>855</v>
+        <v>839</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -8494,35 +8482,35 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J115" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K115" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L115" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O115" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P115" t="n">
         <v>10</v>
       </c>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="n">
-        <v>692</v>
+        <v>764</v>
       </c>
       <c r="S115" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -8564,32 +8552,36 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J116" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K116" t="n">
+        <v>13</v>
+      </c>
+      <c r="L116" t="n">
+        <v>34</v>
+      </c>
+      <c r="M116" t="n">
+        <v>6</v>
+      </c>
+      <c r="N116" t="n">
+        <v>8</v>
+      </c>
+      <c r="O116" t="n">
         <v>14</v>
       </c>
-      <c r="L116" t="n">
-        <v>36</v>
-      </c>
-      <c r="M116" t="n">
-        <v>5</v>
-      </c>
-      <c r="N116" t="n">
-        <v>9</v>
-      </c>
-      <c r="O116" t="n">
-        <v>13</v>
-      </c>
       <c r="P116" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q116" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>1/6/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R116" t="n">
-        <v>860</v>
+        <v>973</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -8640,7 +8632,7 @@
         <v>86</v>
       </c>
       <c r="K117" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L117" t="n">
         <v>72</v>
@@ -8649,17 +8641,17 @@
         <v>1</v>
       </c>
       <c r="N117" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O117" t="n">
         <v>1</v>
       </c>
       <c r="P117" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="n">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -8704,32 +8696,32 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J118" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K118" t="n">
         <v>19</v>
       </c>
       <c r="L118" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="M118" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N118" t="n">
+        <v>7</v>
+      </c>
+      <c r="O118" t="n">
+        <v>7</v>
+      </c>
+      <c r="P118" t="n">
         <v>9</v>
-      </c>
-      <c r="O118" t="n">
-        <v>5</v>
-      </c>
-      <c r="P118" t="n">
-        <v>13</v>
       </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="n">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -8774,32 +8766,32 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J119" t="n">
         <v>87</v>
       </c>
       <c r="K119" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L119" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="M119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
         <v>3</v>
       </c>
       <c r="O119" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="n">
-        <v>838</v>
+        <v>813</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -8844,32 +8836,32 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J120" t="n">
         <v>93</v>
       </c>
       <c r="K120" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L120" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N120" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O120" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P120" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="n">
-        <v>799</v>
+        <v>938</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -8923,7 +8915,7 @@
         <v>38</v>
       </c>
       <c r="L121" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M121" t="n">
         <v>5</v>
@@ -8935,14 +8927,14 @@
         <v>8</v>
       </c>
       <c r="P121" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="n">
-        <v>781</v>
+        <v>867</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -8984,16 +8976,16 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J122" t="n">
         <v>91</v>
       </c>
       <c r="K122" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L122" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="M122" t="n">
         <v>2</v>
@@ -9005,11 +8997,11 @@
         <v>6</v>
       </c>
       <c r="P122" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="n">
-        <v>769</v>
+        <v>952</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -9063,7 +9055,7 @@
         <v>22</v>
       </c>
       <c r="L123" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M123" t="n">
         <v>2</v>
@@ -9079,10 +9071,10 @@
       </c>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="n">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="S123" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -9127,29 +9119,29 @@
         <v>70</v>
       </c>
       <c r="J124" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K124" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L124" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N124" t="n">
         <v>5</v>
       </c>
       <c r="O124" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P124" t="n">
         <v>15</v>
       </c>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="n">
-        <v>898</v>
+        <v>987</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -9197,29 +9189,29 @@
         <v>77</v>
       </c>
       <c r="J125" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K125" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L125" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M125" t="n">
         <v>2</v>
       </c>
       <c r="N125" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O125" t="n">
         <v>6</v>
       </c>
       <c r="P125" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="n">
-        <v>844</v>
+        <v>867</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -9264,32 +9256,32 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J126" t="n">
         <v>91</v>
       </c>
       <c r="K126" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L126" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M126" t="n">
         <v>2</v>
       </c>
       <c r="N126" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O126" t="n">
         <v>3</v>
       </c>
       <c r="P126" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="n">
-        <v>821</v>
+        <v>837</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -9334,32 +9326,32 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J127" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K127" t="n">
         <v>16</v>
       </c>
       <c r="L127" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="M127" t="n">
+        <v>2</v>
+      </c>
+      <c r="N127" t="n">
+        <v>10</v>
+      </c>
+      <c r="O127" t="n">
         <v>3</v>
       </c>
-      <c r="N127" t="n">
-        <v>11</v>
-      </c>
-      <c r="O127" t="n">
-        <v>5</v>
-      </c>
       <c r="P127" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="n">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -9404,32 +9396,32 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J128" t="n">
         <v>86</v>
       </c>
       <c r="K128" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L128" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="M128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N128" t="n">
         <v>9</v>
       </c>
       <c r="O128" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P128" t="n">
         <v>13</v>
       </c>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="n">
-        <v>833</v>
+        <v>879</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -9474,7 +9466,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J129" t="n">
         <v>99</v>
@@ -9483,7 +9475,7 @@
         <v>26</v>
       </c>
       <c r="L129" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M129" t="n">
         <v>2</v>
@@ -9499,10 +9491,10 @@
       </c>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="n">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -9544,22 +9536,22 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J130" t="n">
         <v>82</v>
       </c>
       <c r="K130" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L130" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="M130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N130" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O130" t="n">
         <v>9</v>
@@ -9569,7 +9561,7 @@
       </c>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="n">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="S130" t="n">
         <v>0.03</v>
@@ -9614,16 +9606,16 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J131" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K131" t="n">
         <v>26</v>
       </c>
       <c r="L131" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="M131" t="n">
         <v>2</v>
@@ -9632,17 +9624,17 @@
         <v>7</v>
       </c>
       <c r="O131" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P131" t="n">
         <v>16</v>
       </c>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="n">
-        <v>885</v>
+        <v>919</v>
       </c>
       <c r="S131" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -9693,7 +9685,7 @@
         <v>14</v>
       </c>
       <c r="L132" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M132" t="n">
         <v>2</v>
@@ -9709,7 +9701,7 @@
       </c>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="n">
-        <v>867</v>
+        <v>915</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -9754,35 +9746,35 @@
         </is>
       </c>
       <c r="I133" t="n">
+        <v>62</v>
+      </c>
+      <c r="J133" t="n">
+        <v>93</v>
+      </c>
+      <c r="K133" t="n">
+        <v>24</v>
+      </c>
+      <c r="L133" t="n">
         <v>65</v>
       </c>
-      <c r="J133" t="n">
-        <v>94</v>
-      </c>
-      <c r="K133" t="n">
-        <v>22</v>
-      </c>
-      <c r="L133" t="n">
-        <v>56</v>
-      </c>
       <c r="M133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
+        <v>5</v>
+      </c>
+      <c r="O133" t="n">
         <v>3</v>
       </c>
-      <c r="O133" t="n">
-        <v>5</v>
-      </c>
       <c r="P133" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="n">
-        <v>696</v>
+        <v>771</v>
       </c>
       <c r="S133" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -9824,35 +9816,35 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J134" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K134" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L134" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M134" t="n">
         <v>2</v>
       </c>
       <c r="N134" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O134" t="n">
         <v>3</v>
       </c>
       <c r="P134" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="n">
-        <v>622</v>
+        <v>809</v>
       </c>
       <c r="S134" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -9900,29 +9892,29 @@
         <v>103</v>
       </c>
       <c r="K135" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L135" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O135" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P135" t="n">
         <v>17</v>
       </c>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="n">
-        <v>826</v>
+        <v>913</v>
       </c>
       <c r="S135" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -9964,16 +9956,16 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J136" t="n">
         <v>90</v>
       </c>
       <c r="K136" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L136" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="M136" t="n">
         <v>3</v>
@@ -9989,7 +9981,7 @@
       </c>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="n">
-        <v>798</v>
+        <v>843</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -10034,16 +10026,16 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J137" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K137" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L137" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M137" t="n">
         <v>5</v>
@@ -10059,10 +10051,10 @@
       </c>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="n">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="S137" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -10104,16 +10096,16 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J138" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K138" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L138" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M138" t="n">
         <v>5</v>
@@ -10122,17 +10114,17 @@
         <v>10</v>
       </c>
       <c r="O138" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P138" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="n">
-        <v>831</v>
+        <v>924</v>
       </c>
       <c r="S138" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -10183,23 +10175,23 @@
         <v>16</v>
       </c>
       <c r="L139" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N139" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P139" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="n">
-        <v>740</v>
+        <v>856</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -10247,10 +10239,10 @@
         <v>62</v>
       </c>
       <c r="J140" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K140" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L140" t="n">
         <v>45</v>
@@ -10265,11 +10257,11 @@
         <v>8</v>
       </c>
       <c r="P140" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="n">
-        <v>856</v>
+        <v>910</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -10314,32 +10306,32 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J141" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K141" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L141" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N141" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O141" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P141" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="n">
-        <v>741</v>
+        <v>877</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -10384,32 +10376,32 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J142" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K142" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L142" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M142" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N142" t="n">
         <v>8</v>
       </c>
       <c r="O142" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P142" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="n">
-        <v>857</v>
+        <v>874</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -10460,29 +10452,29 @@
         <v>89</v>
       </c>
       <c r="K143" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L143" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N143" t="n">
         <v>11</v>
       </c>
       <c r="O143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P143" t="n">
         <v>16</v>
       </c>
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="n">
-        <v>807</v>
+        <v>908</v>
       </c>
       <c r="S143" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -10524,32 +10516,32 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J144" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K144" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L144" t="n">
         <v>62</v>
       </c>
       <c r="M144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N144" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O144" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P144" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="n">
-        <v>798</v>
+        <v>853</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -10594,35 +10586,35 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J145" t="n">
         <v>104</v>
       </c>
       <c r="K145" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L145" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N145" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O145" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P145" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="n">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="S145" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -10664,32 +10656,32 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J146" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K146" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L146" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="M146" t="n">
         <v>5</v>
       </c>
       <c r="N146" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O146" t="n">
         <v>7</v>
       </c>
       <c r="P146" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="n">
-        <v>793</v>
+        <v>854</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -10737,13 +10729,13 @@
         <v>67</v>
       </c>
       <c r="J147" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K147" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L147" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M147" t="n">
         <v>5</v>
@@ -10759,7 +10751,7 @@
       </c>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="n">
-        <v>814</v>
+        <v>915</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -10804,32 +10796,32 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J148" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K148" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L148" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="M148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N148" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P148" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="n">
-        <v>854</v>
+        <v>879</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -10874,7 +10866,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J149" t="n">
         <v>89</v>
@@ -10883,26 +10875,26 @@
         <v>23</v>
       </c>
       <c r="L149" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M149" t="n">
         <v>5</v>
       </c>
       <c r="N149" t="n">
+        <v>9</v>
+      </c>
+      <c r="O149" t="n">
         <v>8</v>
-      </c>
-      <c r="O149" t="n">
-        <v>9</v>
       </c>
       <c r="P149" t="n">
         <v>21</v>
       </c>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="n">
-        <v>845</v>
+        <v>881</v>
       </c>
       <c r="S149" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -10944,16 +10936,16 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J150" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K150" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L150" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -10962,17 +10954,17 @@
         <v>2</v>
       </c>
       <c r="O150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P150" t="n">
         <v>9</v>
       </c>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="n">
-        <v>704</v>
+        <v>810</v>
       </c>
       <c r="S150" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -11017,29 +11009,29 @@
         <v>77</v>
       </c>
       <c r="J151" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K151" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L151" t="n">
         <v>29</v>
       </c>
       <c r="M151" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N151" t="n">
         <v>13</v>
       </c>
       <c r="O151" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P151" t="n">
         <v>28</v>
       </c>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="n">
-        <v>744</v>
+        <v>926</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -11090,10 +11082,10 @@
         <v>97</v>
       </c>
       <c r="K152" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L152" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M152" t="n">
         <v>2</v>
@@ -11105,11 +11097,11 @@
         <v>6</v>
       </c>
       <c r="P152" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="n">
-        <v>854</v>
+        <v>889</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -11154,19 +11146,19 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J153" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K153" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L153" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="M153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N153" t="n">
         <v>3</v>
@@ -11179,7 +11171,7 @@
       </c>
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="n">
-        <v>750</v>
+        <v>797</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -11224,35 +11216,35 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J154" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K154" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L154" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M154" t="n">
         <v>5</v>
       </c>
       <c r="N154" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O154" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P154" t="n">
         <v>13</v>
       </c>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="n">
-        <v>553</v>
+        <v>594</v>
       </c>
       <c r="S154" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -11300,29 +11292,29 @@
         <v>77</v>
       </c>
       <c r="K155" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L155" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M155" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N155" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O155" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P155" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="n">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="S155" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -11364,7 +11356,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J156" t="n">
         <v>86</v>
@@ -11373,23 +11365,23 @@
         <v>19</v>
       </c>
       <c r="L156" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="M156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N156" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P156" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="n">
-        <v>810</v>
+        <v>934</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -11443,7 +11435,7 @@
         <v>23</v>
       </c>
       <c r="L157" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M157" t="n">
         <v>2</v>
@@ -11452,17 +11444,17 @@
         <v>5</v>
       </c>
       <c r="O157" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P157" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="n">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="S157" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -11504,32 +11496,32 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J158" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K158" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L158" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N158" t="n">
+        <v>10</v>
+      </c>
+      <c r="O158" t="n">
+        <v>1</v>
+      </c>
+      <c r="P158" t="n">
         <v>15</v>
-      </c>
-      <c r="O158" t="n">
-        <v>3</v>
-      </c>
-      <c r="P158" t="n">
-        <v>21</v>
       </c>
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="n">
-        <v>781</v>
+        <v>913</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>

--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -561,23 +561,27 @@
         <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
         <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R2" t="n">
-        <v>782</v>
+        <v>636</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -613,7 +617,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -622,32 +626,36 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J3" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K3" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="L3" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R3" t="n">
-        <v>866</v>
+        <v>890</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -683,7 +691,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -695,29 +703,33 @@
         <v>60</v>
       </c>
       <c r="J4" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>58</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" t="n">
         <v>17</v>
       </c>
-      <c r="L4" t="n">
-        <v>65</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>15</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R4" t="n">
-        <v>886</v>
+        <v>751</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -753,7 +765,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -762,32 +774,36 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J5" t="n">
         <v>80</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
         <v>13</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R5" t="n">
-        <v>886</v>
+        <v>690</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -823,7 +839,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -832,32 +848,36 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J6" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="L6" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7</v>
+      </c>
+      <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="N6" t="n">
-        <v>9</v>
-      </c>
-      <c r="O6" t="n">
-        <v>7</v>
-      </c>
       <c r="P6" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R6" t="n">
-        <v>927</v>
+        <v>898</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -893,7 +913,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -902,35 +922,39 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J7" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
         <v>58</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R7" t="n">
-        <v>773</v>
+        <v>625</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -963,7 +987,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -975,7 +999,7 @@
         <v>76</v>
       </c>
       <c r="J8" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K8" t="n">
         <v>13</v>
@@ -984,20 +1008,24 @@
         <v>31</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
         <v>11</v>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R8" t="n">
-        <v>950</v>
+        <v>821</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1033,7 +1061,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1042,16 +1070,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L9" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="M9" t="n">
         <v>2</v>
@@ -1065,9 +1093,13 @@
       <c r="P9" t="n">
         <v>11</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="R9" t="n">
-        <v>922</v>
+        <v>765</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1103,7 +1135,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1112,32 +1144,36 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J10" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K10" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
         <v>7</v>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R10" t="n">
-        <v>914</v>
+        <v>901</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1173,7 +1209,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1185,29 +1221,33 @@
         <v>79</v>
       </c>
       <c r="J11" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L11" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R11" t="n">
-        <v>827</v>
+        <v>881</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1243,7 +1283,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1252,35 +1292,39 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K12" t="n">
         <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O12" t="n">
         <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R12" t="n">
-        <v>930</v>
+        <v>747</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1313,7 +1357,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1322,32 +1366,36 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J13" t="n">
         <v>83</v>
       </c>
       <c r="K13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L13" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
         <v>2</v>
       </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
       <c r="O13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R13" t="n">
-        <v>898</v>
+        <v>832</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1383,7 +1431,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1392,16 +1440,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L14" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="M14" t="n">
         <v>2</v>
@@ -1415,12 +1463,16 @@
       <c r="P14" t="n">
         <v>11</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R14" t="n">
-        <v>732</v>
+        <v>750</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1453,7 +1505,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1462,32 +1514,36 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J15" t="n">
         <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
         <v>11</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
         <v>16</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R15" t="n">
-        <v>937</v>
+        <v>886</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1523,7 +1579,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1532,13 +1588,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J16" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K16" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L16" t="n">
         <v>55</v>
@@ -1550,14 +1606,18 @@
         <v>9</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R16" t="n">
-        <v>815</v>
+        <v>844</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1593,7 +1653,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1602,32 +1662,36 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J17" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L17" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R17" t="n">
-        <v>753</v>
+        <v>680</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1663,7 +1727,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1672,32 +1736,36 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J18" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K18" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L18" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R18" t="n">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1733,7 +1801,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1742,32 +1810,36 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J19" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K19" t="n">
         <v>15</v>
       </c>
       <c r="L19" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M19" t="n">
         <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R19" t="n">
-        <v>804</v>
+        <v>762</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -1803,7 +1875,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1812,35 +1884,39 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J20" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K20" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L20" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P20" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R20" t="n">
-        <v>923</v>
+        <v>909</v>
       </c>
       <c r="S20" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1873,7 +1949,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1885,33 +1961,33 @@
         <v>72</v>
       </c>
       <c r="J21" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N21" t="n">
         <v>15</v>
       </c>
       <c r="O21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P21" t="n">
         <v>22</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>976</v>
+        <v>818</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -1947,7 +2023,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1956,22 +2032,22 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J22" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L22" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O22" t="n">
         <v>7</v>
@@ -1979,9 +2055,13 @@
       <c r="P22" t="n">
         <v>23</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R22" t="n">
-        <v>941</v>
+        <v>911</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2017,7 +2097,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2029,29 +2109,33 @@
         <v>83</v>
       </c>
       <c r="J23" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K23" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L23" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="M23" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" t="n">
+        <v>8</v>
+      </c>
+      <c r="O23" t="n">
         <v>3</v>
       </c>
-      <c r="N23" t="n">
-        <v>9</v>
-      </c>
-      <c r="O23" t="n">
-        <v>5</v>
-      </c>
       <c r="P23" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R23" t="n">
-        <v>911</v>
+        <v>881</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2087,7 +2171,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2096,19 +2180,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J24" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="K24" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L24" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
         <v>7</v>
@@ -2119,9 +2203,13 @@
       <c r="P24" t="n">
         <v>17</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R24" t="n">
-        <v>811</v>
+        <v>766</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2157,7 +2245,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2166,32 +2254,36 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J25" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K25" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L25" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="M25" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>8</v>
+      </c>
+      <c r="O25" t="n">
         <v>6</v>
       </c>
-      <c r="N25" t="n">
-        <v>10</v>
-      </c>
-      <c r="O25" t="n">
-        <v>9</v>
-      </c>
       <c r="P25" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R25" t="n">
-        <v>841</v>
+        <v>783</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2227,7 +2319,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2236,16 +2328,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J26" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K26" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="L26" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M26" t="n">
         <v>2</v>
@@ -2254,14 +2346,18 @@
         <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P26" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R26" t="n">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2297,7 +2393,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2306,32 +2402,36 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J27" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K27" t="n">
         <v>13</v>
       </c>
       <c r="L27" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>10</v>
+      </c>
+      <c r="O27" t="n">
         <v>3</v>
       </c>
-      <c r="N27" t="n">
-        <v>7</v>
-      </c>
-      <c r="O27" t="n">
-        <v>5</v>
-      </c>
       <c r="P27" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R27" t="n">
-        <v>972</v>
+        <v>814</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2367,7 +2467,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2379,29 +2479,33 @@
         <v>86</v>
       </c>
       <c r="J28" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K28" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="L28" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P28" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q28" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R28" t="n">
-        <v>913</v>
+        <v>896</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2437,7 +2541,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2446,35 +2550,39 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J29" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K29" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L29" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M29" t="n">
         <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R29" t="n">
-        <v>654</v>
+        <v>682</v>
       </c>
       <c r="S29" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2507,7 +2615,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2516,32 +2624,36 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J30" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K30" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L30" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>7</v>
+      </c>
+      <c r="O30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>14</v>
       </c>
-      <c r="O30" t="n">
-        <v>7</v>
-      </c>
-      <c r="P30" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R30" t="n">
-        <v>932</v>
+        <v>904</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2577,7 +2689,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2586,32 +2698,36 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J31" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K31" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L31" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P31" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R31" t="n">
-        <v>646</v>
+        <v>683</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -2647,7 +2763,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2656,13 +2772,13 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J32" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K32" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L32" t="n">
         <v>37</v>
@@ -2671,17 +2787,21 @@
         <v>2</v>
       </c>
       <c r="N32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
         <v>7</v>
       </c>
       <c r="P32" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q32" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R32" t="n">
-        <v>910</v>
+        <v>598</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -2717,7 +2837,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2726,32 +2846,36 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J33" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K33" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L33" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="M33" t="n">
         <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O33" t="n">
         <v>7</v>
       </c>
       <c r="P33" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q33" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R33" t="n">
-        <v>786</v>
+        <v>459</v>
       </c>
       <c r="S33" t="n">
         <v>0.02</v>
@@ -2787,7 +2911,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2796,16 +2920,16 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J34" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K34" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L34" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="M34" t="n">
         <v>2</v>
@@ -2814,17 +2938,21 @@
         <v>5</v>
       </c>
       <c r="O34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q34" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R34" t="n">
-        <v>791</v>
+        <v>867</v>
       </c>
       <c r="S34" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -2857,7 +2985,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2869,29 +2997,33 @@
         <v>59</v>
       </c>
       <c r="J35" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K35" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L35" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="M35" t="n">
         <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R35" t="n">
-        <v>897</v>
+        <v>759</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -2927,7 +3059,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2936,35 +3068,39 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J36" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K36" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L36" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P36" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R36" t="n">
-        <v>717</v>
+        <v>613</v>
       </c>
       <c r="S36" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -2997,7 +3133,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3006,7 +3142,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J37" t="n">
         <v>85</v>
@@ -3015,23 +3151,27 @@
         <v>15</v>
       </c>
       <c r="L37" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="M37" t="n">
         <v>2</v>
       </c>
       <c r="N37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q37" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R37" t="n">
-        <v>833</v>
+        <v>758</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3067,7 +3207,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3076,32 +3216,36 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J38" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K38" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="L38" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="M38" t="n">
         <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q38" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R38" t="n">
-        <v>926</v>
+        <v>900</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3137,7 +3281,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3146,32 +3290,36 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J39" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K39" t="n">
         <v>12</v>
       </c>
       <c r="L39" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M39" t="n">
         <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O39" t="n">
         <v>6</v>
       </c>
       <c r="P39" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q39" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R39" t="n">
-        <v>989</v>
+        <v>830</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3207,7 +3355,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3219,13 +3367,13 @@
         <v>64</v>
       </c>
       <c r="J40" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K40" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L40" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M40" t="n">
         <v>3</v>
@@ -3237,11 +3385,15 @@
         <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R40" t="n">
-        <v>764</v>
+        <v>682</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3277,7 +3429,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3286,35 +3438,39 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J41" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K41" t="n">
         <v>29</v>
       </c>
       <c r="L41" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q41" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R41" t="n">
-        <v>797</v>
+        <v>742</v>
       </c>
       <c r="S41" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -3347,7 +3503,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3359,29 +3515,33 @@
         <v>51</v>
       </c>
       <c r="J42" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K42" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L42" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="M42" t="n">
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q42" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R42" t="n">
-        <v>877</v>
+        <v>721</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3417,7 +3577,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3429,33 +3589,33 @@
         <v>69</v>
       </c>
       <c r="J43" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L43" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M43" t="n">
         <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O43" t="n">
         <v>5</v>
       </c>
       <c r="P43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>895</v>
+        <v>827</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3491,7 +3651,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3500,32 +3660,36 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J44" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K44" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L44" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
         <v>7</v>
       </c>
       <c r="O44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P44" t="n">
         <v>16</v>
       </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R44" t="n">
-        <v>842</v>
+        <v>901</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -3561,7 +3725,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3570,16 +3734,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J45" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K45" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L45" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M45" t="n">
         <v>5</v>
@@ -3593,9 +3757,13 @@
       <c r="P45" t="n">
         <v>13</v>
       </c>
-      <c r="Q45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="R45" t="n">
-        <v>967</v>
+        <v>803</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -3631,7 +3799,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3640,32 +3808,36 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J46" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K46" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L46" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P46" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q46" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R46" t="n">
-        <v>922</v>
+        <v>835</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -3701,7 +3873,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3710,35 +3882,39 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J47" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K47" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L47" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O47" t="n">
         <v>5</v>
       </c>
       <c r="P47" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q47" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R47" t="n">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="S47" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -3771,7 +3947,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3783,29 +3959,33 @@
         <v>86</v>
       </c>
       <c r="J48" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K48" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L48" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="M48" t="n">
+        <v>2</v>
+      </c>
+      <c r="N48" t="n">
+        <v>7</v>
+      </c>
+      <c r="O48" t="n">
         <v>3</v>
       </c>
-      <c r="N48" t="n">
-        <v>10</v>
-      </c>
-      <c r="O48" t="n">
-        <v>7</v>
-      </c>
       <c r="P48" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q48" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R48" t="n">
-        <v>925</v>
+        <v>898</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -3841,7 +4021,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3850,16 +4030,16 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J49" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K49" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L49" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M49" t="n">
         <v>2</v>
@@ -3871,14 +4051,18 @@
         <v>6</v>
       </c>
       <c r="P49" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q49" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R49" t="n">
-        <v>653</v>
+        <v>754</v>
       </c>
       <c r="S49" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -3911,7 +4095,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3920,35 +4104,39 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J50" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K50" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L50" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M50" t="n">
         <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O50" t="n">
         <v>5</v>
       </c>
       <c r="P50" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q50" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R50" t="n">
-        <v>764</v>
+        <v>828</v>
       </c>
       <c r="S50" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -3981,7 +4169,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3990,32 +4178,36 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J51" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K51" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L51" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="M51" t="n">
+        <v>2</v>
+      </c>
+      <c r="N51" t="n">
         <v>6</v>
       </c>
-      <c r="N51" t="n">
-        <v>15</v>
-      </c>
       <c r="O51" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="P51" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q51" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R51" t="n">
-        <v>931</v>
+        <v>902</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -4051,7 +4243,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4063,29 +4255,33 @@
         <v>56</v>
       </c>
       <c r="J52" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K52" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L52" t="n">
         <v>72</v>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
         <v>8</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P52" t="n">
         <v>11</v>
       </c>
-      <c r="Q52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="R52" t="n">
-        <v>948</v>
+        <v>779</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -4121,7 +4317,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4133,32 +4329,36 @@
         <v>77</v>
       </c>
       <c r="J53" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K53" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L53" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
         <v>8</v>
       </c>
       <c r="O53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P53" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q53" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R53" t="n">
-        <v>905</v>
+        <v>865</v>
       </c>
       <c r="S53" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4191,7 +4391,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4200,32 +4400,36 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J54" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K54" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L54" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N54" t="n">
         <v>7</v>
       </c>
       <c r="O54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P54" t="n">
         <v>13</v>
       </c>
-      <c r="Q54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R54" t="n">
-        <v>870</v>
+        <v>895</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -4261,7 +4465,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4273,32 +4477,36 @@
         <v>72</v>
       </c>
       <c r="J55" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K55" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L55" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q55" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R55" t="n">
-        <v>895</v>
+        <v>908</v>
       </c>
       <c r="S55" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -4331,7 +4539,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4340,16 +4548,16 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J56" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K56" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L56" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="M56" t="n">
         <v>2</v>
@@ -4363,9 +4571,13 @@
       <c r="P56" t="n">
         <v>9</v>
       </c>
-      <c r="Q56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R56" t="n">
-        <v>756</v>
+        <v>728</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -4401,7 +4613,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4410,16 +4622,16 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J57" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K57" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L57" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="M57" t="n">
         <v>1</v>
@@ -4433,12 +4645,16 @@
       <c r="P57" t="n">
         <v>14</v>
       </c>
-      <c r="Q57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R57" t="n">
-        <v>783</v>
+        <v>807</v>
       </c>
       <c r="S57" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -4471,7 +4687,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4483,13 +4699,13 @@
         <v>56</v>
       </c>
       <c r="J58" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K58" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L58" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M58" t="n">
         <v>2</v>
@@ -4498,14 +4714,18 @@
         <v>6</v>
       </c>
       <c r="O58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P58" t="n">
         <v>11</v>
       </c>
-      <c r="Q58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="R58" t="n">
-        <v>745</v>
+        <v>720</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -4541,7 +4761,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4550,35 +4770,39 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J59" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K59" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L59" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O59" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P59" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q59" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R59" t="n">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="S59" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -4611,7 +4835,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4620,32 +4844,36 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J60" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K60" t="n">
         <v>15</v>
       </c>
       <c r="L60" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O60" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P60" t="n">
         <v>26</v>
       </c>
-      <c r="Q60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R60" t="n">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -4681,7 +4909,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4690,32 +4918,36 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J61" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K61" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L61" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M61" t="n">
         <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O61" t="n">
         <v>5</v>
       </c>
       <c r="P61" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q61" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R61" t="n">
-        <v>973</v>
+        <v>905</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -4751,7 +4983,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4760,35 +4992,39 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J62" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K62" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L62" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O62" t="n">
         <v>3</v>
       </c>
       <c r="P62" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q62" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R62" t="n">
-        <v>673</v>
+        <v>864</v>
       </c>
       <c r="S62" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -4821,7 +5057,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4830,32 +5066,36 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J63" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K63" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L63" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q63" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R63" t="n">
-        <v>872</v>
+        <v>886</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -4891,7 +5131,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4900,16 +5140,16 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J64" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K64" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L64" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
@@ -4923,12 +5163,16 @@
       <c r="P64" t="n">
         <v>13</v>
       </c>
-      <c r="Q64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R64" t="n">
-        <v>948</v>
+        <v>832</v>
       </c>
       <c r="S64" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -4961,7 +5205,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4973,32 +5217,36 @@
         <v>59</v>
       </c>
       <c r="J65" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K65" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L65" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>5</v>
       </c>
       <c r="O65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P65" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q65" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R65" t="n">
-        <v>849</v>
+        <v>774</v>
       </c>
       <c r="S65" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -5031,7 +5279,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5043,29 +5291,33 @@
         <v>61</v>
       </c>
       <c r="J66" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K66" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L66" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M66" t="n">
         <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P66" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q66" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1/3/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R66" t="n">
-        <v>917</v>
+        <v>905</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5101,7 +5353,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5113,29 +5365,33 @@
         <v>62</v>
       </c>
       <c r="J67" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K67" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L67" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M67" t="n">
         <v>2</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O67" t="n">
         <v>6</v>
       </c>
       <c r="P67" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q67" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R67" t="n">
-        <v>847</v>
+        <v>765</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -5171,7 +5427,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5180,35 +5436,39 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J68" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K68" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L68" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="M68" t="n">
         <v>5</v>
       </c>
       <c r="N68" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O68" t="n">
         <v>8</v>
       </c>
       <c r="P68" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q68" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R68" t="n">
-        <v>877</v>
+        <v>794</v>
       </c>
       <c r="S68" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5241,7 +5501,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5250,32 +5510,36 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J69" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K69" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L69" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="M69" t="n">
         <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P69" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q69" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R69" t="n">
-        <v>876</v>
+        <v>828</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -5311,7 +5575,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5320,32 +5584,36 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J70" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K70" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="L70" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N70" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O70" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P70" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q70" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R70" t="n">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -5381,7 +5649,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5390,32 +5658,36 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J71" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K71" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L71" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M71" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O71" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q71" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R71" t="n">
-        <v>904</v>
+        <v>866</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -5451,7 +5723,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5463,13 +5735,13 @@
         <v>63</v>
       </c>
       <c r="J72" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K72" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="L72" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M72" t="n">
         <v>1</v>
@@ -5478,17 +5750,21 @@
         <v>5</v>
       </c>
       <c r="O72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q72" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R72" t="n">
-        <v>875</v>
+        <v>838</v>
       </c>
       <c r="S72" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -5521,7 +5797,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5533,32 +5809,36 @@
         <v>55</v>
       </c>
       <c r="J73" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K73" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L73" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M73" t="n">
         <v>2</v>
       </c>
       <c r="N73" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O73" t="n">
         <v>3</v>
       </c>
       <c r="P73" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q73" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R73" t="n">
-        <v>714</v>
+        <v>657</v>
       </c>
       <c r="S73" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5591,7 +5871,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5600,16 +5880,16 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J74" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K74" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L74" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="M74" t="n">
         <v>3</v>
@@ -5623,9 +5903,13 @@
       <c r="P74" t="n">
         <v>17</v>
       </c>
-      <c r="Q74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R74" t="n">
-        <v>677</v>
+        <v>764</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -5661,7 +5945,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5670,7 +5954,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J75" t="n">
         <v>94</v>
@@ -5679,26 +5963,30 @@
         <v>15</v>
       </c>
       <c r="L75" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="M75" t="n">
         <v>2</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O75" t="n">
         <v>3</v>
       </c>
       <c r="P75" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q75" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R75" t="n">
-        <v>912</v>
+        <v>847</v>
       </c>
       <c r="S75" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -5731,7 +6019,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5743,32 +6031,36 @@
         <v>58</v>
       </c>
       <c r="J76" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K76" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L76" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N76" t="n">
         <v>5</v>
       </c>
       <c r="O76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P76" t="n">
         <v>13</v>
       </c>
-      <c r="Q76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R76" t="n">
-        <v>756</v>
+        <v>772</v>
       </c>
       <c r="S76" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -5801,7 +6093,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5810,32 +6102,36 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J77" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K77" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L77" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M77" t="n">
         <v>2</v>
       </c>
       <c r="N77" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P77" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q77" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1/4/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R77" t="n">
-        <v>921</v>
+        <v>811</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -5871,7 +6167,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5880,22 +6176,22 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J78" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K78" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L78" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="M78" t="n">
         <v>2</v>
       </c>
       <c r="N78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O78" t="n">
         <v>6</v>
@@ -5903,12 +6199,16 @@
       <c r="P78" t="n">
         <v>11</v>
       </c>
-      <c r="Q78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="R78" t="n">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="S78" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -5941,7 +6241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5950,35 +6250,39 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J79" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K79" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L79" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="M79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q79" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R79" t="n">
-        <v>777</v>
+        <v>745</v>
       </c>
       <c r="S79" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -6011,7 +6315,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6020,16 +6324,16 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J80" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K80" t="n">
         <v>21</v>
       </c>
       <c r="L80" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="M80" t="n">
         <v>3</v>
@@ -6043,9 +6347,13 @@
       <c r="P80" t="n">
         <v>11</v>
       </c>
-      <c r="Q80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R80" t="n">
-        <v>790</v>
+        <v>733</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -6081,7 +6389,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6090,35 +6398,39 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J81" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K81" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L81" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="M81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P81" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q81" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R81" t="n">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="S81" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -6151,7 +6463,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6160,16 +6472,16 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J82" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K82" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L82" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M82" t="n">
         <v>2</v>
@@ -6181,15 +6493,15 @@
         <v>8</v>
       </c>
       <c r="P82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R82" t="n">
-        <v>767</v>
+        <v>646</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -6225,7 +6537,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6234,10 +6546,10 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J83" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K83" t="n">
         <v>12</v>
@@ -6246,20 +6558,24 @@
         <v>38</v>
       </c>
       <c r="M83" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N83" t="n">
+        <v>9</v>
+      </c>
+      <c r="O83" t="n">
         <v>7</v>
       </c>
-      <c r="O83" t="n">
-        <v>6</v>
-      </c>
       <c r="P83" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q83" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R83" t="n">
-        <v>985</v>
+        <v>809</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -6295,7 +6611,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6304,36 +6620,36 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J84" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K84" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L84" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="M84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N84" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P84" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>1/5/1 17:00 LMT</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R84" t="n">
-        <v>948</v>
+        <v>720</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -6369,7 +6685,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6378,32 +6694,36 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J85" t="n">
         <v>89</v>
       </c>
       <c r="K85" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L85" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M85" t="n">
         <v>2</v>
       </c>
       <c r="N85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P85" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q85" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R85" t="n">
-        <v>966</v>
+        <v>767</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -6439,7 +6759,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6457,23 +6777,27 @@
         <v>24</v>
       </c>
       <c r="L86" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M86" t="n">
         <v>2</v>
       </c>
       <c r="N86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O86" t="n">
         <v>3</v>
       </c>
       <c r="P86" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q86" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R86" t="n">
-        <v>929</v>
+        <v>673</v>
       </c>
       <c r="S86" t="n">
         <v>0.04</v>
@@ -6509,7 +6833,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6518,35 +6842,39 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J87" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K87" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L87" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="M87" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N87" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O87" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P87" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q87" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R87" t="n">
-        <v>956</v>
+        <v>770</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -6579,7 +6907,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6588,10 +6916,10 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J88" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K88" t="n">
         <v>18</v>
@@ -6603,17 +6931,21 @@
         <v>2</v>
       </c>
       <c r="N88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
       </c>
       <c r="P88" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q88" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R88" t="n">
-        <v>852</v>
+        <v>756</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -6649,7 +6981,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6658,32 +6990,36 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J89" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K89" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="L89" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="M89" t="n">
         <v>2</v>
       </c>
       <c r="N89" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O89" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P89" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q89" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R89" t="n">
-        <v>926</v>
+        <v>898</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -6719,7 +7055,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6728,22 +7064,22 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J90" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K90" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L90" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="M90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O90" t="n">
         <v>3</v>
@@ -6751,12 +7087,16 @@
       <c r="P90" t="n">
         <v>11</v>
       </c>
-      <c r="Q90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R90" t="n">
-        <v>689</v>
+        <v>773</v>
       </c>
       <c r="S90" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -6789,7 +7129,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6798,35 +7138,39 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J91" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K91" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="L91" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M91" t="n">
         <v>3</v>
       </c>
       <c r="N91" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O91" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P91" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q91" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R91" t="n">
-        <v>712</v>
+        <v>813</v>
       </c>
       <c r="S91" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -6859,7 +7203,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6868,32 +7212,36 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J92" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L92" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N92" t="n">
         <v>7</v>
       </c>
       <c r="O92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P92" t="n">
         <v>9</v>
       </c>
-      <c r="Q92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="R92" t="n">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -6929,7 +7277,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6944,26 +7292,30 @@
         <v>84</v>
       </c>
       <c r="K93" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L93" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M93" t="n">
         <v>1</v>
       </c>
       <c r="N93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q93" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R93" t="n">
-        <v>759</v>
+        <v>657</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -6999,7 +7351,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7008,35 +7360,39 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J94" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K94" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L94" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M94" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N94" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O94" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P94" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q94" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R94" t="n">
-        <v>875</v>
+        <v>855</v>
       </c>
       <c r="S94" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -7069,7 +7425,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7078,32 +7434,36 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J95" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K95" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L95" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="M95" t="n">
         <v>2</v>
       </c>
       <c r="N95" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q95" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R95" t="n">
-        <v>868</v>
+        <v>850</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -7139,7 +7499,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7148,32 +7508,36 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J96" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K96" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L96" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M96" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O96" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P96" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q96" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R96" t="n">
-        <v>907</v>
+        <v>891</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -7209,7 +7573,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7221,32 +7585,36 @@
         <v>60</v>
       </c>
       <c r="J97" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K97" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L97" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="M97" t="n">
         <v>2</v>
       </c>
       <c r="N97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P97" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q97" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R97" t="n">
-        <v>735</v>
+        <v>764</v>
       </c>
       <c r="S97" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -7279,7 +7647,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7288,36 +7656,36 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J98" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K98" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L98" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M98" t="n">
+        <v>3</v>
+      </c>
+      <c r="N98" t="n">
+        <v>8</v>
+      </c>
+      <c r="O98" t="n">
         <v>6</v>
       </c>
-      <c r="N98" t="n">
+      <c r="P98" t="n">
         <v>10</v>
       </c>
-      <c r="O98" t="n">
-        <v>9</v>
-      </c>
-      <c r="P98" t="n">
-        <v>14</v>
-      </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R98" t="n">
-        <v>905</v>
+        <v>878</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -7353,7 +7721,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7362,35 +7730,39 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J99" t="n">
         <v>84</v>
       </c>
       <c r="K99" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L99" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="M99" t="n">
         <v>1</v>
       </c>
       <c r="N99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O99" t="n">
         <v>3</v>
       </c>
       <c r="P99" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q99" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R99" t="n">
-        <v>876</v>
+        <v>746</v>
       </c>
       <c r="S99" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -7423,7 +7795,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7432,32 +7804,36 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J100" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K100" t="n">
         <v>14</v>
       </c>
       <c r="L100" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N100" t="n">
         <v>11</v>
       </c>
       <c r="O100" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P100" t="n">
         <v>21</v>
       </c>
-      <c r="Q100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R100" t="n">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -7493,7 +7869,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7502,32 +7878,36 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J101" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K101" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L101" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="M101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O101" t="n">
         <v>7</v>
       </c>
       <c r="P101" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q101" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>1/4/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R101" t="n">
-        <v>834</v>
+        <v>911</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -7563,7 +7943,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7572,35 +7952,39 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J102" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K102" t="n">
         <v>18</v>
       </c>
       <c r="L102" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N102" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O102" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P102" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q102" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R102" t="n">
-        <v>811</v>
+        <v>640</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -7633,7 +8017,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7645,29 +8029,33 @@
         <v>85</v>
       </c>
       <c r="J103" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K103" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="L103" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="M103" t="n">
+        <v>2</v>
+      </c>
+      <c r="N103" t="n">
+        <v>6</v>
+      </c>
+      <c r="O103" t="n">
         <v>3</v>
       </c>
-      <c r="N103" t="n">
-        <v>11</v>
-      </c>
-      <c r="O103" t="n">
-        <v>7</v>
-      </c>
       <c r="P103" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q103" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R103" t="n">
-        <v>831</v>
+        <v>894</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -7703,7 +8091,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7712,7 +8100,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J104" t="n">
         <v>103</v>
@@ -7721,23 +8109,27 @@
         <v>14</v>
       </c>
       <c r="L104" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="M104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N104" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O104" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P104" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q104" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="R104" t="n">
-        <v>922</v>
+        <v>861</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -7773,7 +8165,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7785,29 +8177,33 @@
         <v>74</v>
       </c>
       <c r="J105" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K105" t="n">
         <v>15</v>
       </c>
       <c r="L105" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="M105" t="n">
         <v>7</v>
       </c>
       <c r="N105" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O105" t="n">
         <v>10</v>
       </c>
       <c r="P105" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q105" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R105" t="n">
-        <v>970</v>
+        <v>824</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -7843,7 +8239,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7852,16 +8248,16 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J106" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K106" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L106" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M106" t="n">
         <v>2</v>
@@ -7873,14 +8269,18 @@
         <v>6</v>
       </c>
       <c r="P106" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q106" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R106" t="n">
-        <v>731</v>
+        <v>805</v>
       </c>
       <c r="S106" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -7913,7 +8313,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7922,32 +8322,36 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J107" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K107" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L107" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N107" t="n">
         <v>7</v>
       </c>
       <c r="O107" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P107" t="n">
         <v>14</v>
       </c>
-      <c r="Q107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R107" t="n">
-        <v>825</v>
+        <v>849</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -7983,7 +8387,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7992,35 +8396,39 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J108" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K108" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L108" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="M108" t="n">
+        <v>2</v>
+      </c>
+      <c r="N108" t="n">
+        <v>10</v>
+      </c>
+      <c r="O108" t="n">
         <v>3</v>
       </c>
-      <c r="N108" t="n">
-        <v>8</v>
-      </c>
-      <c r="O108" t="n">
-        <v>5</v>
-      </c>
       <c r="P108" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q108" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R108" t="n">
-        <v>606</v>
+        <v>760</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -8053,7 +8461,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8062,32 +8470,36 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J109" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K109" t="n">
         <v>18</v>
       </c>
       <c r="L109" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="M109" t="n">
         <v>3</v>
       </c>
       <c r="N109" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O109" t="n">
         <v>5</v>
       </c>
       <c r="P109" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q109" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R109" t="n">
-        <v>835</v>
+        <v>743</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -8123,7 +8535,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8135,29 +8547,33 @@
         <v>80</v>
       </c>
       <c r="J110" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K110" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L110" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="M110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N110" t="n">
         <v>8</v>
       </c>
       <c r="O110" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P110" t="n">
         <v>14</v>
       </c>
-      <c r="Q110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R110" t="n">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -8193,7 +8609,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8202,32 +8618,36 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J111" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K111" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="L111" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="M111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N111" t="n">
         <v>7</v>
       </c>
       <c r="O111" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P111" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q111" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>1/5/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R111" t="n">
-        <v>823</v>
+        <v>911</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -8263,7 +8683,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8272,16 +8692,16 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J112" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K112" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L112" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M112" t="n">
         <v>2</v>
@@ -8293,14 +8713,18 @@
         <v>5</v>
       </c>
       <c r="P112" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q112" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R112" t="n">
-        <v>873</v>
+        <v>769</v>
       </c>
       <c r="S112" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -8333,7 +8757,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8342,35 +8766,39 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J113" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K113" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L113" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="M113" t="n">
         <v>2</v>
       </c>
       <c r="N113" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O113" t="n">
         <v>6</v>
       </c>
       <c r="P113" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q113" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R113" t="n">
-        <v>759</v>
+        <v>631</v>
       </c>
       <c r="S113" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -8403,7 +8831,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8412,32 +8840,36 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J114" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K114" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L114" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="M114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O114" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P114" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q114" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R114" t="n">
-        <v>839</v>
+        <v>886</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -8473,7 +8905,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8482,16 +8914,16 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J115" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K115" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L115" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M115" t="n">
         <v>1</v>
@@ -8500,14 +8932,18 @@
         <v>3</v>
       </c>
       <c r="O115" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P115" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q115" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R115" t="n">
-        <v>764</v>
+        <v>883</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -8543,7 +8979,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8552,36 +8988,36 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J116" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K116" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L116" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M116" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N116" t="n">
+        <v>9</v>
+      </c>
+      <c r="O116" t="n">
         <v>8</v>
       </c>
-      <c r="O116" t="n">
-        <v>14</v>
-      </c>
       <c r="P116" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>1/6/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R116" t="n">
-        <v>973</v>
+        <v>802</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -8617,7 +9053,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8626,32 +9062,36 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J117" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K117" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L117" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="M117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N117" t="n">
+        <v>8</v>
+      </c>
+      <c r="O117" t="n">
+        <v>5</v>
+      </c>
+      <c r="P117" t="n">
         <v>11</v>
       </c>
-      <c r="O117" t="n">
-        <v>1</v>
-      </c>
-      <c r="P117" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R117" t="n">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -8687,7 +9127,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8696,32 +9136,36 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J118" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K118" t="n">
         <v>19</v>
       </c>
       <c r="L118" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="M118" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N118" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O118" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P118" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q118" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="R118" t="n">
-        <v>818</v>
+        <v>596</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -8757,7 +9201,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8766,32 +9210,36 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J119" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K119" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L119" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N119" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O119" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P119" t="n">
         <v>11</v>
       </c>
-      <c r="Q119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R119" t="n">
-        <v>813</v>
+        <v>844</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -8827,7 +9275,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8839,29 +9287,33 @@
         <v>58</v>
       </c>
       <c r="J120" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K120" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L120" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N120" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P120" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q120" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R120" t="n">
-        <v>938</v>
+        <v>770</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -8897,7 +9349,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8906,35 +9358,39 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J121" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K121" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L121" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="M121" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O121" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P121" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q121" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>1/1/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R121" t="n">
-        <v>867</v>
+        <v>799</v>
       </c>
       <c r="S121" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -8967,7 +9423,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8976,16 +9432,16 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J122" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K122" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L122" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="M122" t="n">
         <v>2</v>
@@ -8999,9 +9455,13 @@
       <c r="P122" t="n">
         <v>15</v>
       </c>
-      <c r="Q122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R122" t="n">
-        <v>952</v>
+        <v>797</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -9037,7 +9497,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9046,35 +9506,39 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J123" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K123" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="L123" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="M123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N123" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O123" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P123" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q123" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R123" t="n">
-        <v>848</v>
+        <v>877</v>
       </c>
       <c r="S123" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -9107,7 +9571,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9116,32 +9580,36 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J124" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K124" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L124" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N124" t="n">
         <v>5</v>
       </c>
       <c r="O124" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P124" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q124" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R124" t="n">
-        <v>987</v>
+        <v>820</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -9177,7 +9645,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9189,29 +9657,33 @@
         <v>77</v>
       </c>
       <c r="J125" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K125" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L125" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M125" t="n">
         <v>2</v>
       </c>
       <c r="N125" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O125" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P125" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q125" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R125" t="n">
-        <v>867</v>
+        <v>901</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -9247,7 +9719,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9256,7 +9728,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J126" t="n">
         <v>91</v>
@@ -9265,7 +9737,7 @@
         <v>19</v>
       </c>
       <c r="L126" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="M126" t="n">
         <v>2</v>
@@ -9279,9 +9751,13 @@
       <c r="P126" t="n">
         <v>11</v>
       </c>
-      <c r="Q126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R126" t="n">
-        <v>837</v>
+        <v>731</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -9317,7 +9793,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9326,32 +9802,36 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J127" t="n">
         <v>99</v>
       </c>
       <c r="K127" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L127" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="M127" t="n">
         <v>2</v>
       </c>
       <c r="N127" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O127" t="n">
         <v>3</v>
       </c>
       <c r="P127" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q127" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R127" t="n">
-        <v>854</v>
+        <v>819</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -9387,7 +9867,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9405,26 +9885,30 @@
         <v>19</v>
       </c>
       <c r="L128" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="M128" t="n">
+        <v>2</v>
+      </c>
+      <c r="N128" t="n">
+        <v>10</v>
+      </c>
+      <c r="O128" t="n">
         <v>3</v>
       </c>
-      <c r="N128" t="n">
-        <v>9</v>
-      </c>
-      <c r="O128" t="n">
-        <v>5</v>
-      </c>
       <c r="P128" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q128" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R128" t="n">
-        <v>879</v>
+        <v>761</v>
       </c>
       <c r="S128" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -9457,7 +9941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9466,32 +9950,36 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J129" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K129" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="L129" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="M129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N129" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O129" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P129" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q129" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R129" t="n">
-        <v>914</v>
+        <v>813</v>
       </c>
       <c r="S129" t="n">
         <v>0.04</v>
@@ -9527,7 +10015,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -9536,35 +10024,39 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J130" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K130" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L130" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="M130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N130" t="n">
         <v>9</v>
       </c>
       <c r="O130" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P130" t="n">
         <v>16</v>
       </c>
-      <c r="Q130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="R130" t="n">
-        <v>760</v>
+        <v>794</v>
       </c>
       <c r="S130" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -9597,7 +10089,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -9606,35 +10098,39 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J131" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K131" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="L131" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="M131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N131" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O131" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P131" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q131" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R131" t="n">
-        <v>919</v>
+        <v>905</v>
       </c>
       <c r="S131" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -9667,7 +10163,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9679,29 +10175,33 @@
         <v>67</v>
       </c>
       <c r="J132" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K132" t="n">
         <v>14</v>
       </c>
       <c r="L132" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="M132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N132" t="n">
         <v>7</v>
       </c>
       <c r="O132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P132" t="n">
         <v>9</v>
       </c>
-      <c r="Q132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="R132" t="n">
-        <v>915</v>
+        <v>847</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -9737,7 +10237,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -9746,35 +10246,39 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J133" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K133" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L133" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N133" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O133" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P133" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q133" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R133" t="n">
-        <v>771</v>
+        <v>907</v>
       </c>
       <c r="S133" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -9807,7 +10311,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9816,35 +10320,39 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J134" t="n">
         <v>81</v>
       </c>
       <c r="K134" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L134" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N134" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P134" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q134" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R134" t="n">
-        <v>809</v>
+        <v>602</v>
       </c>
       <c r="S134" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -9877,7 +10385,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9886,32 +10394,36 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J135" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="K135" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L135" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N135" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O135" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P135" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q135" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R135" t="n">
-        <v>913</v>
+        <v>903</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -9947,7 +10459,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9956,32 +10468,36 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J136" t="n">
         <v>90</v>
       </c>
       <c r="K136" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L136" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N136" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O136" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P136" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q136" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R136" t="n">
-        <v>843</v>
+        <v>659</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -10017,7 +10533,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10026,35 +10542,39 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J137" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K137" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L137" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M137" t="n">
+        <v>3</v>
+      </c>
+      <c r="N137" t="n">
+        <v>7</v>
+      </c>
+      <c r="O137" t="n">
         <v>5</v>
       </c>
-      <c r="N137" t="n">
-        <v>8</v>
-      </c>
-      <c r="O137" t="n">
-        <v>8</v>
-      </c>
       <c r="P137" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q137" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R137" t="n">
-        <v>727</v>
+        <v>849</v>
       </c>
       <c r="S137" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -10087,7 +10607,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10096,35 +10616,39 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J138" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K138" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="L138" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M138" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N138" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O138" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P138" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q138" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R138" t="n">
-        <v>924</v>
+        <v>766</v>
       </c>
       <c r="S138" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -10157,7 +10681,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10169,29 +10693,33 @@
         <v>54</v>
       </c>
       <c r="J139" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K139" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L139" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="M139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N139" t="n">
         <v>11</v>
       </c>
       <c r="O139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P139" t="n">
         <v>16</v>
       </c>
-      <c r="Q139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R139" t="n">
-        <v>856</v>
+        <v>761</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -10227,7 +10755,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10239,29 +10767,33 @@
         <v>62</v>
       </c>
       <c r="J140" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K140" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L140" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M140" t="n">
         <v>3</v>
       </c>
       <c r="N140" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O140" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P140" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q140" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>1/1/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R140" t="n">
-        <v>910</v>
+        <v>762</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -10297,7 +10829,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10306,32 +10838,36 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J141" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K141" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L141" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M141" t="n">
         <v>2</v>
       </c>
       <c r="N141" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O141" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P141" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q141" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R141" t="n">
-        <v>877</v>
+        <v>901</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -10367,7 +10903,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -10379,29 +10915,33 @@
         <v>63</v>
       </c>
       <c r="J142" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K142" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L142" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M142" t="n">
         <v>3</v>
       </c>
       <c r="N142" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O142" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P142" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q142" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>1/3/1 17:00 LMT</t>
+        </is>
+      </c>
       <c r="R142" t="n">
-        <v>874</v>
+        <v>786</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -10437,7 +10977,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10455,7 +10995,7 @@
         <v>21</v>
       </c>
       <c r="L143" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="M143" t="n">
         <v>1</v>
@@ -10469,12 +11009,16 @@
       <c r="P143" t="n">
         <v>16</v>
       </c>
-      <c r="Q143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R143" t="n">
-        <v>908</v>
+        <v>771</v>
       </c>
       <c r="S143" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -10507,7 +11051,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10525,23 +11069,27 @@
         <v>20</v>
       </c>
       <c r="L144" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N144" t="n">
         <v>6</v>
       </c>
       <c r="O144" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P144" t="n">
         <v>8</v>
       </c>
-      <c r="Q144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R144" t="n">
-        <v>853</v>
+        <v>754</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -10577,7 +11125,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -10589,32 +11137,36 @@
         <v>78</v>
       </c>
       <c r="J145" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K145" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L145" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="M145" t="n">
         <v>1</v>
       </c>
       <c r="N145" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O145" t="n">
         <v>5</v>
       </c>
       <c r="P145" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q145" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="R145" t="n">
-        <v>852</v>
+        <v>902</v>
       </c>
       <c r="S145" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -10647,7 +11199,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10662,26 +11214,30 @@
         <v>93</v>
       </c>
       <c r="K146" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L146" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M146" t="n">
+        <v>3</v>
+      </c>
+      <c r="N146" t="n">
+        <v>11</v>
+      </c>
+      <c r="O146" t="n">
         <v>5</v>
       </c>
-      <c r="N146" t="n">
-        <v>13</v>
-      </c>
-      <c r="O146" t="n">
-        <v>7</v>
-      </c>
       <c r="P146" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q146" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R146" t="n">
-        <v>854</v>
+        <v>757</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -10717,7 +11273,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -10729,19 +11285,19 @@
         <v>67</v>
       </c>
       <c r="J147" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K147" t="n">
         <v>15</v>
       </c>
       <c r="L147" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M147" t="n">
         <v>5</v>
       </c>
       <c r="N147" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O147" t="n">
         <v>8</v>
@@ -10749,9 +11305,13 @@
       <c r="P147" t="n">
         <v>17</v>
       </c>
-      <c r="Q147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R147" t="n">
-        <v>915</v>
+        <v>788</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -10787,7 +11347,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10805,23 +11365,27 @@
         <v>20</v>
       </c>
       <c r="L148" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="M148" t="n">
         <v>2</v>
       </c>
       <c r="N148" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O148" t="n">
         <v>3</v>
       </c>
       <c r="P148" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q148" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R148" t="n">
-        <v>879</v>
+        <v>765</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -10857,7 +11421,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10866,35 +11430,39 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J149" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K149" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L149" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M149" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N149" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O149" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P149" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q149" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R149" t="n">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="S149" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -10927,7 +11495,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10936,10 +11504,10 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J150" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K150" t="n">
         <v>24</v>
@@ -10954,17 +11522,21 @@
         <v>2</v>
       </c>
       <c r="O150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P150" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q150" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R150" t="n">
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="S150" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -10997,7 +11569,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11006,7 +11578,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J151" t="n">
         <v>92</v>
@@ -11015,23 +11587,27 @@
         <v>18</v>
       </c>
       <c r="L151" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="M151" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N151" t="n">
+        <v>9</v>
+      </c>
+      <c r="O151" t="n">
         <v>13</v>
       </c>
-      <c r="O151" t="n">
-        <v>15</v>
-      </c>
       <c r="P151" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q151" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R151" t="n">
-        <v>926</v>
+        <v>843</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -11067,7 +11643,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11076,32 +11652,36 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J152" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K152" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="L152" t="n">
         <v>37</v>
       </c>
       <c r="M152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N152" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O152" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P152" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q152" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R152" t="n">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -11137,7 +11717,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11146,16 +11726,16 @@
         </is>
       </c>
       <c r="I153" t="n">
+        <v>69</v>
+      </c>
+      <c r="J153" t="n">
+        <v>105</v>
+      </c>
+      <c r="K153" t="n">
+        <v>16</v>
+      </c>
+      <c r="L153" t="n">
         <v>70</v>
-      </c>
-      <c r="J153" t="n">
-        <v>101</v>
-      </c>
-      <c r="K153" t="n">
-        <v>21</v>
-      </c>
-      <c r="L153" t="n">
-        <v>73</v>
       </c>
       <c r="M153" t="n">
         <v>1</v>
@@ -11164,14 +11744,18 @@
         <v>3</v>
       </c>
       <c r="O153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P153" t="n">
         <v>11</v>
       </c>
-      <c r="Q153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R153" t="n">
-        <v>797</v>
+        <v>870</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -11207,7 +11791,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11216,35 +11800,39 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J154" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K154" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L154" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="M154" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N154" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O154" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P154" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q154" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="R154" t="n">
-        <v>594</v>
+        <v>724</v>
       </c>
       <c r="S154" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -11277,7 +11865,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11286,35 +11874,39 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J155" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K155" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L155" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="M155" t="n">
         <v>2</v>
       </c>
       <c r="N155" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O155" t="n">
         <v>3</v>
       </c>
       <c r="P155" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q155" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R155" t="n">
-        <v>671</v>
+        <v>594</v>
       </c>
       <c r="S155" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -11347,7 +11939,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11356,35 +11948,39 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J156" t="n">
         <v>86</v>
       </c>
       <c r="K156" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L156" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N156" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O156" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P156" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q156" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R156" t="n">
-        <v>934</v>
+        <v>770</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -11417,7 +12013,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11426,32 +12022,36 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J157" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K157" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L157" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="M157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N157" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O157" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P157" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q157" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R157" t="n">
-        <v>802</v>
+        <v>836</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -11487,7 +12087,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>8/23/2026</t>
+          <t>8/24/2026</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11499,29 +12099,33 @@
         <v>58</v>
       </c>
       <c r="J158" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K158" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L158" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="M158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N158" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P158" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q158" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R158" t="n">
-        <v>913</v>
+        <v>755</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>

--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -558,30 +558,30 @@
         <v>77</v>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L2" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>636</v>
+        <v>846</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -629,13 +629,13 @@
         <v>85</v>
       </c>
       <c r="J3" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K3" t="n">
         <v>17</v>
       </c>
       <c r="L3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -644,7 +644,7 @@
         <v>7</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
         <v>14</v>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>890</v>
+        <v>933</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -703,33 +703,33 @@
         <v>60</v>
       </c>
       <c r="J4" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>751</v>
+        <v>862</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -777,25 +777,25 @@
         <v>57</v>
       </c>
       <c r="J5" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>690</v>
+        <v>911</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -851,16 +851,16 @@
         <v>85</v>
       </c>
       <c r="J6" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K6" t="n">
         <v>17</v>
       </c>
       <c r="L6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
         <v>7</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>898</v>
+        <v>943</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -928,33 +928,33 @@
         <v>78</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L7" t="n">
         <v>58</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N7" t="n">
         <v>9</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
         <v>13</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>625</v>
+        <v>727</v>
       </c>
       <c r="S7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
         <v>31</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
@@ -1021,11 +1021,11 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>821</v>
+        <v>832</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J9" t="n">
         <v>91</v>
@@ -1079,27 +1079,27 @@
         <v>17</v>
       </c>
       <c r="L9" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>765</v>
+        <v>942</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1147,33 +1147,33 @@
         <v>84</v>
       </c>
       <c r="J10" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K10" t="n">
         <v>14</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
         <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>901</v>
+        <v>946</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1221,13 +1221,13 @@
         <v>79</v>
       </c>
       <c r="J11" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M11" t="n">
         <v>2</v>
@@ -1239,15 +1239,15 @@
         <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>881</v>
+        <v>958</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1292,39 +1292,39 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K12" t="n">
         <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>13</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
         <v>17</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1369,13 +1369,13 @@
         <v>65</v>
       </c>
       <c r="J13" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K13" t="n">
         <v>24</v>
       </c>
       <c r="L13" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -1387,15 +1387,15 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>832</v>
+        <v>871</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1440,16 +1440,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J14" t="n">
         <v>83</v>
       </c>
       <c r="K14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M14" t="n">
         <v>2</v>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R14" t="n">
@@ -1514,28 +1514,28 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7</v>
+      </c>
+      <c r="O15" t="n">
         <v>3</v>
       </c>
-      <c r="N15" t="n">
-        <v>11</v>
-      </c>
-      <c r="O15" t="n">
-        <v>5</v>
-      </c>
       <c r="P15" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>886</v>
+        <v>965</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1588,16 +1588,16 @@
         </is>
       </c>
       <c r="I16" t="n">
+        <v>57</v>
+      </c>
+      <c r="J16" t="n">
+        <v>83</v>
+      </c>
+      <c r="K16" t="n">
+        <v>21</v>
+      </c>
+      <c r="L16" t="n">
         <v>58</v>
-      </c>
-      <c r="J16" t="n">
-        <v>82</v>
-      </c>
-      <c r="K16" t="n">
-        <v>23</v>
-      </c>
-      <c r="L16" t="n">
-        <v>55</v>
       </c>
       <c r="M16" t="n">
         <v>2</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>844</v>
+        <v>946</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1671,27 +1671,27 @@
         <v>21</v>
       </c>
       <c r="L17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M17" t="n">
         <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O17" t="n">
         <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>680</v>
+        <v>749</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1736,36 +1736,36 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J18" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L18" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>751</v>
+        <v>933</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1810,28 +1810,28 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J19" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M19" t="n">
         <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>762</v>
+        <v>832</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -1887,33 +1887,33 @@
         <v>68</v>
       </c>
       <c r="J20" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L20" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
+        <v>9</v>
+      </c>
+      <c r="O20" t="n">
         <v>8</v>
-      </c>
-      <c r="O20" t="n">
-        <v>7</v>
       </c>
       <c r="P20" t="n">
         <v>17</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>909</v>
+        <v>964</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1961,16 +1961,16 @@
         <v>72</v>
       </c>
       <c r="J21" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L21" t="n">
         <v>39</v>
       </c>
       <c r="M21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N21" t="n">
         <v>15</v>
@@ -1979,7 +1979,7 @@
         <v>10</v>
       </c>
       <c r="P21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>818</v>
+        <v>909</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2035,33 +2035,33 @@
         <v>70</v>
       </c>
       <c r="J22" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L22" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>01</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>911</v>
+        <v>986</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J23" t="n">
         <v>109</v>
@@ -2115,7 +2115,7 @@
         <v>15</v>
       </c>
       <c r="L23" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M23" t="n">
         <v>2</v>
@@ -2131,11 +2131,11 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>881</v>
+        <v>946</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>13</v>
       </c>
       <c r="L24" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M24" t="n">
         <v>2</v>
@@ -2201,7 +2201,7 @@
         <v>5</v>
       </c>
       <c r="P24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>766</v>
+        <v>951</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>75</v>
       </c>
       <c r="J25" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L25" t="n">
         <v>47</v>
@@ -2269,7 +2269,7 @@
         <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O25" t="n">
         <v>6</v>
@@ -2279,11 +2279,11 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>783</v>
+        <v>951</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2334,22 +2334,22 @@
         <v>95</v>
       </c>
       <c r="K26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L26" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M26" t="n">
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
         <v>7</v>
       </c>
       <c r="P26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>904</v>
+        <v>953</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2405,33 +2405,33 @@
         <v>68</v>
       </c>
       <c r="J27" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L27" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
         <v>10</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
         <v>15</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>814</v>
+        <v>949</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2479,13 +2479,13 @@
         <v>86</v>
       </c>
       <c r="J28" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L28" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M28" t="n">
         <v>2</v>
@@ -2494,18 +2494,18 @@
         <v>6</v>
       </c>
       <c r="O28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>896</v>
+        <v>934</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2559,19 +2559,19 @@
         <v>26</v>
       </c>
       <c r="L29" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2627,13 +2627,13 @@
         <v>86</v>
       </c>
       <c r="J30" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L30" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M30" t="n">
         <v>1</v>
@@ -2649,11 +2649,11 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>904</v>
+        <v>948</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2701,10 +2701,10 @@
         <v>55</v>
       </c>
       <c r="J31" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L31" t="n">
         <v>64</v>
@@ -2716,7 +2716,7 @@
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P31" t="n">
         <v>14</v>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>683</v>
+        <v>822</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -2772,36 +2772,36 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J32" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K32" t="n">
         <v>24</v>
       </c>
       <c r="L32" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M32" t="n">
         <v>2</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O32" t="n">
         <v>7</v>
       </c>
       <c r="P32" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>598</v>
+        <v>727</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -2849,7 +2849,7 @@
         <v>54</v>
       </c>
       <c r="J33" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K33" t="n">
         <v>20</v>
@@ -2858,27 +2858,27 @@
         <v>59</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
         <v>13</v>
       </c>
       <c r="O33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P33" t="n">
         <v>17</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>459</v>
+        <v>671</v>
       </c>
       <c r="S33" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
         <v>91</v>
       </c>
       <c r="K34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L34" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M34" t="n">
         <v>2</v>
@@ -2945,11 +2945,11 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>867</v>
+        <v>908</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -2997,33 +2997,33 @@
         <v>59</v>
       </c>
       <c r="J35" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K35" t="n">
         <v>14</v>
       </c>
       <c r="L35" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M35" t="n">
         <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>759</v>
+        <v>910</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3068,28 +3068,28 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J36" t="n">
         <v>83</v>
       </c>
       <c r="K36" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L36" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M36" t="n">
+        <v>3</v>
+      </c>
+      <c r="N36" t="n">
+        <v>7</v>
+      </c>
+      <c r="O36" t="n">
         <v>5</v>
       </c>
-      <c r="N36" t="n">
-        <v>8</v>
-      </c>
-      <c r="O36" t="n">
-        <v>7</v>
-      </c>
       <c r="P36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>613</v>
+        <v>891</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J37" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K37" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L37" t="n">
         <v>49</v>
@@ -3157,21 +3157,21 @@
         <v>2</v>
       </c>
       <c r="N37" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>758</v>
+        <v>782</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3219,13 +3219,13 @@
         <v>85</v>
       </c>
       <c r="J38" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K38" t="n">
         <v>17</v>
       </c>
       <c r="L38" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M38" t="n">
         <v>2</v>
@@ -3237,15 +3237,15 @@
         <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>900</v>
+        <v>934</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3290,36 +3290,36 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J39" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K39" t="n">
         <v>12</v>
       </c>
       <c r="L39" t="n">
+        <v>23</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" t="n">
+        <v>8</v>
+      </c>
+      <c r="O39" t="n">
+        <v>7</v>
+      </c>
+      <c r="P39" t="n">
         <v>22</v>
       </c>
-      <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>7</v>
-      </c>
-      <c r="O39" t="n">
-        <v>6</v>
-      </c>
-      <c r="P39" t="n">
-        <v>19</v>
-      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>830</v>
+        <v>981</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3364,16 +3364,16 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J40" t="n">
         <v>92</v>
       </c>
       <c r="K40" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L40" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M40" t="n">
         <v>3</v>
@@ -3389,11 +3389,11 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>682</v>
+        <v>914</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3444,16 +3444,16 @@
         <v>78</v>
       </c>
       <c r="K41" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L41" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M41" t="n">
         <v>1</v>
       </c>
       <c r="N41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -3463,11 +3463,11 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>742</v>
+        <v>797</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -3515,10 +3515,10 @@
         <v>51</v>
       </c>
       <c r="J42" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L42" t="n">
         <v>80</v>
@@ -3527,21 +3527,21 @@
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>721</v>
+        <v>743</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3586,39 +3586,39 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J43" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K43" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L43" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M43" t="n">
         <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O43" t="n">
         <v>5</v>
       </c>
       <c r="P43" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>827</v>
+        <v>948</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3660,16 +3660,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J44" t="n">
         <v>89</v>
       </c>
       <c r="K44" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L44" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M44" t="n">
         <v>2</v>
@@ -3681,15 +3681,15 @@
         <v>7</v>
       </c>
       <c r="P44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>901</v>
+        <v>924</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -3734,36 +3734,36 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J45" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K45" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L45" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M45" t="n">
         <v>5</v>
       </c>
       <c r="N45" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="O45" t="n">
         <v>7</v>
       </c>
       <c r="P45" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>803</v>
+        <v>903</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -3811,10 +3811,10 @@
         <v>68</v>
       </c>
       <c r="J46" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K46" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L46" t="n">
         <v>68</v>
@@ -3826,18 +3826,18 @@
         <v>6</v>
       </c>
       <c r="O46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P46" t="n">
         <v>16</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R46" t="n">
-        <v>835</v>
+        <v>964</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -3885,13 +3885,13 @@
         <v>55</v>
       </c>
       <c r="J47" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L47" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -3900,18 +3900,18 @@
         <v>5</v>
       </c>
       <c r="O47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
         <v>14</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>773</v>
+        <v>934</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -3959,16 +3959,16 @@
         <v>86</v>
       </c>
       <c r="J48" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K48" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L48" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
         <v>7</v>
@@ -3981,11 +3981,11 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>898</v>
+        <v>939</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -4036,30 +4036,30 @@
         <v>85</v>
       </c>
       <c r="K49" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L49" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P49" t="n">
         <v>13</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R49" t="n">
-        <v>754</v>
+        <v>943</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4104,36 +4104,36 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J50" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K50" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L50" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M50" t="n">
         <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P50" t="n">
         <v>9</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>828</v>
+        <v>942</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -4181,19 +4181,19 @@
         <v>87</v>
       </c>
       <c r="J51" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K51" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L51" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M51" t="n">
         <v>2</v>
       </c>
       <c r="N51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="R51" t="n">
-        <v>902</v>
+        <v>945</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -4255,33 +4255,33 @@
         <v>56</v>
       </c>
       <c r="J52" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K52" t="n">
         <v>15</v>
       </c>
       <c r="L52" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N52" t="n">
         <v>8</v>
       </c>
       <c r="O52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P52" t="n">
         <v>11</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>779</v>
+        <v>974</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -4326,16 +4326,16 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J53" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K53" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L53" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M53" t="n">
         <v>3</v>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>865</v>
+        <v>956</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -4403,13 +4403,13 @@
         <v>84</v>
       </c>
       <c r="J54" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K54" t="n">
         <v>14</v>
       </c>
       <c r="L54" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M54" t="n">
         <v>2</v>
@@ -4425,11 +4425,11 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R54" t="n">
-        <v>895</v>
+        <v>946</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -4480,13 +4480,13 @@
         <v>100</v>
       </c>
       <c r="K55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L55" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N55" t="n">
         <v>9</v>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>908</v>
+        <v>939</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J56" t="n">
         <v>83</v>
@@ -4557,7 +4557,7 @@
         <v>20</v>
       </c>
       <c r="L56" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M56" t="n">
         <v>2</v>
@@ -4573,11 +4573,11 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>728</v>
+        <v>784</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -4622,16 +4622,16 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J57" t="n">
         <v>84</v>
       </c>
       <c r="K57" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L57" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M57" t="n">
         <v>1</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>807</v>
+        <v>843</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -4702,10 +4702,10 @@
         <v>79</v>
       </c>
       <c r="K58" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L58" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M58" t="n">
         <v>2</v>
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -4776,22 +4776,22 @@
         <v>94</v>
       </c>
       <c r="K59" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L59" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M59" t="n">
         <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O59" t="n">
         <v>3</v>
       </c>
       <c r="P59" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>827</v>
+        <v>938</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -4850,22 +4850,22 @@
         <v>94</v>
       </c>
       <c r="K60" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L60" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M60" t="n">
         <v>2</v>
       </c>
       <c r="N60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O60" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P60" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>859</v>
+        <v>960</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -4918,28 +4918,28 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J61" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M61" t="n">
         <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O61" t="n">
         <v>5</v>
       </c>
       <c r="P61" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>905</v>
+        <v>982</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -4995,13 +4995,13 @@
         <v>55</v>
       </c>
       <c r="J62" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K62" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L62" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -5013,7 +5013,7 @@
         <v>3</v>
       </c>
       <c r="P62" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>864</v>
+        <v>823</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5069,33 +5069,33 @@
         <v>83</v>
       </c>
       <c r="J63" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K63" t="n">
         <v>13</v>
       </c>
       <c r="L63" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M63" t="n">
         <v>1</v>
       </c>
       <c r="N63" t="n">
+        <v>5</v>
+      </c>
+      <c r="O63" t="n">
         <v>3</v>
-      </c>
-      <c r="O63" t="n">
-        <v>5</v>
       </c>
       <c r="P63" t="n">
         <v>13</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R63" t="n">
-        <v>886</v>
+        <v>928</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -5143,33 +5143,33 @@
         <v>69</v>
       </c>
       <c r="J64" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K64" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L64" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O64" t="n">
         <v>6</v>
       </c>
       <c r="P64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R64" t="n">
-        <v>832</v>
+        <v>986</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -5220,13 +5220,13 @@
         <v>86</v>
       </c>
       <c r="K65" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L65" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
         <v>5</v>
@@ -5235,15 +5235,15 @@
         <v>3</v>
       </c>
       <c r="P65" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R65" t="n">
-        <v>774</v>
+        <v>958</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -5288,16 +5288,16 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J66" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K66" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L66" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M66" t="n">
         <v>2</v>
@@ -5306,7 +5306,7 @@
         <v>6</v>
       </c>
       <c r="O66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P66" t="n">
         <v>15</v>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>905</v>
+        <v>870</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5362,28 +5362,28 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J67" t="n">
         <v>95</v>
       </c>
       <c r="K67" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L67" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O67" t="n">
         <v>6</v>
       </c>
       <c r="P67" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>765</v>
+        <v>950</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -5436,36 +5436,36 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J68" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K68" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L68" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M68" t="n">
         <v>5</v>
       </c>
       <c r="N68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O68" t="n">
         <v>8</v>
       </c>
       <c r="P68" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>794</v>
+        <v>949</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -5513,10 +5513,10 @@
         <v>76</v>
       </c>
       <c r="J69" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K69" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L69" t="n">
         <v>45</v>
@@ -5528,18 +5528,18 @@
         <v>10</v>
       </c>
       <c r="O69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P69" t="n">
         <v>22</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>828</v>
+        <v>951</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -5593,27 +5593,27 @@
         <v>19</v>
       </c>
       <c r="L70" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M70" t="n">
         <v>5</v>
       </c>
       <c r="N70" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P70" t="n">
         <v>24</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R70" t="n">
-        <v>859</v>
+        <v>955</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -5661,33 +5661,33 @@
         <v>65</v>
       </c>
       <c r="J71" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K71" t="n">
         <v>18</v>
       </c>
       <c r="L71" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M71" t="n">
         <v>3</v>
       </c>
       <c r="N71" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O71" t="n">
         <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R71" t="n">
-        <v>866</v>
+        <v>936</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -5738,13 +5738,13 @@
         <v>91</v>
       </c>
       <c r="K72" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L72" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N72" t="n">
         <v>5</v>
@@ -5753,7 +5753,7 @@
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         </is>
       </c>
       <c r="R72" t="n">
-        <v>838</v>
+        <v>905</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -5806,28 +5806,28 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J73" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K73" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L73" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M73" t="n">
         <v>2</v>
       </c>
       <c r="N73" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O73" t="n">
         <v>3</v>
       </c>
       <c r="P73" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>657</v>
+        <v>702</v>
       </c>
       <c r="S73" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5880,16 +5880,16 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J74" t="n">
         <v>87</v>
       </c>
       <c r="K74" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L74" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M74" t="n">
         <v>3</v>
@@ -5905,11 +5905,11 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R74" t="n">
-        <v>764</v>
+        <v>843</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -5957,33 +5957,33 @@
         <v>66</v>
       </c>
       <c r="J75" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K75" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L75" t="n">
         <v>45</v>
       </c>
       <c r="M75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P75" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R75" t="n">
-        <v>847</v>
+        <v>959</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -6031,16 +6031,16 @@
         <v>58</v>
       </c>
       <c r="J76" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K76" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L76" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N76" t="n">
         <v>5</v>
@@ -6049,15 +6049,15 @@
         <v>6</v>
       </c>
       <c r="P76" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R76" t="n">
-        <v>772</v>
+        <v>752</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -6105,25 +6105,25 @@
         <v>64</v>
       </c>
       <c r="J77" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K77" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L77" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M77" t="n">
         <v>2</v>
       </c>
       <c r="N77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P77" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>811</v>
+        <v>948</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -6182,10 +6182,10 @@
         <v>79</v>
       </c>
       <c r="K78" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L78" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M78" t="n">
         <v>2</v>
@@ -6201,11 +6201,11 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R78" t="n">
-        <v>809</v>
+        <v>900</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -6259,7 +6259,7 @@
         <v>18</v>
       </c>
       <c r="L79" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M79" t="n">
         <v>3</v>
@@ -6275,11 +6275,11 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R79" t="n">
-        <v>745</v>
+        <v>932</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -6324,36 +6324,36 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J80" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K80" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L80" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M80" t="n">
         <v>3</v>
       </c>
       <c r="N80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O80" t="n">
         <v>5</v>
       </c>
       <c r="P80" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R80" t="n">
-        <v>733</v>
+        <v>795</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -6401,33 +6401,33 @@
         <v>56</v>
       </c>
       <c r="J81" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K81" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L81" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N81" t="n">
         <v>8</v>
       </c>
       <c r="O81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P81" t="n">
         <v>11</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R81" t="n">
-        <v>731</v>
+        <v>837</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -6472,39 +6472,39 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J82" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K82" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L82" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M82" t="n">
         <v>2</v>
       </c>
       <c r="N82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O82" t="n">
         <v>8</v>
       </c>
       <c r="P82" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R82" t="n">
-        <v>646</v>
+        <v>789</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -6546,16 +6546,16 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J83" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K83" t="n">
         <v>12</v>
       </c>
       <c r="L83" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M83" t="n">
         <v>3</v>
@@ -6564,18 +6564,18 @@
         <v>9</v>
       </c>
       <c r="O83" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P83" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R83" t="n">
-        <v>809</v>
+        <v>962</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -6623,36 +6623,36 @@
         <v>70</v>
       </c>
       <c r="J84" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K84" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L84" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N84" t="n">
         <v>16</v>
       </c>
       <c r="O84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P84" t="n">
         <v>23</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R84" t="n">
-        <v>720</v>
+        <v>955</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -6694,16 +6694,16 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J85" t="n">
         <v>89</v>
       </c>
       <c r="K85" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L85" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M85" t="n">
         <v>2</v>
@@ -6712,18 +6712,18 @@
         <v>6</v>
       </c>
       <c r="O85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P85" t="n">
         <v>13</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R85" t="n">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -6768,28 +6768,28 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J86" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K86" t="n">
         <v>24</v>
       </c>
       <c r="L86" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M86" t="n">
         <v>2</v>
       </c>
       <c r="N86" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O86" t="n">
         <v>3</v>
       </c>
       <c r="P86" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="R86" t="n">
-        <v>673</v>
+        <v>690</v>
       </c>
       <c r="S86" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -6845,36 +6845,36 @@
         <v>59</v>
       </c>
       <c r="J87" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K87" t="n">
         <v>22</v>
       </c>
       <c r="L87" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M87" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N87" t="n">
+        <v>13</v>
+      </c>
+      <c r="O87" t="n">
+        <v>5</v>
+      </c>
+      <c r="P87" t="n">
         <v>17</v>
       </c>
-      <c r="O87" t="n">
-        <v>8</v>
-      </c>
-      <c r="P87" t="n">
-        <v>24</v>
-      </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R87" t="n">
-        <v>770</v>
+        <v>921</v>
       </c>
       <c r="S87" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -6922,30 +6922,30 @@
         <v>90</v>
       </c>
       <c r="K88" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L88" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M88" t="n">
         <v>2</v>
       </c>
       <c r="N88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
       </c>
       <c r="P88" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>01</t>
         </is>
       </c>
       <c r="R88" t="n">
-        <v>756</v>
+        <v>813</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J89" t="n">
         <v>113</v>
@@ -6999,19 +6999,19 @@
         <v>16</v>
       </c>
       <c r="L89" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M89" t="n">
         <v>2</v>
       </c>
       <c r="N89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O89" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P89" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         </is>
       </c>
       <c r="R89" t="n">
-        <v>898</v>
+        <v>940</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -7073,7 +7073,7 @@
         <v>25</v>
       </c>
       <c r="L90" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -7082,18 +7082,18 @@
         <v>3</v>
       </c>
       <c r="O90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P90" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R90" t="n">
-        <v>773</v>
+        <v>907</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -7141,19 +7141,19 @@
         <v>65</v>
       </c>
       <c r="J91" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K91" t="n">
         <v>23</v>
       </c>
       <c r="L91" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M91" t="n">
         <v>3</v>
       </c>
       <c r="N91" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O91" t="n">
         <v>6</v>
@@ -7163,14 +7163,14 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R91" t="n">
-        <v>813</v>
+        <v>924</v>
       </c>
       <c r="S91" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -7218,30 +7218,30 @@
         <v>93</v>
       </c>
       <c r="K92" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L92" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N92" t="n">
         <v>7</v>
       </c>
       <c r="O92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P92" t="n">
         <v>9</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R92" t="n">
-        <v>798</v>
+        <v>914</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -7286,16 +7286,16 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J93" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K93" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L93" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M93" t="n">
         <v>1</v>
@@ -7311,11 +7311,11 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R93" t="n">
-        <v>657</v>
+        <v>703</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -7363,10 +7363,10 @@
         <v>63</v>
       </c>
       <c r="J94" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K94" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L94" t="n">
         <v>48</v>
@@ -7381,15 +7381,15 @@
         <v>7</v>
       </c>
       <c r="P94" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R94" t="n">
-        <v>855</v>
+        <v>901</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -7434,16 +7434,16 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J95" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K95" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L95" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M95" t="n">
         <v>2</v>
@@ -7455,7 +7455,7 @@
         <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="R95" t="n">
-        <v>850</v>
+        <v>964</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -7508,28 +7508,28 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J96" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K96" t="n">
         <v>18</v>
       </c>
       <c r="L96" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M96" t="n">
         <v>3</v>
       </c>
       <c r="N96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O96" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P96" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="R96" t="n">
-        <v>891</v>
+        <v>931</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -7582,16 +7582,16 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J97" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K97" t="n">
         <v>21</v>
       </c>
       <c r="L97" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="M97" t="n">
         <v>2</v>
@@ -7611,7 +7611,7 @@
         </is>
       </c>
       <c r="R97" t="n">
-        <v>764</v>
+        <v>936</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -7656,36 +7656,36 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J98" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K98" t="n">
         <v>14</v>
       </c>
       <c r="L98" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M98" t="n">
         <v>3</v>
       </c>
       <c r="N98" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P98" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R98" t="n">
-        <v>878</v>
+        <v>919</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -7733,25 +7733,25 @@
         <v>59</v>
       </c>
       <c r="J99" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K99" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L99" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M99" t="n">
         <v>1</v>
       </c>
       <c r="N99" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P99" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="R99" t="n">
-        <v>746</v>
+        <v>917</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="J100" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K100" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L100" t="n">
         <v>39</v>
@@ -7825,7 +7825,7 @@
         <v>7</v>
       </c>
       <c r="P100" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="R100" t="n">
-        <v>834</v>
+        <v>957</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -7878,36 +7878,36 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J101" t="n">
         <v>98</v>
       </c>
       <c r="K101" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L101" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N101" t="n">
         <v>6</v>
       </c>
       <c r="O101" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P101" t="n">
         <v>15</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>1/4/1 17:00 LMT</t>
+          <t>1/3/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R101" t="n">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -7952,28 +7952,28 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J102" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K102" t="n">
         <v>18</v>
       </c>
       <c r="L102" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M102" t="n">
+        <v>2</v>
+      </c>
+      <c r="N102" t="n">
+        <v>10</v>
+      </c>
+      <c r="O102" t="n">
         <v>3</v>
       </c>
-      <c r="N102" t="n">
-        <v>8</v>
-      </c>
-      <c r="O102" t="n">
-        <v>5</v>
-      </c>
       <c r="P102" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="R102" t="n">
-        <v>640</v>
+        <v>861</v>
       </c>
       <c r="S102" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -8029,10 +8029,10 @@
         <v>85</v>
       </c>
       <c r="J103" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K103" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L103" t="n">
         <v>48</v>
@@ -8044,18 +8044,18 @@
         <v>6</v>
       </c>
       <c r="O103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P103" t="n">
         <v>14</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R103" t="n">
-        <v>894</v>
+        <v>940</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -8103,33 +8103,33 @@
         <v>79</v>
       </c>
       <c r="J104" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K104" t="n">
         <v>14</v>
       </c>
       <c r="L104" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M104" t="n">
         <v>2</v>
       </c>
       <c r="N104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O104" t="n">
         <v>7</v>
       </c>
       <c r="P104" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1/5/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R104" t="n">
-        <v>861</v>
+        <v>912</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J105" t="n">
         <v>101</v>
@@ -8183,7 +8183,7 @@
         <v>15</v>
       </c>
       <c r="L105" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M105" t="n">
         <v>7</v>
@@ -8192,7 +8192,7 @@
         <v>14</v>
       </c>
       <c r="O105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P105" t="n">
         <v>23</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="R105" t="n">
-        <v>824</v>
+        <v>782</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -8251,25 +8251,25 @@
         <v>63</v>
       </c>
       <c r="J106" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K106" t="n">
         <v>21</v>
       </c>
       <c r="L106" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M106" t="n">
         <v>2</v>
       </c>
       <c r="N106" t="n">
+        <v>3</v>
+      </c>
+      <c r="O106" t="n">
         <v>5</v>
       </c>
-      <c r="O106" t="n">
-        <v>6</v>
-      </c>
       <c r="P106" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="R106" t="n">
-        <v>805</v>
+        <v>946</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -8331,10 +8331,10 @@
         <v>20</v>
       </c>
       <c r="L107" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N107" t="n">
         <v>7</v>
@@ -8347,11 +8347,11 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R107" t="n">
-        <v>849</v>
+        <v>955</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -8399,25 +8399,25 @@
         <v>60</v>
       </c>
       <c r="J108" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K108" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L108" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M108" t="n">
         <v>2</v>
       </c>
       <c r="N108" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O108" t="n">
         <v>3</v>
       </c>
       <c r="P108" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -8425,10 +8425,10 @@
         </is>
       </c>
       <c r="R108" t="n">
-        <v>760</v>
+        <v>827</v>
       </c>
       <c r="S108" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -8470,36 +8470,36 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J109" t="n">
         <v>86</v>
       </c>
       <c r="K109" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L109" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M109" t="n">
+        <v>2</v>
+      </c>
+      <c r="N109" t="n">
+        <v>7</v>
+      </c>
+      <c r="O109" t="n">
         <v>3</v>
       </c>
-      <c r="N109" t="n">
-        <v>8</v>
-      </c>
-      <c r="O109" t="n">
-        <v>5</v>
-      </c>
       <c r="P109" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R109" t="n">
-        <v>743</v>
+        <v>872</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -8547,13 +8547,13 @@
         <v>80</v>
       </c>
       <c r="J110" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K110" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L110" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M110" t="n">
         <v>1</v>
@@ -8569,11 +8569,11 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R110" t="n">
-        <v>900</v>
+        <v>945</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -8624,30 +8624,30 @@
         <v>95</v>
       </c>
       <c r="K111" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L111" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N111" t="n">
         <v>7</v>
       </c>
       <c r="O111" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P111" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>1/5/1 17:00 LMT</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R111" t="n">
-        <v>911</v>
+        <v>942</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -8707,21 +8707,21 @@
         <v>2</v>
       </c>
       <c r="N112" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O112" t="n">
         <v>5</v>
       </c>
       <c r="P112" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R112" t="n">
-        <v>769</v>
+        <v>951</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -8772,16 +8772,16 @@
         <v>80</v>
       </c>
       <c r="K113" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L113" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M113" t="n">
         <v>2</v>
       </c>
       <c r="N113" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O113" t="n">
         <v>6</v>
@@ -8791,11 +8791,11 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R113" t="n">
-        <v>631</v>
+        <v>743</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -8846,10 +8846,10 @@
         <v>96</v>
       </c>
       <c r="K114" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L114" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M114" t="n">
         <v>2</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="R114" t="n">
-        <v>886</v>
+        <v>963</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -8914,16 +8914,16 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J115" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K115" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L115" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M115" t="n">
         <v>1</v>
@@ -8935,15 +8935,15 @@
         <v>7</v>
       </c>
       <c r="P115" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R115" t="n">
-        <v>883</v>
+        <v>829</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -8994,7 +8994,7 @@
         <v>95</v>
       </c>
       <c r="K116" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L116" t="n">
         <v>32</v>
@@ -9003,21 +9003,21 @@
         <v>3</v>
       </c>
       <c r="N116" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O116" t="n">
         <v>8</v>
       </c>
       <c r="P116" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R116" t="n">
-        <v>802</v>
+        <v>841</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J117" t="n">
         <v>87</v>
@@ -9071,7 +9071,7 @@
         <v>19</v>
       </c>
       <c r="L117" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M117" t="n">
         <v>3</v>
@@ -9087,11 +9087,11 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R117" t="n">
-        <v>719</v>
+        <v>828</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -9142,30 +9142,30 @@
         <v>81</v>
       </c>
       <c r="K118" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L118" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M118" t="n">
         <v>2</v>
       </c>
       <c r="N118" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O118" t="n">
         <v>3</v>
       </c>
       <c r="P118" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R118" t="n">
-        <v>596</v>
+        <v>811</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -9213,33 +9213,33 @@
         <v>59</v>
       </c>
       <c r="J119" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K119" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L119" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
         <v>5</v>
       </c>
       <c r="O119" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P119" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R119" t="n">
-        <v>844</v>
+        <v>941</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -9287,33 +9287,33 @@
         <v>58</v>
       </c>
       <c r="J120" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K120" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L120" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N120" t="n">
         <v>9</v>
       </c>
       <c r="O120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P120" t="n">
         <v>13</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R120" t="n">
-        <v>770</v>
+        <v>957</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -9361,33 +9361,33 @@
         <v>61</v>
       </c>
       <c r="J121" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K121" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L121" t="n">
         <v>58</v>
       </c>
       <c r="M121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N121" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O121" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P121" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R121" t="n">
-        <v>799</v>
+        <v>951</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -9432,36 +9432,36 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J122" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K122" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L122" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N122" t="n">
         <v>5</v>
       </c>
       <c r="O122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P122" t="n">
         <v>15</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R122" t="n">
-        <v>797</v>
+        <v>983</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -9509,33 +9509,33 @@
         <v>79</v>
       </c>
       <c r="J123" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K123" t="n">
         <v>16</v>
       </c>
       <c r="L123" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M123" t="n">
         <v>1</v>
       </c>
       <c r="N123" t="n">
+        <v>6</v>
+      </c>
+      <c r="O123" t="n">
         <v>5</v>
       </c>
-      <c r="O123" t="n">
-        <v>3</v>
-      </c>
       <c r="P123" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R123" t="n">
-        <v>877</v>
+        <v>952</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -9580,36 +9580,36 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J124" t="n">
         <v>96</v>
       </c>
       <c r="K124" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L124" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M124" t="n">
         <v>2</v>
       </c>
       <c r="N124" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O124" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P124" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R124" t="n">
-        <v>820</v>
+        <v>977</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -9654,36 +9654,36 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J125" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K125" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L125" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M125" t="n">
         <v>2</v>
       </c>
       <c r="N125" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O125" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P125" t="n">
         <v>16</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R125" t="n">
-        <v>901</v>
+        <v>952</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -9734,30 +9734,30 @@
         <v>91</v>
       </c>
       <c r="K126" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L126" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M126" t="n">
         <v>2</v>
       </c>
       <c r="N126" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O126" t="n">
         <v>3</v>
       </c>
       <c r="P126" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R126" t="n">
-        <v>731</v>
+        <v>814</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -9805,33 +9805,33 @@
         <v>66</v>
       </c>
       <c r="J127" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K127" t="n">
         <v>15</v>
       </c>
       <c r="L127" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N127" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P127" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R127" t="n">
-        <v>819</v>
+        <v>949</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -9882,33 +9882,33 @@
         <v>86</v>
       </c>
       <c r="K128" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L128" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M128" t="n">
         <v>2</v>
       </c>
       <c r="N128" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O128" t="n">
         <v>3</v>
       </c>
       <c r="P128" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R128" t="n">
-        <v>761</v>
+        <v>860</v>
       </c>
       <c r="S128" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -9953,36 +9953,36 @@
         <v>73</v>
       </c>
       <c r="J129" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K129" t="n">
         <v>19</v>
       </c>
       <c r="L129" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M129" t="n">
         <v>3</v>
       </c>
       <c r="N129" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O129" t="n">
         <v>7</v>
       </c>
       <c r="P129" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R129" t="n">
-        <v>813</v>
+        <v>944</v>
       </c>
       <c r="S129" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -10024,36 +10024,36 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J130" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K130" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L130" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M130" t="n">
         <v>2</v>
       </c>
       <c r="N130" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O130" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P130" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R130" t="n">
-        <v>794</v>
+        <v>951</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -10101,33 +10101,33 @@
         <v>80</v>
       </c>
       <c r="J131" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K131" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L131" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M131" t="n">
         <v>1</v>
       </c>
       <c r="N131" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O131" t="n">
         <v>5</v>
       </c>
       <c r="P131" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R131" t="n">
-        <v>905</v>
+        <v>947</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -10175,33 +10175,33 @@
         <v>67</v>
       </c>
       <c r="J132" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K132" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L132" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M132" t="n">
         <v>3</v>
       </c>
       <c r="N132" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O132" t="n">
         <v>5</v>
       </c>
       <c r="P132" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R132" t="n">
-        <v>847</v>
+        <v>960</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -10255,27 +10255,27 @@
         <v>19</v>
       </c>
       <c r="L133" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N133" t="n">
         <v>6</v>
       </c>
       <c r="O133" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P133" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R133" t="n">
-        <v>907</v>
+        <v>893</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -10320,36 +10320,36 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J134" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K134" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L134" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M134" t="n">
+        <v>2</v>
+      </c>
+      <c r="N134" t="n">
+        <v>7</v>
+      </c>
+      <c r="O134" t="n">
         <v>3</v>
       </c>
-      <c r="N134" t="n">
+      <c r="P134" t="n">
         <v>9</v>
       </c>
-      <c r="O134" t="n">
-        <v>5</v>
-      </c>
-      <c r="P134" t="n">
-        <v>13</v>
-      </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R134" t="n">
-        <v>602</v>
+        <v>846</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -10394,16 +10394,16 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J135" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K135" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L135" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M135" t="n">
         <v>2</v>
@@ -10415,15 +10415,15 @@
         <v>7</v>
       </c>
       <c r="P135" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R135" t="n">
-        <v>903</v>
+        <v>940</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J136" t="n">
         <v>90</v>
@@ -10477,27 +10477,27 @@
         <v>20</v>
       </c>
       <c r="L136" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N136" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P136" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R136" t="n">
-        <v>659</v>
+        <v>742</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -10548,13 +10548,13 @@
         <v>87</v>
       </c>
       <c r="K137" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L137" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N137" t="n">
         <v>7</v>
@@ -10567,11 +10567,11 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R137" t="n">
-        <v>849</v>
+        <v>926</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -10625,7 +10625,7 @@
         <v>16</v>
       </c>
       <c r="L138" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M138" t="n">
         <v>3</v>
@@ -10634,10 +10634,10 @@
         <v>11</v>
       </c>
       <c r="O138" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P138" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="R138" t="n">
-        <v>766</v>
+        <v>955</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -10693,33 +10693,33 @@
         <v>54</v>
       </c>
       <c r="J139" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K139" t="n">
         <v>15</v>
       </c>
       <c r="L139" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N139" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P139" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R139" t="n">
-        <v>761</v>
+        <v>784</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -10770,7 +10770,7 @@
         <v>82</v>
       </c>
       <c r="K140" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L140" t="n">
         <v>43</v>
@@ -10782,18 +10782,18 @@
         <v>16</v>
       </c>
       <c r="O140" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P140" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>01</t>
         </is>
       </c>
       <c r="R140" t="n">
-        <v>762</v>
+        <v>950</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -10841,25 +10841,25 @@
         <v>77</v>
       </c>
       <c r="J141" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K141" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L141" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M141" t="n">
         <v>2</v>
       </c>
       <c r="N141" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O141" t="n">
         <v>8</v>
       </c>
       <c r="P141" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         </is>
       </c>
       <c r="R141" t="n">
-        <v>901</v>
+        <v>953</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -10912,19 +10912,19 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J142" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K142" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L142" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N142" t="n">
         <v>10</v>
@@ -10933,15 +10933,15 @@
         <v>6</v>
       </c>
       <c r="P142" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>1/5/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R142" t="n">
-        <v>786</v>
+        <v>916</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -10995,27 +10995,27 @@
         <v>21</v>
       </c>
       <c r="L143" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N143" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P143" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R143" t="n">
-        <v>771</v>
+        <v>939</v>
       </c>
       <c r="S143" t="n">
         <v>0.01</v>
@@ -11060,36 +11060,36 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J144" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K144" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L144" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M144" t="n">
+        <v>2</v>
+      </c>
+      <c r="N144" t="n">
+        <v>7</v>
+      </c>
+      <c r="O144" t="n">
         <v>3</v>
       </c>
-      <c r="N144" t="n">
-        <v>6</v>
-      </c>
-      <c r="O144" t="n">
-        <v>5</v>
-      </c>
       <c r="P144" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R144" t="n">
-        <v>754</v>
+        <v>854</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -11134,22 +11134,22 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J145" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K145" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L145" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M145" t="n">
         <v>1</v>
       </c>
       <c r="N145" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O145" t="n">
         <v>5</v>
@@ -11163,7 +11163,7 @@
         </is>
       </c>
       <c r="R145" t="n">
-        <v>902</v>
+        <v>953</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -11208,16 +11208,16 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J146" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K146" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L146" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M146" t="n">
         <v>3</v>
@@ -11233,14 +11233,14 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R146" t="n">
-        <v>757</v>
+        <v>913</v>
       </c>
       <c r="S146" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -11288,30 +11288,30 @@
         <v>94</v>
       </c>
       <c r="K147" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L147" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M147" t="n">
         <v>5</v>
       </c>
       <c r="N147" t="n">
+        <v>10</v>
+      </c>
+      <c r="O147" t="n">
         <v>9</v>
       </c>
-      <c r="O147" t="n">
-        <v>8</v>
-      </c>
       <c r="P147" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/6/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R147" t="n">
-        <v>788</v>
+        <v>909</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J148" t="n">
         <v>83</v>
@@ -11365,27 +11365,27 @@
         <v>20</v>
       </c>
       <c r="L148" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M148" t="n">
         <v>2</v>
       </c>
       <c r="N148" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O148" t="n">
         <v>3</v>
       </c>
       <c r="P148" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R148" t="n">
-        <v>765</v>
+        <v>870</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -11433,13 +11433,13 @@
         <v>71</v>
       </c>
       <c r="J149" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K149" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L149" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="M149" t="n">
         <v>2</v>
@@ -11451,15 +11451,15 @@
         <v>6</v>
       </c>
       <c r="P149" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R149" t="n">
-        <v>883</v>
+        <v>940</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -11504,13 +11504,13 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J150" t="n">
         <v>87</v>
       </c>
       <c r="K150" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L150" t="n">
         <v>80</v>
@@ -11522,7 +11522,7 @@
         <v>2</v>
       </c>
       <c r="O150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P150" t="n">
         <v>8</v>
@@ -11533,7 +11533,7 @@
         </is>
       </c>
       <c r="R150" t="n">
-        <v>795</v>
+        <v>944</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -11581,33 +11581,33 @@
         <v>74</v>
       </c>
       <c r="J151" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K151" t="n">
         <v>18</v>
       </c>
       <c r="L151" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M151" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N151" t="n">
         <v>9</v>
       </c>
       <c r="O151" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P151" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R151" t="n">
-        <v>843</v>
+        <v>915</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -11655,13 +11655,13 @@
         <v>80</v>
       </c>
       <c r="J152" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K152" t="n">
         <v>16</v>
       </c>
       <c r="L152" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M152" t="n">
         <v>1</v>
@@ -11670,18 +11670,18 @@
         <v>7</v>
       </c>
       <c r="O152" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P152" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R152" t="n">
-        <v>883</v>
+        <v>931</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -11726,19 +11726,19 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J153" t="n">
         <v>105</v>
       </c>
       <c r="K153" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L153" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="M153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N153" t="n">
         <v>3</v>
@@ -11747,15 +11747,15 @@
         <v>6</v>
       </c>
       <c r="P153" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R153" t="n">
-        <v>870</v>
+        <v>950</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -11806,30 +11806,30 @@
         <v>81</v>
       </c>
       <c r="K154" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L154" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M154" t="n">
+        <v>1</v>
+      </c>
+      <c r="N154" t="n">
+        <v>5</v>
+      </c>
+      <c r="O154" t="n">
         <v>3</v>
       </c>
-      <c r="N154" t="n">
-        <v>6</v>
-      </c>
-      <c r="O154" t="n">
-        <v>6</v>
-      </c>
       <c r="P154" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R154" t="n">
-        <v>724</v>
+        <v>837</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -11874,7 +11874,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J155" t="n">
         <v>79</v>
@@ -11883,27 +11883,27 @@
         <v>24</v>
       </c>
       <c r="L155" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M155" t="n">
         <v>2</v>
       </c>
       <c r="N155" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O155" t="n">
         <v>3</v>
       </c>
       <c r="P155" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R155" t="n">
-        <v>594</v>
+        <v>743</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -11948,36 +11948,36 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J156" t="n">
         <v>86</v>
       </c>
       <c r="K156" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L156" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M156" t="n">
         <v>3</v>
       </c>
       <c r="N156" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O156" t="n">
         <v>5</v>
       </c>
       <c r="P156" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R156" t="n">
-        <v>770</v>
+        <v>816</v>
       </c>
       <c r="S156" t="n">
         <v>0.04</v>
@@ -12022,28 +12022,28 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J157" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K157" t="n">
         <v>20</v>
       </c>
       <c r="L157" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M157" t="n">
         <v>1</v>
       </c>
       <c r="N157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O157" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P157" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         </is>
       </c>
       <c r="R157" t="n">
-        <v>836</v>
+        <v>922</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -12102,30 +12102,30 @@
         <v>93</v>
       </c>
       <c r="K158" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L158" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M158" t="n">
         <v>2</v>
       </c>
       <c r="N158" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O158" t="n">
         <v>3</v>
       </c>
       <c r="P158" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R158" t="n">
-        <v>755</v>
+        <v>933</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>

--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -552,39 +552,39 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J2" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L2" t="n">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>846</v>
+        <v>788</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -626,36 +626,36 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J3" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>933</v>
+        <v>800</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -691,7 +691,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -706,30 +706,30 @@
         <v>91</v>
       </c>
       <c r="K4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>11</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
         <v>16</v>
       </c>
-      <c r="L4" t="n">
-        <v>60</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>17</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>24</v>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>862</v>
+        <v>822</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J5" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="M5" t="n">
         <v>2</v>
@@ -795,15 +795,15 @@
         <v>7</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>911</v>
+        <v>698</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -848,36 +848,36 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J6" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="M6" t="n">
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>943</v>
+        <v>866</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -922,16 +922,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J7" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K7" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L7" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="M7" t="n">
         <v>2</v>
@@ -947,14 +947,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -996,28 +996,28 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J8" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1070,36 +1070,36 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L9" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>942</v>
+        <v>768</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1144,36 +1144,36 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J10" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1/3/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>946</v>
+        <v>853</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J11" t="n">
         <v>107</v>
@@ -1227,7 +1227,7 @@
         <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="M11" t="n">
         <v>2</v>
@@ -1243,11 +1243,11 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>958</v>
+        <v>883</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1292,39 +1292,39 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L12" t="n">
         <v>65</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
         <v>13</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
         <v>17</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>755</v>
+        <v>796</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1366,36 +1366,36 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J13" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K13" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L13" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>871</v>
+        <v>893</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1440,39 +1440,39 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J14" t="n">
         <v>83</v>
       </c>
       <c r="K14" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>750</v>
+        <v>660</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1514,36 +1514,36 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J15" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L15" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>965</v>
+        <v>860</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1588,28 +1588,28 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J16" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K16" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L16" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>946</v>
+        <v>865</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1665,36 +1665,36 @@
         <v>58</v>
       </c>
       <c r="J17" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K17" t="n">
         <v>21</v>
       </c>
       <c r="L17" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>8</v>
+      </c>
+      <c r="O17" t="n">
         <v>3</v>
       </c>
-      <c r="N17" t="n">
-        <v>10</v>
-      </c>
-      <c r="O17" t="n">
-        <v>5</v>
-      </c>
       <c r="P17" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>749</v>
+        <v>689</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1736,36 +1736,36 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J18" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L18" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>933</v>
+        <v>854</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1810,36 +1810,36 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="J19" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K19" t="n">
+        <v>13</v>
+      </c>
+      <c r="L19" t="n">
+        <v>23</v>
+      </c>
+      <c r="M19" t="n">
+        <v>7</v>
+      </c>
+      <c r="N19" t="n">
         <v>14</v>
       </c>
-      <c r="L19" t="n">
-        <v>32</v>
-      </c>
-      <c r="M19" t="n">
-        <v>5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>10</v>
-      </c>
       <c r="O19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1/4/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>832</v>
+        <v>654</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1884,36 +1884,36 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J20" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L20" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>916</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1958,36 +1958,36 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J21" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K21" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L21" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>909</v>
+        <v>701</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2032,22 +2032,22 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J22" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L22" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O22" t="n">
         <v>8</v>
@@ -2057,11 +2057,11 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>986</v>
+        <v>908</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J23" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L23" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="M23" t="n">
         <v>2</v>
@@ -2131,11 +2131,11 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>946</v>
+        <v>870</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2180,36 +2180,36 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J24" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L24" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O24" t="n">
         <v>5</v>
       </c>
       <c r="P24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/2/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>951</v>
+        <v>864</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2254,36 +2254,36 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J25" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L25" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>951</v>
+        <v>779</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2328,25 +2328,25 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J26" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L26" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P26" t="n">
         <v>15</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>953</v>
+        <v>849</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2402,16 +2402,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J27" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L27" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="M27" t="n">
         <v>3</v>
@@ -2427,11 +2427,11 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>949</v>
+        <v>794</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2476,36 +2476,36 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J28" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K28" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L28" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="M28" t="n">
         <v>2</v>
       </c>
       <c r="N28" t="n">
+        <v>7</v>
+      </c>
+      <c r="O28" t="n">
         <v>6</v>
       </c>
-      <c r="O28" t="n">
-        <v>5</v>
-      </c>
       <c r="P28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>934</v>
+        <v>612</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2553,36 +2553,36 @@
         <v>49</v>
       </c>
       <c r="J29" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K29" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="L29" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N29" t="n">
         <v>7</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
         <v>9</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>680</v>
+        <v>563</v>
       </c>
       <c r="S29" t="n">
-        <v>0.06</v>
+        <v>0.2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2624,36 +2624,36 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J30" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K30" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L30" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>948</v>
+        <v>843</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2698,36 +2698,36 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J31" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K31" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L31" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P31" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>822</v>
+        <v>725</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2775,13 +2775,13 @@
         <v>62</v>
       </c>
       <c r="J32" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K32" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L32" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="M32" t="n">
         <v>2</v>
@@ -2790,21 +2790,21 @@
         <v>7</v>
       </c>
       <c r="O32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2846,39 +2846,39 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J33" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K33" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L33" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
         <v>13</v>
       </c>
       <c r="O33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P33" t="n">
         <v>17</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>671</v>
+        <v>768</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2920,36 +2920,36 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J34" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K34" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L34" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M34" t="n">
         <v>2</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>908</v>
+        <v>797</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2997,33 +2997,33 @@
         <v>59</v>
       </c>
       <c r="J35" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K35" t="n">
+        <v>15</v>
+      </c>
+      <c r="L35" t="n">
+        <v>51</v>
+      </c>
+      <c r="M35" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" t="n">
         <v>14</v>
       </c>
-      <c r="L35" t="n">
-        <v>50</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2</v>
-      </c>
-      <c r="N35" t="n">
-        <v>15</v>
-      </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P35" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>910</v>
+        <v>812</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3068,39 +3068,39 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J36" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K36" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L36" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M36" t="n">
+        <v>2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>11</v>
+      </c>
+      <c r="O36" t="n">
         <v>3</v>
       </c>
-      <c r="N36" t="n">
-        <v>7</v>
-      </c>
-      <c r="O36" t="n">
-        <v>5</v>
-      </c>
       <c r="P36" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>891</v>
+        <v>650</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3145,10 +3145,10 @@
         <v>57</v>
       </c>
       <c r="J37" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K37" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L37" t="n">
         <v>49</v>
@@ -3157,24 +3157,24 @@
         <v>2</v>
       </c>
       <c r="N37" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>782</v>
+        <v>812</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3216,36 +3216,36 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J38" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K38" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L38" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="M38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
+        <v>7</v>
+      </c>
+      <c r="O38" t="n">
         <v>6</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3</v>
       </c>
       <c r="P38" t="n">
         <v>14</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>934</v>
+        <v>872</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3290,28 +3290,28 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J39" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K39" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L39" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
         <v>8</v>
       </c>
       <c r="O39" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>981</v>
+        <v>684</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3364,36 +3364,36 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J40" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K40" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L40" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
         <v>7</v>
       </c>
       <c r="O40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P40" t="n">
         <v>15</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>914</v>
+        <v>591</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3438,36 +3438,36 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J41" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K41" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L41" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="M41" t="n">
         <v>1</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>797</v>
+        <v>881</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J42" t="n">
         <v>91</v>
@@ -3524,24 +3524,24 @@
         <v>80</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>743</v>
+        <v>780</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3586,39 +3586,39 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J43" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="K43" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L43" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="M43" t="n">
         <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O43" t="n">
         <v>5</v>
       </c>
       <c r="P43" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>948</v>
+        <v>796</v>
       </c>
       <c r="S43" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3660,36 +3660,36 @@
         </is>
       </c>
       <c r="I44" t="n">
+        <v>60</v>
+      </c>
+      <c r="J44" t="n">
+        <v>91</v>
+      </c>
+      <c r="K44" t="n">
+        <v>17</v>
+      </c>
+      <c r="L44" t="n">
         <v>58</v>
       </c>
-      <c r="J44" t="n">
-        <v>89</v>
-      </c>
-      <c r="K44" t="n">
-        <v>19</v>
-      </c>
-      <c r="L44" t="n">
-        <v>69</v>
-      </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P44" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>924</v>
+        <v>854</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3734,39 +3734,39 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J45" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K45" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L45" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="M45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N45" t="n">
         <v>18</v>
       </c>
       <c r="O45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P45" t="n">
         <v>25</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>903</v>
+        <v>840</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3808,22 +3808,22 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J46" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K46" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L46" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O46" t="n">
         <v>6</v>
@@ -3833,11 +3833,11 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R46" t="n">
-        <v>964</v>
+        <v>877</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3882,36 +3882,36 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J47" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K47" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L47" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>934</v>
+        <v>718</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3956,36 +3956,36 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J48" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K48" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L48" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P48" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>939</v>
+        <v>708</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4030,36 +4030,36 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J49" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K49" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L49" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="M49" t="n">
         <v>1</v>
       </c>
       <c r="N49" t="n">
+        <v>6</v>
+      </c>
+      <c r="O49" t="n">
         <v>5</v>
       </c>
-      <c r="O49" t="n">
-        <v>3</v>
-      </c>
       <c r="P49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R49" t="n">
-        <v>943</v>
+        <v>694</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4104,36 +4104,36 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J50" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L50" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="M50" t="n">
         <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
       </c>
       <c r="P50" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>942</v>
+        <v>807</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4178,36 +4178,36 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J51" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K51" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L51" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="M51" t="n">
         <v>2</v>
       </c>
       <c r="N51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P51" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R51" t="n">
-        <v>945</v>
+        <v>794</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J52" t="n">
         <v>95</v>
@@ -4261,27 +4261,27 @@
         <v>15</v>
       </c>
       <c r="L52" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P52" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>974</v>
+        <v>784</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4326,25 +4326,25 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J53" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K53" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L53" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P53" t="n">
         <v>17</v>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>956</v>
+        <v>860</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4400,36 +4400,36 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J54" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K54" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L54" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="M54" t="n">
         <v>2</v>
       </c>
       <c r="N54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P54" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R54" t="n">
-        <v>946</v>
+        <v>874</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4474,28 +4474,28 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J55" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K55" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L55" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P55" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>939</v>
+        <v>665</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4554,19 +4554,19 @@
         <v>83</v>
       </c>
       <c r="K56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L56" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="M56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N56" t="n">
         <v>7</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P56" t="n">
         <v>9</v>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>784</v>
+        <v>631</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4622,28 +4622,28 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J57" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K57" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L57" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="M57" t="n">
         <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O57" t="n">
         <v>5</v>
       </c>
       <c r="P57" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>843</v>
+        <v>727</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J58" t="n">
         <v>79</v>
@@ -4705,7 +4705,7 @@
         <v>25</v>
       </c>
       <c r="L58" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="M58" t="n">
         <v>2</v>
@@ -4714,21 +4714,21 @@
         <v>6</v>
       </c>
       <c r="O58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>715</v>
+        <v>531</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4770,28 +4770,28 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J59" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K59" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L59" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="M59" t="n">
         <v>1</v>
       </c>
       <c r="N59" t="n">
+        <v>7</v>
+      </c>
+      <c r="O59" t="n">
         <v>5</v>
       </c>
-      <c r="O59" t="n">
-        <v>3</v>
-      </c>
       <c r="P59" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>938</v>
+        <v>892</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4844,36 +4844,36 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J60" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L60" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M60" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N60" t="n">
+        <v>17</v>
+      </c>
+      <c r="O60" t="n">
         <v>15</v>
       </c>
-      <c r="O60" t="n">
-        <v>9</v>
-      </c>
       <c r="P60" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/3/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R60" t="n">
-        <v>960</v>
+        <v>861</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4921,22 +4921,22 @@
         <v>72</v>
       </c>
       <c r="J61" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L61" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N61" t="n">
         <v>10</v>
       </c>
       <c r="O61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P61" t="n">
         <v>15</v>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>982</v>
+        <v>903</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4992,28 +4992,28 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J62" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K62" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L62" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O62" t="n">
         <v>3</v>
       </c>
       <c r="P62" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>823</v>
+        <v>682</v>
       </c>
       <c r="S62" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5066,16 +5066,16 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J63" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K63" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L63" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M63" t="n">
         <v>1</v>
@@ -5087,15 +5087,15 @@
         <v>3</v>
       </c>
       <c r="P63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R63" t="n">
-        <v>928</v>
+        <v>871</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J64" t="n">
         <v>99</v>
@@ -5149,27 +5149,27 @@
         <v>13</v>
       </c>
       <c r="L64" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O64" t="n">
         <v>6</v>
       </c>
       <c r="P64" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R64" t="n">
-        <v>986</v>
+        <v>740</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5214,28 +5214,28 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J65" t="n">
         <v>86</v>
       </c>
       <c r="K65" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L65" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>5</v>
       </c>
       <c r="O65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>958</v>
+        <v>767</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5288,25 +5288,25 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J66" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K66" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L66" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N66" t="n">
         <v>6</v>
       </c>
       <c r="O66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P66" t="n">
         <v>15</v>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>870</v>
+        <v>745</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5362,28 +5362,28 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J67" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K67" t="n">
         <v>14</v>
       </c>
       <c r="L67" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M67" t="n">
         <v>3</v>
       </c>
       <c r="N67" t="n">
+        <v>9</v>
+      </c>
+      <c r="O67" t="n">
         <v>7</v>
       </c>
-      <c r="O67" t="n">
-        <v>6</v>
-      </c>
       <c r="P67" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>950</v>
+        <v>890</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5436,16 +5436,16 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J68" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K68" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L68" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="M68" t="n">
         <v>5</v>
@@ -5454,18 +5454,18 @@
         <v>10</v>
       </c>
       <c r="O68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P68" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>949</v>
+        <v>797</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5510,36 +5510,36 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J69" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K69" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L69" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="M69" t="n">
         <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>951</v>
+        <v>880</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5584,36 +5584,36 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J70" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K70" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L70" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="M70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N70" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O70" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P70" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R70" t="n">
-        <v>955</v>
+        <v>825</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5658,28 +5658,28 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J71" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K71" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L71" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N71" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O71" t="n">
         <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>936</v>
+        <v>892</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5732,28 +5732,28 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J72" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K72" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L72" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="M72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         </is>
       </c>
       <c r="R72" t="n">
-        <v>905</v>
+        <v>758</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5806,28 +5806,28 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J73" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K73" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L73" t="n">
         <v>64</v>
       </c>
       <c r="M73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N73" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O73" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>702</v>
+        <v>767</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5883,36 +5883,36 @@
         <v>56</v>
       </c>
       <c r="J74" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K74" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L74" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M74" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N74" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O74" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R74" t="n">
-        <v>843</v>
+        <v>764</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5954,36 +5954,36 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J75" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K75" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L75" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N75" t="n">
         <v>8</v>
       </c>
       <c r="O75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P75" t="n">
         <v>11</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R75" t="n">
-        <v>959</v>
+        <v>789</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J76" t="n">
         <v>85</v>
@@ -6037,27 +6037,27 @@
         <v>24</v>
       </c>
       <c r="L76" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="M76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O76" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P76" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R76" t="n">
-        <v>752</v>
+        <v>621</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6102,36 +6102,36 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J77" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L77" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="M77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P77" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>1/4/1 17:00 LMT</t>
+          <t>1/5/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R77" t="n">
-        <v>948</v>
+        <v>750</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6176,28 +6176,28 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J78" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K78" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L78" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="M78" t="n">
         <v>2</v>
       </c>
       <c r="N78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O78" t="n">
         <v>6</v>
       </c>
       <c r="P78" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="R78" t="n">
-        <v>900</v>
+        <v>830</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J79" t="n">
         <v>88</v>
@@ -6259,27 +6259,27 @@
         <v>18</v>
       </c>
       <c r="L79" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="M79" t="n">
+        <v>2</v>
+      </c>
+      <c r="N79" t="n">
+        <v>9</v>
+      </c>
+      <c r="O79" t="n">
         <v>3</v>
       </c>
-      <c r="N79" t="n">
-        <v>8</v>
-      </c>
-      <c r="O79" t="n">
-        <v>5</v>
-      </c>
       <c r="P79" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R79" t="n">
-        <v>932</v>
+        <v>769</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6324,36 +6324,36 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J80" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K80" t="n">
         <v>20</v>
       </c>
       <c r="L80" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R80" t="n">
-        <v>795</v>
+        <v>691</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6410,27 +6410,27 @@
         <v>67</v>
       </c>
       <c r="M81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P81" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R81" t="n">
-        <v>837</v>
+        <v>756</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6472,39 +6472,39 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J82" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K82" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L82" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="M82" t="n">
         <v>2</v>
       </c>
       <c r="N82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P82" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R82" t="n">
-        <v>789</v>
+        <v>731</v>
       </c>
       <c r="S82" t="n">
-        <v>0.01</v>
+        <v>0.17</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6546,36 +6546,36 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J83" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K83" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L83" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N83" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P83" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R83" t="n">
-        <v>962</v>
+        <v>750</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6620,39 +6620,39 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J84" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="K84" t="n">
+        <v>22</v>
+      </c>
+      <c r="L84" t="n">
+        <v>78</v>
+      </c>
+      <c r="M84" t="n">
+        <v>7</v>
+      </c>
+      <c r="N84" t="n">
         <v>14</v>
       </c>
-      <c r="L84" t="n">
-        <v>52</v>
-      </c>
-      <c r="M84" t="n">
-        <v>6</v>
-      </c>
-      <c r="N84" t="n">
-        <v>16</v>
-      </c>
       <c r="O84" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P84" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R84" t="n">
-        <v>955</v>
+        <v>786</v>
       </c>
       <c r="S84" t="n">
-        <v>0.02</v>
+        <v>0.17</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6697,36 +6697,36 @@
         <v>58</v>
       </c>
       <c r="J85" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K85" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L85" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M85" t="n">
         <v>2</v>
       </c>
       <c r="N85" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P85" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R85" t="n">
-        <v>763</v>
+        <v>727</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6768,39 +6768,39 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J86" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K86" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L86" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M86" t="n">
         <v>2</v>
       </c>
       <c r="N86" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O86" t="n">
         <v>3</v>
       </c>
       <c r="P86" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R86" t="n">
-        <v>690</v>
+        <v>650</v>
       </c>
       <c r="S86" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6842,39 +6842,39 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J87" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="K87" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="L87" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="M87" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N87" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O87" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P87" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R87" t="n">
-        <v>921</v>
+        <v>802</v>
       </c>
       <c r="S87" t="n">
-        <v>0.09</v>
+        <v>0.31</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J88" t="n">
         <v>90</v>
@@ -6925,27 +6925,27 @@
         <v>16</v>
       </c>
       <c r="L88" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M88" t="n">
         <v>2</v>
       </c>
       <c r="N88" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
       </c>
       <c r="P88" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R88" t="n">
-        <v>813</v>
+        <v>745</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6990,16 +6990,16 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J89" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K89" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L89" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="M89" t="n">
         <v>2</v>
@@ -7011,7 +7011,7 @@
         <v>5</v>
       </c>
       <c r="P89" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         </is>
       </c>
       <c r="R89" t="n">
-        <v>940</v>
+        <v>855</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7064,16 +7064,16 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J90" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K90" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L90" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -7085,15 +7085,15 @@
         <v>2</v>
       </c>
       <c r="P90" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R90" t="n">
-        <v>907</v>
+        <v>690</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7138,39 +7138,39 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J91" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K91" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="L91" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M91" t="n">
         <v>3</v>
       </c>
       <c r="N91" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O91" t="n">
         <v>6</v>
       </c>
       <c r="P91" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R91" t="n">
-        <v>924</v>
+        <v>797</v>
       </c>
       <c r="S91" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7212,39 +7212,39 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J92" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K92" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L92" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N92" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P92" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R92" t="n">
-        <v>914</v>
+        <v>791</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J93" t="n">
         <v>86</v>
@@ -7295,27 +7295,27 @@
         <v>20</v>
       </c>
       <c r="L93" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M93" t="n">
         <v>1</v>
       </c>
       <c r="N93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R93" t="n">
-        <v>703</v>
+        <v>472</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7360,36 +7360,36 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J94" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K94" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L94" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="M94" t="n">
         <v>3</v>
       </c>
       <c r="N94" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O94" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R94" t="n">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7434,16 +7434,16 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J95" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K95" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L95" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="M95" t="n">
         <v>2</v>
@@ -7452,18 +7452,18 @@
         <v>7</v>
       </c>
       <c r="O95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P95" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R95" t="n">
-        <v>964</v>
+        <v>845</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7508,28 +7508,28 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J96" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K96" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L96" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="M96" t="n">
         <v>3</v>
       </c>
       <c r="N96" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O96" t="n">
         <v>7</v>
       </c>
       <c r="P96" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="R96" t="n">
-        <v>931</v>
+        <v>856</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7582,36 +7582,36 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J97" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K97" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L97" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="M97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N97" t="n">
+        <v>7</v>
+      </c>
+      <c r="O97" t="n">
         <v>6</v>
       </c>
-      <c r="O97" t="n">
-        <v>5</v>
-      </c>
       <c r="P97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R97" t="n">
-        <v>936</v>
+        <v>770</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7656,28 +7656,28 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J98" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K98" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L98" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="M98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N98" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P98" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="R98" t="n">
-        <v>919</v>
+        <v>884</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7730,28 +7730,28 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J99" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K99" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L99" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M99" t="n">
         <v>1</v>
       </c>
       <c r="N99" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O99" t="n">
         <v>2</v>
       </c>
       <c r="P99" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="R99" t="n">
-        <v>917</v>
+        <v>901</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7804,28 +7804,28 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J100" t="n">
         <v>102</v>
       </c>
       <c r="K100" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L100" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="M100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N100" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O100" t="n">
         <v>7</v>
       </c>
       <c r="P100" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="R100" t="n">
-        <v>957</v>
+        <v>787</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7878,25 +7878,25 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J101" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K101" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L101" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N101" t="n">
         <v>6</v>
       </c>
       <c r="O101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P101" t="n">
         <v>15</v>
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="R101" t="n">
-        <v>935</v>
+        <v>799</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7952,16 +7952,16 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J102" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K102" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L102" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="M102" t="n">
         <v>2</v>
@@ -7977,14 +7977,14 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R102" t="n">
-        <v>861</v>
+        <v>802</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8026,36 +8026,36 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J103" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K103" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L103" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="M103" t="n">
         <v>2</v>
       </c>
       <c r="N103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O103" t="n">
         <v>5</v>
       </c>
       <c r="P103" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R103" t="n">
-        <v>940</v>
+        <v>858</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8100,36 +8100,36 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J104" t="n">
         <v>105</v>
       </c>
       <c r="K104" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L104" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M104" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N104" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O104" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P104" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>1/5/1 17:00 LMT</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R104" t="n">
-        <v>912</v>
+        <v>891</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8174,22 +8174,22 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J105" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K105" t="n">
+        <v>19</v>
+      </c>
+      <c r="L105" t="n">
+        <v>52</v>
+      </c>
+      <c r="M105" t="n">
+        <v>6</v>
+      </c>
+      <c r="N105" t="n">
         <v>15</v>
-      </c>
-      <c r="L105" t="n">
-        <v>41</v>
-      </c>
-      <c r="M105" t="n">
-        <v>7</v>
-      </c>
-      <c r="N105" t="n">
-        <v>14</v>
       </c>
       <c r="O105" t="n">
         <v>9</v>
@@ -8199,11 +8199,11 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R105" t="n">
-        <v>782</v>
+        <v>810</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8248,28 +8248,28 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J106" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K106" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L106" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M106" t="n">
         <v>2</v>
       </c>
       <c r="N106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O106" t="n">
         <v>5</v>
       </c>
       <c r="P106" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="R106" t="n">
-        <v>946</v>
+        <v>837</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8322,36 +8322,36 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J107" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K107" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L107" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="M107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N107" t="n">
         <v>7</v>
       </c>
       <c r="O107" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P107" t="n">
         <v>14</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R107" t="n">
-        <v>955</v>
+        <v>715</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8396,39 +8396,39 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J108" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K108" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L108" t="n">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="M108" t="n">
         <v>2</v>
       </c>
       <c r="N108" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O108" t="n">
         <v>3</v>
       </c>
       <c r="P108" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R108" t="n">
-        <v>827</v>
+        <v>796</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8470,16 +8470,16 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J109" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K109" t="n">
         <v>17</v>
       </c>
       <c r="L109" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M109" t="n">
         <v>2</v>
@@ -8495,11 +8495,11 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R109" t="n">
-        <v>872</v>
+        <v>566</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8544,36 +8544,36 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J110" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K110" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L110" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="M110" t="n">
         <v>1</v>
       </c>
       <c r="N110" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O110" t="n">
         <v>3</v>
       </c>
       <c r="P110" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R110" t="n">
-        <v>945</v>
+        <v>829</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8618,36 +8618,36 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J111" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K111" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L111" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="M111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O111" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P111" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R111" t="n">
-        <v>942</v>
+        <v>723</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8692,25 +8692,25 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J112" t="n">
         <v>89</v>
       </c>
       <c r="K112" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L112" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="M112" t="n">
         <v>2</v>
       </c>
       <c r="N112" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O112" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P112" t="n">
         <v>14</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="R112" t="n">
-        <v>951</v>
+        <v>715</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8766,16 +8766,16 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J113" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K113" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L113" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="M113" t="n">
         <v>2</v>
@@ -8787,7 +8787,7 @@
         <v>6</v>
       </c>
       <c r="P113" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="R113" t="n">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8840,16 +8840,16 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J114" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K114" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L114" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="M114" t="n">
         <v>2</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="R114" t="n">
-        <v>963</v>
+        <v>656</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8914,19 +8914,19 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J115" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K115" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L115" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="M115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N115" t="n">
         <v>3</v>
@@ -8935,15 +8935,15 @@
         <v>7</v>
       </c>
       <c r="P115" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R115" t="n">
-        <v>829</v>
+        <v>632</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8988,28 +8988,28 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J116" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K116" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L116" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="M116" t="n">
         <v>3</v>
       </c>
       <c r="N116" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O116" t="n">
         <v>8</v>
       </c>
       <c r="P116" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         </is>
       </c>
       <c r="R116" t="n">
-        <v>841</v>
+        <v>697</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9062,36 +9062,36 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J117" t="n">
         <v>87</v>
       </c>
       <c r="K117" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L117" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M117" t="n">
         <v>3</v>
       </c>
       <c r="N117" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O117" t="n">
         <v>5</v>
       </c>
       <c r="P117" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R117" t="n">
-        <v>828</v>
+        <v>700</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9136,39 +9136,39 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J118" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K118" t="n">
+        <v>20</v>
+      </c>
+      <c r="L118" t="n">
+        <v>67</v>
+      </c>
+      <c r="M118" t="n">
+        <v>3</v>
+      </c>
+      <c r="N118" t="n">
+        <v>11</v>
+      </c>
+      <c r="O118" t="n">
+        <v>5</v>
+      </c>
+      <c r="P118" t="n">
         <v>16</v>
       </c>
-      <c r="L118" t="n">
-        <v>42</v>
-      </c>
-      <c r="M118" t="n">
-        <v>2</v>
-      </c>
-      <c r="N118" t="n">
-        <v>8</v>
-      </c>
-      <c r="O118" t="n">
-        <v>3</v>
-      </c>
-      <c r="P118" t="n">
-        <v>11</v>
-      </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R118" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9210,36 +9210,36 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J119" t="n">
         <v>90</v>
       </c>
       <c r="K119" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L119" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N119" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O119" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P119" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>1/4/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R119" t="n">
-        <v>941</v>
+        <v>706</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9284,7 +9284,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J120" t="n">
         <v>94</v>
@@ -9293,27 +9293,27 @@
         <v>13</v>
       </c>
       <c r="L120" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="M120" t="n">
+        <v>2</v>
+      </c>
+      <c r="N120" t="n">
+        <v>10</v>
+      </c>
+      <c r="O120" t="n">
         <v>3</v>
       </c>
-      <c r="N120" t="n">
-        <v>9</v>
-      </c>
-      <c r="O120" t="n">
-        <v>5</v>
-      </c>
       <c r="P120" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R120" t="n">
-        <v>957</v>
+        <v>812</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9358,36 +9358,36 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J121" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K121" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L121" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="M121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O121" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P121" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R121" t="n">
-        <v>951</v>
+        <v>793</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9435,13 +9435,13 @@
         <v>65</v>
       </c>
       <c r="J122" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K122" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L122" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="M122" t="n">
         <v>1</v>
@@ -9457,11 +9457,11 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R122" t="n">
-        <v>983</v>
+        <v>777</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9506,28 +9506,28 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J123" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K123" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L123" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="M123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N123" t="n">
+        <v>5</v>
+      </c>
+      <c r="O123" t="n">
         <v>6</v>
       </c>
-      <c r="O123" t="n">
-        <v>5</v>
-      </c>
       <c r="P123" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="R123" t="n">
-        <v>952</v>
+        <v>877</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9580,36 +9580,36 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J124" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K124" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L124" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N124" t="n">
         <v>6</v>
       </c>
       <c r="O124" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P124" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R124" t="n">
-        <v>977</v>
+        <v>856</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9654,25 +9654,25 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J125" t="n">
         <v>109</v>
       </c>
       <c r="K125" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L125" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N125" t="n">
+        <v>9</v>
+      </c>
+      <c r="O125" t="n">
         <v>8</v>
-      </c>
-      <c r="O125" t="n">
-        <v>5</v>
       </c>
       <c r="P125" t="n">
         <v>16</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="R125" t="n">
-        <v>952</v>
+        <v>866</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9728,39 +9728,39 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J126" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K126" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L126" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="M126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N126" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P126" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R126" t="n">
-        <v>814</v>
+        <v>794</v>
       </c>
       <c r="S126" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9805,33 +9805,33 @@
         <v>66</v>
       </c>
       <c r="J127" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K127" t="n">
+        <v>18</v>
+      </c>
+      <c r="L127" t="n">
+        <v>63</v>
+      </c>
+      <c r="M127" t="n">
+        <v>3</v>
+      </c>
+      <c r="N127" t="n">
         <v>15</v>
       </c>
-      <c r="L127" t="n">
-        <v>55</v>
-      </c>
-      <c r="M127" t="n">
-        <v>1</v>
-      </c>
-      <c r="N127" t="n">
-        <v>10</v>
-      </c>
       <c r="O127" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P127" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R127" t="n">
-        <v>949</v>
+        <v>832</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9876,39 +9876,39 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J128" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K128" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L128" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="M128" t="n">
         <v>2</v>
       </c>
       <c r="N128" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O128" t="n">
         <v>3</v>
       </c>
       <c r="P128" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R128" t="n">
-        <v>860</v>
+        <v>750</v>
       </c>
       <c r="S128" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9950,28 +9950,28 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J129" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K129" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L129" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="M129" t="n">
         <v>3</v>
       </c>
       <c r="N129" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O129" t="n">
         <v>7</v>
       </c>
       <c r="P129" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="R129" t="n">
-        <v>944</v>
+        <v>864</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10024,16 +10024,16 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J130" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K130" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L130" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="M130" t="n">
         <v>2</v>
@@ -10042,18 +10042,18 @@
         <v>10</v>
       </c>
       <c r="O130" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P130" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R130" t="n">
-        <v>951</v>
+        <v>805</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -10098,36 +10098,36 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J131" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K131" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L131" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="M131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N131" t="n">
         <v>7</v>
       </c>
       <c r="O131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P131" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R131" t="n">
-        <v>947</v>
+        <v>855</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -10172,36 +10172,36 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J132" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K132" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L132" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="M132" t="n">
         <v>3</v>
       </c>
       <c r="N132" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O132" t="n">
         <v>5</v>
       </c>
       <c r="P132" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R132" t="n">
-        <v>960</v>
+        <v>816</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10246,36 +10246,36 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J133" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K133" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L133" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="M133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N133" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O133" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P133" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R133" t="n">
-        <v>893</v>
+        <v>741</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10320,36 +10320,36 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J134" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K134" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L134" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="M134" t="n">
         <v>2</v>
       </c>
       <c r="N134" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O134" t="n">
         <v>3</v>
       </c>
       <c r="P134" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R134" t="n">
-        <v>846</v>
+        <v>665</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10394,36 +10394,36 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J135" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K135" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L135" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="M135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N135" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O135" t="n">
         <v>7</v>
       </c>
       <c r="P135" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R135" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10471,36 +10471,36 @@
         <v>56</v>
       </c>
       <c r="J136" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K136" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L136" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="M136" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N136" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O136" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P136" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R136" t="n">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="S136" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10542,36 +10542,36 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J137" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K137" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L137" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N137" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O137" t="n">
         <v>5</v>
       </c>
       <c r="P137" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R137" t="n">
-        <v>926</v>
+        <v>863</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10616,28 +10616,28 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J138" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K138" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L138" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M138" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N138" t="n">
         <v>11</v>
       </c>
       <c r="O138" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P138" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="R138" t="n">
-        <v>955</v>
+        <v>817</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10693,36 +10693,36 @@
         <v>54</v>
       </c>
       <c r="J139" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K139" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L139" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N139" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O139" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P139" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R139" t="n">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="S139" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J140" t="n">
         <v>82</v>
@@ -10773,27 +10773,27 @@
         <v>19</v>
       </c>
       <c r="L140" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M140" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N140" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O140" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P140" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>1/3/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R140" t="n">
-        <v>950</v>
+        <v>695</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10838,25 +10838,25 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J141" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K141" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L141" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="M141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N141" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O141" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P141" t="n">
         <v>19</v>
@@ -10867,7 +10867,7 @@
         </is>
       </c>
       <c r="R141" t="n">
-        <v>953</v>
+        <v>801</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J142" t="n">
         <v>93</v>
@@ -10921,27 +10921,27 @@
         <v>18</v>
       </c>
       <c r="L142" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M142" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N142" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O142" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P142" t="n">
         <v>22</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>1/5/1 17:00 LMT</t>
+          <t>1/3/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R142" t="n">
-        <v>916</v>
+        <v>747</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10986,39 +10986,39 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J143" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K143" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L143" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="M143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N143" t="n">
         <v>13</v>
       </c>
       <c r="O143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P143" t="n">
         <v>17</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R143" t="n">
-        <v>939</v>
+        <v>796</v>
       </c>
       <c r="S143" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11060,36 +11060,36 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J144" t="n">
         <v>84</v>
       </c>
       <c r="K144" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L144" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="M144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N144" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P144" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R144" t="n">
-        <v>854</v>
+        <v>731</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -11134,36 +11134,36 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J145" t="n">
         <v>109</v>
       </c>
       <c r="K145" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L145" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N145" t="n">
         <v>10</v>
       </c>
       <c r="O145" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P145" t="n">
         <v>21</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R145" t="n">
-        <v>953</v>
+        <v>838</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11208,36 +11208,36 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J146" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="K146" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L146" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M146" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N146" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O146" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P146" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R146" t="n">
-        <v>913</v>
+        <v>796</v>
       </c>
       <c r="S146" t="n">
         <v>0.03</v>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11282,36 +11282,36 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J147" t="n">
         <v>94</v>
       </c>
       <c r="K147" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L147" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M147" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N147" t="n">
+        <v>9</v>
+      </c>
+      <c r="O147" t="n">
         <v>10</v>
-      </c>
-      <c r="O147" t="n">
-        <v>9</v>
       </c>
       <c r="P147" t="n">
         <v>18</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>1/6/1 17:00 LMT</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R147" t="n">
-        <v>909</v>
+        <v>768</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11356,39 +11356,39 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J148" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K148" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L148" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N148" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O148" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P148" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R148" t="n">
-        <v>870</v>
+        <v>770</v>
       </c>
       <c r="S148" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11430,36 +11430,36 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J149" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K149" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L149" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="M149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N149" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O149" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P149" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R149" t="n">
-        <v>940</v>
+        <v>893</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11504,16 +11504,16 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J150" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K150" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L150" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -11522,18 +11522,18 @@
         <v>2</v>
       </c>
       <c r="O150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P150" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R150" t="n">
-        <v>944</v>
+        <v>861</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11578,36 +11578,36 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J151" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K151" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L151" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M151" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N151" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O151" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P151" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R151" t="n">
-        <v>915</v>
+        <v>893</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11652,36 +11652,36 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J152" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K152" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L152" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="M152" t="n">
         <v>1</v>
       </c>
       <c r="N152" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O152" t="n">
         <v>3</v>
       </c>
       <c r="P152" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R152" t="n">
-        <v>931</v>
+        <v>889</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -11717,7 +11717,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11726,16 +11726,16 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J153" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K153" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L153" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M153" t="n">
         <v>2</v>
@@ -11747,15 +11747,15 @@
         <v>6</v>
       </c>
       <c r="P153" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R153" t="n">
-        <v>950</v>
+        <v>855</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11800,36 +11800,36 @@
         </is>
       </c>
       <c r="I154" t="n">
+        <v>57</v>
+      </c>
+      <c r="J154" t="n">
+        <v>82</v>
+      </c>
+      <c r="K154" t="n">
+        <v>22</v>
+      </c>
+      <c r="L154" t="n">
         <v>55</v>
       </c>
-      <c r="J154" t="n">
-        <v>81</v>
-      </c>
-      <c r="K154" t="n">
-        <v>27</v>
-      </c>
-      <c r="L154" t="n">
-        <v>60</v>
-      </c>
       <c r="M154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N154" t="n">
+        <v>6</v>
+      </c>
+      <c r="O154" t="n">
         <v>5</v>
       </c>
-      <c r="O154" t="n">
-        <v>3</v>
-      </c>
       <c r="P154" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R154" t="n">
-        <v>837</v>
+        <v>612</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -11865,7 +11865,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11874,36 +11874,36 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J155" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K155" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L155" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="M155" t="n">
         <v>2</v>
       </c>
       <c r="N155" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O155" t="n">
         <v>3</v>
       </c>
       <c r="P155" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R155" t="n">
-        <v>743</v>
+        <v>624</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11948,39 +11948,39 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J156" t="n">
+        <v>84</v>
+      </c>
+      <c r="K156" t="n">
+        <v>24</v>
+      </c>
+      <c r="L156" t="n">
         <v>86</v>
       </c>
-      <c r="K156" t="n">
-        <v>19</v>
-      </c>
-      <c r="L156" t="n">
-        <v>77</v>
-      </c>
       <c r="M156" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N156" t="n">
         <v>11</v>
       </c>
       <c r="O156" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P156" t="n">
         <v>16</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R156" t="n">
-        <v>816</v>
+        <v>802</v>
       </c>
       <c r="S156" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12022,28 +12022,28 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J157" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K157" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L157" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="M157" t="n">
         <v>1</v>
       </c>
       <c r="N157" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O157" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P157" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         </is>
       </c>
       <c r="R157" t="n">
-        <v>922</v>
+        <v>896</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>8/24/2026</t>
+          <t>8/25/2026</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12096,7 +12096,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J158" t="n">
         <v>93</v>
@@ -12105,27 +12105,27 @@
         <v>15</v>
       </c>
       <c r="L158" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="M158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N158" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O158" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P158" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R158" t="n">
-        <v>933</v>
+        <v>773</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>

--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -555,25 +555,25 @@
         <v>53</v>
       </c>
       <c r="J2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -581,10 +581,10 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>788</v>
+        <v>832</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -626,16 +626,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K3" t="n">
         <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -647,15 +647,15 @@
         <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>800</v>
+        <v>935</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J4" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K4" t="n">
         <v>15</v>
@@ -712,24 +712,24 @@
         <v>55</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>822</v>
+        <v>886</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -777,22 +777,22 @@
         <v>58</v>
       </c>
       <c r="J5" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
+        <v>8</v>
+      </c>
+      <c r="O5" t="n">
         <v>5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>7</v>
       </c>
       <c r="P5" t="n">
         <v>13</v>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>698</v>
+        <v>750</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -851,19 +851,19 @@
         <v>87</v>
       </c>
       <c r="J6" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K6" t="n">
         <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>5</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>866</v>
+        <v>881</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -922,39 +922,39 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J7" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K7" t="n">
         <v>38</v>
       </c>
       <c r="L7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
+        <v>7</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
         <v>9</v>
       </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>13</v>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>713</v>
+        <v>742</v>
       </c>
       <c r="S7" t="n">
-        <v>0.41</v>
+        <v>0.17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
         <v>98</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M8" t="n">
         <v>5</v>
@@ -1017,15 +1017,15 @@
         <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>822</v>
+        <v>865</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1073,33 +1073,33 @@
         <v>56</v>
       </c>
       <c r="J9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K9" t="n">
         <v>16</v>
       </c>
       <c r="L9" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>768</v>
+        <v>800</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1144,16 +1144,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J10" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K10" t="n">
         <v>11</v>
       </c>
       <c r="L10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M10" t="n">
         <v>3</v>
@@ -1162,7 +1162,7 @@
         <v>10</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
         <v>21</v>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>853</v>
+        <v>915</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1221,33 +1221,33 @@
         <v>80</v>
       </c>
       <c r="J11" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
         <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>883</v>
+        <v>946</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1295,36 +1295,36 @@
         <v>60</v>
       </c>
       <c r="J12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L12" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="N12" t="n">
-        <v>13</v>
-      </c>
-      <c r="O12" t="n">
-        <v>5</v>
-      </c>
       <c r="P12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>796</v>
+        <v>874</v>
       </c>
       <c r="S12" t="n">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1366,16 +1366,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K13" t="n">
         <v>19</v>
       </c>
       <c r="L13" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -1387,15 +1387,15 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>893</v>
+        <v>926</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1440,36 +1440,36 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J14" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L14" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>660</v>
+        <v>763</v>
       </c>
       <c r="S14" t="n">
         <v>0.01</v>
@@ -1514,28 +1514,28 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J15" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L15" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M15" t="n">
         <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O15" t="n">
         <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>860</v>
+        <v>897</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1588,36 +1588,36 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J16" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
         <v>15</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>865</v>
+        <v>944</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1662,36 +1662,36 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J17" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K17" t="n">
         <v>21</v>
       </c>
       <c r="L17" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>689</v>
+        <v>739</v>
       </c>
       <c r="S17" t="n">
         <v>0.01</v>
@@ -1736,36 +1736,36 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J18" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L18" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>854</v>
+        <v>868</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1810,36 +1810,36 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J19" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K19" t="n">
         <v>13</v>
       </c>
       <c r="L19" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P19" t="n">
         <v>21</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1/4/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>654</v>
+        <v>917</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -1884,16 +1884,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J20" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L20" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
@@ -1905,7 +1905,7 @@
         <v>7</v>
       </c>
       <c r="P20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>916</v>
+        <v>975</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J21" t="n">
         <v>98</v>
@@ -1967,16 +1967,16 @@
         <v>17</v>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
         <v>18</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P21" t="n">
         <v>24</v>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>701</v>
+        <v>842</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2035,33 +2035,33 @@
         <v>71</v>
       </c>
       <c r="J22" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L22" t="n">
         <v>47</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P22" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>908</v>
+        <v>979</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2109,33 +2109,33 @@
         <v>83</v>
       </c>
       <c r="J23" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K23" t="n">
         <v>13</v>
       </c>
       <c r="L23" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
         <v>14</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>870</v>
+        <v>921</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2189,27 +2189,27 @@
         <v>11</v>
       </c>
       <c r="L24" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1/2/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>864</v>
+        <v>923</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2254,36 +2254,36 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J25" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L25" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>779</v>
+        <v>958</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J26" t="n">
         <v>96</v>
@@ -2337,27 +2337,27 @@
         <v>18</v>
       </c>
       <c r="L26" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>7</v>
+      </c>
+      <c r="O26" t="n">
         <v>3</v>
       </c>
-      <c r="N26" t="n">
-        <v>5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>8</v>
-      </c>
       <c r="P26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>849</v>
+        <v>938</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J27" t="n">
         <v>96</v>
@@ -2411,27 +2411,27 @@
         <v>14</v>
       </c>
       <c r="L27" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M27" t="n">
         <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O27" t="n">
         <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2476,28 +2476,28 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J28" t="n">
         <v>118</v>
       </c>
       <c r="K28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L28" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
+        <v>8</v>
+      </c>
+      <c r="O28" t="n">
         <v>7</v>
       </c>
-      <c r="O28" t="n">
-        <v>6</v>
-      </c>
       <c r="P28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>612</v>
+        <v>840</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2550,39 +2550,39 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J29" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K29" t="n">
         <v>37</v>
       </c>
       <c r="L29" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>563</v>
+        <v>743</v>
       </c>
       <c r="S29" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2624,16 +2624,16 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J30" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L30" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
@@ -2642,18 +2642,18 @@
         <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P30" t="n">
         <v>15</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2698,16 +2698,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J31" t="n">
         <v>79</v>
       </c>
       <c r="K31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L31" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -2716,18 +2716,18 @@
         <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P31" t="n">
         <v>11</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>725</v>
+        <v>908</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -2775,36 +2775,36 @@
         <v>62</v>
       </c>
       <c r="J32" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L32" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M32" t="n">
         <v>2</v>
       </c>
       <c r="N32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
         <v>6</v>
       </c>
       <c r="P32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>721</v>
+        <v>750</v>
       </c>
       <c r="S32" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -2846,39 +2846,39 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J33" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>768</v>
+        <v>673</v>
       </c>
       <c r="S33" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2920,25 +2920,25 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J34" t="n">
         <v>93</v>
       </c>
       <c r="K34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L34" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M34" t="n">
         <v>2</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O34" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P34" t="n">
         <v>15</v>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -2994,36 +2994,36 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J35" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K35" t="n">
         <v>15</v>
       </c>
       <c r="L35" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" t="n">
+        <v>13</v>
+      </c>
+      <c r="O35" t="n">
         <v>5</v>
       </c>
-      <c r="N35" t="n">
-        <v>14</v>
-      </c>
-      <c r="O35" t="n">
-        <v>7</v>
-      </c>
       <c r="P35" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>812</v>
+        <v>920</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3074,33 +3074,33 @@
         <v>82</v>
       </c>
       <c r="K36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L36" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
+        <v>8</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
         <v>11</v>
       </c>
-      <c r="O36" t="n">
-        <v>3</v>
-      </c>
-      <c r="P36" t="n">
-        <v>16</v>
-      </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>650</v>
+        <v>696</v>
       </c>
       <c r="S36" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3145,36 +3145,36 @@
         <v>57</v>
       </c>
       <c r="J37" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L37" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
         <v>9</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P37" t="n">
         <v>13</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="S37" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3216,25 +3216,25 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J38" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K38" t="n">
         <v>14</v>
       </c>
       <c r="L38" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M38" t="n">
         <v>3</v>
       </c>
       <c r="N38" t="n">
+        <v>6</v>
+      </c>
+      <c r="O38" t="n">
         <v>7</v>
-      </c>
-      <c r="O38" t="n">
-        <v>6</v>
       </c>
       <c r="P38" t="n">
         <v>14</v>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>872</v>
+        <v>907</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3290,25 +3290,25 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J39" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K39" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
         <v>8</v>
       </c>
       <c r="O39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P39" t="n">
         <v>21</v>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>684</v>
+        <v>905</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3370,10 +3370,10 @@
         <v>93</v>
       </c>
       <c r="K40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L40" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M40" t="n">
         <v>5</v>
@@ -3389,11 +3389,11 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/8/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>591</v>
+        <v>922</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3438,36 +3438,36 @@
         </is>
       </c>
       <c r="I41" t="n">
+        <v>54</v>
+      </c>
+      <c r="J41" t="n">
+        <v>81</v>
+      </c>
+      <c r="K41" t="n">
+        <v>22</v>
+      </c>
+      <c r="L41" t="n">
         <v>55</v>
       </c>
-      <c r="J41" t="n">
-        <v>80</v>
-      </c>
-      <c r="K41" t="n">
-        <v>24</v>
-      </c>
-      <c r="L41" t="n">
-        <v>57</v>
-      </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -3512,39 +3512,39 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J42" t="n">
         <v>91</v>
       </c>
       <c r="K42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L42" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M42" t="n">
         <v>2</v>
       </c>
       <c r="N42" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>780</v>
+        <v>880</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -3586,39 +3586,39 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J43" t="n">
         <v>93</v>
       </c>
       <c r="K43" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L43" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N43" t="n">
         <v>10</v>
       </c>
       <c r="O43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P43" t="n">
         <v>15</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>796</v>
+        <v>869</v>
       </c>
       <c r="S43" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3660,28 +3660,28 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L44" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="M44" t="n">
         <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P44" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>854</v>
+        <v>905</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -3734,39 +3734,39 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J45" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K45" t="n">
         <v>17</v>
       </c>
       <c r="L45" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O45" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P45" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>840</v>
+        <v>939</v>
       </c>
       <c r="S45" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -3808,22 +3808,22 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J46" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K46" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L46" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
         <v>6</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>877</v>
+        <v>972</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -3882,36 +3882,36 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J47" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K47" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L47" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>718</v>
+        <v>858</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -3959,13 +3959,13 @@
         <v>88</v>
       </c>
       <c r="J48" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K48" t="n">
         <v>14</v>
       </c>
       <c r="L48" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M48" t="n">
         <v>3</v>
@@ -3977,15 +3977,15 @@
         <v>6</v>
       </c>
       <c r="P48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>708</v>
+        <v>725</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -4036,30 +4036,30 @@
         <v>87</v>
       </c>
       <c r="K49" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L49" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M49" t="n">
         <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P49" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R49" t="n">
-        <v>694</v>
+        <v>824</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4113,27 +4113,27 @@
         <v>19</v>
       </c>
       <c r="L50" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M50" t="n">
         <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
       </c>
       <c r="P50" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>807</v>
+        <v>940</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -4181,13 +4181,13 @@
         <v>89</v>
       </c>
       <c r="J51" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K51" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L51" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M51" t="n">
         <v>2</v>
@@ -4203,11 +4203,11 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R51" t="n">
-        <v>794</v>
+        <v>764</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -4252,36 +4252,36 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J52" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K52" t="n">
         <v>15</v>
       </c>
       <c r="L52" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P52" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>784</v>
+        <v>847</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -4329,13 +4329,13 @@
         <v>80</v>
       </c>
       <c r="J53" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K53" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L53" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M53" t="n">
         <v>5</v>
@@ -4344,18 +4344,18 @@
         <v>7</v>
       </c>
       <c r="O53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P53" t="n">
         <v>17</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R53" t="n">
-        <v>860</v>
+        <v>948</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -4409,7 +4409,7 @@
         <v>11</v>
       </c>
       <c r="L54" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M54" t="n">
         <v>2</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>874</v>
+        <v>930</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -4486,24 +4486,24 @@
         <v>40</v>
       </c>
       <c r="M55" t="n">
+        <v>3</v>
+      </c>
+      <c r="N55" t="n">
+        <v>14</v>
+      </c>
+      <c r="O55" t="n">
         <v>6</v>
       </c>
-      <c r="N55" t="n">
-        <v>11</v>
-      </c>
-      <c r="O55" t="n">
-        <v>8</v>
-      </c>
       <c r="P55" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>665</v>
+        <v>853</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -4548,39 +4548,39 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J56" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K56" t="n">
         <v>21</v>
       </c>
       <c r="L56" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N56" t="n">
         <v>7</v>
       </c>
       <c r="O56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P56" t="n">
         <v>9</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>631</v>
+        <v>909</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -4622,28 +4622,28 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J57" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K57" t="n">
         <v>20</v>
       </c>
       <c r="L57" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P57" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>727</v>
+        <v>815</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -4696,28 +4696,28 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J58" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K58" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L58" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M58" t="n">
         <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P58" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>531</v>
+        <v>669</v>
       </c>
       <c r="S58" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -4770,36 +4770,36 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J59" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K59" t="n">
         <v>13</v>
       </c>
       <c r="L59" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M59" t="n">
         <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P59" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R59" t="n">
-        <v>892</v>
+        <v>940</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -4847,33 +4847,33 @@
         <v>74</v>
       </c>
       <c r="J60" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K60" t="n">
         <v>12</v>
       </c>
       <c r="L60" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="M60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N60" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O60" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P60" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>1/2/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R60" t="n">
-        <v>861</v>
+        <v>958</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -4921,10 +4921,10 @@
         <v>72</v>
       </c>
       <c r="J61" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L61" t="n">
         <v>30</v>
@@ -4933,13 +4933,13 @@
         <v>2</v>
       </c>
       <c r="N61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O61" t="n">
         <v>3</v>
       </c>
       <c r="P61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>903</v>
+        <v>986</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J62" t="n">
         <v>87</v>
@@ -5004,24 +5004,24 @@
         <v>64</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
         <v>6</v>
       </c>
       <c r="O62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P62" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R62" t="n">
-        <v>682</v>
+        <v>707</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -5066,16 +5066,16 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J63" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L63" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M63" t="n">
         <v>1</v>
@@ -5087,15 +5087,15 @@
         <v>3</v>
       </c>
       <c r="P63" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R63" t="n">
-        <v>871</v>
+        <v>935</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -5143,13 +5143,13 @@
         <v>71</v>
       </c>
       <c r="J64" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K64" t="n">
         <v>13</v>
       </c>
       <c r="L64" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
@@ -5158,10 +5158,10 @@
         <v>6</v>
       </c>
       <c r="O64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>740</v>
+        <v>932</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -5214,28 +5214,28 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J65" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K65" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L65" t="n">
         <v>52</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N65" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P65" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>767</v>
+        <v>865</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -5288,28 +5288,28 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J66" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K66" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L66" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N66" t="n">
         <v>6</v>
       </c>
       <c r="O66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>745</v>
+        <v>960</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5368,30 +5368,30 @@
         <v>96</v>
       </c>
       <c r="K67" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L67" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O67" t="n">
         <v>7</v>
       </c>
       <c r="P67" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R67" t="n">
-        <v>890</v>
+        <v>953</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -5439,19 +5439,19 @@
         <v>69</v>
       </c>
       <c r="J68" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K68" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L68" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O68" t="n">
         <v>9</v>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>797</v>
+        <v>961</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -5513,36 +5513,36 @@
         <v>78</v>
       </c>
       <c r="J69" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K69" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L69" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M69" t="n">
         <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>880</v>
+        <v>926</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -5584,36 +5584,36 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J70" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K70" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L70" t="n">
         <v>32</v>
       </c>
       <c r="M70" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O70" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P70" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R70" t="n">
-        <v>825</v>
+        <v>932</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -5661,25 +5661,25 @@
         <v>67</v>
       </c>
       <c r="J71" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K71" t="n">
         <v>15</v>
       </c>
       <c r="L71" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N71" t="n">
         <v>8</v>
       </c>
       <c r="O71" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P71" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>892</v>
+        <v>929</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -5732,36 +5732,36 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J72" t="n">
         <v>93</v>
       </c>
       <c r="K72" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L72" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N72" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>758</v>
+        <v>791</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -5806,39 +5806,39 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J73" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K73" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L73" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N73" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O73" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P73" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R73" t="n">
-        <v>767</v>
+        <v>743</v>
       </c>
       <c r="S73" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5880,39 +5880,39 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J74" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K74" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L74" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M74" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O74" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R74" t="n">
-        <v>764</v>
+        <v>801</v>
       </c>
       <c r="S74" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -5960,30 +5960,30 @@
         <v>93</v>
       </c>
       <c r="K75" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L75" t="n">
         <v>47</v>
       </c>
       <c r="M75" t="n">
+        <v>3</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9</v>
+      </c>
+      <c r="O75" t="n">
         <v>5</v>
       </c>
-      <c r="N75" t="n">
-        <v>8</v>
-      </c>
-      <c r="O75" t="n">
-        <v>7</v>
-      </c>
       <c r="P75" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R75" t="n">
-        <v>789</v>
+        <v>931</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -6028,36 +6028,36 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J76" t="n">
         <v>85</v>
       </c>
       <c r="K76" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L76" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M76" t="n">
         <v>3</v>
       </c>
       <c r="N76" t="n">
+        <v>8</v>
+      </c>
+      <c r="O76" t="n">
         <v>6</v>
-      </c>
-      <c r="O76" t="n">
-        <v>8</v>
       </c>
       <c r="P76" t="n">
         <v>13</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R76" t="n">
-        <v>621</v>
+        <v>816</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -6105,33 +6105,33 @@
         <v>66</v>
       </c>
       <c r="J77" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K77" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L77" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M77" t="n">
         <v>3</v>
       </c>
       <c r="N77" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P77" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>1/5/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R77" t="n">
-        <v>750</v>
+        <v>922</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -6176,36 +6176,36 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J78" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K78" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L78" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M78" t="n">
         <v>2</v>
       </c>
       <c r="N78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O78" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P78" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R78" t="n">
-        <v>830</v>
+        <v>937</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -6250,25 +6250,25 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J79" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K79" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L79" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="M79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
         <v>9</v>
       </c>
       <c r="O79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
         <v>13</v>
@@ -6279,7 +6279,7 @@
         </is>
       </c>
       <c r="R79" t="n">
-        <v>769</v>
+        <v>858</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -6324,28 +6324,28 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J80" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K80" t="n">
         <v>20</v>
       </c>
       <c r="L80" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M80" t="n">
         <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O80" t="n">
         <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="R80" t="n">
-        <v>691</v>
+        <v>827</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J81" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K81" t="n">
         <v>20</v>
@@ -6410,27 +6410,27 @@
         <v>67</v>
       </c>
       <c r="M81" t="n">
+        <v>2</v>
+      </c>
+      <c r="N81" t="n">
+        <v>8</v>
+      </c>
+      <c r="O81" t="n">
         <v>3</v>
       </c>
-      <c r="N81" t="n">
-        <v>13</v>
-      </c>
-      <c r="O81" t="n">
-        <v>5</v>
-      </c>
       <c r="P81" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R81" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="S81" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -6472,16 +6472,16 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J82" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K82" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L82" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="M82" t="n">
         <v>2</v>
@@ -6490,21 +6490,21 @@
         <v>5</v>
       </c>
       <c r="O82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P82" t="n">
         <v>15</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R82" t="n">
-        <v>731</v>
+        <v>807</v>
       </c>
       <c r="S82" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -6546,25 +6546,25 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J83" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K83" t="n">
         <v>14</v>
       </c>
       <c r="L83" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M83" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N83" t="n">
         <v>15</v>
       </c>
       <c r="O83" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P83" t="n">
         <v>22</v>
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>750</v>
+        <v>928</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -6620,39 +6620,39 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J84" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K84" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L84" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M84" t="n">
+        <v>5</v>
+      </c>
+      <c r="N84" t="n">
+        <v>16</v>
+      </c>
+      <c r="O84" t="n">
         <v>7</v>
       </c>
-      <c r="N84" t="n">
-        <v>14</v>
-      </c>
-      <c r="O84" t="n">
-        <v>9</v>
-      </c>
       <c r="P84" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R84" t="n">
-        <v>786</v>
+        <v>884</v>
       </c>
       <c r="S84" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -6694,16 +6694,16 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J85" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K85" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L85" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M85" t="n">
         <v>2</v>
@@ -6712,7 +6712,7 @@
         <v>9</v>
       </c>
       <c r="O85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P85" t="n">
         <v>21</v>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="R85" t="n">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="S85" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -6768,39 +6768,39 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J86" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="K86" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L86" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M86" t="n">
         <v>2</v>
       </c>
       <c r="N86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O86" t="n">
         <v>3</v>
       </c>
       <c r="P86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R86" t="n">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="S86" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -6842,39 +6842,39 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J87" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K87" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L87" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M87" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N87" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O87" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R87" t="n">
-        <v>802</v>
+        <v>943</v>
       </c>
       <c r="S87" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -6922,22 +6922,22 @@
         <v>90</v>
       </c>
       <c r="K88" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L88" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M88" t="n">
         <v>2</v>
       </c>
       <c r="N88" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
       </c>
       <c r="P88" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="R88" t="n">
-        <v>745</v>
+        <v>847</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -6990,25 +6990,25 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J89" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K89" t="n">
         <v>13</v>
       </c>
       <c r="L89" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N89" t="n">
         <v>7</v>
       </c>
       <c r="O89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P89" t="n">
         <v>15</v>
@@ -7019,7 +7019,7 @@
         </is>
       </c>
       <c r="R89" t="n">
-        <v>855</v>
+        <v>882</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -7064,28 +7064,28 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J90" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K90" t="n">
         <v>19</v>
       </c>
       <c r="L90" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O90" t="n">
         <v>2</v>
       </c>
       <c r="P90" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -7093,10 +7093,10 @@
         </is>
       </c>
       <c r="R90" t="n">
-        <v>690</v>
+        <v>716</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -7138,16 +7138,16 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J91" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K91" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L91" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="M91" t="n">
         <v>3</v>
@@ -7159,7 +7159,7 @@
         <v>6</v>
       </c>
       <c r="P91" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>797</v>
+        <v>954</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J92" t="n">
         <v>91</v>
@@ -7227,21 +7227,21 @@
         <v>3</v>
       </c>
       <c r="N92" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O92" t="n">
         <v>5</v>
       </c>
       <c r="P92" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R92" t="n">
-        <v>791</v>
+        <v>840</v>
       </c>
       <c r="S92" t="n">
         <v>0.02</v>
@@ -7286,36 +7286,36 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J93" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K93" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L93" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O93" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R93" t="n">
-        <v>472</v>
+        <v>712</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -7360,16 +7360,16 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J94" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K94" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L94" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M94" t="n">
         <v>3</v>
@@ -7381,7 +7381,7 @@
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         </is>
       </c>
       <c r="R94" t="n">
-        <v>900</v>
+        <v>952</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -7437,33 +7437,33 @@
         <v>74</v>
       </c>
       <c r="J95" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K95" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L95" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M95" t="n">
         <v>2</v>
       </c>
       <c r="N95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P95" t="n">
         <v>16</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R95" t="n">
-        <v>845</v>
+        <v>950</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -7511,13 +7511,13 @@
         <v>70</v>
       </c>
       <c r="J96" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K96" t="n">
         <v>14</v>
       </c>
       <c r="L96" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M96" t="n">
         <v>3</v>
@@ -7526,18 +7526,18 @@
         <v>9</v>
       </c>
       <c r="O96" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P96" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R96" t="n">
-        <v>856</v>
+        <v>951</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J97" t="n">
         <v>87</v>
@@ -7594,24 +7594,24 @@
         <v>48</v>
       </c>
       <c r="M97" t="n">
+        <v>2</v>
+      </c>
+      <c r="N97" t="n">
+        <v>11</v>
+      </c>
+      <c r="O97" t="n">
         <v>3</v>
       </c>
-      <c r="N97" t="n">
-        <v>7</v>
-      </c>
-      <c r="O97" t="n">
-        <v>6</v>
-      </c>
       <c r="P97" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R97" t="n">
-        <v>770</v>
+        <v>739</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -7659,16 +7659,16 @@
         <v>85</v>
       </c>
       <c r="J98" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K98" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L98" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N98" t="n">
         <v>9</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="R98" t="n">
-        <v>884</v>
+        <v>932</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -7733,13 +7733,13 @@
         <v>61</v>
       </c>
       <c r="J99" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K99" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L99" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M99" t="n">
         <v>1</v>
@@ -7751,15 +7751,15 @@
         <v>2</v>
       </c>
       <c r="P99" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R99" t="n">
-        <v>901</v>
+        <v>938</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -7807,25 +7807,25 @@
         <v>73</v>
       </c>
       <c r="J100" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K100" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L100" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O100" t="n">
         <v>7</v>
       </c>
       <c r="P100" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="R100" t="n">
-        <v>787</v>
+        <v>957</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -7878,36 +7878,36 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J101" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K101" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L101" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="M101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N101" t="n">
+        <v>9</v>
+      </c>
+      <c r="O101" t="n">
         <v>6</v>
       </c>
-      <c r="O101" t="n">
-        <v>7</v>
-      </c>
       <c r="P101" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R101" t="n">
-        <v>799</v>
+        <v>931</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -7952,36 +7952,36 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J102" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K102" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L102" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M102" t="n">
         <v>2</v>
       </c>
       <c r="N102" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O102" t="n">
         <v>3</v>
       </c>
       <c r="P102" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R102" t="n">
-        <v>802</v>
+        <v>945</v>
       </c>
       <c r="S102" t="n">
         <v>0.06</v>
@@ -8026,16 +8026,16 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J103" t="n">
         <v>115</v>
       </c>
       <c r="K103" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L103" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M103" t="n">
         <v>2</v>
@@ -8044,18 +8044,18 @@
         <v>7</v>
       </c>
       <c r="O103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P103" t="n">
         <v>15</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R103" t="n">
-        <v>858</v>
+        <v>902</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -8103,33 +8103,33 @@
         <v>81</v>
       </c>
       <c r="J104" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L104" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N104" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O104" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P104" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1/4/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R104" t="n">
-        <v>891</v>
+        <v>934</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -8174,39 +8174,39 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J105" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K105" t="n">
         <v>19</v>
       </c>
       <c r="L105" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N105" t="n">
         <v>15</v>
       </c>
       <c r="O105" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P105" t="n">
         <v>23</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R105" t="n">
-        <v>810</v>
+        <v>920</v>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -8251,33 +8251,33 @@
         <v>66</v>
       </c>
       <c r="J106" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K106" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L106" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M106" t="n">
         <v>2</v>
       </c>
       <c r="N106" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O106" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P106" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R106" t="n">
-        <v>837</v>
+        <v>939</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -8322,36 +8322,36 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J107" t="n">
         <v>97</v>
       </c>
       <c r="K107" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L107" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="M107" t="n">
         <v>3</v>
       </c>
       <c r="N107" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O107" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P107" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R107" t="n">
-        <v>715</v>
+        <v>931</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -8399,36 +8399,36 @@
         <v>57</v>
       </c>
       <c r="J108" t="n">
+        <v>80</v>
+      </c>
+      <c r="K108" t="n">
+        <v>31</v>
+      </c>
+      <c r="L108" t="n">
         <v>81</v>
-      </c>
-      <c r="K108" t="n">
-        <v>32</v>
-      </c>
-      <c r="L108" t="n">
-        <v>77</v>
       </c>
       <c r="M108" t="n">
         <v>2</v>
       </c>
       <c r="N108" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O108" t="n">
         <v>3</v>
       </c>
       <c r="P108" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R108" t="n">
-        <v>796</v>
+        <v>892</v>
       </c>
       <c r="S108" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -8470,36 +8470,36 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J109" t="n">
         <v>85</v>
       </c>
       <c r="K109" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L109" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N109" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P109" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R109" t="n">
-        <v>566</v>
+        <v>717</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -8547,33 +8547,33 @@
         <v>81</v>
       </c>
       <c r="J110" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K110" t="n">
         <v>13</v>
       </c>
       <c r="L110" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N110" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P110" t="n">
         <v>13</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R110" t="n">
-        <v>829</v>
+        <v>936</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -8618,28 +8618,28 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J111" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K111" t="n">
         <v>17</v>
       </c>
       <c r="L111" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M111" t="n">
         <v>3</v>
       </c>
       <c r="N111" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O111" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P111" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         </is>
       </c>
       <c r="R111" t="n">
-        <v>723</v>
+        <v>852</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J112" t="n">
         <v>89</v>
@@ -8707,13 +8707,13 @@
         <v>2</v>
       </c>
       <c r="N112" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O112" t="n">
         <v>3</v>
       </c>
       <c r="P112" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="R112" t="n">
-        <v>715</v>
+        <v>892</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -8766,36 +8766,36 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J113" t="n">
         <v>81</v>
       </c>
       <c r="K113" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L113" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M113" t="n">
         <v>2</v>
       </c>
       <c r="N113" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O113" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P113" t="n">
         <v>13</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R113" t="n">
-        <v>745</v>
+        <v>731</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -8843,33 +8843,33 @@
         <v>66</v>
       </c>
       <c r="J114" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K114" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L114" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N114" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O114" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P114" t="n">
         <v>13</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R114" t="n">
-        <v>656</v>
+        <v>951</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -8914,13 +8914,13 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J115" t="n">
         <v>83</v>
       </c>
       <c r="K115" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L115" t="n">
         <v>43</v>
@@ -8929,21 +8929,21 @@
         <v>2</v>
       </c>
       <c r="N115" t="n">
+        <v>8</v>
+      </c>
+      <c r="O115" t="n">
         <v>3</v>
       </c>
-      <c r="O115" t="n">
-        <v>7</v>
-      </c>
       <c r="P115" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R115" t="n">
-        <v>632</v>
+        <v>747</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -8997,19 +8997,19 @@
         <v>18</v>
       </c>
       <c r="L116" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N116" t="n">
         <v>8</v>
       </c>
       <c r="O116" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P116" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         </is>
       </c>
       <c r="R116" t="n">
-        <v>697</v>
+        <v>950</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -9062,28 +9062,28 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J117" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L117" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M117" t="n">
+        <v>2</v>
+      </c>
+      <c r="N117" t="n">
+        <v>9</v>
+      </c>
+      <c r="O117" t="n">
         <v>3</v>
       </c>
-      <c r="N117" t="n">
-        <v>14</v>
-      </c>
-      <c r="O117" t="n">
-        <v>5</v>
-      </c>
       <c r="P117" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         </is>
       </c>
       <c r="R117" t="n">
-        <v>700</v>
+        <v>808</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J118" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K118" t="n">
         <v>20</v>
@@ -9151,24 +9151,24 @@
         <v>3</v>
       </c>
       <c r="N118" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O118" t="n">
         <v>5</v>
       </c>
       <c r="P118" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R118" t="n">
-        <v>712</v>
+        <v>909</v>
       </c>
       <c r="S118" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -9210,36 +9210,36 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J119" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K119" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L119" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N119" t="n">
+        <v>7</v>
+      </c>
+      <c r="O119" t="n">
         <v>3</v>
       </c>
-      <c r="O119" t="n">
-        <v>6</v>
-      </c>
       <c r="P119" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>1/4/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R119" t="n">
-        <v>706</v>
+        <v>905</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -9284,28 +9284,28 @@
         </is>
       </c>
       <c r="I120" t="n">
+        <v>59</v>
+      </c>
+      <c r="J120" t="n">
+        <v>96</v>
+      </c>
+      <c r="K120" t="n">
+        <v>12</v>
+      </c>
+      <c r="L120" t="n">
         <v>60</v>
       </c>
-      <c r="J120" t="n">
-        <v>94</v>
-      </c>
-      <c r="K120" t="n">
-        <v>13</v>
-      </c>
-      <c r="L120" t="n">
-        <v>53</v>
-      </c>
       <c r="M120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N120" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P120" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="R120" t="n">
-        <v>812</v>
+        <v>897</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -9361,33 +9361,33 @@
         <v>63</v>
       </c>
       <c r="J121" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K121" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L121" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M121" t="n">
         <v>3</v>
       </c>
       <c r="N121" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O121" t="n">
         <v>8</v>
       </c>
       <c r="P121" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>01</t>
         </is>
       </c>
       <c r="R121" t="n">
-        <v>793</v>
+        <v>921</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -9435,25 +9435,25 @@
         <v>65</v>
       </c>
       <c r="J122" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K122" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L122" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O122" t="n">
         <v>5</v>
       </c>
       <c r="P122" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="R122" t="n">
-        <v>777</v>
+        <v>946</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -9509,13 +9509,13 @@
         <v>81</v>
       </c>
       <c r="J123" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K123" t="n">
         <v>13</v>
       </c>
       <c r="L123" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M123" t="n">
         <v>2</v>
@@ -9524,18 +9524,18 @@
         <v>5</v>
       </c>
       <c r="O123" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P123" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R123" t="n">
-        <v>877</v>
+        <v>945</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -9580,19 +9580,19 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J124" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K124" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L124" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N124" t="n">
         <v>6</v>
@@ -9601,18 +9601,18 @@
         <v>8</v>
       </c>
       <c r="P124" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R124" t="n">
-        <v>856</v>
+        <v>910</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -9657,33 +9657,33 @@
         <v>79</v>
       </c>
       <c r="J125" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L125" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M125" t="n">
         <v>3</v>
       </c>
       <c r="N125" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O125" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P125" t="n">
         <v>16</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R125" t="n">
-        <v>866</v>
+        <v>953</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -9728,28 +9728,28 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J126" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K126" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L126" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N126" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O126" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P126" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="R126" t="n">
-        <v>794</v>
+        <v>940</v>
       </c>
       <c r="S126" t="n">
         <v>0.03</v>
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J127" t="n">
         <v>97</v>
@@ -9811,30 +9811,30 @@
         <v>18</v>
       </c>
       <c r="L127" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M127" t="n">
+        <v>2</v>
+      </c>
+      <c r="N127" t="n">
+        <v>10</v>
+      </c>
+      <c r="O127" t="n">
         <v>3</v>
       </c>
-      <c r="N127" t="n">
+      <c r="P127" t="n">
         <v>15</v>
       </c>
-      <c r="O127" t="n">
-        <v>5</v>
-      </c>
-      <c r="P127" t="n">
-        <v>21</v>
-      </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R127" t="n">
-        <v>832</v>
+        <v>943</v>
       </c>
       <c r="S127" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -9876,39 +9876,39 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J128" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K128" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L128" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="M128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N128" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P128" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R128" t="n">
-        <v>750</v>
+        <v>888</v>
       </c>
       <c r="S128" t="n">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -9959,19 +9959,19 @@
         <v>16</v>
       </c>
       <c r="L129" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M129" t="n">
         <v>3</v>
       </c>
       <c r="N129" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O129" t="n">
         <v>7</v>
       </c>
       <c r="P129" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -9979,10 +9979,10 @@
         </is>
       </c>
       <c r="R129" t="n">
-        <v>864</v>
+        <v>946</v>
       </c>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -10024,16 +10024,16 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J130" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K130" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L130" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M130" t="n">
         <v>2</v>
@@ -10042,21 +10042,21 @@
         <v>10</v>
       </c>
       <c r="O130" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P130" t="n">
         <v>18</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R130" t="n">
-        <v>805</v>
+        <v>929</v>
       </c>
       <c r="S130" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J131" t="n">
         <v>109</v>
@@ -10107,7 +10107,7 @@
         <v>15</v>
       </c>
       <c r="L131" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M131" t="n">
         <v>2</v>
@@ -10116,18 +10116,18 @@
         <v>7</v>
       </c>
       <c r="O131" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P131" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R131" t="n">
-        <v>855</v>
+        <v>940</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -10178,30 +10178,30 @@
         <v>97</v>
       </c>
       <c r="K132" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L132" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N132" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O132" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P132" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R132" t="n">
-        <v>816</v>
+        <v>865</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -10249,25 +10249,25 @@
         <v>66</v>
       </c>
       <c r="J133" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K133" t="n">
         <v>17</v>
       </c>
       <c r="L133" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M133" t="n">
         <v>2</v>
       </c>
       <c r="N133" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O133" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P133" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="R133" t="n">
-        <v>741</v>
+        <v>784</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -10320,36 +10320,36 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J134" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K134" t="n">
         <v>22</v>
       </c>
       <c r="L134" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N134" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P134" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R134" t="n">
-        <v>665</v>
+        <v>728</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -10394,16 +10394,16 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J135" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K135" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L135" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M135" t="n">
         <v>3</v>
@@ -10423,7 +10423,7 @@
         </is>
       </c>
       <c r="R135" t="n">
-        <v>780</v>
+        <v>910</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -10468,36 +10468,36 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J136" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K136" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L136" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M136" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N136" t="n">
+        <v>7</v>
+      </c>
+      <c r="O136" t="n">
+        <v>3</v>
+      </c>
+      <c r="P136" t="n">
         <v>9</v>
       </c>
-      <c r="O136" t="n">
-        <v>7</v>
-      </c>
-      <c r="P136" t="n">
-        <v>13</v>
-      </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R136" t="n">
-        <v>738</v>
+        <v>721</v>
       </c>
       <c r="S136" t="n">
         <v>0.06</v>
@@ -10542,7 +10542,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J137" t="n">
         <v>89</v>
@@ -10551,27 +10551,27 @@
         <v>17</v>
       </c>
       <c r="L137" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M137" t="n">
         <v>3</v>
       </c>
       <c r="N137" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O137" t="n">
         <v>5</v>
       </c>
       <c r="P137" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R137" t="n">
-        <v>863</v>
+        <v>941</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -10619,25 +10619,25 @@
         <v>83</v>
       </c>
       <c r="J138" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K138" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L138" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M138" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N138" t="n">
         <v>11</v>
       </c>
       <c r="O138" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="P138" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="R138" t="n">
-        <v>817</v>
+        <v>945</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -10705,24 +10705,24 @@
         <v>3</v>
       </c>
       <c r="N139" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O139" t="n">
         <v>5</v>
       </c>
       <c r="P139" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R139" t="n">
-        <v>785</v>
+        <v>877</v>
       </c>
       <c r="S139" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -10767,33 +10767,33 @@
         <v>64</v>
       </c>
       <c r="J140" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K140" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L140" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M140" t="n">
         <v>5</v>
       </c>
       <c r="N140" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O140" t="n">
         <v>10</v>
       </c>
       <c r="P140" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R140" t="n">
-        <v>695</v>
+        <v>910</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -10841,33 +10841,33 @@
         <v>79</v>
       </c>
       <c r="J141" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K141" t="n">
         <v>12</v>
       </c>
       <c r="L141" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M141" t="n">
+        <v>2</v>
+      </c>
+      <c r="N141" t="n">
+        <v>11</v>
+      </c>
+      <c r="O141" t="n">
         <v>3</v>
       </c>
-      <c r="N141" t="n">
-        <v>13</v>
-      </c>
-      <c r="O141" t="n">
-        <v>9</v>
-      </c>
       <c r="P141" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/5/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R141" t="n">
-        <v>801</v>
+        <v>937</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -10912,28 +10912,28 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J142" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K142" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L142" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M142" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N142" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O142" t="n">
         <v>9</v>
       </c>
       <c r="P142" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         </is>
       </c>
       <c r="R142" t="n">
-        <v>747</v>
+        <v>955</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -10989,36 +10989,36 @@
         <v>55</v>
       </c>
       <c r="J143" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K143" t="n">
         <v>24</v>
       </c>
       <c r="L143" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N143" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O143" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P143" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R143" t="n">
-        <v>796</v>
+        <v>848</v>
       </c>
       <c r="S143" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -11069,27 +11069,27 @@
         <v>19</v>
       </c>
       <c r="L144" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N144" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P144" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R144" t="n">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -11137,25 +11137,25 @@
         <v>81</v>
       </c>
       <c r="J145" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K145" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L145" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M145" t="n">
         <v>2</v>
       </c>
       <c r="N145" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O145" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P145" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         </is>
       </c>
       <c r="R145" t="n">
-        <v>838</v>
+        <v>941</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -11208,39 +11208,39 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J146" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K146" t="n">
         <v>22</v>
       </c>
       <c r="L146" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M146" t="n">
         <v>5</v>
       </c>
       <c r="N146" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O146" t="n">
         <v>7</v>
       </c>
       <c r="P146" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R146" t="n">
-        <v>796</v>
+        <v>932</v>
       </c>
       <c r="S146" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>69</v>
       </c>
       <c r="J147" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K147" t="n">
         <v>12</v>
@@ -11297,7 +11297,7 @@
         <v>6</v>
       </c>
       <c r="N147" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O147" t="n">
         <v>10</v>
@@ -11307,11 +11307,11 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R147" t="n">
-        <v>768</v>
+        <v>961</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -11356,39 +11356,39 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J148" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K148" t="n">
         <v>24</v>
       </c>
       <c r="L148" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="M148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N148" t="n">
         <v>7</v>
       </c>
       <c r="O148" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P148" t="n">
         <v>9</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R148" t="n">
-        <v>770</v>
+        <v>839</v>
       </c>
       <c r="S148" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -11430,28 +11430,28 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J149" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K149" t="n">
         <v>15</v>
       </c>
       <c r="L149" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M149" t="n">
         <v>1</v>
       </c>
       <c r="N149" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O149" t="n">
         <v>5</v>
       </c>
       <c r="P149" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="R149" t="n">
-        <v>893</v>
+        <v>947</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -11504,36 +11504,36 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J150" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K150" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L150" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P150" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R150" t="n">
-        <v>861</v>
+        <v>940</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -11578,28 +11578,28 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J151" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K151" t="n">
         <v>14</v>
       </c>
       <c r="L151" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M151" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N151" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O151" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P151" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="R151" t="n">
-        <v>893</v>
+        <v>939</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -11652,16 +11652,16 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J152" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K152" t="n">
         <v>12</v>
       </c>
       <c r="L152" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M152" t="n">
         <v>1</v>
@@ -11673,15 +11673,15 @@
         <v>3</v>
       </c>
       <c r="P152" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R152" t="n">
-        <v>889</v>
+        <v>945</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -11729,33 +11729,33 @@
         <v>72</v>
       </c>
       <c r="J153" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K153" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L153" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M153" t="n">
         <v>2</v>
       </c>
       <c r="N153" t="n">
+        <v>7</v>
+      </c>
+      <c r="O153" t="n">
         <v>3</v>
-      </c>
-      <c r="O153" t="n">
-        <v>6</v>
       </c>
       <c r="P153" t="n">
         <v>11</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R153" t="n">
-        <v>855</v>
+        <v>944</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -11803,33 +11803,33 @@
         <v>57</v>
       </c>
       <c r="J154" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K154" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L154" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M154" t="n">
         <v>2</v>
       </c>
       <c r="N154" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O154" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P154" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R154" t="n">
-        <v>612</v>
+        <v>708</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -11874,36 +11874,36 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J155" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K155" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L155" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M155" t="n">
         <v>2</v>
       </c>
       <c r="N155" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O155" t="n">
         <v>3</v>
       </c>
       <c r="P155" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R155" t="n">
-        <v>624</v>
+        <v>702</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -11948,39 +11948,39 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J156" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K156" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L156" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M156" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N156" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O156" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P156" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R156" t="n">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="S156" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -12025,25 +12025,25 @@
         <v>56</v>
       </c>
       <c r="J157" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K157" t="n">
         <v>16</v>
       </c>
       <c r="L157" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="M157" t="n">
         <v>1</v>
       </c>
       <c r="N157" t="n">
+        <v>3</v>
+      </c>
+      <c r="O157" t="n">
         <v>5</v>
       </c>
-      <c r="O157" t="n">
-        <v>3</v>
-      </c>
       <c r="P157" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         </is>
       </c>
       <c r="R157" t="n">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -12096,36 +12096,36 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J158" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K158" t="n">
         <v>15</v>
       </c>
       <c r="L158" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M158" t="n">
         <v>3</v>
       </c>
       <c r="N158" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="O158" t="n">
         <v>5</v>
       </c>
       <c r="P158" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R158" t="n">
-        <v>773</v>
+        <v>934</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>

--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
         <v>80</v>
@@ -577,14 +577,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>832</v>
+        <v>789</v>
       </c>
       <c r="S2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -629,33 +629,33 @@
         <v>87</v>
       </c>
       <c r="J3" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
         <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>935</v>
+        <v>780</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -691,7 +691,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -703,25 +703,25 @@
         <v>59</v>
       </c>
       <c r="J4" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L4" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O4" t="n">
         <v>7</v>
       </c>
       <c r="P4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>886</v>
+        <v>769</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -774,39 +774,39 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J5" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>750</v>
+        <v>688</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -848,36 +848,36 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J6" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O6" t="n">
         <v>7</v>
       </c>
-      <c r="O6" t="n">
-        <v>5</v>
-      </c>
       <c r="P6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>881</v>
+        <v>808</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -922,39 +922,39 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L7" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>742</v>
+        <v>789</v>
       </c>
       <c r="S7" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J8" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L8" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="M8" t="n">
         <v>5</v>
@@ -1021,11 +1021,11 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>865</v>
+        <v>855</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1070,39 +1070,39 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J9" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="K9" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>800</v>
+        <v>719</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1144,36 +1144,36 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J10" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P10" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>915</v>
+        <v>847</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1221,33 +1221,33 @@
         <v>80</v>
       </c>
       <c r="J11" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
         <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>946</v>
+        <v>860</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1292,39 +1292,39 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K12" t="n">
         <v>22</v>
       </c>
       <c r="L12" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>874</v>
+        <v>852</v>
       </c>
       <c r="S12" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1366,36 +1366,36 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J13" t="n">
         <v>86</v>
       </c>
       <c r="K13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L13" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>926</v>
+        <v>773</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1440,39 +1440,39 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L14" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1/4/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>763</v>
+        <v>680</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1514,36 +1514,36 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J15" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K15" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L15" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>11</v>
+      </c>
+      <c r="O15" t="n">
         <v>3</v>
       </c>
-      <c r="N15" t="n">
-        <v>10</v>
-      </c>
-      <c r="O15" t="n">
-        <v>5</v>
-      </c>
       <c r="P15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>897</v>
+        <v>842</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1588,36 +1588,36 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J16" t="n">
         <v>86</v>
       </c>
       <c r="K16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L16" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M16" t="n">
         <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O16" t="n">
         <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>944</v>
+        <v>722</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1662,39 +1662,39 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J17" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L17" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="M17" t="n">
         <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
         <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>739</v>
+        <v>761</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1736,36 +1736,36 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J18" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L18" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>868</v>
+        <v>750</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1813,33 +1813,33 @@
         <v>72</v>
       </c>
       <c r="J19" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K19" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L19" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O19" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="P19" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1/5/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>917</v>
+        <v>742</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1884,28 +1884,28 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J20" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K20" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L20" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
         <v>7</v>
       </c>
       <c r="P20" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>975</v>
+        <v>771</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1958,28 +1958,28 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J21" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="K21" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="L21" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N21" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O21" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>842</v>
+        <v>810</v>
       </c>
       <c r="S21" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2035,33 +2035,33 @@
         <v>71</v>
       </c>
       <c r="J22" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L22" t="n">
         <v>47</v>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P22" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>979</v>
+        <v>780</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2106,36 +2106,36 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J23" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L23" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O23" t="n">
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>921</v>
+        <v>831</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2183,25 +2183,25 @@
         <v>74</v>
       </c>
       <c r="J24" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L24" t="n">
         <v>37</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>923</v>
+        <v>832</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2257,10 +2257,10 @@
         <v>78</v>
       </c>
       <c r="J25" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L25" t="n">
         <v>31</v>
@@ -2269,24 +2269,24 @@
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>958</v>
+        <v>793</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J26" t="n">
         <v>96</v>
@@ -2337,27 +2337,27 @@
         <v>18</v>
       </c>
       <c r="L26" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
         <v>7</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
         <v>10</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>938</v>
+        <v>803</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2402,36 +2402,36 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J27" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K27" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L27" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J28" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L28" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M28" t="n">
         <v>3</v>
@@ -2497,7 +2497,7 @@
         <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>840</v>
+        <v>739</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2553,10 +2553,10 @@
         <v>51</v>
       </c>
       <c r="J29" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K29" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L29" t="n">
         <v>86</v>
@@ -2565,24 +2565,24 @@
         <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>743</v>
+        <v>720</v>
       </c>
       <c r="S29" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2624,36 +2624,36 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J30" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L30" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" t="n">
         <v>8</v>
       </c>
-      <c r="O30" t="n">
-        <v>7</v>
-      </c>
       <c r="P30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>841</v>
+        <v>788</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2698,28 +2698,28 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J31" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K31" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L31" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
         <v>6</v>
       </c>
       <c r="P31" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>908</v>
+        <v>774</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2772,39 +2772,39 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J32" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K32" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L32" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P32" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="S32" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2846,39 +2846,39 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J33" t="n">
         <v>80</v>
       </c>
       <c r="K33" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L33" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>673</v>
+        <v>737</v>
       </c>
       <c r="S33" t="n">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2920,28 +2920,28 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J34" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K34" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L34" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2994,36 +2994,36 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J35" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K35" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L35" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N35" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P35" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>920</v>
+        <v>828</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3068,39 +3068,39 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J36" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K36" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L36" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>696</v>
+        <v>735</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3142,39 +3142,39 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J37" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K37" t="n">
         <v>16</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="M37" t="n">
         <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O37" t="n">
         <v>5</v>
       </c>
       <c r="P37" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="S37" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3216,36 +3216,36 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J38" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K38" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L38" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>907</v>
+        <v>875</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3290,39 +3290,39 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J39" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K39" t="n">
+        <v>20</v>
+      </c>
+      <c r="L39" t="n">
+        <v>37</v>
+      </c>
+      <c r="M39" t="n">
+        <v>6</v>
+      </c>
+      <c r="N39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" t="n">
-        <v>24</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3</v>
-      </c>
-      <c r="N39" t="n">
-        <v>8</v>
-      </c>
       <c r="O39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P39" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>905</v>
+        <v>794</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3367,33 +3367,33 @@
         <v>66</v>
       </c>
       <c r="J40" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K40" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L40" t="n">
         <v>36</v>
       </c>
       <c r="M40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
         <v>11</v>
       </c>
       <c r="P40" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1/8/1 17:00 LMT</t>
+          <t>1/7/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>922</v>
+        <v>674</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3438,36 +3438,36 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J41" t="n">
         <v>81</v>
       </c>
       <c r="K41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L41" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M41" t="n">
         <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>884</v>
+        <v>722</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3515,36 +3515,36 @@
         <v>49</v>
       </c>
       <c r="J42" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L42" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>880</v>
+        <v>763</v>
       </c>
       <c r="S42" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3586,39 +3586,39 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J43" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K43" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L43" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="M43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O43" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P43" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>869</v>
+        <v>771</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3660,25 +3660,25 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J44" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K44" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L44" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="M44" t="n">
         <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P44" t="n">
         <v>16</v>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>905</v>
+        <v>645</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3734,28 +3734,28 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J45" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K45" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L45" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N45" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="O45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P45" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="R45" t="n">
-        <v>939</v>
+        <v>846</v>
       </c>
       <c r="S45" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J46" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K46" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L46" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P46" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>972</v>
+        <v>778</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3882,36 +3882,36 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J47" t="n">
         <v>86</v>
       </c>
       <c r="K47" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L47" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>858</v>
+        <v>599</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3959,13 +3959,13 @@
         <v>88</v>
       </c>
       <c r="J48" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K48" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L48" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="M48" t="n">
         <v>3</v>
@@ -3974,18 +3974,18 @@
         <v>8</v>
       </c>
       <c r="O48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P48" t="n">
         <v>15</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>725</v>
+        <v>705</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4033,33 +4033,33 @@
         <v>67</v>
       </c>
       <c r="J49" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L49" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R49" t="n">
-        <v>824</v>
+        <v>691</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4104,28 +4104,28 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J50" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K50" t="n">
         <v>19</v>
       </c>
       <c r="L50" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P50" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="R50" t="n">
-        <v>940</v>
+        <v>768</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4178,36 +4178,36 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J51" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K51" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L51" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N51" t="n">
+        <v>10</v>
+      </c>
+      <c r="O51" t="n">
         <v>8</v>
       </c>
-      <c r="O51" t="n">
-        <v>5</v>
-      </c>
       <c r="P51" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1/7/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R51" t="n">
-        <v>764</v>
+        <v>788</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4252,39 +4252,39 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J52" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K52" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L52" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M52" t="n">
         <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
       </c>
       <c r="P52" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>847</v>
+        <v>727</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4329,10 +4329,10 @@
         <v>80</v>
       </c>
       <c r="J53" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K53" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L53" t="n">
         <v>29</v>
@@ -4344,18 +4344,18 @@
         <v>7</v>
       </c>
       <c r="O53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P53" t="n">
         <v>17</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R53" t="n">
-        <v>948</v>
+        <v>851</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4403,13 +4403,13 @@
         <v>86</v>
       </c>
       <c r="J54" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K54" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L54" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M54" t="n">
         <v>2</v>
@@ -4421,7 +4421,7 @@
         <v>5</v>
       </c>
       <c r="P54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>930</v>
+        <v>854</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4474,36 +4474,36 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J55" t="n">
         <v>102</v>
       </c>
       <c r="K55" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L55" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N55" t="n">
         <v>14</v>
       </c>
       <c r="O55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P55" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>853</v>
+        <v>763</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4548,39 +4548,39 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J56" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L56" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="M56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
+        <v>5</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" t="n">
         <v>7</v>
       </c>
-      <c r="O56" t="n">
-        <v>3</v>
-      </c>
-      <c r="P56" t="n">
-        <v>9</v>
-      </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>909</v>
+        <v>768</v>
       </c>
       <c r="S56" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4622,19 +4622,19 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J57" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K57" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L57" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="M57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N57" t="n">
         <v>10</v>
@@ -4647,11 +4647,11 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>815</v>
+        <v>660</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4696,39 +4696,39 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J58" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K58" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L58" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
         <v>9</v>
       </c>
       <c r="O58" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>669</v>
+        <v>548</v>
       </c>
       <c r="S58" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4770,36 +4770,36 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J59" t="n">
         <v>97</v>
       </c>
       <c r="K59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L59" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N59" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P59" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R59" t="n">
-        <v>940</v>
+        <v>746</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4847,33 +4847,33 @@
         <v>74</v>
       </c>
       <c r="J60" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K60" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L60" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O60" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="P60" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>1/2/1 17:00 LMT</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R60" t="n">
-        <v>958</v>
+        <v>775</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4918,36 +4918,36 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J61" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K61" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L61" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="M61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
+        <v>7</v>
+      </c>
+      <c r="O61" t="n">
+        <v>5</v>
+      </c>
+      <c r="P61" t="n">
         <v>11</v>
       </c>
-      <c r="O61" t="n">
-        <v>3</v>
-      </c>
-      <c r="P61" t="n">
-        <v>16</v>
-      </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>986</v>
+        <v>865</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5001,27 +5001,27 @@
         <v>21</v>
       </c>
       <c r="L62" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O62" t="n">
         <v>2</v>
       </c>
       <c r="P62" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R62" t="n">
-        <v>707</v>
+        <v>653</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5069,33 +5069,33 @@
         <v>86</v>
       </c>
       <c r="J63" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L63" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M63" t="n">
         <v>1</v>
       </c>
       <c r="N63" t="n">
+        <v>8</v>
+      </c>
+      <c r="O63" t="n">
         <v>5</v>
       </c>
-      <c r="O63" t="n">
-        <v>3</v>
-      </c>
       <c r="P63" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R63" t="n">
-        <v>935</v>
+        <v>701</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5140,16 +5140,16 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J64" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K64" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L64" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
@@ -5158,10 +5158,10 @@
         <v>6</v>
       </c>
       <c r="O64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P64" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>932</v>
+        <v>731</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5217,13 +5217,13 @@
         <v>61</v>
       </c>
       <c r="J65" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K65" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L65" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M65" t="n">
         <v>2</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>865</v>
+        <v>713</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5288,36 +5288,36 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J66" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K66" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L66" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M66" t="n">
         <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
         <v>7</v>
       </c>
       <c r="P66" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R66" t="n">
-        <v>960</v>
+        <v>843</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5371,16 +5371,16 @@
         <v>13</v>
       </c>
       <c r="L67" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
         <v>15</v>
       </c>
       <c r="O67" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P67" t="n">
         <v>23</v>
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>953</v>
+        <v>697</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5439,36 +5439,36 @@
         <v>69</v>
       </c>
       <c r="J68" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K68" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L68" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N68" t="n">
         <v>9</v>
       </c>
       <c r="O68" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P68" t="n">
         <v>14</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>961</v>
+        <v>785</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5513,36 +5513,36 @@
         <v>78</v>
       </c>
       <c r="J69" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K69" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L69" t="n">
         <v>30</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N69" t="n">
         <v>9</v>
       </c>
       <c r="O69" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P69" t="n">
         <v>21</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>926</v>
+        <v>797</v>
       </c>
       <c r="S69" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5587,33 +5587,33 @@
         <v>76</v>
       </c>
       <c r="J70" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K70" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L70" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N70" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R70" t="n">
-        <v>932</v>
+        <v>796</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5670,24 +5670,24 @@
         <v>42</v>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N71" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O71" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P71" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R71" t="n">
-        <v>929</v>
+        <v>668</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5732,36 +5732,36 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J72" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L72" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="M72" t="n">
         <v>2</v>
       </c>
       <c r="N72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P72" t="n">
         <v>14</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>791</v>
+        <v>744</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5806,39 +5806,39 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J73" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K73" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="L73" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="M73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P73" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R73" t="n">
-        <v>743</v>
+        <v>710</v>
       </c>
       <c r="S73" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5880,39 +5880,39 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J74" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K74" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L74" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="M74" t="n">
         <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R74" t="n">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="S74" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5954,36 +5954,36 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J75" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K75" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L75" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M75" t="n">
+        <v>2</v>
+      </c>
+      <c r="N75" t="n">
+        <v>7</v>
+      </c>
+      <c r="O75" t="n">
         <v>3</v>
       </c>
-      <c r="N75" t="n">
+      <c r="P75" t="n">
         <v>9</v>
       </c>
-      <c r="O75" t="n">
-        <v>5</v>
-      </c>
-      <c r="P75" t="n">
-        <v>13</v>
-      </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R75" t="n">
-        <v>931</v>
+        <v>790</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J76" t="n">
         <v>85</v>
@@ -6040,24 +6040,24 @@
         <v>54</v>
       </c>
       <c r="M76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O76" t="n">
         <v>6</v>
       </c>
       <c r="P76" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1/8/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R76" t="n">
-        <v>816</v>
+        <v>644</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6102,28 +6102,28 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J77" t="n">
         <v>90</v>
       </c>
       <c r="K77" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L77" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N77" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P77" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>922</v>
+        <v>783</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6176,36 +6176,36 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J78" t="n">
         <v>82</v>
       </c>
       <c r="K78" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L78" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M78" t="n">
         <v>2</v>
       </c>
       <c r="N78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O78" t="n">
         <v>3</v>
       </c>
       <c r="P78" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R78" t="n">
-        <v>937</v>
+        <v>736</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6250,36 +6250,36 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J79" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K79" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L79" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R79" t="n">
-        <v>858</v>
+        <v>712</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6327,36 +6327,36 @@
         <v>61</v>
       </c>
       <c r="J80" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K80" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L80" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="M80" t="n">
         <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O80" t="n">
         <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R80" t="n">
-        <v>827</v>
+        <v>686</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6398,36 +6398,36 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J81" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K81" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L81" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="M81" t="n">
         <v>2</v>
       </c>
       <c r="N81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O81" t="n">
         <v>3</v>
       </c>
       <c r="P81" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R81" t="n">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6472,39 +6472,39 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J82" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K82" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L82" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="M82" t="n">
         <v>2</v>
       </c>
       <c r="N82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O82" t="n">
         <v>8</v>
       </c>
       <c r="P82" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R82" t="n">
-        <v>807</v>
+        <v>756</v>
       </c>
       <c r="S82" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6546,39 +6546,39 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J83" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="K83" t="n">
+        <v>23</v>
+      </c>
+      <c r="L83" t="n">
+        <v>55</v>
+      </c>
+      <c r="M83" t="n">
+        <v>6</v>
+      </c>
+      <c r="N83" t="n">
         <v>14</v>
       </c>
-      <c r="L83" t="n">
-        <v>39</v>
-      </c>
-      <c r="M83" t="n">
-        <v>3</v>
-      </c>
-      <c r="N83" t="n">
-        <v>15</v>
-      </c>
       <c r="O83" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P83" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R83" t="n">
-        <v>928</v>
+        <v>789</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6620,39 +6620,39 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J84" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K84" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L84" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="M84" t="n">
+        <v>3</v>
+      </c>
+      <c r="N84" t="n">
+        <v>13</v>
+      </c>
+      <c r="O84" t="n">
         <v>5</v>
       </c>
-      <c r="N84" t="n">
-        <v>16</v>
-      </c>
-      <c r="O84" t="n">
-        <v>7</v>
-      </c>
       <c r="P84" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R84" t="n">
-        <v>884</v>
+        <v>839</v>
       </c>
       <c r="S84" t="n">
-        <v>0.21</v>
+        <v>0.01</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6694,36 +6694,36 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J85" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K85" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L85" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="M85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N85" t="n">
         <v>9</v>
       </c>
       <c r="O85" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R85" t="n">
-        <v>739</v>
+        <v>789</v>
       </c>
       <c r="S85" t="n">
         <v>0.04</v>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6768,39 +6768,39 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J86" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K86" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L86" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N86" t="n">
         <v>7</v>
       </c>
       <c r="O86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P86" t="n">
         <v>9</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R86" t="n">
-        <v>649</v>
+        <v>786</v>
       </c>
       <c r="S86" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6842,39 +6842,39 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J87" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K87" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L87" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="M87" t="n">
+        <v>2</v>
+      </c>
+      <c r="N87" t="n">
+        <v>9</v>
+      </c>
+      <c r="O87" t="n">
         <v>3</v>
       </c>
-      <c r="N87" t="n">
-        <v>11</v>
-      </c>
-      <c r="O87" t="n">
-        <v>5</v>
-      </c>
       <c r="P87" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R87" t="n">
-        <v>943</v>
+        <v>847</v>
       </c>
       <c r="S87" t="n">
-        <v>0.38</v>
+        <v>0.03</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6916,36 +6916,36 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J88" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K88" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L88" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N88" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R88" t="n">
-        <v>847</v>
+        <v>729</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6990,36 +6990,36 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J89" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K89" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L89" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O89" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P89" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R89" t="n">
-        <v>882</v>
+        <v>844</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7064,22 +7064,22 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J90" t="n">
         <v>86</v>
       </c>
       <c r="K90" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L90" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M90" t="n">
         <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O90" t="n">
         <v>2</v>
@@ -7089,14 +7089,14 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R90" t="n">
-        <v>716</v>
+        <v>612</v>
       </c>
       <c r="S90" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7144,10 +7144,10 @@
         <v>94</v>
       </c>
       <c r="K91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L91" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M91" t="n">
         <v>3</v>
@@ -7156,10 +7156,10 @@
         <v>9</v>
       </c>
       <c r="O91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P91" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>954</v>
+        <v>639</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7212,39 +7212,39 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J92" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K92" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L92" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="M92" t="n">
         <v>3</v>
       </c>
       <c r="N92" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O92" t="n">
         <v>5</v>
       </c>
       <c r="P92" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R92" t="n">
-        <v>840</v>
+        <v>802</v>
       </c>
       <c r="S92" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7289,33 +7289,33 @@
         <v>61</v>
       </c>
       <c r="J93" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K93" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L93" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M93" t="n">
+        <v>2</v>
+      </c>
+      <c r="N93" t="n">
+        <v>6</v>
+      </c>
+      <c r="O93" t="n">
         <v>3</v>
       </c>
-      <c r="N93" t="n">
+      <c r="P93" t="n">
         <v>9</v>
       </c>
-      <c r="O93" t="n">
-        <v>6</v>
-      </c>
-      <c r="P93" t="n">
-        <v>15</v>
-      </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R93" t="n">
-        <v>712</v>
+        <v>644</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7366,22 +7366,22 @@
         <v>83</v>
       </c>
       <c r="K94" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L94" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N94" t="n">
         <v>8</v>
       </c>
       <c r="O94" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P94" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         </is>
       </c>
       <c r="R94" t="n">
-        <v>952</v>
+        <v>727</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7437,13 +7437,13 @@
         <v>74</v>
       </c>
       <c r="J95" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K95" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L95" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M95" t="n">
         <v>2</v>
@@ -7452,18 +7452,18 @@
         <v>6</v>
       </c>
       <c r="O95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P95" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R95" t="n">
-        <v>950</v>
+        <v>754</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7508,7 +7508,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J96" t="n">
         <v>98</v>
@@ -7517,27 +7517,27 @@
         <v>14</v>
       </c>
       <c r="L96" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="M96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N96" t="n">
+        <v>10</v>
+      </c>
+      <c r="O96" t="n">
         <v>9</v>
       </c>
-      <c r="O96" t="n">
-        <v>6</v>
-      </c>
       <c r="P96" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R96" t="n">
-        <v>951</v>
+        <v>732</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7582,28 +7582,28 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J97" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K97" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L97" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N97" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P97" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         </is>
       </c>
       <c r="R97" t="n">
-        <v>739</v>
+        <v>800</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7656,36 +7656,36 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J98" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L98" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O98" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P98" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R98" t="n">
-        <v>932</v>
+        <v>754</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7730,16 +7730,16 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J99" t="n">
         <v>88</v>
       </c>
       <c r="K99" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L99" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="M99" t="n">
         <v>1</v>
@@ -7748,10 +7748,10 @@
         <v>6</v>
       </c>
       <c r="O99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P99" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="R99" t="n">
-        <v>938</v>
+        <v>720</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7807,33 +7807,33 @@
         <v>73</v>
       </c>
       <c r="J100" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K100" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L100" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M100" t="n">
         <v>3</v>
       </c>
       <c r="N100" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P100" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/7/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R100" t="n">
-        <v>957</v>
+        <v>709</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7881,7 +7881,7 @@
         <v>70</v>
       </c>
       <c r="J101" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K101" t="n">
         <v>13</v>
@@ -7890,16 +7890,16 @@
         <v>41</v>
       </c>
       <c r="M101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P101" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="R101" t="n">
-        <v>931</v>
+        <v>647</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7952,39 +7952,39 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J102" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K102" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L102" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="M102" t="n">
         <v>2</v>
       </c>
       <c r="N102" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O102" t="n">
         <v>3</v>
       </c>
       <c r="P102" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R102" t="n">
-        <v>945</v>
+        <v>800</v>
       </c>
       <c r="S102" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8026,36 +8026,36 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J103" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K103" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L103" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N103" t="n">
         <v>7</v>
       </c>
       <c r="O103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P103" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R103" t="n">
-        <v>902</v>
+        <v>848</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8100,36 +8100,36 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J104" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K104" t="n">
+        <v>11</v>
+      </c>
+      <c r="L104" t="n">
+        <v>23</v>
+      </c>
+      <c r="M104" t="n">
+        <v>6</v>
+      </c>
+      <c r="N104" t="n">
         <v>10</v>
       </c>
-      <c r="L104" t="n">
-        <v>26</v>
-      </c>
-      <c r="M104" t="n">
-        <v>2</v>
-      </c>
-      <c r="N104" t="n">
-        <v>13</v>
-      </c>
       <c r="O104" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P104" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>1/4/1 17:00 LMT</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R104" t="n">
-        <v>934</v>
+        <v>791</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8177,36 +8177,36 @@
         <v>73</v>
       </c>
       <c r="J105" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K105" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L105" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="M105" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N105" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O105" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P105" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R105" t="n">
-        <v>920</v>
+        <v>846</v>
       </c>
       <c r="S105" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8251,13 +8251,13 @@
         <v>66</v>
       </c>
       <c r="J106" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K106" t="n">
         <v>18</v>
       </c>
       <c r="L106" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M106" t="n">
         <v>2</v>
@@ -8273,11 +8273,11 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R106" t="n">
-        <v>939</v>
+        <v>688</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8322,7 +8322,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J107" t="n">
         <v>97</v>
@@ -8334,24 +8334,24 @@
         <v>48</v>
       </c>
       <c r="M107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N107" t="n">
         <v>8</v>
       </c>
       <c r="O107" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P107" t="n">
         <v>13</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R107" t="n">
-        <v>931</v>
+        <v>822</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8399,36 +8399,36 @@
         <v>57</v>
       </c>
       <c r="J108" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K108" t="n">
         <v>31</v>
       </c>
       <c r="L108" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="M108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N108" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R108" t="n">
-        <v>892</v>
+        <v>807</v>
       </c>
       <c r="S108" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8473,36 +8473,36 @@
         <v>62</v>
       </c>
       <c r="J109" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K109" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L109" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="M109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N109" t="n">
+        <v>7</v>
+      </c>
+      <c r="O109" t="n">
+        <v>7</v>
+      </c>
+      <c r="P109" t="n">
         <v>9</v>
       </c>
-      <c r="O109" t="n">
-        <v>5</v>
-      </c>
-      <c r="P109" t="n">
-        <v>13</v>
-      </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R109" t="n">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8544,36 +8544,36 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J110" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K110" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L110" t="n">
         <v>37</v>
       </c>
       <c r="M110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N110" t="n">
+        <v>7</v>
+      </c>
+      <c r="O110" t="n">
         <v>6</v>
       </c>
-      <c r="O110" t="n">
-        <v>5</v>
-      </c>
       <c r="P110" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R110" t="n">
-        <v>936</v>
+        <v>852</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8618,36 +8618,36 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J111" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K111" t="n">
         <v>17</v>
       </c>
       <c r="L111" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M111" t="n">
         <v>3</v>
       </c>
       <c r="N111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O111" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P111" t="n">
         <v>11</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R111" t="n">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8695,33 +8695,33 @@
         <v>65</v>
       </c>
       <c r="J112" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K112" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L112" t="n">
         <v>45</v>
       </c>
       <c r="M112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N112" t="n">
         <v>10</v>
       </c>
       <c r="O112" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P112" t="n">
         <v>16</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R112" t="n">
-        <v>892</v>
+        <v>762</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8772,22 +8772,22 @@
         <v>81</v>
       </c>
       <c r="K113" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L113" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M113" t="n">
         <v>2</v>
       </c>
       <c r="N113" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O113" t="n">
         <v>3</v>
       </c>
       <c r="P113" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="R113" t="n">
-        <v>731</v>
+        <v>711</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8846,10 +8846,10 @@
         <v>98</v>
       </c>
       <c r="K114" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L114" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M114" t="n">
         <v>3</v>
@@ -8865,11 +8865,11 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R114" t="n">
-        <v>951</v>
+        <v>824</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J115" t="n">
         <v>83</v>
@@ -8923,27 +8923,27 @@
         <v>25</v>
       </c>
       <c r="L115" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M115" t="n">
         <v>2</v>
       </c>
       <c r="N115" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O115" t="n">
         <v>3</v>
       </c>
       <c r="P115" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R115" t="n">
-        <v>747</v>
+        <v>692</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8988,28 +8988,28 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J116" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="K116" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="L116" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="M116" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N116" t="n">
+        <v>7</v>
+      </c>
+      <c r="O116" t="n">
         <v>8</v>
       </c>
-      <c r="O116" t="n">
-        <v>9</v>
-      </c>
       <c r="P116" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="R116" t="n">
-        <v>950</v>
+        <v>812</v>
       </c>
       <c r="S116" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9062,36 +9062,36 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J117" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K117" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L117" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="M117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N117" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O117" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P117" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R117" t="n">
-        <v>808</v>
+        <v>736</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9136,39 +9136,39 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J118" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K118" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L118" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M118" t="n">
         <v>3</v>
       </c>
       <c r="N118" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O118" t="n">
         <v>5</v>
       </c>
       <c r="P118" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R118" t="n">
-        <v>909</v>
+        <v>804</v>
       </c>
       <c r="S118" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9210,28 +9210,28 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J119" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K119" t="n">
         <v>20</v>
       </c>
       <c r="L119" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M119" t="n">
         <v>2</v>
       </c>
       <c r="N119" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O119" t="n">
         <v>3</v>
       </c>
       <c r="P119" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="R119" t="n">
-        <v>905</v>
+        <v>808</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9284,36 +9284,36 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J120" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K120" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L120" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N120" t="n">
+        <v>5</v>
+      </c>
+      <c r="O120" t="n">
+        <v>3</v>
+      </c>
+      <c r="P120" t="n">
         <v>7</v>
       </c>
-      <c r="O120" t="n">
-        <v>1</v>
-      </c>
-      <c r="P120" t="n">
-        <v>9</v>
-      </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R120" t="n">
-        <v>897</v>
+        <v>708</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9361,33 +9361,33 @@
         <v>63</v>
       </c>
       <c r="J121" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K121" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L121" t="n">
         <v>43</v>
       </c>
       <c r="M121" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P121" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>1/5/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R121" t="n">
-        <v>921</v>
+        <v>766</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9432,28 +9432,28 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J122" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K122" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L122" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M122" t="n">
         <v>2</v>
       </c>
       <c r="N122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O122" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P122" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="R122" t="n">
-        <v>946</v>
+        <v>673</v>
       </c>
       <c r="S122" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9506,16 +9506,16 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J123" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K123" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L123" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M123" t="n">
         <v>2</v>
@@ -9524,18 +9524,18 @@
         <v>5</v>
       </c>
       <c r="O123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P123" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R123" t="n">
-        <v>945</v>
+        <v>839</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9580,39 +9580,39 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J124" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K124" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L124" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="M124" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N124" t="n">
         <v>6</v>
       </c>
       <c r="O124" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P124" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R124" t="n">
-        <v>910</v>
+        <v>864</v>
       </c>
       <c r="S124" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9657,33 +9657,33 @@
         <v>79</v>
       </c>
       <c r="J125" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K125" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L125" t="n">
         <v>31</v>
       </c>
       <c r="M125" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N125" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O125" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P125" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R125" t="n">
-        <v>953</v>
+        <v>864</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9728,39 +9728,39 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J126" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K126" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L126" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="M126" t="n">
+        <v>3</v>
+      </c>
+      <c r="N126" t="n">
+        <v>14</v>
+      </c>
+      <c r="O126" t="n">
         <v>5</v>
       </c>
-      <c r="N126" t="n">
-        <v>16</v>
-      </c>
-      <c r="O126" t="n">
-        <v>7</v>
-      </c>
       <c r="P126" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R126" t="n">
-        <v>940</v>
+        <v>847</v>
       </c>
       <c r="S126" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J127" t="n">
         <v>97</v>
@@ -9811,30 +9811,30 @@
         <v>18</v>
       </c>
       <c r="L127" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="M127" t="n">
         <v>2</v>
       </c>
       <c r="N127" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O127" t="n">
         <v>3</v>
       </c>
       <c r="P127" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R127" t="n">
-        <v>943</v>
+        <v>860</v>
       </c>
       <c r="S127" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9876,39 +9876,39 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J128" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K128" t="n">
         <v>25</v>
       </c>
       <c r="L128" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="M128" t="n">
         <v>1</v>
       </c>
       <c r="N128" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O128" t="n">
         <v>1</v>
       </c>
       <c r="P128" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R128" t="n">
-        <v>888</v>
+        <v>788</v>
       </c>
       <c r="S128" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9950,28 +9950,28 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J129" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K129" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L129" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="M129" t="n">
         <v>3</v>
       </c>
       <c r="N129" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O129" t="n">
         <v>7</v>
       </c>
       <c r="P129" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -9979,10 +9979,10 @@
         </is>
       </c>
       <c r="R129" t="n">
-        <v>946</v>
+        <v>813</v>
       </c>
       <c r="S129" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10027,25 +10027,25 @@
         <v>68</v>
       </c>
       <c r="J130" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K130" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L130" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N130" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O130" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P130" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -10053,10 +10053,10 @@
         </is>
       </c>
       <c r="R130" t="n">
-        <v>929</v>
+        <v>765</v>
       </c>
       <c r="S130" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -10101,19 +10101,19 @@
         <v>81</v>
       </c>
       <c r="J131" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K131" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L131" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M131" t="n">
         <v>2</v>
       </c>
       <c r="N131" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O131" t="n">
         <v>5</v>
@@ -10123,11 +10123,11 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R131" t="n">
-        <v>940</v>
+        <v>875</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -10172,36 +10172,36 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J132" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K132" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L132" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="M132" t="n">
         <v>5</v>
       </c>
       <c r="N132" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O132" t="n">
         <v>7</v>
       </c>
       <c r="P132" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R132" t="n">
-        <v>865</v>
+        <v>834</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10252,22 +10252,22 @@
         <v>98</v>
       </c>
       <c r="K133" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L133" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N133" t="n">
         <v>7</v>
       </c>
       <c r="O133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P133" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="R133" t="n">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10323,33 +10323,33 @@
         <v>59</v>
       </c>
       <c r="J134" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K134" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L134" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M134" t="n">
         <v>1</v>
       </c>
       <c r="N134" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O134" t="n">
         <v>1</v>
       </c>
       <c r="P134" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R134" t="n">
-        <v>728</v>
+        <v>637</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10397,25 +10397,25 @@
         <v>87</v>
       </c>
       <c r="J135" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K135" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L135" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M135" t="n">
         <v>3</v>
       </c>
       <c r="N135" t="n">
+        <v>7</v>
+      </c>
+      <c r="O135" t="n">
         <v>8</v>
       </c>
-      <c r="O135" t="n">
-        <v>7</v>
-      </c>
       <c r="P135" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         </is>
       </c>
       <c r="R135" t="n">
-        <v>910</v>
+        <v>688</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10468,39 +10468,39 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J136" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K136" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="L136" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="M136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N136" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P136" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R136" t="n">
-        <v>721</v>
+        <v>791</v>
       </c>
       <c r="S136" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10542,7 +10542,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J137" t="n">
         <v>89</v>
@@ -10551,27 +10551,27 @@
         <v>17</v>
       </c>
       <c r="L137" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M137" t="n">
         <v>3</v>
       </c>
       <c r="N137" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O137" t="n">
         <v>5</v>
       </c>
       <c r="P137" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R137" t="n">
-        <v>941</v>
+        <v>703</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10619,33 +10619,33 @@
         <v>83</v>
       </c>
       <c r="J138" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K138" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L138" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="M138" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N138" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O138" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P138" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R138" t="n">
-        <v>945</v>
+        <v>806</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10693,33 +10693,33 @@
         <v>54</v>
       </c>
       <c r="J139" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K139" t="n">
         <v>17</v>
       </c>
       <c r="L139" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M139" t="n">
+        <v>2</v>
+      </c>
+      <c r="N139" t="n">
+        <v>8</v>
+      </c>
+      <c r="O139" t="n">
         <v>3</v>
       </c>
-      <c r="N139" t="n">
-        <v>10</v>
-      </c>
-      <c r="O139" t="n">
-        <v>5</v>
-      </c>
       <c r="P139" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R139" t="n">
-        <v>877</v>
+        <v>809</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -10755,7 +10755,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10767,36 +10767,36 @@
         <v>64</v>
       </c>
       <c r="J140" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K140" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L140" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M140" t="n">
         <v>5</v>
       </c>
       <c r="N140" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O140" t="n">
         <v>10</v>
       </c>
       <c r="P140" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R140" t="n">
-        <v>910</v>
+        <v>673</v>
       </c>
       <c r="S140" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10841,33 +10841,33 @@
         <v>79</v>
       </c>
       <c r="J141" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K141" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L141" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M141" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N141" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O141" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P141" t="n">
         <v>17</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>1/5/1 17:00 LMT</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R141" t="n">
-        <v>937</v>
+        <v>846</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -10912,36 +10912,36 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J142" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K142" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L142" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M142" t="n">
         <v>3</v>
       </c>
       <c r="N142" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O142" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P142" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R142" t="n">
-        <v>955</v>
+        <v>857</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10986,39 +10986,39 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J143" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K143" t="n">
         <v>24</v>
       </c>
       <c r="L143" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="M143" t="n">
         <v>1</v>
       </c>
       <c r="N143" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O143" t="n">
         <v>1</v>
       </c>
       <c r="P143" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R143" t="n">
-        <v>848</v>
+        <v>804</v>
       </c>
       <c r="S143" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11060,39 +11060,39 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J144" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K144" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L144" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="M144" t="n">
         <v>2</v>
       </c>
       <c r="N144" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O144" t="n">
         <v>3</v>
       </c>
       <c r="P144" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R144" t="n">
-        <v>740</v>
+        <v>710</v>
       </c>
       <c r="S144" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -11134,28 +11134,28 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J145" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K145" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L145" t="n">
         <v>32</v>
       </c>
       <c r="M145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N145" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O145" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P145" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         </is>
       </c>
       <c r="R145" t="n">
-        <v>941</v>
+        <v>812</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11208,39 +11208,39 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J146" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K146" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L146" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="M146" t="n">
+        <v>3</v>
+      </c>
+      <c r="N146" t="n">
+        <v>7</v>
+      </c>
+      <c r="O146" t="n">
         <v>5</v>
       </c>
-      <c r="N146" t="n">
+      <c r="P146" t="n">
         <v>9</v>
       </c>
-      <c r="O146" t="n">
-        <v>7</v>
-      </c>
-      <c r="P146" t="n">
-        <v>13</v>
-      </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R146" t="n">
-        <v>932</v>
+        <v>795</v>
       </c>
       <c r="S146" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11282,16 +11282,16 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J147" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K147" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L147" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M147" t="n">
         <v>6</v>
@@ -11300,18 +11300,18 @@
         <v>8</v>
       </c>
       <c r="O147" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P147" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R147" t="n">
-        <v>961</v>
+        <v>740</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11356,39 +11356,39 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J148" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K148" t="n">
         <v>24</v>
       </c>
       <c r="L148" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="M148" t="n">
         <v>2</v>
       </c>
       <c r="N148" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O148" t="n">
         <v>3</v>
       </c>
       <c r="P148" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R148" t="n">
-        <v>839</v>
+        <v>807</v>
       </c>
       <c r="S148" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11430,28 +11430,28 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J149" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K149" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L149" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="M149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N149" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O149" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P149" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="R149" t="n">
-        <v>947</v>
+        <v>677</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11504,36 +11504,36 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J150" t="n">
         <v>90</v>
       </c>
       <c r="K150" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L150" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N150" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P150" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R150" t="n">
-        <v>940</v>
+        <v>650</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11578,28 +11578,28 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J151" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K151" t="n">
         <v>14</v>
       </c>
       <c r="L151" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M151" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N151" t="n">
         <v>14</v>
       </c>
       <c r="O151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P151" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="R151" t="n">
-        <v>939</v>
+        <v>789</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11655,13 +11655,13 @@
         <v>84</v>
       </c>
       <c r="J152" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K152" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L152" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M152" t="n">
         <v>1</v>
@@ -11670,18 +11670,18 @@
         <v>8</v>
       </c>
       <c r="O152" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P152" t="n">
         <v>21</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R152" t="n">
-        <v>945</v>
+        <v>758</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -11717,7 +11717,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11732,22 +11732,22 @@
         <v>107</v>
       </c>
       <c r="K153" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L153" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M153" t="n">
         <v>2</v>
       </c>
       <c r="N153" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O153" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P153" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         </is>
       </c>
       <c r="R153" t="n">
-        <v>944</v>
+        <v>801</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11806,30 +11806,30 @@
         <v>83</v>
       </c>
       <c r="K154" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L154" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M154" t="n">
         <v>2</v>
       </c>
       <c r="N154" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O154" t="n">
         <v>3</v>
       </c>
       <c r="P154" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R154" t="n">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -11865,7 +11865,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11874,36 +11874,36 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J155" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K155" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L155" t="n">
         <v>46</v>
       </c>
       <c r="M155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N155" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P155" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R155" t="n">
-        <v>702</v>
+        <v>661</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11948,39 +11948,39 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J156" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K156" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L156" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N156" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P156" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R156" t="n">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="S156" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12031,19 +12031,19 @@
         <v>16</v>
       </c>
       <c r="L157" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M157" t="n">
         <v>1</v>
       </c>
       <c r="N157" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O157" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P157" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         </is>
       </c>
       <c r="R157" t="n">
-        <v>950</v>
+        <v>710</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>8/25/2026</t>
+          <t>8/26/2026</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12096,36 +12096,36 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J158" t="n">
         <v>92</v>
       </c>
       <c r="K158" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L158" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="M158" t="n">
         <v>3</v>
       </c>
       <c r="N158" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O158" t="n">
         <v>5</v>
       </c>
       <c r="P158" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R158" t="n">
-        <v>934</v>
+        <v>802</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>

--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -555,33 +555,33 @@
         <v>52</v>
       </c>
       <c r="J2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L2" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>789</v>
+        <v>900</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K3" t="n">
         <v>15</v>
@@ -641,21 +641,21 @@
         <v>2</v>
       </c>
       <c r="N3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O3" t="n">
         <v>8</v>
       </c>
-      <c r="O3" t="n">
-        <v>6</v>
-      </c>
       <c r="P3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>780</v>
+        <v>813</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -703,33 +703,33 @@
         <v>59</v>
       </c>
       <c r="J4" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K4" t="n">
         <v>16</v>
       </c>
       <c r="L4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
         <v>7</v>
       </c>
       <c r="P4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>769</v>
+        <v>928</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -777,36 +777,36 @@
         <v>57</v>
       </c>
       <c r="J5" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M5" t="n">
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>688</v>
+        <v>705</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -848,36 +848,36 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J6" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L6" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>808</v>
+        <v>855</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -922,16 +922,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K7" t="n">
         <v>34</v>
       </c>
       <c r="L7" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -947,14 +947,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>789</v>
+        <v>868</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1</v>
+        <v>0.28</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -996,39 +996,39 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J8" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L8" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M8" t="n">
         <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O8" t="n">
         <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>855</v>
+        <v>953</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1073,36 +1073,36 @@
         <v>58</v>
       </c>
       <c r="J9" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L9" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>5</v>
       </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>7</v>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>719</v>
+        <v>787</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1144,13 +1144,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J10" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
         <v>27</v>
@@ -1159,21 +1159,21 @@
         <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
         <v>9</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>847</v>
+        <v>871</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J11" t="n">
         <v>107</v>
@@ -1227,19 +1227,19 @@
         <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>860</v>
+        <v>919</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1295,25 +1295,25 @@
         <v>59</v>
       </c>
       <c r="J12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M12" t="n">
         <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>852</v>
+        <v>950</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1366,28 +1366,28 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J13" t="n">
         <v>86</v>
       </c>
       <c r="K13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>773</v>
+        <v>723</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J14" t="n">
         <v>81</v>
@@ -1449,7 +1449,7 @@
         <v>24</v>
       </c>
       <c r="L14" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
@@ -1465,14 +1465,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1/4/1 17:00 LMT</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>680</v>
+        <v>732</v>
       </c>
       <c r="S14" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1514,36 +1514,36 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J15" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L15" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>01</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>842</v>
+        <v>935</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1588,36 +1588,36 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J16" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
         <v>11</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>722</v>
+        <v>847</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
         <v>81</v>
       </c>
       <c r="K17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L17" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="M17" t="n">
         <v>3</v>
@@ -1687,11 +1687,11 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1736,28 +1736,28 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J18" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>750</v>
+        <v>816</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1813,36 +1813,36 @@
         <v>72</v>
       </c>
       <c r="J19" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1/5/1 17:00 LMT</t>
+          <t>1/4/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>742</v>
+        <v>834</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1887,25 +1887,25 @@
         <v>69</v>
       </c>
       <c r="J20" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L20" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
         <v>6</v>
       </c>
       <c r="O20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>771</v>
+        <v>946</v>
       </c>
       <c r="S20" t="n">
         <v>0.02</v>
@@ -1961,36 +1961,36 @@
         <v>70</v>
       </c>
       <c r="J21" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L21" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>810</v>
+        <v>927</v>
       </c>
       <c r="S21" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2035,33 +2035,33 @@
         <v>71</v>
       </c>
       <c r="J22" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L22" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>780</v>
+        <v>942</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2106,36 +2106,36 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J23" t="n">
         <v>110</v>
       </c>
       <c r="K23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L23" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P23" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>831</v>
+        <v>894</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2186,30 +2186,30 @@
         <v>106</v>
       </c>
       <c r="K24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L24" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2257,36 +2257,36 @@
         <v>78</v>
       </c>
       <c r="J25" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L25" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>793</v>
+        <v>901</v>
       </c>
       <c r="S25" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J26" t="n">
         <v>96</v>
@@ -2337,27 +2337,27 @@
         <v>18</v>
       </c>
       <c r="L26" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="M26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>8</v>
+      </c>
+      <c r="O26" t="n">
         <v>3</v>
       </c>
-      <c r="N26" t="n">
-        <v>7</v>
-      </c>
-      <c r="O26" t="n">
-        <v>5</v>
-      </c>
       <c r="P26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2402,28 +2402,28 @@
         </is>
       </c>
       <c r="I27" t="n">
+        <v>65</v>
+      </c>
+      <c r="J27" t="n">
+        <v>94</v>
+      </c>
+      <c r="K27" t="n">
+        <v>19</v>
+      </c>
+      <c r="L27" t="n">
         <v>66</v>
       </c>
-      <c r="J27" t="n">
-        <v>93</v>
-      </c>
-      <c r="K27" t="n">
-        <v>20</v>
-      </c>
-      <c r="L27" t="n">
-        <v>68</v>
-      </c>
       <c r="M27" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>9</v>
+      </c>
+      <c r="O27" t="n">
         <v>5</v>
       </c>
-      <c r="N27" t="n">
-        <v>16</v>
-      </c>
-      <c r="O27" t="n">
-        <v>7</v>
-      </c>
       <c r="P27" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>802</v>
+        <v>899</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2479,33 +2479,33 @@
         <v>88</v>
       </c>
       <c r="J28" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L28" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O28" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P28" t="n">
         <v>17</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1/7/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>739</v>
+        <v>868</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J29" t="n">
         <v>75</v>
       </c>
       <c r="K29" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L29" t="n">
         <v>86</v>
@@ -2565,24 +2565,24 @@
         <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>720</v>
+        <v>747</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2624,36 +2624,36 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J30" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K30" t="n">
         <v>20</v>
       </c>
       <c r="L30" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O30" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P30" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1/6/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>788</v>
+        <v>883</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2701,13 +2701,13 @@
         <v>57</v>
       </c>
       <c r="J31" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L31" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -2719,15 +2719,15 @@
         <v>6</v>
       </c>
       <c r="P31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>774</v>
+        <v>818</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -2775,36 +2775,36 @@
         <v>59</v>
       </c>
       <c r="J32" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K32" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L32" t="n">
         <v>60</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
         <v>7</v>
       </c>
       <c r="O32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P32" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>741</v>
+        <v>814</v>
       </c>
       <c r="S32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         <v>80</v>
       </c>
       <c r="K33" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="M33" t="n">
         <v>1</v>
@@ -2871,14 +2871,14 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="S33" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2920,36 +2920,36 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J34" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M34" t="n">
         <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P34" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>792</v>
+        <v>870</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -2994,36 +2994,36 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J35" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L35" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="M35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" t="n">
+        <v>9</v>
+      </c>
+      <c r="O35" t="n">
         <v>5</v>
       </c>
-      <c r="N35" t="n">
-        <v>8</v>
-      </c>
-      <c r="O35" t="n">
-        <v>7</v>
-      </c>
       <c r="P35" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>828</v>
+        <v>943</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3071,36 +3071,36 @@
         <v>58</v>
       </c>
       <c r="J36" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K36" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L36" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1/8/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>735</v>
+        <v>775</v>
       </c>
       <c r="S36" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3142,16 +3142,16 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J37" t="n">
         <v>82</v>
       </c>
       <c r="K37" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L37" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M37" t="n">
         <v>3</v>
@@ -3167,14 +3167,14 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>782</v>
+        <v>917</v>
       </c>
       <c r="S37" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3216,39 +3216,39 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J38" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L38" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="M38" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N38" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O38" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="P38" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1/6/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>875</v>
+        <v>817</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -3296,33 +3296,33 @@
         <v>93</v>
       </c>
       <c r="K39" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L39" t="n">
         <v>37</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O39" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P39" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>01</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>794</v>
+        <v>897</v>
       </c>
       <c r="S39" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J40" t="n">
         <v>92</v>
@@ -3373,7 +3373,7 @@
         <v>16</v>
       </c>
       <c r="L40" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M40" t="n">
         <v>3</v>
@@ -3385,18 +3385,18 @@
         <v>11</v>
       </c>
       <c r="P40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1/7/1 17:00 LMT</t>
+          <t>1/8/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>674</v>
+        <v>881</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -3441,10 +3441,10 @@
         <v>55</v>
       </c>
       <c r="J41" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L41" t="n">
         <v>50</v>
@@ -3463,11 +3463,11 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -3512,13 +3512,13 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J42" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L42" t="n">
         <v>89</v>
@@ -3527,21 +3527,21 @@
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>763</v>
+        <v>913</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3595,19 +3595,19 @@
         <v>28</v>
       </c>
       <c r="L43" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="M43" t="n">
         <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O43" t="n">
         <v>5</v>
       </c>
       <c r="P43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>771</v>
+        <v>852</v>
       </c>
       <c r="S43" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3663,25 +3663,25 @@
         <v>57</v>
       </c>
       <c r="J44" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L44" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O44" t="n">
         <v>6</v>
       </c>
       <c r="P44" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>645</v>
+        <v>852</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -3737,25 +3737,25 @@
         <v>69</v>
       </c>
       <c r="J45" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K45" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L45" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M45" t="n">
+        <v>3</v>
+      </c>
+      <c r="N45" t="n">
+        <v>13</v>
+      </c>
+      <c r="O45" t="n">
         <v>5</v>
       </c>
-      <c r="N45" t="n">
-        <v>11</v>
-      </c>
-      <c r="O45" t="n">
-        <v>7</v>
-      </c>
       <c r="P45" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="R45" t="n">
-        <v>846</v>
+        <v>920</v>
       </c>
       <c r="S45" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J46" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K46" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L46" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
@@ -3826,21 +3826,21 @@
         <v>5</v>
       </c>
       <c r="O46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R46" t="n">
-        <v>778</v>
+        <v>948</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -3885,33 +3885,33 @@
         <v>52</v>
       </c>
       <c r="J47" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K47" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L47" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>599</v>
+        <v>699</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -3956,36 +3956,36 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J48" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K48" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L48" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N48" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1/7/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>705</v>
+        <v>897</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>88</v>
       </c>
       <c r="K49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L49" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M49" t="n">
         <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>691</v>
+        <v>638</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4107,33 +4107,33 @@
         <v>66</v>
       </c>
       <c r="J50" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K50" t="n">
         <v>19</v>
       </c>
       <c r="L50" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M50" t="n">
+        <v>2</v>
+      </c>
+      <c r="N50" t="n">
+        <v>13</v>
+      </c>
+      <c r="O50" t="n">
         <v>3</v>
       </c>
-      <c r="N50" t="n">
-        <v>14</v>
-      </c>
-      <c r="O50" t="n">
-        <v>5</v>
-      </c>
       <c r="P50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>768</v>
+        <v>658</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -4181,33 +4181,33 @@
         <v>88</v>
       </c>
       <c r="J51" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K51" t="n">
         <v>19</v>
       </c>
       <c r="L51" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="M51" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N51" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O51" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P51" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1/7/1 17:00 LMT</t>
+          <t>1/6/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R51" t="n">
-        <v>788</v>
+        <v>910</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -4255,13 +4255,13 @@
         <v>59</v>
       </c>
       <c r="J52" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K52" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L52" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="M52" t="n">
         <v>1</v>
@@ -4277,14 +4277,14 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>727</v>
+        <v>828</v>
       </c>
       <c r="S52" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -4329,33 +4329,33 @@
         <v>80</v>
       </c>
       <c r="J53" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L53" t="n">
         <v>29</v>
       </c>
       <c r="M53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R53" t="n">
-        <v>851</v>
+        <v>899</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -4400,36 +4400,36 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J54" t="n">
         <v>112</v>
       </c>
       <c r="K54" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L54" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
+        <v>11</v>
+      </c>
+      <c r="O54" t="n">
         <v>6</v>
       </c>
-      <c r="O54" t="n">
-        <v>5</v>
-      </c>
       <c r="P54" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R54" t="n">
-        <v>854</v>
+        <v>899</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J55" t="n">
         <v>102</v>
@@ -4483,27 +4483,27 @@
         <v>14</v>
       </c>
       <c r="L55" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N55" t="n">
         <v>14</v>
       </c>
       <c r="O55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>763</v>
+        <v>710</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -4551,13 +4551,13 @@
         <v>53</v>
       </c>
       <c r="J56" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K56" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L56" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="M56" t="n">
         <v>1</v>
@@ -4573,11 +4573,11 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>768</v>
+        <v>790</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J57" t="n">
         <v>87</v>
@@ -4631,30 +4631,30 @@
         <v>19</v>
       </c>
       <c r="L57" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O57" t="n">
         <v>3</v>
       </c>
       <c r="P57" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>660</v>
+        <v>734</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -4699,36 +4699,36 @@
         <v>58</v>
       </c>
       <c r="J58" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K58" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L58" t="n">
         <v>50</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O58" t="n">
         <v>6</v>
       </c>
       <c r="P58" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>548</v>
+        <v>689</v>
       </c>
       <c r="S58" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -4770,28 +4770,28 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J59" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K59" t="n">
         <v>14</v>
       </c>
       <c r="L59" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O59" t="n">
         <v>3</v>
       </c>
       <c r="P59" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>746</v>
+        <v>834</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -4850,30 +4850,30 @@
         <v>94</v>
       </c>
       <c r="K60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L60" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M60" t="n">
         <v>6</v>
       </c>
       <c r="N60" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O60" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P60" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R60" t="n">
-        <v>775</v>
+        <v>917</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -4921,7 +4921,7 @@
         <v>73</v>
       </c>
       <c r="J61" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K61" t="n">
         <v>12</v>
@@ -4939,15 +4939,15 @@
         <v>5</v>
       </c>
       <c r="P61" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>865</v>
+        <v>925</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -4995,25 +4995,25 @@
         <v>56</v>
       </c>
       <c r="J62" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K62" t="n">
         <v>21</v>
       </c>
       <c r="L62" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>653</v>
+        <v>751</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -5066,36 +5066,36 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J63" t="n">
         <v>117</v>
       </c>
       <c r="K63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L63" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M63" t="n">
         <v>1</v>
       </c>
       <c r="N63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R63" t="n">
-        <v>701</v>
+        <v>877</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -5149,7 +5149,7 @@
         <v>17</v>
       </c>
       <c r="L64" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
@@ -5165,11 +5165,11 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R64" t="n">
-        <v>731</v>
+        <v>821</v>
       </c>
       <c r="S64" t="n">
         <v>0.02</v>
@@ -5229,13 +5229,13 @@
         <v>2</v>
       </c>
       <c r="N65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O65" t="n">
         <v>3</v>
       </c>
       <c r="P65" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>713</v>
+        <v>816</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -5288,36 +5288,36 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J66" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K66" t="n">
+        <v>16</v>
+      </c>
+      <c r="L66" t="n">
+        <v>48</v>
+      </c>
+      <c r="M66" t="n">
+        <v>3</v>
+      </c>
+      <c r="N66" t="n">
+        <v>10</v>
+      </c>
+      <c r="O66" t="n">
+        <v>10</v>
+      </c>
+      <c r="P66" t="n">
         <v>18</v>
       </c>
-      <c r="L66" t="n">
-        <v>52</v>
-      </c>
-      <c r="M66" t="n">
-        <v>2</v>
-      </c>
-      <c r="N66" t="n">
-        <v>5</v>
-      </c>
-      <c r="O66" t="n">
-        <v>7</v>
-      </c>
-      <c r="P66" t="n">
-        <v>14</v>
-      </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R66" t="n">
-        <v>843</v>
+        <v>920</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5362,28 +5362,28 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J67" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K67" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L67" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M67" t="n">
         <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O67" t="n">
         <v>5</v>
       </c>
       <c r="P67" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>697</v>
+        <v>911</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>88</v>
       </c>
       <c r="K68" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L68" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
         <v>9</v>
@@ -5457,18 +5457,18 @@
         <v>8</v>
       </c>
       <c r="P68" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>785</v>
+        <v>923</v>
       </c>
       <c r="S68" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5519,27 +5519,27 @@
         <v>13</v>
       </c>
       <c r="L69" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M69" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N69" t="n">
+        <v>10</v>
+      </c>
+      <c r="O69" t="n">
         <v>9</v>
       </c>
-      <c r="O69" t="n">
-        <v>11</v>
-      </c>
       <c r="P69" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>797</v>
+        <v>913</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -5584,36 +5584,36 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J70" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K70" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L70" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M70" t="n">
         <v>6</v>
       </c>
       <c r="N70" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R70" t="n">
-        <v>796</v>
+        <v>832</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -5658,19 +5658,19 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J71" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K71" t="n">
         <v>15</v>
       </c>
       <c r="L71" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="M71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N71" t="n">
         <v>13</v>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -5732,36 +5732,36 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J72" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K72" t="n">
         <v>17</v>
       </c>
       <c r="L72" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>744</v>
+        <v>871</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -5809,22 +5809,22 @@
         <v>55</v>
       </c>
       <c r="J73" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K73" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L73" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="M73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N73" t="n">
         <v>5</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P73" t="n">
         <v>7</v>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>710</v>
+        <v>739</v>
       </c>
       <c r="S73" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5883,13 +5883,13 @@
         <v>54</v>
       </c>
       <c r="J74" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K74" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L74" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="M74" t="n">
         <v>1</v>
@@ -5909,10 +5909,10 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>800</v>
+        <v>784</v>
       </c>
       <c r="S74" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -5957,33 +5957,33 @@
         <v>65</v>
       </c>
       <c r="J75" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K75" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L75" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="M75" t="n">
         <v>2</v>
       </c>
       <c r="N75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O75" t="n">
         <v>3</v>
       </c>
       <c r="P75" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R75" t="n">
-        <v>790</v>
+        <v>944</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -6031,33 +6031,33 @@
         <v>59</v>
       </c>
       <c r="J76" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K76" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L76" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M76" t="n">
         <v>5</v>
       </c>
       <c r="N76" t="n">
+        <v>8</v>
+      </c>
+      <c r="O76" t="n">
         <v>7</v>
       </c>
-      <c r="O76" t="n">
-        <v>6</v>
-      </c>
       <c r="P76" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>1/8/1 17:00 LMT</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R76" t="n">
-        <v>644</v>
+        <v>787</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -6102,16 +6102,16 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J77" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K77" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L77" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M77" t="n">
         <v>2</v>
@@ -6120,10 +6120,10 @@
         <v>9</v>
       </c>
       <c r="O77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P77" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>783</v>
+        <v>888</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -6176,36 +6176,36 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J78" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K78" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L78" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" t="n">
+        <v>9</v>
+      </c>
+      <c r="O78" t="n">
         <v>2</v>
       </c>
-      <c r="N78" t="n">
-        <v>10</v>
-      </c>
-      <c r="O78" t="n">
-        <v>3</v>
-      </c>
       <c r="P78" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R78" t="n">
-        <v>736</v>
+        <v>783</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -6250,16 +6250,16 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J79" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K79" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L79" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         </is>
       </c>
       <c r="R79" t="n">
-        <v>712</v>
+        <v>879</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -6327,36 +6327,36 @@
         <v>61</v>
       </c>
       <c r="J80" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K80" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L80" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M80" t="n">
         <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O80" t="n">
         <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R80" t="n">
-        <v>686</v>
+        <v>762</v>
       </c>
       <c r="S80" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -6398,32 +6398,32 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J81" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K81" t="n">
         <v>21</v>
       </c>
       <c r="L81" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="M81" t="n">
         <v>2</v>
       </c>
       <c r="N81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O81" t="n">
         <v>3</v>
       </c>
       <c r="P81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R81" t="n">
@@ -6475,10 +6475,10 @@
         <v>59</v>
       </c>
       <c r="J82" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K82" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L82" t="n">
         <v>75</v>
@@ -6490,18 +6490,18 @@
         <v>3</v>
       </c>
       <c r="O82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P82" t="n">
         <v>13</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R82" t="n">
-        <v>756</v>
+        <v>711</v>
       </c>
       <c r="S82" t="n">
         <v>0.13</v>
@@ -6549,25 +6549,25 @@
         <v>70</v>
       </c>
       <c r="J83" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K83" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L83" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N83" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O83" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P83" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>789</v>
+        <v>906</v>
       </c>
       <c r="S83" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -6623,10 +6623,10 @@
         <v>65</v>
       </c>
       <c r="J84" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K84" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L84" t="n">
         <v>90</v>
@@ -6649,10 +6649,10 @@
         </is>
       </c>
       <c r="R84" t="n">
-        <v>839</v>
+        <v>941</v>
       </c>
       <c r="S84" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -6697,36 +6697,36 @@
         <v>57</v>
       </c>
       <c r="J85" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K85" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L85" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P85" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R85" t="n">
-        <v>789</v>
+        <v>811</v>
       </c>
       <c r="S85" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -6768,13 +6768,13 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J86" t="n">
         <v>68</v>
       </c>
       <c r="K86" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L86" t="n">
         <v>93</v>
@@ -6793,14 +6793,14 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R86" t="n">
-        <v>786</v>
+        <v>821</v>
       </c>
       <c r="S86" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -6842,16 +6842,16 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J87" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K87" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L87" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M87" t="n">
         <v>2</v>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="R87" t="n">
-        <v>847</v>
+        <v>940</v>
       </c>
       <c r="S87" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -6919,13 +6919,13 @@
         <v>66</v>
       </c>
       <c r="J88" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K88" t="n">
         <v>20</v>
       </c>
       <c r="L88" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M88" t="n">
         <v>1</v>
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="R88" t="n">
-        <v>729</v>
+        <v>766</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -6990,36 +6990,36 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J89" t="n">
         <v>113</v>
       </c>
       <c r="K89" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L89" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="M89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N89" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O89" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P89" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1/6/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R89" t="n">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -7067,33 +7067,33 @@
         <v>56</v>
       </c>
       <c r="J90" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K90" t="n">
         <v>18</v>
       </c>
       <c r="L90" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N90" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P90" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R90" t="n">
-        <v>612</v>
+        <v>655</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -7138,13 +7138,13 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J91" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K91" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L91" t="n">
         <v>37</v>
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>639</v>
+        <v>788</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -7212,28 +7212,28 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J92" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K92" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L92" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M92" t="n">
         <v>3</v>
       </c>
       <c r="N92" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O92" t="n">
         <v>5</v>
       </c>
       <c r="P92" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         </is>
       </c>
       <c r="R92" t="n">
-        <v>802</v>
+        <v>907</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -7286,36 +7286,36 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J93" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K93" t="n">
         <v>22</v>
       </c>
       <c r="L93" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P93" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R93" t="n">
-        <v>644</v>
+        <v>704</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -7360,36 +7360,36 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J94" t="n">
         <v>83</v>
       </c>
       <c r="K94" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L94" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M94" t="n">
         <v>5</v>
       </c>
       <c r="N94" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O94" t="n">
         <v>9</v>
       </c>
       <c r="P94" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R94" t="n">
-        <v>727</v>
+        <v>697</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -7440,30 +7440,30 @@
         <v>101</v>
       </c>
       <c r="K95" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L95" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M95" t="n">
         <v>2</v>
       </c>
       <c r="N95" t="n">
+        <v>5</v>
+      </c>
+      <c r="O95" t="n">
         <v>6</v>
       </c>
-      <c r="O95" t="n">
-        <v>7</v>
-      </c>
       <c r="P95" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R95" t="n">
-        <v>754</v>
+        <v>924</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -7508,36 +7508,36 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J96" t="n">
         <v>98</v>
       </c>
       <c r="K96" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L96" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="M96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O96" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P96" t="n">
         <v>21</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R96" t="n">
-        <v>732</v>
+        <v>799</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -7588,30 +7588,30 @@
         <v>88</v>
       </c>
       <c r="K97" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L97" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M97" t="n">
+        <v>2</v>
+      </c>
+      <c r="N97" t="n">
+        <v>8</v>
+      </c>
+      <c r="O97" t="n">
         <v>3</v>
       </c>
-      <c r="N97" t="n">
-        <v>10</v>
-      </c>
-      <c r="O97" t="n">
-        <v>5</v>
-      </c>
       <c r="P97" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R97" t="n">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -7656,28 +7656,28 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J98" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K98" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L98" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N98" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O98" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P98" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="R98" t="n">
-        <v>754</v>
+        <v>814</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -7730,28 +7730,28 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J99" t="n">
         <v>88</v>
       </c>
       <c r="K99" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L99" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M99" t="n">
         <v>1</v>
       </c>
       <c r="N99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O99" t="n">
         <v>3</v>
       </c>
       <c r="P99" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="R99" t="n">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -7813,19 +7813,19 @@
         <v>13</v>
       </c>
       <c r="L100" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M100" t="n">
         <v>3</v>
       </c>
       <c r="N100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P100" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="R100" t="n">
-        <v>709</v>
+        <v>915</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -7881,25 +7881,25 @@
         <v>70</v>
       </c>
       <c r="J101" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K101" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L101" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M101" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N101" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O101" t="n">
         <v>7</v>
       </c>
       <c r="P101" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="R101" t="n">
-        <v>647</v>
+        <v>767</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -7952,36 +7952,36 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J102" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K102" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L102" t="n">
         <v>83</v>
       </c>
       <c r="M102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N102" t="n">
         <v>5</v>
       </c>
       <c r="O102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P102" t="n">
         <v>7</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R102" t="n">
-        <v>800</v>
+        <v>892</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -8026,36 +8026,36 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J103" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K103" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L103" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M103" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N103" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O103" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P103" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R103" t="n">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -8100,7 +8100,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J104" t="n">
         <v>106</v>
@@ -8109,27 +8109,27 @@
         <v>11</v>
       </c>
       <c r="L104" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M104" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N104" t="n">
         <v>10</v>
       </c>
       <c r="O104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P104" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R104" t="n">
-        <v>791</v>
+        <v>761</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -8174,39 +8174,39 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J105" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K105" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L105" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M105" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N105" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O105" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P105" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R105" t="n">
-        <v>846</v>
+        <v>921</v>
       </c>
       <c r="S105" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -8251,33 +8251,33 @@
         <v>66</v>
       </c>
       <c r="J106" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K106" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L106" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N106" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O106" t="n">
         <v>3</v>
       </c>
       <c r="P106" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R106" t="n">
-        <v>688</v>
+        <v>825</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -8322,16 +8322,16 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J107" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K107" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L107" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M107" t="n">
         <v>1</v>
@@ -8343,15 +8343,15 @@
         <v>2</v>
       </c>
       <c r="P107" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R107" t="n">
-        <v>822</v>
+        <v>836</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -8399,36 +8399,36 @@
         <v>57</v>
       </c>
       <c r="J108" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K108" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L108" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="M108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P108" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R108" t="n">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="S108" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -8473,13 +8473,13 @@
         <v>62</v>
       </c>
       <c r="J109" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K109" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L109" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M109" t="n">
         <v>5</v>
@@ -8495,14 +8495,14 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R109" t="n">
-        <v>720</v>
+        <v>806</v>
       </c>
       <c r="S109" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -8547,16 +8547,16 @@
         <v>82</v>
       </c>
       <c r="J110" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K110" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L110" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="M110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N110" t="n">
         <v>7</v>
@@ -8565,15 +8565,15 @@
         <v>6</v>
       </c>
       <c r="P110" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R110" t="n">
-        <v>852</v>
+        <v>916</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -8618,36 +8618,36 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J111" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K111" t="n">
         <v>17</v>
       </c>
       <c r="L111" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M111" t="n">
+        <v>2</v>
+      </c>
+      <c r="N111" t="n">
+        <v>9</v>
+      </c>
+      <c r="O111" t="n">
         <v>3</v>
       </c>
-      <c r="N111" t="n">
-        <v>7</v>
-      </c>
-      <c r="O111" t="n">
-        <v>5</v>
-      </c>
       <c r="P111" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R111" t="n">
-        <v>851</v>
+        <v>779</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -8695,33 +8695,33 @@
         <v>65</v>
       </c>
       <c r="J112" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K112" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L112" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M112" t="n">
+        <v>2</v>
+      </c>
+      <c r="N112" t="n">
+        <v>9</v>
+      </c>
+      <c r="O112" t="n">
         <v>3</v>
       </c>
-      <c r="N112" t="n">
-        <v>10</v>
-      </c>
-      <c r="O112" t="n">
-        <v>5</v>
-      </c>
       <c r="P112" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R112" t="n">
-        <v>762</v>
+        <v>881</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -8766,36 +8766,36 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J113" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K113" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L113" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M113" t="n">
+        <v>1</v>
+      </c>
+      <c r="N113" t="n">
+        <v>9</v>
+      </c>
+      <c r="O113" t="n">
         <v>2</v>
       </c>
-      <c r="N113" t="n">
-        <v>7</v>
-      </c>
-      <c r="O113" t="n">
-        <v>3</v>
-      </c>
       <c r="P113" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R113" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -8843,33 +8843,33 @@
         <v>66</v>
       </c>
       <c r="J114" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K114" t="n">
         <v>15</v>
       </c>
       <c r="L114" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N114" t="n">
         <v>8</v>
       </c>
       <c r="O114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P114" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R114" t="n">
-        <v>824</v>
+        <v>861</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -8917,36 +8917,36 @@
         <v>63</v>
       </c>
       <c r="J115" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K115" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L115" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M115" t="n">
         <v>2</v>
       </c>
       <c r="N115" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O115" t="n">
         <v>3</v>
       </c>
       <c r="P115" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R115" t="n">
-        <v>692</v>
+        <v>808</v>
       </c>
       <c r="S115" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -8988,16 +8988,16 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J116" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K116" t="n">
         <v>26</v>
       </c>
       <c r="L116" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="M116" t="n">
         <v>3</v>
@@ -9006,21 +9006,21 @@
         <v>7</v>
       </c>
       <c r="O116" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P116" t="n">
         <v>16</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R116" t="n">
-        <v>812</v>
+        <v>923</v>
       </c>
       <c r="S116" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J117" t="n">
         <v>85</v>
@@ -9071,27 +9071,27 @@
         <v>20</v>
       </c>
       <c r="L117" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="M117" t="n">
         <v>3</v>
       </c>
       <c r="N117" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O117" t="n">
         <v>5</v>
       </c>
       <c r="P117" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R117" t="n">
-        <v>736</v>
+        <v>768</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -9136,36 +9136,36 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J118" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K118" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L118" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="M118" t="n">
+        <v>2</v>
+      </c>
+      <c r="N118" t="n">
+        <v>9</v>
+      </c>
+      <c r="O118" t="n">
         <v>3</v>
       </c>
-      <c r="N118" t="n">
-        <v>11</v>
-      </c>
-      <c r="O118" t="n">
-        <v>5</v>
-      </c>
       <c r="P118" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R118" t="n">
-        <v>804</v>
+        <v>923</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -9213,33 +9213,33 @@
         <v>60</v>
       </c>
       <c r="J119" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K119" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L119" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M119" t="n">
         <v>2</v>
       </c>
       <c r="N119" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O119" t="n">
         <v>3</v>
       </c>
       <c r="P119" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R119" t="n">
-        <v>808</v>
+        <v>836</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -9287,33 +9287,33 @@
         <v>60</v>
       </c>
       <c r="J120" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K120" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L120" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="M120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N120" t="n">
         <v>5</v>
       </c>
       <c r="O120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P120" t="n">
         <v>7</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R120" t="n">
-        <v>708</v>
+        <v>913</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -9358,39 +9358,39 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J121" t="n">
         <v>81</v>
       </c>
       <c r="K121" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L121" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M121" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P121" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>1/5/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R121" t="n">
-        <v>766</v>
+        <v>933</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>19</v>
       </c>
       <c r="L122" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M122" t="n">
         <v>2</v>
@@ -9450,21 +9450,21 @@
         <v>5</v>
       </c>
       <c r="O122" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P122" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R122" t="n">
-        <v>673</v>
+        <v>786</v>
       </c>
       <c r="S122" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -9506,28 +9506,28 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J123" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K123" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L123" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="M123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N123" t="n">
         <v>5</v>
       </c>
       <c r="O123" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P123" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="R123" t="n">
-        <v>839</v>
+        <v>915</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -9583,25 +9583,25 @@
         <v>72</v>
       </c>
       <c r="J124" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K124" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L124" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M124" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N124" t="n">
         <v>6</v>
       </c>
       <c r="O124" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P124" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -9609,10 +9609,10 @@
         </is>
       </c>
       <c r="R124" t="n">
-        <v>864</v>
+        <v>926</v>
       </c>
       <c r="S124" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -9654,36 +9654,36 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J125" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K125" t="n">
         <v>11</v>
       </c>
       <c r="L125" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M125" t="n">
         <v>5</v>
       </c>
       <c r="N125" t="n">
+        <v>11</v>
+      </c>
+      <c r="O125" t="n">
         <v>7</v>
       </c>
-      <c r="O125" t="n">
-        <v>9</v>
-      </c>
       <c r="P125" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R125" t="n">
-        <v>864</v>
+        <v>916</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -9728,13 +9728,13 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J126" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K126" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L126" t="n">
         <v>75</v>
@@ -9743,21 +9743,21 @@
         <v>3</v>
       </c>
       <c r="N126" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O126" t="n">
         <v>5</v>
       </c>
       <c r="P126" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R126" t="n">
-        <v>847</v>
+        <v>936</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -9802,36 +9802,36 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J127" t="n">
         <v>97</v>
       </c>
       <c r="K127" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L127" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="M127" t="n">
         <v>2</v>
       </c>
       <c r="N127" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O127" t="n">
         <v>3</v>
       </c>
       <c r="P127" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R127" t="n">
-        <v>860</v>
+        <v>936</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -9882,33 +9882,33 @@
         <v>81</v>
       </c>
       <c r="K128" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L128" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="M128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N128" t="n">
         <v>5</v>
       </c>
       <c r="O128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P128" t="n">
         <v>7</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R128" t="n">
-        <v>788</v>
+        <v>912</v>
       </c>
       <c r="S128" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -9950,16 +9950,16 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J129" t="n">
         <v>103</v>
       </c>
       <c r="K129" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L129" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="M129" t="n">
         <v>3</v>
@@ -9971,18 +9971,18 @@
         <v>7</v>
       </c>
       <c r="P129" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R129" t="n">
-        <v>813</v>
+        <v>912</v>
       </c>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -10027,25 +10027,25 @@
         <v>68</v>
       </c>
       <c r="J130" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K130" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L130" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N130" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O130" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P130" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -10053,10 +10053,10 @@
         </is>
       </c>
       <c r="R130" t="n">
-        <v>765</v>
+        <v>920</v>
       </c>
       <c r="S130" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -10098,36 +10098,36 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J131" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K131" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L131" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="M131" t="n">
         <v>2</v>
       </c>
       <c r="N131" t="n">
+        <v>7</v>
+      </c>
+      <c r="O131" t="n">
         <v>6</v>
       </c>
-      <c r="O131" t="n">
-        <v>5</v>
-      </c>
       <c r="P131" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R131" t="n">
-        <v>875</v>
+        <v>857</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -10172,36 +10172,36 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J132" t="n">
         <v>95</v>
       </c>
       <c r="K132" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L132" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M132" t="n">
+        <v>3</v>
+      </c>
+      <c r="N132" t="n">
+        <v>11</v>
+      </c>
+      <c r="O132" t="n">
         <v>5</v>
       </c>
-      <c r="N132" t="n">
+      <c r="P132" t="n">
         <v>16</v>
       </c>
-      <c r="O132" t="n">
-        <v>7</v>
-      </c>
-      <c r="P132" t="n">
-        <v>23</v>
-      </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R132" t="n">
-        <v>834</v>
+        <v>946</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -10246,36 +10246,36 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J133" t="n">
         <v>98</v>
       </c>
       <c r="K133" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L133" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M133" t="n">
         <v>1</v>
       </c>
       <c r="N133" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O133" t="n">
         <v>2</v>
       </c>
       <c r="P133" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R133" t="n">
-        <v>786</v>
+        <v>799</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -10320,16 +10320,16 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J134" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K134" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L134" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M134" t="n">
         <v>1</v>
@@ -10345,11 +10345,11 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>1/3/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R134" t="n">
-        <v>637</v>
+        <v>824</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -10394,36 +10394,36 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J135" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K135" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L135" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M135" t="n">
         <v>3</v>
       </c>
       <c r="N135" t="n">
+        <v>9</v>
+      </c>
+      <c r="O135" t="n">
         <v>7</v>
-      </c>
-      <c r="O135" t="n">
-        <v>8</v>
       </c>
       <c r="P135" t="n">
         <v>18</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R135" t="n">
-        <v>688</v>
+        <v>817</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -10468,16 +10468,16 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J136" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K136" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L136" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="M136" t="n">
         <v>3</v>
@@ -10497,10 +10497,10 @@
         </is>
       </c>
       <c r="R136" t="n">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="S136" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J137" t="n">
         <v>89</v>
@@ -10551,7 +10551,7 @@
         <v>17</v>
       </c>
       <c r="L137" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M137" t="n">
         <v>3</v>
@@ -10563,15 +10563,15 @@
         <v>5</v>
       </c>
       <c r="P137" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R137" t="n">
-        <v>703</v>
+        <v>838</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -10619,13 +10619,13 @@
         <v>83</v>
       </c>
       <c r="J138" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K138" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L138" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M138" t="n">
         <v>5</v>
@@ -10634,18 +10634,18 @@
         <v>10</v>
       </c>
       <c r="O138" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P138" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R138" t="n">
-        <v>806</v>
+        <v>845</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -10690,36 +10690,36 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J139" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K139" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L139" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M139" t="n">
         <v>2</v>
       </c>
       <c r="N139" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O139" t="n">
         <v>3</v>
       </c>
       <c r="P139" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R139" t="n">
-        <v>809</v>
+        <v>941</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -10764,28 +10764,28 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J140" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K140" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L140" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="M140" t="n">
         <v>5</v>
       </c>
       <c r="N140" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O140" t="n">
         <v>10</v>
       </c>
       <c r="P140" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -10793,10 +10793,10 @@
         </is>
       </c>
       <c r="R140" t="n">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="S140" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -10841,33 +10841,33 @@
         <v>79</v>
       </c>
       <c r="J141" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K141" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L141" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M141" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N141" t="n">
         <v>10</v>
       </c>
       <c r="O141" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P141" t="n">
         <v>17</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R141" t="n">
-        <v>846</v>
+        <v>795</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -10912,36 +10912,36 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J142" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K142" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L142" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M142" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N142" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O142" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P142" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/7/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R142" t="n">
-        <v>857</v>
+        <v>918</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J143" t="n">
         <v>85</v>
@@ -10995,27 +10995,27 @@
         <v>24</v>
       </c>
       <c r="L143" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M143" t="n">
         <v>1</v>
       </c>
       <c r="N143" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O143" t="n">
         <v>1</v>
       </c>
       <c r="P143" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R143" t="n">
-        <v>804</v>
+        <v>939</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -11060,16 +11060,16 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J144" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K144" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L144" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="M144" t="n">
         <v>2</v>
@@ -11085,14 +11085,14 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R144" t="n">
-        <v>710</v>
+        <v>754</v>
       </c>
       <c r="S144" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -11134,36 +11134,36 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J145" t="n">
         <v>109</v>
       </c>
       <c r="K145" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L145" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M145" t="n">
         <v>3</v>
       </c>
       <c r="N145" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O145" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P145" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R145" t="n">
-        <v>812</v>
+        <v>910</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -11208,13 +11208,13 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J146" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K146" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L146" t="n">
         <v>75</v>
@@ -11233,14 +11233,14 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R146" t="n">
-        <v>795</v>
+        <v>922</v>
       </c>
       <c r="S146" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -11282,28 +11282,28 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J147" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K147" t="n">
         <v>15</v>
       </c>
       <c r="L147" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N147" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O147" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P147" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         </is>
       </c>
       <c r="R147" t="n">
-        <v>740</v>
+        <v>918</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -11356,16 +11356,16 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J148" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K148" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L148" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M148" t="n">
         <v>2</v>
@@ -11381,14 +11381,14 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R148" t="n">
-        <v>807</v>
+        <v>915</v>
       </c>
       <c r="S148" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J149" t="n">
         <v>94</v>
@@ -11439,7 +11439,7 @@
         <v>16</v>
       </c>
       <c r="L149" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M149" t="n">
         <v>2</v>
@@ -11448,7 +11448,7 @@
         <v>10</v>
       </c>
       <c r="O149" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P149" t="n">
         <v>23</v>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="R149" t="n">
-        <v>677</v>
+        <v>803</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -11504,28 +11504,28 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J150" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K150" t="n">
         <v>16</v>
       </c>
       <c r="L150" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M150" t="n">
         <v>1</v>
       </c>
       <c r="N150" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O150" t="n">
         <v>2</v>
       </c>
       <c r="P150" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         </is>
       </c>
       <c r="R150" t="n">
-        <v>650</v>
+        <v>801</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -11578,36 +11578,36 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J151" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K151" t="n">
         <v>14</v>
       </c>
       <c r="L151" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M151" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N151" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O151" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P151" t="n">
         <v>31</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R151" t="n">
-        <v>789</v>
+        <v>759</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -11652,36 +11652,36 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J152" t="n">
         <v>102</v>
       </c>
       <c r="K152" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L152" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M152" t="n">
         <v>1</v>
       </c>
       <c r="N152" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O152" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P152" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R152" t="n">
-        <v>758</v>
+        <v>846</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -11729,33 +11729,33 @@
         <v>72</v>
       </c>
       <c r="J153" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K153" t="n">
         <v>14</v>
       </c>
       <c r="L153" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N153" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O153" t="n">
         <v>5</v>
       </c>
       <c r="P153" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R153" t="n">
-        <v>801</v>
+        <v>851</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -11803,25 +11803,25 @@
         <v>57</v>
       </c>
       <c r="J154" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K154" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L154" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M154" t="n">
         <v>2</v>
       </c>
       <c r="N154" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O154" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P154" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         </is>
       </c>
       <c r="R154" t="n">
-        <v>698</v>
+        <v>568</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -11877,25 +11877,25 @@
         <v>60</v>
       </c>
       <c r="J155" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K155" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L155" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M155" t="n">
+        <v>2</v>
+      </c>
+      <c r="N155" t="n">
+        <v>5</v>
+      </c>
+      <c r="O155" t="n">
         <v>3</v>
       </c>
-      <c r="N155" t="n">
-        <v>3</v>
-      </c>
-      <c r="O155" t="n">
-        <v>5</v>
-      </c>
       <c r="P155" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -11903,10 +11903,10 @@
         </is>
       </c>
       <c r="R155" t="n">
-        <v>661</v>
+        <v>772</v>
       </c>
       <c r="S155" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -11951,13 +11951,13 @@
         <v>47</v>
       </c>
       <c r="J156" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K156" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L156" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="M156" t="n">
         <v>1</v>
@@ -11977,10 +11977,10 @@
         </is>
       </c>
       <c r="R156" t="n">
-        <v>800</v>
+        <v>892</v>
       </c>
       <c r="S156" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J157" t="n">
         <v>92</v>
@@ -12031,27 +12031,27 @@
         <v>16</v>
       </c>
       <c r="L157" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="M157" t="n">
         <v>1</v>
       </c>
       <c r="N157" t="n">
+        <v>6</v>
+      </c>
+      <c r="O157" t="n">
         <v>5</v>
       </c>
-      <c r="O157" t="n">
-        <v>6</v>
-      </c>
       <c r="P157" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R157" t="n">
-        <v>710</v>
+        <v>735</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -12096,36 +12096,36 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J158" t="n">
         <v>92</v>
       </c>
       <c r="K158" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L158" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="M158" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N158" t="n">
         <v>8</v>
       </c>
       <c r="O158" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P158" t="n">
         <v>11</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R158" t="n">
-        <v>802</v>
+        <v>865</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>

--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -552,39 +552,39 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K2" t="n">
         <v>27</v>
       </c>
       <c r="L2" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
         <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
         <v>17</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>900</v>
+        <v>663</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -626,36 +626,36 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J3" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P3" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>813</v>
+        <v>877</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -691,7 +691,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -706,10 +706,10 @@
         <v>90</v>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -725,11 +725,11 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>928</v>
+        <v>777</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -774,39 +774,39 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J5" t="n">
         <v>81</v>
       </c>
       <c r="K5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L5" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>705</v>
+        <v>751</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -854,30 +854,30 @@
         <v>111</v>
       </c>
       <c r="K6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L6" t="n">
         <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
         <v>19</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>855</v>
+        <v>875</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -925,36 +925,36 @@
         <v>54</v>
       </c>
       <c r="J7" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>868</v>
+        <v>783</v>
       </c>
       <c r="S7" t="n">
-        <v>0.28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -996,39 +996,39 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J8" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
         <v>11</v>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>953</v>
+        <v>851</v>
       </c>
       <c r="S8" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1070,16 +1070,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J9" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1095,14 +1095,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1144,39 +1144,39 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J10" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>871</v>
+        <v>849</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1218,28 +1218,28 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J11" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L11" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>919</v>
+        <v>874</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1295,33 +1295,33 @@
         <v>59</v>
       </c>
       <c r="J12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M12" t="n">
         <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>950</v>
+        <v>794</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1366,28 +1366,28 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J13" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K13" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L13" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P13" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>723</v>
+        <v>619</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1449,30 +1449,30 @@
         <v>24</v>
       </c>
       <c r="L14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
         <v>5</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1/3/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1517,36 +1517,36 @@
         <v>66</v>
       </c>
       <c r="J15" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L15" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="M15" t="n">
         <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
         <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>935</v>
+        <v>867</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1588,36 +1588,36 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J16" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K16" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L16" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>847</v>
+        <v>641</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1671,7 +1671,7 @@
         <v>23</v>
       </c>
       <c r="L17" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M17" t="n">
         <v>3</v>
@@ -1687,14 +1687,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1739,33 +1739,33 @@
         <v>64</v>
       </c>
       <c r="J18" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L18" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>816</v>
+        <v>608</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1810,39 +1810,39 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J19" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K19" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L19" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="M19" t="n">
         <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O19" t="n">
         <v>14</v>
       </c>
       <c r="P19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1/4/1 17:00 LMT</t>
+          <t>01</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>834</v>
+        <v>788</v>
       </c>
       <c r="S19" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1884,25 +1884,25 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J20" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L20" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P20" t="n">
         <v>15</v>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>946</v>
+        <v>806</v>
       </c>
       <c r="S20" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1958,36 +1958,36 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J21" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L21" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P21" t="n">
         <v>19</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>927</v>
+        <v>797</v>
       </c>
       <c r="S21" t="n">
         <v>0.01</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2032,13 +2032,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J22" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K22" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L22" t="n">
         <v>54</v>
@@ -2053,18 +2053,18 @@
         <v>7</v>
       </c>
       <c r="P22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>942</v>
+        <v>844</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J23" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K23" t="n">
         <v>16</v>
@@ -2121,21 +2121,21 @@
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>894</v>
+        <v>795</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2183,19 +2183,19 @@
         <v>74</v>
       </c>
       <c r="J24" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L24" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
         <v>6</v>
@@ -2205,11 +2205,11 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>827</v>
+        <v>779</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2254,39 +2254,39 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J25" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L25" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
+        <v>8</v>
+      </c>
+      <c r="O25" t="n">
         <v>9</v>
-      </c>
-      <c r="O25" t="n">
-        <v>7</v>
       </c>
       <c r="P25" t="n">
         <v>16</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>901</v>
+        <v>750</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2328,36 +2328,36 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J26" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K26" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L26" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="M26" t="n">
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>815</v>
+        <v>799</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2405,25 +2405,25 @@
         <v>65</v>
       </c>
       <c r="J27" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K27" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L27" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>899</v>
+        <v>814</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2476,36 +2476,36 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J28" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="K28" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L28" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P28" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1/7/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2550,39 +2550,39 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J29" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K29" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L29" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="M29" t="n">
         <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>01</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>747</v>
+        <v>770</v>
       </c>
       <c r="S29" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2624,36 +2624,36 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J30" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L30" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M30" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>11</v>
+      </c>
+      <c r="O30" t="n">
         <v>8</v>
       </c>
-      <c r="N30" t="n">
-        <v>15</v>
-      </c>
-      <c r="O30" t="n">
-        <v>15</v>
-      </c>
       <c r="P30" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1/6/1 17:00 LMT</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2698,16 +2698,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J31" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K31" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L31" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -2723,14 +2723,14 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>818</v>
+        <v>836</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2772,16 +2772,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J32" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K32" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L32" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="M32" t="n">
         <v>2</v>
@@ -2793,7 +2793,7 @@
         <v>7</v>
       </c>
       <c r="P32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>814</v>
+        <v>569</v>
       </c>
       <c r="S32" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2849,36 +2849,36 @@
         <v>52</v>
       </c>
       <c r="J33" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K33" t="n">
         <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
+        <v>5</v>
+      </c>
+      <c r="O33" t="n">
         <v>3</v>
       </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
       <c r="P33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>718</v>
+        <v>731</v>
       </c>
       <c r="S33" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2923,33 +2923,33 @@
         <v>66</v>
       </c>
       <c r="J34" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K34" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L34" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="M34" t="n">
         <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O34" t="n">
         <v>5</v>
       </c>
       <c r="P34" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>870</v>
+        <v>660</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2994,39 +2994,39 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J35" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K35" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L35" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N35" t="n">
         <v>9</v>
       </c>
       <c r="O35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P35" t="n">
         <v>13</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>943</v>
+        <v>803</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3071,13 +3071,13 @@
         <v>58</v>
       </c>
       <c r="J36" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K36" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L36" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
@@ -3093,14 +3093,14 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1/8/1 17:00 LMT</t>
+          <t>1/6/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3145,33 +3145,33 @@
         <v>55</v>
       </c>
       <c r="J37" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K37" t="n">
         <v>15</v>
       </c>
       <c r="L37" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M37" t="n">
         <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O37" t="n">
         <v>5</v>
       </c>
       <c r="P37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>917</v>
+        <v>780</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3219,36 +3219,36 @@
         <v>85</v>
       </c>
       <c r="J38" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K38" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L38" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M38" t="n">
+        <v>3</v>
+      </c>
+      <c r="N38" t="n">
         <v>8</v>
       </c>
-      <c r="N38" t="n">
-        <v>14</v>
-      </c>
       <c r="O38" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1/6/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>817</v>
+        <v>867</v>
       </c>
       <c r="S38" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3290,22 +3290,22 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J39" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K39" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L39" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="M39" t="n">
         <v>5</v>
       </c>
       <c r="N39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O39" t="n">
         <v>11</v>
@@ -3315,14 +3315,14 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>897</v>
+        <v>795</v>
       </c>
       <c r="S39" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3367,36 +3367,36 @@
         <v>67</v>
       </c>
       <c r="J40" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K40" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L40" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
         <v>11</v>
       </c>
       <c r="P40" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1/8/1 17:00 LMT</t>
+          <t>1/4/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>881</v>
+        <v>777</v>
       </c>
       <c r="S40" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3441,33 +3441,33 @@
         <v>55</v>
       </c>
       <c r="J41" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K41" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L41" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>14</v>
+      </c>
+      <c r="O41" t="n">
         <v>2</v>
       </c>
-      <c r="N41" t="n">
-        <v>10</v>
-      </c>
-      <c r="O41" t="n">
-        <v>3</v>
-      </c>
       <c r="P41" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>761</v>
+        <v>653</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J42" t="n">
         <v>91</v>
@@ -3521,27 +3521,27 @@
         <v>16</v>
       </c>
       <c r="L42" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M42" t="n">
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>913</v>
+        <v>806</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J43" t="n">
         <v>90</v>
@@ -3595,30 +3595,30 @@
         <v>28</v>
       </c>
       <c r="L43" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="M43" t="n">
         <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O43" t="n">
         <v>5</v>
       </c>
       <c r="P43" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>852</v>
+        <v>842</v>
       </c>
       <c r="S43" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3660,36 +3660,36 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J44" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K44" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L44" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="M44" t="n">
         <v>5</v>
       </c>
       <c r="N44" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O44" t="n">
         <v>6</v>
       </c>
       <c r="P44" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>852</v>
+        <v>654</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3737,33 +3737,33 @@
         <v>69</v>
       </c>
       <c r="J45" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K45" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L45" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N45" t="n">
         <v>13</v>
       </c>
       <c r="O45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P45" t="n">
         <v>17</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>920</v>
+        <v>828</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3811,25 +3811,25 @@
         <v>69</v>
       </c>
       <c r="J46" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K46" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L46" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
         <v>6</v>
       </c>
       <c r="P46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>948</v>
+        <v>873</v>
       </c>
       <c r="S46" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3885,33 +3885,33 @@
         <v>52</v>
       </c>
       <c r="J47" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K47" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L47" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>699</v>
+        <v>731</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3956,36 +3956,36 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J48" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K48" t="n">
         <v>19</v>
       </c>
       <c r="L48" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P48" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>1/7/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>897</v>
+        <v>865</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4033,25 +4033,25 @@
         <v>67</v>
       </c>
       <c r="J49" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K49" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M49" t="n">
         <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>638</v>
+        <v>732</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4107,36 +4107,36 @@
         <v>66</v>
       </c>
       <c r="J50" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K50" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L50" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N50" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P50" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4178,36 +4178,36 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J51" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K51" t="n">
+        <v>20</v>
+      </c>
+      <c r="L51" t="n">
+        <v>53</v>
+      </c>
+      <c r="M51" t="n">
+        <v>6</v>
+      </c>
+      <c r="N51" t="n">
+        <v>11</v>
+      </c>
+      <c r="O51" t="n">
+        <v>9</v>
+      </c>
+      <c r="P51" t="n">
         <v>19</v>
       </c>
-      <c r="L51" t="n">
-        <v>58</v>
-      </c>
-      <c r="M51" t="n">
-        <v>9</v>
-      </c>
-      <c r="N51" t="n">
-        <v>16</v>
-      </c>
-      <c r="O51" t="n">
-        <v>15</v>
-      </c>
-      <c r="P51" t="n">
-        <v>25</v>
-      </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1/6/1 17:00 LMT</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R51" t="n">
-        <v>910</v>
+        <v>884</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4252,39 +4252,39 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J52" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K52" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L52" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>828</v>
+        <v>787</v>
       </c>
       <c r="S52" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4326,39 +4326,39 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J53" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K53" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L53" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N53" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O53" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P53" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R53" t="n">
-        <v>899</v>
+        <v>821</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4400,36 +4400,36 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J54" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L54" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M54" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" t="n">
+        <v>7</v>
+      </c>
+      <c r="O54" t="n">
         <v>3</v>
       </c>
-      <c r="N54" t="n">
+      <c r="P54" t="n">
         <v>11</v>
       </c>
-      <c r="O54" t="n">
-        <v>6</v>
-      </c>
-      <c r="P54" t="n">
-        <v>17</v>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R54" t="n">
-        <v>899</v>
+        <v>779</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4474,22 +4474,22 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J55" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="K55" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L55" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
@@ -4499,11 +4499,11 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J56" t="n">
         <v>82</v>
@@ -4560,27 +4560,27 @@
         <v>72</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>790</v>
+        <v>772</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4622,28 +4622,28 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J57" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K57" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L57" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P57" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>734</v>
+        <v>679</v>
       </c>
       <c r="S57" t="n">
         <v>0.01</v>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4696,39 +4696,39 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J58" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K58" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L58" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M58" t="n">
         <v>5</v>
       </c>
       <c r="N58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O58" t="n">
         <v>6</v>
       </c>
       <c r="P58" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>689</v>
+        <v>705</v>
       </c>
       <c r="S58" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4773,33 +4773,33 @@
         <v>69</v>
       </c>
       <c r="J59" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K59" t="n">
+        <v>18</v>
+      </c>
+      <c r="L59" t="n">
+        <v>39</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2</v>
+      </c>
+      <c r="N59" t="n">
         <v>14</v>
       </c>
-      <c r="L59" t="n">
-        <v>35</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1</v>
-      </c>
-      <c r="N59" t="n">
-        <v>13</v>
-      </c>
       <c r="O59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P59" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R59" t="n">
-        <v>834</v>
+        <v>657</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4844,39 +4844,39 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J60" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K60" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L60" t="n">
+        <v>40</v>
+      </c>
+      <c r="M60" t="n">
+        <v>7</v>
+      </c>
+      <c r="N60" t="n">
+        <v>17</v>
+      </c>
+      <c r="O60" t="n">
+        <v>16</v>
+      </c>
+      <c r="P60" t="n">
         <v>28</v>
       </c>
-      <c r="M60" t="n">
-        <v>6</v>
-      </c>
-      <c r="N60" t="n">
-        <v>14</v>
-      </c>
-      <c r="O60" t="n">
-        <v>15</v>
-      </c>
-      <c r="P60" t="n">
-        <v>24</v>
-      </c>
       <c r="Q60" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
       <c r="R60" t="n">
-        <v>917</v>
+        <v>874</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4918,36 +4918,36 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J61" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K61" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L61" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N61" t="n">
+        <v>9</v>
+      </c>
+      <c r="O61" t="n">
         <v>7</v>
       </c>
-      <c r="O61" t="n">
-        <v>5</v>
-      </c>
       <c r="P61" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>925</v>
+        <v>870</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4992,39 +4992,39 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J62" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K62" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L62" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P62" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R62" t="n">
-        <v>751</v>
+        <v>598</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5066,36 +5066,36 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J63" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="K63" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L63" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R63" t="n">
-        <v>877</v>
+        <v>861</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5140,19 +5140,19 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J64" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K64" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L64" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="M64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N64" t="n">
         <v>6</v>
@@ -5165,11 +5165,11 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R64" t="n">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="S64" t="n">
         <v>0.02</v>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5214,39 +5214,39 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J65" t="n">
         <v>88</v>
       </c>
       <c r="K65" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L65" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P65" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R65" t="n">
-        <v>816</v>
+        <v>734</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5288,36 +5288,36 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J66" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K66" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L66" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P66" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R66" t="n">
-        <v>920</v>
+        <v>819</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J67" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K67" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L67" t="n">
         <v>45</v>
@@ -5377,13 +5377,13 @@
         <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P67" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>911</v>
+        <v>737</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5439,33 +5439,33 @@
         <v>69</v>
       </c>
       <c r="J68" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K68" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L68" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N68" t="n">
+        <v>8</v>
+      </c>
+      <c r="O68" t="n">
         <v>9</v>
-      </c>
-      <c r="O68" t="n">
-        <v>8</v>
       </c>
       <c r="P68" t="n">
         <v>13</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>923</v>
+        <v>787</v>
       </c>
       <c r="S68" t="n">
         <v>0.05</v>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5510,36 +5510,36 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J69" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K69" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L69" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N69" t="n">
         <v>10</v>
       </c>
       <c r="O69" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P69" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>913</v>
+        <v>832</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5584,36 +5584,36 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J70" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K70" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L70" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N70" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P70" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R70" t="n">
-        <v>832</v>
+        <v>632</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5661,36 +5661,36 @@
         <v>68</v>
       </c>
       <c r="J71" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K71" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L71" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M71" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N71" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O71" t="n">
         <v>11</v>
       </c>
       <c r="P71" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R71" t="n">
-        <v>692</v>
+        <v>646</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5735,19 +5735,19 @@
         <v>63</v>
       </c>
       <c r="J72" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K72" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L72" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="M72" t="n">
         <v>3</v>
       </c>
       <c r="N72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
@@ -5757,11 +5757,11 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>871</v>
+        <v>701</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5809,10 +5809,10 @@
         <v>55</v>
       </c>
       <c r="J73" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K73" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L73" t="n">
         <v>66</v>
@@ -5821,24 +5821,24 @@
         <v>2</v>
       </c>
       <c r="N73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O73" t="n">
         <v>3</v>
       </c>
       <c r="P73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R73" t="n">
-        <v>739</v>
+        <v>763</v>
       </c>
       <c r="S73" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5883,13 +5883,13 @@
         <v>54</v>
       </c>
       <c r="J74" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K74" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L74" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M74" t="n">
         <v>1</v>
@@ -5905,14 +5905,14 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R74" t="n">
-        <v>784</v>
+        <v>758</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5954,39 +5954,39 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J75" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L75" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P75" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R75" t="n">
-        <v>944</v>
+        <v>827</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6028,16 +6028,16 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J76" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K76" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L76" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="M76" t="n">
         <v>5</v>
@@ -6053,14 +6053,14 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R76" t="n">
-        <v>787</v>
+        <v>677</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6102,16 +6102,16 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J77" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K77" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L77" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M77" t="n">
         <v>2</v>
@@ -6123,15 +6123,15 @@
         <v>3</v>
       </c>
       <c r="P77" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R77" t="n">
-        <v>888</v>
+        <v>742</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6179,33 +6179,33 @@
         <v>54</v>
       </c>
       <c r="J78" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K78" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L78" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="M78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N78" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P78" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R78" t="n">
-        <v>783</v>
+        <v>640</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6250,16 +6250,16 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J79" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K79" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L79" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -6275,14 +6275,14 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R79" t="n">
-        <v>879</v>
+        <v>757</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6324,16 +6324,16 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J80" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K80" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L80" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M80" t="n">
         <v>1</v>
@@ -6349,14 +6349,14 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R80" t="n">
-        <v>762</v>
+        <v>636</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6404,33 +6404,33 @@
         <v>86</v>
       </c>
       <c r="K81" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L81" t="n">
         <v>67</v>
       </c>
       <c r="M81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R81" t="n">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6472,22 +6472,22 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J82" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K82" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L82" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M82" t="n">
         <v>2</v>
       </c>
       <c r="N82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O82" t="n">
         <v>7</v>
@@ -6497,14 +6497,14 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R82" t="n">
-        <v>711</v>
+        <v>788</v>
       </c>
       <c r="S82" t="n">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6546,39 +6546,39 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J83" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L83" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M83" t="n">
         <v>5</v>
       </c>
       <c r="N83" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O83" t="n">
         <v>7</v>
       </c>
       <c r="P83" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R83" t="n">
-        <v>906</v>
+        <v>808</v>
       </c>
       <c r="S83" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6626,30 +6626,30 @@
         <v>95</v>
       </c>
       <c r="K84" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L84" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M84" t="n">
         <v>3</v>
       </c>
       <c r="N84" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R84" t="n">
-        <v>941</v>
+        <v>831</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6694,25 +6694,25 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J85" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K85" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L85" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="M85" t="n">
         <v>3</v>
       </c>
       <c r="N85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O85" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P85" t="n">
         <v>15</v>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="R85" t="n">
-        <v>811</v>
+        <v>771</v>
       </c>
       <c r="S85" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6771,13 +6771,13 @@
         <v>45</v>
       </c>
       <c r="J86" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K86" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L86" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="M86" t="n">
         <v>3</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="R86" t="n">
-        <v>821</v>
+        <v>730</v>
       </c>
       <c r="S86" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6842,39 +6842,39 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J87" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K87" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L87" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="M87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N87" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R87" t="n">
-        <v>940</v>
+        <v>796</v>
       </c>
       <c r="S87" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6916,28 +6916,28 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J88" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K88" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L88" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="M88" t="n">
         <v>1</v>
       </c>
       <c r="N88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O88" t="n">
         <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="R88" t="n">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6990,36 +6990,36 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J89" t="n">
         <v>113</v>
       </c>
       <c r="K89" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L89" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M89" t="n">
+        <v>2</v>
+      </c>
+      <c r="N89" t="n">
+        <v>9</v>
+      </c>
+      <c r="O89" t="n">
         <v>6</v>
       </c>
-      <c r="N89" t="n">
-        <v>13</v>
-      </c>
-      <c r="O89" t="n">
-        <v>10</v>
-      </c>
       <c r="P89" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>1/6/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R89" t="n">
-        <v>845</v>
+        <v>867</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7064,36 +7064,36 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J90" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L90" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="M90" t="n">
         <v>2</v>
       </c>
       <c r="N90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O90" t="n">
         <v>3</v>
       </c>
       <c r="P90" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R90" t="n">
-        <v>655</v>
+        <v>697</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7138,36 +7138,36 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J91" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K91" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L91" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="M91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N91" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O91" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P91" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R91" t="n">
-        <v>788</v>
+        <v>816</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7212,16 +7212,16 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J92" t="n">
         <v>90</v>
       </c>
       <c r="K92" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L92" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="M92" t="n">
         <v>3</v>
@@ -7237,11 +7237,11 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R92" t="n">
-        <v>907</v>
+        <v>800</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7286,22 +7286,22 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J93" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K93" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L93" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O93" t="n">
         <v>5</v>
@@ -7311,14 +7311,14 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R93" t="n">
-        <v>704</v>
+        <v>624</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7360,36 +7360,36 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J94" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K94" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L94" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N94" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O94" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P94" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R94" t="n">
-        <v>697</v>
+        <v>681</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7434,39 +7434,39 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J95" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K95" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L95" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="M95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P95" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R95" t="n">
-        <v>924</v>
+        <v>849</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7511,33 +7511,33 @@
         <v>73</v>
       </c>
       <c r="J96" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K96" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L96" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N96" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O96" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P96" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R96" t="n">
-        <v>799</v>
+        <v>728</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7582,36 +7582,36 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J97" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K97" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L97" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M97" t="n">
         <v>2</v>
       </c>
       <c r="N97" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P97" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R97" t="n">
-        <v>792</v>
+        <v>680</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7656,28 +7656,28 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J98" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K98" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L98" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M98" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N98" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O98" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P98" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="R98" t="n">
-        <v>814</v>
+        <v>692</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7730,36 +7730,36 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J99" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K99" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L99" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N99" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O99" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P99" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R99" t="n">
-        <v>713</v>
+        <v>670</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7804,19 +7804,19 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J100" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K100" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L100" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="M100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N100" t="n">
         <v>9</v>
@@ -7829,14 +7829,14 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>1/7/1 17:00 LMT</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R100" t="n">
-        <v>915</v>
+        <v>869</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7878,36 +7878,36 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J101" t="n">
         <v>99</v>
       </c>
       <c r="K101" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L101" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="M101" t="n">
+        <v>3</v>
+      </c>
+      <c r="N101" t="n">
+        <v>8</v>
+      </c>
+      <c r="O101" t="n">
         <v>5</v>
-      </c>
-      <c r="N101" t="n">
-        <v>9</v>
-      </c>
-      <c r="O101" t="n">
-        <v>7</v>
       </c>
       <c r="P101" t="n">
         <v>13</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R101" t="n">
-        <v>767</v>
+        <v>781</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7952,39 +7952,39 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J102" t="n">
         <v>88</v>
       </c>
       <c r="K102" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L102" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="M102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N102" t="n">
+        <v>3</v>
+      </c>
+      <c r="O102" t="n">
+        <v>3</v>
+      </c>
+      <c r="P102" t="n">
         <v>5</v>
       </c>
-      <c r="O102" t="n">
-        <v>1</v>
-      </c>
-      <c r="P102" t="n">
-        <v>7</v>
-      </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R102" t="n">
-        <v>892</v>
+        <v>799</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8026,36 +8026,36 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J103" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K103" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L103" t="n">
         <v>43</v>
       </c>
       <c r="M103" t="n">
+        <v>2</v>
+      </c>
+      <c r="N103" t="n">
+        <v>8</v>
+      </c>
+      <c r="O103" t="n">
         <v>6</v>
       </c>
-      <c r="N103" t="n">
-        <v>10</v>
-      </c>
-      <c r="O103" t="n">
-        <v>11</v>
-      </c>
       <c r="P103" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R103" t="n">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8100,36 +8100,36 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J104" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K104" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L104" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="M104" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O104" t="n">
         <v>10</v>
       </c>
       <c r="P104" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R104" t="n">
-        <v>761</v>
+        <v>703</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8177,36 +8177,36 @@
         <v>72</v>
       </c>
       <c r="J105" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K105" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L105" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="M105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N105" t="n">
         <v>13</v>
       </c>
       <c r="O105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P105" t="n">
         <v>19</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R105" t="n">
-        <v>921</v>
+        <v>813</v>
       </c>
       <c r="S105" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8248,19 +8248,19 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J106" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K106" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L106" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N106" t="n">
         <v>10</v>
@@ -8269,7 +8269,7 @@
         <v>3</v>
       </c>
       <c r="P106" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="R106" t="n">
-        <v>825</v>
+        <v>804</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8322,36 +8322,36 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J107" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K107" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L107" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N107" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P107" t="n">
         <v>14</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R107" t="n">
-        <v>836</v>
+        <v>704</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8399,36 +8399,36 @@
         <v>57</v>
       </c>
       <c r="J108" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K108" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L108" t="n">
         <v>72</v>
       </c>
       <c r="M108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P108" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R108" t="n">
-        <v>812</v>
+        <v>795</v>
       </c>
       <c r="S108" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8470,16 +8470,16 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J109" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K109" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L109" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M109" t="n">
         <v>5</v>
@@ -8495,14 +8495,14 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R109" t="n">
-        <v>806</v>
+        <v>768</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8550,30 +8550,30 @@
         <v>105</v>
       </c>
       <c r="K110" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L110" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N110" t="n">
         <v>7</v>
       </c>
       <c r="O110" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P110" t="n">
         <v>13</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R110" t="n">
-        <v>916</v>
+        <v>769</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8618,16 +8618,16 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J111" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K111" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L111" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M111" t="n">
         <v>2</v>
@@ -8643,11 +8643,11 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R111" t="n">
-        <v>779</v>
+        <v>680</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8692,36 +8692,36 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J112" t="n">
         <v>91</v>
       </c>
       <c r="K112" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L112" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N112" t="n">
         <v>9</v>
       </c>
       <c r="O112" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P112" t="n">
         <v>14</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R112" t="n">
-        <v>881</v>
+        <v>742</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8772,19 +8772,19 @@
         <v>84</v>
       </c>
       <c r="K113" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L113" t="n">
         <v>51</v>
       </c>
       <c r="M113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N113" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O113" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P113" t="n">
         <v>14</v>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8840,28 +8840,28 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J114" t="n">
         <v>97</v>
       </c>
       <c r="K114" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L114" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="M114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N114" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O114" t="n">
         <v>3</v>
       </c>
       <c r="P114" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="R114" t="n">
-        <v>861</v>
+        <v>760</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8914,22 +8914,22 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J115" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K115" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L115" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M115" t="n">
         <v>2</v>
       </c>
       <c r="N115" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O115" t="n">
         <v>3</v>
@@ -8939,14 +8939,14 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R115" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
       <c r="S115" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8988,36 +8988,36 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J116" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K116" t="n">
         <v>26</v>
       </c>
       <c r="L116" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M116" t="n">
         <v>3</v>
       </c>
       <c r="N116" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O116" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P116" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R116" t="n">
-        <v>923</v>
+        <v>823</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9071,7 +9071,7 @@
         <v>20</v>
       </c>
       <c r="L117" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M117" t="n">
         <v>3</v>
@@ -9087,14 +9087,14 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R117" t="n">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="S117" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9136,39 +9136,39 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J118" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K118" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L118" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="M118" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N118" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O118" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P118" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R118" t="n">
-        <v>923</v>
+        <v>799</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9210,36 +9210,36 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J119" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K119" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L119" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="M119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N119" t="n">
         <v>8</v>
       </c>
       <c r="O119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P119" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R119" t="n">
-        <v>836</v>
+        <v>771</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9284,25 +9284,25 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J120" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K120" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L120" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
         <v>5</v>
       </c>
       <c r="O120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P120" t="n">
         <v>7</v>
@@ -9313,10 +9313,10 @@
         </is>
       </c>
       <c r="R120" t="n">
-        <v>913</v>
+        <v>776</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9358,39 +9358,39 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J121" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K121" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L121" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="M121" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P121" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1/4/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R121" t="n">
-        <v>933</v>
+        <v>823</v>
       </c>
       <c r="S121" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9432,16 +9432,16 @@
         </is>
       </c>
       <c r="I122" t="n">
+        <v>65</v>
+      </c>
+      <c r="J122" t="n">
+        <v>91</v>
+      </c>
+      <c r="K122" t="n">
+        <v>24</v>
+      </c>
+      <c r="L122" t="n">
         <v>66</v>
-      </c>
-      <c r="J122" t="n">
-        <v>93</v>
-      </c>
-      <c r="K122" t="n">
-        <v>19</v>
-      </c>
-      <c r="L122" t="n">
-        <v>48</v>
       </c>
       <c r="M122" t="n">
         <v>2</v>
@@ -9453,15 +9453,15 @@
         <v>6</v>
       </c>
       <c r="P122" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R122" t="n">
-        <v>786</v>
+        <v>758</v>
       </c>
       <c r="S122" t="n">
         <v>0.04</v>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9509,22 +9509,22 @@
         <v>81</v>
       </c>
       <c r="J123" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K123" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L123" t="n">
         <v>46</v>
       </c>
       <c r="M123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N123" t="n">
         <v>5</v>
       </c>
       <c r="O123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P123" t="n">
         <v>15</v>
@@ -9535,10 +9535,10 @@
         </is>
       </c>
       <c r="R123" t="n">
-        <v>915</v>
+        <v>847</v>
       </c>
       <c r="S123" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9580,16 +9580,16 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J124" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K124" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L124" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="M124" t="n">
         <v>3</v>
@@ -9601,15 +9601,15 @@
         <v>9</v>
       </c>
       <c r="P124" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R124" t="n">
-        <v>926</v>
+        <v>850</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9654,36 +9654,36 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J125" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K125" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L125" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M125" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N125" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O125" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P125" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R125" t="n">
-        <v>916</v>
+        <v>808</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9728,36 +9728,36 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J126" t="n">
         <v>91</v>
       </c>
       <c r="K126" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L126" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N126" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O126" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P126" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R126" t="n">
-        <v>936</v>
+        <v>796</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9802,36 +9802,36 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J127" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K127" t="n">
         <v>17</v>
       </c>
       <c r="L127" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N127" t="n">
+        <v>7</v>
+      </c>
+      <c r="O127" t="n">
+        <v>5</v>
+      </c>
+      <c r="P127" t="n">
         <v>9</v>
       </c>
-      <c r="O127" t="n">
-        <v>3</v>
-      </c>
-      <c r="P127" t="n">
-        <v>13</v>
-      </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R127" t="n">
-        <v>936</v>
+        <v>862</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9879,7 +9879,7 @@
         <v>53</v>
       </c>
       <c r="J128" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K128" t="n">
         <v>23</v>
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="R128" t="n">
-        <v>912</v>
+        <v>800</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9950,22 +9950,22 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J129" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K129" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L129" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M129" t="n">
         <v>3</v>
       </c>
       <c r="N129" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O129" t="n">
         <v>7</v>
@@ -9979,10 +9979,10 @@
         </is>
       </c>
       <c r="R129" t="n">
-        <v>912</v>
+        <v>837</v>
       </c>
       <c r="S129" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10027,36 +10027,36 @@
         <v>68</v>
       </c>
       <c r="J130" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K130" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L130" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="M130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N130" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O130" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P130" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R130" t="n">
-        <v>920</v>
+        <v>856</v>
       </c>
       <c r="S130" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -10098,16 +10098,16 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J131" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K131" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L131" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="M131" t="n">
         <v>2</v>
@@ -10123,11 +10123,11 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R131" t="n">
-        <v>857</v>
+        <v>813</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -10172,36 +10172,36 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J132" t="n">
         <v>95</v>
       </c>
       <c r="K132" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L132" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M132" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N132" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O132" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P132" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R132" t="n">
-        <v>946</v>
+        <v>860</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10246,36 +10246,36 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J133" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K133" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L133" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M133" t="n">
         <v>1</v>
       </c>
       <c r="N133" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O133" t="n">
         <v>2</v>
       </c>
       <c r="P133" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R133" t="n">
-        <v>799</v>
+        <v>676</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10320,16 +10320,16 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J134" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K134" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L134" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="M134" t="n">
         <v>1</v>
@@ -10345,14 +10345,14 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>01</t>
         </is>
       </c>
       <c r="R134" t="n">
-        <v>824</v>
+        <v>704</v>
       </c>
       <c r="S134" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10394,36 +10394,36 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="J135" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="K135" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L135" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N135" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P135" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R135" t="n">
-        <v>817</v>
+        <v>847</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10468,39 +10468,39 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J136" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K136" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L136" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="M136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N136" t="n">
         <v>6</v>
       </c>
       <c r="O136" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P136" t="n">
         <v>8</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R136" t="n">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="S136" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10542,39 +10542,39 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J137" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K137" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L137" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M137" t="n">
         <v>3</v>
       </c>
       <c r="N137" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O137" t="n">
         <v>5</v>
       </c>
       <c r="P137" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R137" t="n">
-        <v>838</v>
+        <v>679</v>
       </c>
       <c r="S137" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10619,33 +10619,33 @@
         <v>83</v>
       </c>
       <c r="J138" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K138" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L138" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="M138" t="n">
         <v>5</v>
       </c>
       <c r="N138" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O138" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P138" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R138" t="n">
-        <v>845</v>
+        <v>784</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10699,27 +10699,27 @@
         <v>16</v>
       </c>
       <c r="L139" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M139" t="n">
         <v>2</v>
       </c>
       <c r="N139" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O139" t="n">
         <v>3</v>
       </c>
       <c r="P139" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R139" t="n">
-        <v>941</v>
+        <v>781</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -10755,7 +10755,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10764,39 +10764,39 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J140" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K140" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L140" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="M140" t="n">
         <v>5</v>
       </c>
       <c r="N140" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O140" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P140" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R140" t="n">
-        <v>693</v>
+        <v>735</v>
       </c>
       <c r="S140" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10838,36 +10838,36 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J141" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K141" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L141" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M141" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N141" t="n">
         <v>10</v>
       </c>
       <c r="O141" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P141" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R141" t="n">
-        <v>795</v>
+        <v>769</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -10912,39 +10912,39 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J142" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K142" t="n">
+        <v>22</v>
+      </c>
+      <c r="L142" t="n">
+        <v>50</v>
+      </c>
+      <c r="M142" t="n">
+        <v>3</v>
+      </c>
+      <c r="N142" t="n">
+        <v>9</v>
+      </c>
+      <c r="O142" t="n">
+        <v>11</v>
+      </c>
+      <c r="P142" t="n">
         <v>17</v>
       </c>
-      <c r="L142" t="n">
-        <v>42</v>
-      </c>
-      <c r="M142" t="n">
-        <v>5</v>
-      </c>
-      <c r="N142" t="n">
-        <v>11</v>
-      </c>
-      <c r="O142" t="n">
-        <v>10</v>
-      </c>
-      <c r="P142" t="n">
-        <v>22</v>
-      </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>1/7/1 17:00 LMT</t>
+          <t>1/3/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R142" t="n">
-        <v>918</v>
+        <v>827</v>
       </c>
       <c r="S142" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10986,16 +10986,16 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J143" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K143" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L143" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M143" t="n">
         <v>1</v>
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="R143" t="n">
-        <v>939</v>
+        <v>791</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11060,25 +11060,25 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J144" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K144" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L144" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="M144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N144" t="n">
         <v>7</v>
       </c>
       <c r="O144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P144" t="n">
         <v>9</v>
@@ -11089,10 +11089,10 @@
         </is>
       </c>
       <c r="R144" t="n">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="S144" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -11134,36 +11134,36 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J145" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K145" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L145" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M145" t="n">
         <v>3</v>
       </c>
       <c r="N145" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O145" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P145" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R145" t="n">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11208,16 +11208,16 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J146" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K146" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L146" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M146" t="n">
         <v>3</v>
@@ -11237,10 +11237,10 @@
         </is>
       </c>
       <c r="R146" t="n">
-        <v>922</v>
+        <v>788</v>
       </c>
       <c r="S146" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11282,39 +11282,39 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J147" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K147" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L147" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="M147" t="n">
         <v>5</v>
       </c>
       <c r="N147" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O147" t="n">
         <v>10</v>
       </c>
       <c r="P147" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R147" t="n">
-        <v>918</v>
+        <v>833</v>
       </c>
       <c r="S147" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11356,16 +11356,16 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J148" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K148" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L148" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M148" t="n">
         <v>2</v>
@@ -11381,11 +11381,11 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R148" t="n">
-        <v>915</v>
+        <v>803</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11433,25 +11433,25 @@
         <v>77</v>
       </c>
       <c r="J149" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K149" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L149" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N149" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O149" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P149" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="R149" t="n">
-        <v>803</v>
+        <v>735</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11504,36 +11504,36 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J150" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K150" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L150" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>9</v>
+      </c>
+      <c r="O150" t="n">
         <v>1</v>
       </c>
-      <c r="N150" t="n">
-        <v>8</v>
-      </c>
-      <c r="O150" t="n">
-        <v>2</v>
-      </c>
       <c r="P150" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R150" t="n">
-        <v>801</v>
+        <v>628</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11578,36 +11578,36 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J151" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K151" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L151" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="M151" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N151" t="n">
+        <v>19</v>
+      </c>
+      <c r="O151" t="n">
         <v>15</v>
       </c>
-      <c r="O151" t="n">
-        <v>13</v>
-      </c>
       <c r="P151" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R151" t="n">
-        <v>759</v>
+        <v>703</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11652,36 +11652,36 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J152" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K152" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L152" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N152" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O152" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P152" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R152" t="n">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -11717,7 +11717,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11729,13 +11729,13 @@
         <v>72</v>
       </c>
       <c r="J153" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K153" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L153" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M153" t="n">
         <v>3</v>
@@ -11747,7 +11747,7 @@
         <v>5</v>
       </c>
       <c r="P153" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         </is>
       </c>
       <c r="R153" t="n">
-        <v>851</v>
+        <v>699</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11803,33 +11803,33 @@
         <v>57</v>
       </c>
       <c r="J154" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K154" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L154" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M154" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N154" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O154" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P154" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R154" t="n">
-        <v>568</v>
+        <v>692</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -11865,7 +11865,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11880,33 +11880,33 @@
         <v>77</v>
       </c>
       <c r="K155" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L155" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N155" t="n">
+        <v>8</v>
+      </c>
+      <c r="O155" t="n">
         <v>5</v>
       </c>
-      <c r="O155" t="n">
-        <v>3</v>
-      </c>
       <c r="P155" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R155" t="n">
-        <v>772</v>
+        <v>692</v>
       </c>
       <c r="S155" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11948,28 +11948,28 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J156" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K156" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L156" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="M156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N156" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P156" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         </is>
       </c>
       <c r="R156" t="n">
-        <v>892</v>
+        <v>753</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12022,36 +12022,36 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J157" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K157" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L157" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="M157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N157" t="n">
+        <v>7</v>
+      </c>
+      <c r="O157" t="n">
         <v>6</v>
       </c>
-      <c r="O157" t="n">
-        <v>5</v>
-      </c>
       <c r="P157" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R157" t="n">
-        <v>735</v>
+        <v>678</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>8/26/2026</t>
+          <t>8/27/2026</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12096,16 +12096,16 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J158" t="n">
         <v>92</v>
       </c>
       <c r="K158" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L158" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M158" t="n">
         <v>5</v>
@@ -12121,11 +12121,11 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R158" t="n">
-        <v>865</v>
+        <v>775</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>

--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -558,22 +558,22 @@
         <v>74</v>
       </c>
       <c r="K2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
         <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -581,10 +581,10 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>663</v>
+        <v>948</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -629,13 +629,13 @@
         <v>87</v>
       </c>
       <c r="J3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K3" t="n">
         <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
         <v>2</v>
@@ -644,7 +644,7 @@
         <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
         <v>23</v>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>877</v>
+        <v>905</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -700,28 +700,28 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" t="n">
         <v>90</v>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
         <v>7</v>
       </c>
       <c r="P4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>777</v>
+        <v>809</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -774,39 +774,39 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J5" t="n">
         <v>81</v>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L5" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M5" t="n">
         <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O5" t="n">
         <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>751</v>
+        <v>683</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -857,19 +857,19 @@
         <v>19</v>
       </c>
       <c r="L6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M6" t="n">
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>875</v>
+        <v>922</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -922,39 +922,39 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L7" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="S7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -999,33 +999,33 @@
         <v>73</v>
       </c>
       <c r="J8" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L8" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="M8" t="n">
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O8" t="n">
         <v>7</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>851</v>
+        <v>928</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1070,39 +1070,39 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J9" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>789</v>
+        <v>771</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1147,36 +1147,36 @@
         <v>86</v>
       </c>
       <c r="J10" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K10" t="n">
         <v>16</v>
       </c>
       <c r="L10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
         <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1/3/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>849</v>
+        <v>909</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J11" t="n">
         <v>106</v>
@@ -1227,30 +1227,30 @@
         <v>13</v>
       </c>
       <c r="L11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
         <v>17</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J12" t="n">
         <v>93</v>
@@ -1301,27 +1301,27 @@
         <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>15</v>
+      </c>
+      <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="N12" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" t="n">
-        <v>5</v>
-      </c>
       <c r="P12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>794</v>
+        <v>926</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1384,18 +1384,18 @@
         <v>7</v>
       </c>
       <c r="O13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P13" t="n">
         <v>24</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>619</v>
+        <v>775</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1443,7 +1443,7 @@
         <v>58</v>
       </c>
       <c r="J14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K14" t="n">
         <v>24</v>
@@ -1455,24 +1455,24 @@
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1514,39 +1514,39 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J15" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L15" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>13</v>
+      </c>
+      <c r="O15" t="n">
         <v>3</v>
       </c>
-      <c r="N15" t="n">
-        <v>6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>5</v>
-      </c>
       <c r="P15" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>867</v>
+        <v>945</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J16" t="n">
         <v>84</v>
@@ -1613,11 +1613,11 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>641</v>
+        <v>791</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1662,39 +1662,39 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J17" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K17" t="n">
         <v>23</v>
       </c>
       <c r="L17" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M17" t="n">
         <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="O17" t="n">
         <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="S17" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1736,36 +1736,36 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J18" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L18" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>608</v>
+        <v>730</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1810,39 +1810,39 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J19" t="n">
         <v>91</v>
       </c>
       <c r="K19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L19" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O19" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>788</v>
+        <v>886</v>
       </c>
       <c r="S19" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1884,16 +1884,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J20" t="n">
         <v>94</v>
       </c>
       <c r="K20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L20" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>806</v>
+        <v>929</v>
       </c>
       <c r="S20" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1961,13 +1961,13 @@
         <v>69</v>
       </c>
       <c r="J21" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K21" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L21" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="M21" t="n">
         <v>8</v>
@@ -1976,21 +1976,21 @@
         <v>13</v>
       </c>
       <c r="O21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P21" t="n">
         <v>19</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>797</v>
+        <v>920</v>
       </c>
       <c r="S21" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J22" t="n">
         <v>96</v>
@@ -2041,7 +2041,7 @@
         <v>25</v>
       </c>
       <c r="L22" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M22" t="n">
         <v>2</v>
@@ -2050,21 +2050,21 @@
         <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>844</v>
+        <v>966</v>
       </c>
       <c r="S22" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2106,36 +2106,36 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J23" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L23" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P23" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>795</v>
+        <v>924</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2189,13 +2189,13 @@
         <v>15</v>
       </c>
       <c r="L24" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M24" t="n">
         <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O24" t="n">
         <v>6</v>
@@ -2205,11 +2205,11 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>779</v>
+        <v>839</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2260,33 +2260,33 @@
         <v>99</v>
       </c>
       <c r="K25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L25" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
         <v>8</v>
       </c>
       <c r="O25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>750</v>
+        <v>924</v>
       </c>
       <c r="S25" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J26" t="n">
         <v>95</v>
@@ -2343,24 +2343,24 @@
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2405,36 +2405,36 @@
         <v>65</v>
       </c>
       <c r="J27" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L27" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>814</v>
+        <v>956</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J28" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K28" t="n">
         <v>18</v>
       </c>
       <c r="L28" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M28" t="n">
         <v>5</v>
@@ -2501,11 +2501,11 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>864</v>
+        <v>917</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2553,36 +2553,36 @@
         <v>51</v>
       </c>
       <c r="J29" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K29" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L29" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="S29" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2624,36 +2624,36 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J30" t="n">
         <v>110</v>
       </c>
       <c r="K30" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L30" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>884</v>
+        <v>920</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2698,16 +2698,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J31" t="n">
         <v>75</v>
       </c>
       <c r="K31" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L31" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -2723,14 +2723,14 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>836</v>
+        <v>812</v>
       </c>
       <c r="S31" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -2778,33 +2778,33 @@
         <v>74</v>
       </c>
       <c r="K32" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L32" t="n">
         <v>69</v>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>569</v>
+        <v>810</v>
       </c>
       <c r="S32" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -2849,36 +2849,36 @@
         <v>52</v>
       </c>
       <c r="J33" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L33" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="M33" t="n">
         <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>731</v>
+        <v>676</v>
       </c>
       <c r="S33" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2923,33 +2923,33 @@
         <v>66</v>
       </c>
       <c r="J34" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K34" t="n">
         <v>23</v>
       </c>
       <c r="L34" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M34" t="n">
         <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O34" t="n">
         <v>5</v>
       </c>
       <c r="P34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>660</v>
+        <v>888</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J35" t="n">
         <v>90</v>
@@ -3003,30 +3003,30 @@
         <v>15</v>
       </c>
       <c r="L35" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M35" t="n">
         <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O35" t="n">
         <v>8</v>
       </c>
       <c r="P35" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>803</v>
+        <v>886</v>
       </c>
       <c r="S35" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3071,36 +3071,36 @@
         <v>58</v>
       </c>
       <c r="J36" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K36" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L36" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1/6/1 17:00 LMT</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="S36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J37" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K37" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L37" t="n">
         <v>57</v>
@@ -3157,21 +3157,21 @@
         <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O37" t="n">
         <v>5</v>
       </c>
       <c r="P37" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>780</v>
+        <v>764</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J38" t="n">
         <v>111</v>
@@ -3234,18 +3234,18 @@
         <v>8</v>
       </c>
       <c r="O38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P38" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>867</v>
+        <v>930</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3296,10 +3296,10 @@
         <v>91</v>
       </c>
       <c r="K39" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L39" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M39" t="n">
         <v>5</v>
@@ -3308,21 +3308,21 @@
         <v>8</v>
       </c>
       <c r="O39" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P39" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>795</v>
+        <v>960</v>
       </c>
       <c r="S39" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3370,13 +3370,13 @@
         <v>90</v>
       </c>
       <c r="K40" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L40" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
         <v>7</v>
@@ -3385,18 +3385,18 @@
         <v>11</v>
       </c>
       <c r="P40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1/4/1 17:00 LMT</t>
+          <t>1/7/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>777</v>
+        <v>824</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -3438,36 +3438,36 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J41" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K41" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L41" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>653</v>
+        <v>801</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -3512,36 +3512,36 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J42" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K42" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L42" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="M42" t="n">
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3589,36 +3589,36 @@
         <v>64</v>
       </c>
       <c r="J43" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K43" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L43" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M43" t="n">
         <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O43" t="n">
         <v>5</v>
       </c>
       <c r="P43" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>842</v>
+        <v>934</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J44" t="n">
         <v>90</v>
@@ -3672,24 +3672,24 @@
         <v>64</v>
       </c>
       <c r="M44" t="n">
+        <v>3</v>
+      </c>
+      <c r="N44" t="n">
+        <v>11</v>
+      </c>
+      <c r="O44" t="n">
         <v>5</v>
       </c>
-      <c r="N44" t="n">
-        <v>13</v>
-      </c>
-      <c r="O44" t="n">
-        <v>6</v>
-      </c>
       <c r="P44" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>654</v>
+        <v>854</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -3737,33 +3737,33 @@
         <v>69</v>
       </c>
       <c r="J45" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K45" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L45" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M45" t="n">
+        <v>3</v>
+      </c>
+      <c r="N45" t="n">
+        <v>11</v>
+      </c>
+      <c r="O45" t="n">
         <v>5</v>
       </c>
-      <c r="N45" t="n">
-        <v>13</v>
-      </c>
-      <c r="O45" t="n">
-        <v>7</v>
-      </c>
       <c r="P45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>828</v>
+        <v>931</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -3808,39 +3808,39 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J46" t="n">
         <v>96</v>
       </c>
       <c r="K46" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L46" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O46" t="n">
         <v>6</v>
       </c>
       <c r="P46" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R46" t="n">
-        <v>873</v>
+        <v>927</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -3882,16 +3882,16 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J47" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K47" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L47" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -3903,18 +3903,18 @@
         <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>731</v>
+        <v>744</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J48" t="n">
         <v>112</v>
@@ -3965,10 +3965,10 @@
         <v>19</v>
       </c>
       <c r="L48" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
         <v>10</v>
@@ -3977,15 +3977,15 @@
         <v>7</v>
       </c>
       <c r="P48" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>865</v>
+        <v>923</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -4033,36 +4033,36 @@
         <v>67</v>
       </c>
       <c r="J49" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K49" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L49" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
         <v>11</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P49" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R49" t="n">
-        <v>732</v>
+        <v>784</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4113,30 +4113,30 @@
         <v>25</v>
       </c>
       <c r="L50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
         <v>16</v>
       </c>
       <c r="O50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P50" t="n">
         <v>25</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>661</v>
+        <v>775</v>
       </c>
       <c r="S50" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4178,16 +4178,16 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J51" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K51" t="n">
         <v>20</v>
       </c>
       <c r="L51" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M51" t="n">
         <v>6</v>
@@ -4203,11 +4203,11 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R51" t="n">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -4252,39 +4252,39 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J52" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K52" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L52" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>787</v>
+        <v>823</v>
       </c>
       <c r="S52" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -4326,16 +4326,16 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J53" t="n">
         <v>100</v>
       </c>
       <c r="K53" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L53" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M53" t="n">
         <v>5</v>
@@ -4344,7 +4344,7 @@
         <v>8</v>
       </c>
       <c r="O53" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P53" t="n">
         <v>18</v>
@@ -4355,10 +4355,10 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>821</v>
+        <v>875</v>
       </c>
       <c r="S53" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4409,27 +4409,27 @@
         <v>15</v>
       </c>
       <c r="L54" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M54" t="n">
         <v>2</v>
       </c>
       <c r="N54" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P54" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R54" t="n">
-        <v>779</v>
+        <v>894</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -4477,33 +4477,33 @@
         <v>75</v>
       </c>
       <c r="J55" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K55" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L55" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M55" t="n">
         <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P55" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>701</v>
+        <v>850</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -4548,39 +4548,39 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J56" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K56" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L56" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="M56" t="n">
         <v>2</v>
       </c>
       <c r="N56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O56" t="n">
         <v>3</v>
       </c>
       <c r="P56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>772</v>
+        <v>817</v>
       </c>
       <c r="S56" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -4622,39 +4622,39 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J57" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K57" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L57" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M57" t="n">
         <v>3</v>
       </c>
       <c r="N57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O57" t="n">
         <v>5</v>
       </c>
       <c r="P57" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>679</v>
+        <v>782</v>
       </c>
       <c r="S57" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -4696,39 +4696,39 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J58" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K58" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L58" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="M58" t="n">
+        <v>3</v>
+      </c>
+      <c r="N58" t="n">
+        <v>10</v>
+      </c>
+      <c r="O58" t="n">
         <v>5</v>
       </c>
-      <c r="N58" t="n">
-        <v>9</v>
-      </c>
-      <c r="O58" t="n">
-        <v>6</v>
-      </c>
       <c r="P58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="S58" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -4770,16 +4770,16 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J59" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K59" t="n">
         <v>18</v>
       </c>
       <c r="L59" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M59" t="n">
         <v>2</v>
@@ -4788,18 +4788,18 @@
         <v>14</v>
       </c>
       <c r="O59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P59" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R59" t="n">
-        <v>657</v>
+        <v>802</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J60" t="n">
         <v>93</v>
@@ -4853,19 +4853,19 @@
         <v>19</v>
       </c>
       <c r="L60" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N60" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P60" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>874</v>
+        <v>885</v>
       </c>
       <c r="S60" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -4921,33 +4921,33 @@
         <v>72</v>
       </c>
       <c r="J61" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K61" t="n">
         <v>15</v>
       </c>
       <c r="L61" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
         <v>9</v>
       </c>
       <c r="O61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P61" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>870</v>
+        <v>951</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -4992,39 +4992,39 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J62" t="n">
         <v>86</v>
       </c>
       <c r="K62" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L62" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M62" t="n">
         <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O62" t="n">
         <v>2</v>
       </c>
       <c r="P62" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R62" t="n">
-        <v>598</v>
+        <v>685</v>
       </c>
       <c r="S62" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5066,16 +5066,16 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J63" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K63" t="n">
         <v>15</v>
       </c>
       <c r="L63" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M63" t="n">
         <v>2</v>
@@ -5084,7 +5084,7 @@
         <v>10</v>
       </c>
       <c r="O63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P63" t="n">
         <v>22</v>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>861</v>
+        <v>889</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -5143,13 +5143,13 @@
         <v>69</v>
       </c>
       <c r="J64" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K64" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L64" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M64" t="n">
         <v>3</v>
@@ -5165,11 +5165,11 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R64" t="n">
-        <v>833</v>
+        <v>875</v>
       </c>
       <c r="S64" t="n">
         <v>0.02</v>
@@ -5214,39 +5214,39 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J65" t="n">
         <v>88</v>
       </c>
       <c r="K65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L65" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M65" t="n">
+        <v>2</v>
+      </c>
+      <c r="N65" t="n">
+        <v>9</v>
+      </c>
+      <c r="O65" t="n">
         <v>3</v>
       </c>
-      <c r="N65" t="n">
-        <v>7</v>
-      </c>
-      <c r="O65" t="n">
-        <v>5</v>
-      </c>
       <c r="P65" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R65" t="n">
-        <v>734</v>
+        <v>757</v>
       </c>
       <c r="S65" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -5288,36 +5288,36 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J66" t="n">
         <v>93</v>
       </c>
       <c r="K66" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L66" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="M66" t="n">
         <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P66" t="n">
         <v>13</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R66" t="n">
-        <v>819</v>
+        <v>875</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5362,28 +5362,28 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J67" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K67" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L67" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M67" t="n">
         <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P67" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>737</v>
+        <v>699</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -5436,39 +5436,39 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J68" t="n">
         <v>86</v>
       </c>
       <c r="K68" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L68" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
+        <v>9</v>
+      </c>
+      <c r="O68" t="n">
         <v>8</v>
       </c>
-      <c r="O68" t="n">
-        <v>9</v>
-      </c>
       <c r="P68" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1/5/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>787</v>
+        <v>740</v>
       </c>
       <c r="S68" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5516,33 +5516,33 @@
         <v>101</v>
       </c>
       <c r="K69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L69" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M69" t="n">
         <v>5</v>
       </c>
       <c r="N69" t="n">
+        <v>9</v>
+      </c>
+      <c r="O69" t="n">
         <v>10</v>
       </c>
-      <c r="O69" t="n">
-        <v>11</v>
-      </c>
       <c r="P69" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>832</v>
+        <v>915</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -5584,36 +5584,36 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J70" t="n">
         <v>94</v>
       </c>
       <c r="K70" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L70" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
         <v>13</v>
       </c>
       <c r="O70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P70" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R70" t="n">
-        <v>632</v>
+        <v>902</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
         <v>92</v>
       </c>
       <c r="K71" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L71" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M71" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N71" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O71" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P71" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>646</v>
+        <v>824</v>
       </c>
       <c r="S71" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -5732,39 +5732,39 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J72" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K72" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L72" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N72" t="n">
         <v>11</v>
       </c>
       <c r="O72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>701</v>
+        <v>890</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -5809,36 +5809,36 @@
         <v>55</v>
       </c>
       <c r="J73" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K73" t="n">
         <v>21</v>
       </c>
       <c r="L73" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M73" t="n">
         <v>2</v>
       </c>
       <c r="N73" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O73" t="n">
         <v>3</v>
       </c>
       <c r="P73" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R73" t="n">
-        <v>763</v>
+        <v>735</v>
       </c>
       <c r="S73" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5880,39 +5880,39 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J74" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K74" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L74" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="M74" t="n">
         <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R74" t="n">
-        <v>758</v>
+        <v>795</v>
       </c>
       <c r="S74" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -5957,25 +5957,25 @@
         <v>66</v>
       </c>
       <c r="J75" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K75" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L75" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M75" t="n">
         <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O75" t="n">
         <v>5</v>
       </c>
       <c r="P75" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="R75" t="n">
-        <v>827</v>
+        <v>930</v>
       </c>
       <c r="S75" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -6028,28 +6028,28 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J76" t="n">
         <v>85</v>
       </c>
       <c r="K76" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L76" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="M76" t="n">
         <v>5</v>
       </c>
       <c r="N76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O76" t="n">
         <v>7</v>
       </c>
       <c r="P76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="R76" t="n">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="S76" t="n">
         <v>0.02</v>
@@ -6102,36 +6102,36 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J77" t="n">
         <v>90</v>
       </c>
       <c r="K77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L77" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P77" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R77" t="n">
-        <v>742</v>
+        <v>785</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -6176,36 +6176,36 @@
         </is>
       </c>
       <c r="I78" t="n">
+        <v>57</v>
+      </c>
+      <c r="J78" t="n">
+        <v>80</v>
+      </c>
+      <c r="K78" t="n">
+        <v>26</v>
+      </c>
+      <c r="L78" t="n">
         <v>54</v>
-      </c>
-      <c r="J78" t="n">
-        <v>82</v>
-      </c>
-      <c r="K78" t="n">
-        <v>24</v>
-      </c>
-      <c r="L78" t="n">
-        <v>57</v>
       </c>
       <c r="M78" t="n">
         <v>2</v>
       </c>
       <c r="N78" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O78" t="n">
         <v>3</v>
       </c>
       <c r="P78" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R78" t="n">
-        <v>640</v>
+        <v>883</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -6253,36 +6253,36 @@
         <v>56</v>
       </c>
       <c r="J79" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K79" t="n">
         <v>23</v>
       </c>
       <c r="L79" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R79" t="n">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="S79" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -6327,10 +6327,10 @@
         <v>60</v>
       </c>
       <c r="J80" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K80" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L80" t="n">
         <v>56</v>
@@ -6339,24 +6339,24 @@
         <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O80" t="n">
         <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R80" t="n">
-        <v>636</v>
+        <v>726</v>
       </c>
       <c r="S80" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -6401,36 +6401,36 @@
         <v>57</v>
       </c>
       <c r="J81" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K81" t="n">
         <v>20</v>
       </c>
       <c r="L81" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M81" t="n">
+        <v>2</v>
+      </c>
+      <c r="N81" t="n">
+        <v>11</v>
+      </c>
+      <c r="O81" t="n">
         <v>3</v>
       </c>
-      <c r="N81" t="n">
-        <v>7</v>
-      </c>
-      <c r="O81" t="n">
-        <v>5</v>
-      </c>
       <c r="P81" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R81" t="n">
-        <v>758</v>
+        <v>740</v>
       </c>
       <c r="S81" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -6475,19 +6475,19 @@
         <v>57</v>
       </c>
       <c r="J82" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K82" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L82" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M82" t="n">
         <v>2</v>
       </c>
       <c r="N82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O82" t="n">
         <v>7</v>
@@ -6497,14 +6497,14 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R82" t="n">
-        <v>788</v>
+        <v>850</v>
       </c>
       <c r="S82" t="n">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -6552,10 +6552,10 @@
         <v>95</v>
       </c>
       <c r="K83" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L83" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M83" t="n">
         <v>5</v>
@@ -6571,11 +6571,11 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R83" t="n">
-        <v>808</v>
+        <v>964</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -6623,33 +6623,33 @@
         <v>65</v>
       </c>
       <c r="J84" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K84" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="L84" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="M84" t="n">
         <v>3</v>
       </c>
       <c r="N84" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R84" t="n">
-        <v>831</v>
+        <v>931</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -6700,7 +6700,7 @@
         <v>84</v>
       </c>
       <c r="K85" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L85" t="n">
         <v>80</v>
@@ -6712,10 +6712,10 @@
         <v>7</v>
       </c>
       <c r="O85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P85" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="R85" t="n">
-        <v>771</v>
+        <v>843</v>
       </c>
       <c r="S85" t="n">
-        <v>0.29</v>
+        <v>0.09</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -6768,36 +6768,36 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J86" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K86" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L86" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="M86" t="n">
         <v>3</v>
       </c>
       <c r="N86" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O86" t="n">
         <v>5</v>
       </c>
       <c r="P86" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R86" t="n">
-        <v>730</v>
+        <v>814</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -6845,33 +6845,33 @@
         <v>57</v>
       </c>
       <c r="J87" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K87" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L87" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M87" t="n">
         <v>3</v>
       </c>
       <c r="N87" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R87" t="n">
-        <v>796</v>
+        <v>942</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -6916,39 +6916,39 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J88" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K88" t="n">
         <v>24</v>
       </c>
       <c r="L88" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M88" t="n">
         <v>1</v>
       </c>
       <c r="N88" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O88" t="n">
         <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R88" t="n">
-        <v>758</v>
+        <v>793</v>
       </c>
       <c r="S88" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -6990,16 +6990,16 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J89" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K89" t="n">
         <v>18</v>
       </c>
       <c r="L89" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M89" t="n">
         <v>2</v>
@@ -7008,18 +7008,18 @@
         <v>9</v>
       </c>
       <c r="O89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P89" t="n">
         <v>17</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R89" t="n">
-        <v>867</v>
+        <v>921</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -7064,13 +7064,13 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J90" t="n">
         <v>86</v>
       </c>
       <c r="K90" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L90" t="n">
         <v>69</v>
@@ -7079,13 +7079,13 @@
         <v>2</v>
       </c>
       <c r="N90" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O90" t="n">
         <v>3</v>
       </c>
       <c r="P90" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -7093,10 +7093,10 @@
         </is>
       </c>
       <c r="R90" t="n">
-        <v>697</v>
+        <v>662</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -7141,13 +7141,13 @@
         <v>68</v>
       </c>
       <c r="J91" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K91" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L91" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M91" t="n">
         <v>5</v>
@@ -7156,7 +7156,7 @@
         <v>13</v>
       </c>
       <c r="O91" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P91" t="n">
         <v>19</v>
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>816</v>
+        <v>852</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -7212,36 +7212,36 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J92" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K92" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L92" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="M92" t="n">
         <v>3</v>
       </c>
       <c r="N92" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O92" t="n">
         <v>5</v>
       </c>
       <c r="P92" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R92" t="n">
-        <v>800</v>
+        <v>919</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -7289,36 +7289,36 @@
         <v>60</v>
       </c>
       <c r="J93" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K93" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L93" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="M93" t="n">
         <v>2</v>
       </c>
       <c r="N93" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O93" t="n">
         <v>5</v>
       </c>
       <c r="P93" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R93" t="n">
-        <v>624</v>
+        <v>709</v>
       </c>
       <c r="S93" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -7363,13 +7363,13 @@
         <v>66</v>
       </c>
       <c r="J94" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K94" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L94" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M94" t="n">
         <v>6</v>
@@ -7381,15 +7381,15 @@
         <v>13</v>
       </c>
       <c r="P94" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R94" t="n">
-        <v>681</v>
+        <v>835</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -7434,28 +7434,28 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J95" t="n">
         <v>99</v>
       </c>
       <c r="K95" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L95" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N95" t="n">
         <v>6</v>
       </c>
       <c r="O95" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P95" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="R95" t="n">
-        <v>849</v>
+        <v>938</v>
       </c>
       <c r="S95" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -7508,28 +7508,28 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J96" t="n">
         <v>95</v>
       </c>
       <c r="K96" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L96" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N96" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="R96" t="n">
-        <v>728</v>
+        <v>843</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -7582,36 +7582,36 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J97" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K97" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L97" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M97" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N97" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P97" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R97" t="n">
-        <v>680</v>
+        <v>780</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
         <v>86</v>
       </c>
       <c r="J98" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K98" t="n">
         <v>15</v>
@@ -7668,24 +7668,24 @@
         <v>27</v>
       </c>
       <c r="M98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N98" t="n">
         <v>17</v>
       </c>
       <c r="O98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P98" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R98" t="n">
-        <v>692</v>
+        <v>842</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -7733,10 +7733,10 @@
         <v>62</v>
       </c>
       <c r="J99" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K99" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L99" t="n">
         <v>51</v>
@@ -7751,18 +7751,18 @@
         <v>5</v>
       </c>
       <c r="P99" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R99" t="n">
-        <v>670</v>
+        <v>817</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -7810,33 +7810,33 @@
         <v>100</v>
       </c>
       <c r="K100" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L100" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N100" t="n">
         <v>9</v>
       </c>
       <c r="O100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P100" t="n">
         <v>14</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R100" t="n">
-        <v>869</v>
+        <v>915</v>
       </c>
       <c r="S100" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -7881,13 +7881,13 @@
         <v>69</v>
       </c>
       <c r="J101" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K101" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L101" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M101" t="n">
         <v>3</v>
@@ -7903,11 +7903,11 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R101" t="n">
-        <v>781</v>
+        <v>795</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -7955,36 +7955,36 @@
         <v>57</v>
       </c>
       <c r="J102" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K102" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L102" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="M102" t="n">
         <v>2</v>
       </c>
       <c r="N102" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O102" t="n">
         <v>3</v>
       </c>
       <c r="P102" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R102" t="n">
-        <v>799</v>
+        <v>924</v>
       </c>
       <c r="S102" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J103" t="n">
         <v>112</v>
@@ -8035,16 +8035,16 @@
         <v>17</v>
       </c>
       <c r="L103" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M103" t="n">
         <v>2</v>
       </c>
       <c r="N103" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P103" t="n">
         <v>15</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="R103" t="n">
-        <v>853</v>
+        <v>916</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -8106,33 +8106,33 @@
         <v>104</v>
       </c>
       <c r="K104" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L104" t="n">
         <v>28</v>
       </c>
       <c r="M104" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N104" t="n">
         <v>15</v>
       </c>
       <c r="O104" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P104" t="n">
         <v>30</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R104" t="n">
-        <v>703</v>
+        <v>822</v>
       </c>
       <c r="S104" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -8177,33 +8177,33 @@
         <v>72</v>
       </c>
       <c r="J105" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K105" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L105" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="M105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N105" t="n">
         <v>13</v>
       </c>
       <c r="O105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P105" t="n">
         <v>19</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R105" t="n">
-        <v>813</v>
+        <v>937</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -8248,39 +8248,39 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J106" t="n">
         <v>87</v>
       </c>
       <c r="K106" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L106" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M106" t="n">
         <v>2</v>
       </c>
       <c r="N106" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P106" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R106" t="n">
-        <v>804</v>
+        <v>781</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -8322,39 +8322,39 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J107" t="n">
         <v>97</v>
       </c>
       <c r="K107" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L107" t="n">
         <v>54</v>
       </c>
       <c r="M107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N107" t="n">
         <v>9</v>
       </c>
       <c r="O107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P107" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R107" t="n">
-        <v>704</v>
+        <v>806</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -8399,33 +8399,33 @@
         <v>57</v>
       </c>
       <c r="J108" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K108" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L108" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="M108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N108" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P108" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R108" t="n">
-        <v>795</v>
+        <v>891</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -8473,36 +8473,36 @@
         <v>61</v>
       </c>
       <c r="J109" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K109" t="n">
         <v>25</v>
       </c>
       <c r="L109" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M109" t="n">
         <v>5</v>
       </c>
       <c r="N109" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O109" t="n">
         <v>7</v>
       </c>
       <c r="P109" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R109" t="n">
-        <v>768</v>
+        <v>750</v>
       </c>
       <c r="S109" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -8550,10 +8550,10 @@
         <v>105</v>
       </c>
       <c r="K110" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L110" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M110" t="n">
         <v>3</v>
@@ -8562,18 +8562,18 @@
         <v>7</v>
       </c>
       <c r="O110" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P110" t="n">
         <v>13</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R110" t="n">
-        <v>769</v>
+        <v>924</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -8618,16 +8618,16 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J111" t="n">
         <v>95</v>
       </c>
       <c r="K111" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L111" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M111" t="n">
         <v>2</v>
@@ -8639,15 +8639,15 @@
         <v>3</v>
       </c>
       <c r="P111" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R111" t="n">
-        <v>680</v>
+        <v>781</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -8692,39 +8692,39 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J112" t="n">
         <v>91</v>
       </c>
       <c r="K112" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L112" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M112" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N112" t="n">
         <v>9</v>
       </c>
       <c r="O112" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P112" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R112" t="n">
-        <v>742</v>
+        <v>765</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -8766,28 +8766,28 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J113" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K113" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L113" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M113" t="n">
         <v>2</v>
       </c>
       <c r="N113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O113" t="n">
         <v>5</v>
       </c>
       <c r="P113" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="R113" t="n">
-        <v>713</v>
+        <v>775</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -8840,16 +8840,16 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J114" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K114" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L114" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M114" t="n">
         <v>2</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="R114" t="n">
-        <v>760</v>
+        <v>815</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -8914,22 +8914,22 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J115" t="n">
         <v>83</v>
       </c>
       <c r="K115" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L115" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M115" t="n">
         <v>2</v>
       </c>
       <c r="N115" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O115" t="n">
         <v>3</v>
@@ -8939,14 +8939,14 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R115" t="n">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="S115" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -8988,16 +8988,16 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J116" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K116" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L116" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M116" t="n">
         <v>3</v>
@@ -9013,11 +9013,11 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R116" t="n">
-        <v>823</v>
+        <v>862</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -9065,36 +9065,36 @@
         <v>57</v>
       </c>
       <c r="J117" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K117" t="n">
         <v>20</v>
       </c>
       <c r="L117" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M117" t="n">
         <v>3</v>
       </c>
       <c r="N117" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O117" t="n">
         <v>5</v>
       </c>
       <c r="P117" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R117" t="n">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="S117" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -9139,36 +9139,36 @@
         <v>59</v>
       </c>
       <c r="J118" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K118" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L118" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M118" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N118" t="n">
+        <v>14</v>
+      </c>
+      <c r="O118" t="n">
         <v>8</v>
       </c>
-      <c r="O118" t="n">
-        <v>7</v>
-      </c>
       <c r="P118" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R118" t="n">
-        <v>799</v>
+        <v>931</v>
       </c>
       <c r="S118" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -9210,16 +9210,16 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J119" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K119" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L119" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="M119" t="n">
         <v>1</v>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="R119" t="n">
-        <v>771</v>
+        <v>809</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -9287,36 +9287,36 @@
         <v>59</v>
       </c>
       <c r="J120" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K120" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L120" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R120" t="n">
-        <v>776</v>
+        <v>821</v>
       </c>
       <c r="S120" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -9364,33 +9364,33 @@
         <v>79</v>
       </c>
       <c r="K121" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L121" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M121" t="n">
         <v>5</v>
       </c>
       <c r="N121" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O121" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P121" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>1/4/1 17:00 LMT</t>
+          <t>1/3/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R121" t="n">
-        <v>823</v>
+        <v>958</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -9432,16 +9432,16 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J122" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K122" t="n">
         <v>24</v>
       </c>
       <c r="L122" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M122" t="n">
         <v>2</v>
@@ -9450,21 +9450,21 @@
         <v>5</v>
       </c>
       <c r="O122" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P122" t="n">
         <v>15</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R122" t="n">
-        <v>758</v>
+        <v>832</v>
       </c>
       <c r="S122" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J123" t="n">
         <v>107</v>
@@ -9515,7 +9515,7 @@
         <v>18</v>
       </c>
       <c r="L123" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M123" t="n">
         <v>2</v>
@@ -9524,18 +9524,18 @@
         <v>5</v>
       </c>
       <c r="O123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P123" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R123" t="n">
-        <v>847</v>
+        <v>824</v>
       </c>
       <c r="S123" t="n">
         <v>0.01</v>
@@ -9586,10 +9586,10 @@
         <v>90</v>
       </c>
       <c r="K124" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L124" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M124" t="n">
         <v>3</v>
@@ -9601,18 +9601,18 @@
         <v>9</v>
       </c>
       <c r="P124" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R124" t="n">
-        <v>850</v>
+        <v>950</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -9657,25 +9657,25 @@
         <v>80</v>
       </c>
       <c r="J125" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K125" t="n">
         <v>13</v>
       </c>
       <c r="L125" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N125" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O125" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P125" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="R125" t="n">
-        <v>808</v>
+        <v>892</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -9731,33 +9731,33 @@
         <v>62</v>
       </c>
       <c r="J126" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K126" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L126" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="M126" t="n">
         <v>5</v>
       </c>
       <c r="N126" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O126" t="n">
         <v>7</v>
       </c>
       <c r="P126" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R126" t="n">
-        <v>796</v>
+        <v>944</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -9805,33 +9805,33 @@
         <v>66</v>
       </c>
       <c r="J127" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K127" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L127" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M127" t="n">
+        <v>2</v>
+      </c>
+      <c r="N127" t="n">
+        <v>9</v>
+      </c>
+      <c r="O127" t="n">
         <v>3</v>
       </c>
-      <c r="N127" t="n">
-        <v>7</v>
-      </c>
-      <c r="O127" t="n">
-        <v>5</v>
-      </c>
       <c r="P127" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R127" t="n">
-        <v>862</v>
+        <v>942</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -9879,33 +9879,33 @@
         <v>53</v>
       </c>
       <c r="J128" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K128" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L128" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M128" t="n">
         <v>2</v>
       </c>
       <c r="N128" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O128" t="n">
         <v>3</v>
       </c>
       <c r="P128" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R128" t="n">
-        <v>800</v>
+        <v>889</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -9965,7 +9965,7 @@
         <v>3</v>
       </c>
       <c r="N129" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O129" t="n">
         <v>7</v>
@@ -9975,14 +9975,14 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R129" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="S129" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -10024,16 +10024,16 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J130" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K130" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L130" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="M130" t="n">
         <v>3</v>
@@ -10049,14 +10049,14 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1/4/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R130" t="n">
-        <v>856</v>
+        <v>931</v>
       </c>
       <c r="S130" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J131" t="n">
         <v>106</v>
@@ -10107,7 +10107,7 @@
         <v>20</v>
       </c>
       <c r="L131" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M131" t="n">
         <v>2</v>
@@ -10119,7 +10119,7 @@
         <v>6</v>
       </c>
       <c r="P131" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         </is>
       </c>
       <c r="R131" t="n">
-        <v>813</v>
+        <v>879</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -10175,13 +10175,13 @@
         <v>66</v>
       </c>
       <c r="J132" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K132" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L132" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M132" t="n">
         <v>6</v>
@@ -10197,11 +10197,11 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R132" t="n">
-        <v>860</v>
+        <v>950</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -10246,25 +10246,25 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J133" t="n">
         <v>97</v>
       </c>
       <c r="K133" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L133" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N133" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P133" t="n">
         <v>14</v>
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="R133" t="n">
-        <v>676</v>
+        <v>774</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -10326,33 +10326,33 @@
         <v>80</v>
       </c>
       <c r="K134" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L134" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M134" t="n">
         <v>1</v>
       </c>
       <c r="N134" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O134" t="n">
         <v>1</v>
       </c>
       <c r="P134" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R134" t="n">
-        <v>704</v>
+        <v>683</v>
       </c>
       <c r="S134" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -10394,36 +10394,36 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J135" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K135" t="n">
         <v>16</v>
       </c>
       <c r="L135" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M135" t="n">
         <v>2</v>
       </c>
       <c r="N135" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O135" t="n">
         <v>6</v>
       </c>
       <c r="P135" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1/3/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R135" t="n">
-        <v>847</v>
+        <v>907</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -10471,36 +10471,36 @@
         <v>57</v>
       </c>
       <c r="J136" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K136" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L136" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M136" t="n">
         <v>2</v>
       </c>
       <c r="N136" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O136" t="n">
         <v>3</v>
       </c>
       <c r="P136" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R136" t="n">
-        <v>771</v>
+        <v>827</v>
       </c>
       <c r="S136" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -10542,22 +10542,22 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J137" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K137" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L137" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M137" t="n">
         <v>3</v>
       </c>
       <c r="N137" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O137" t="n">
         <v>5</v>
@@ -10567,14 +10567,14 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R137" t="n">
-        <v>679</v>
+        <v>828</v>
       </c>
       <c r="S137" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -10619,13 +10619,13 @@
         <v>83</v>
       </c>
       <c r="J138" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K138" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L138" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M138" t="n">
         <v>5</v>
@@ -10634,10 +10634,10 @@
         <v>11</v>
       </c>
       <c r="O138" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P138" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="R138" t="n">
-        <v>784</v>
+        <v>903</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -10690,36 +10690,36 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J139" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K139" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L139" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M139" t="n">
         <v>2</v>
       </c>
       <c r="N139" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O139" t="n">
         <v>3</v>
       </c>
       <c r="P139" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R139" t="n">
-        <v>781</v>
+        <v>812</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -10773,16 +10773,16 @@
         <v>25</v>
       </c>
       <c r="L140" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M140" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N140" t="n">
         <v>8</v>
       </c>
       <c r="O140" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P140" t="n">
         <v>14</v>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="R140" t="n">
-        <v>735</v>
+        <v>768</v>
       </c>
       <c r="S140" t="n">
         <v>0.03</v>
@@ -10838,36 +10838,36 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J141" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K141" t="n">
         <v>16</v>
       </c>
       <c r="L141" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M141" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N141" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O141" t="n">
         <v>6</v>
       </c>
       <c r="P141" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R141" t="n">
-        <v>769</v>
+        <v>848</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J142" t="n">
         <v>92</v>
@@ -10921,30 +10921,30 @@
         <v>22</v>
       </c>
       <c r="L142" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M142" t="n">
         <v>3</v>
       </c>
       <c r="N142" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O142" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P142" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R142" t="n">
-        <v>827</v>
+        <v>841</v>
       </c>
       <c r="S142" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -10986,36 +10986,36 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J143" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K143" t="n">
         <v>20</v>
       </c>
       <c r="L143" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N143" t="n">
         <v>10</v>
       </c>
       <c r="O143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P143" t="n">
         <v>15</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R143" t="n">
-        <v>791</v>
+        <v>927</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -11066,33 +11066,33 @@
         <v>81</v>
       </c>
       <c r="K144" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L144" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M144" t="n">
         <v>1</v>
       </c>
       <c r="N144" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O144" t="n">
         <v>1</v>
       </c>
       <c r="P144" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R144" t="n">
-        <v>758</v>
+        <v>694</v>
       </c>
       <c r="S144" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -11134,28 +11134,28 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J145" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K145" t="n">
         <v>15</v>
       </c>
       <c r="L145" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N145" t="n">
         <v>9</v>
       </c>
       <c r="O145" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P145" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         </is>
       </c>
       <c r="R145" t="n">
-        <v>847</v>
+        <v>813</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -11208,39 +11208,39 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J146" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K146" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L146" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M146" t="n">
         <v>3</v>
       </c>
       <c r="N146" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O146" t="n">
         <v>5</v>
       </c>
       <c r="P146" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R146" t="n">
-        <v>788</v>
+        <v>875</v>
       </c>
       <c r="S146" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -11291,19 +11291,19 @@
         <v>19</v>
       </c>
       <c r="L147" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M147" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N147" t="n">
         <v>8</v>
       </c>
       <c r="O147" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P147" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         </is>
       </c>
       <c r="R147" t="n">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="S147" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J148" t="n">
         <v>82</v>
@@ -11365,27 +11365,27 @@
         <v>20</v>
       </c>
       <c r="L148" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M148" t="n">
         <v>2</v>
       </c>
       <c r="N148" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O148" t="n">
         <v>3</v>
       </c>
       <c r="P148" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R148" t="n">
-        <v>803</v>
+        <v>887</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -11430,7 +11430,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J149" t="n">
         <v>92</v>
@@ -11439,19 +11439,19 @@
         <v>22</v>
       </c>
       <c r="L149" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M149" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N149" t="n">
         <v>14</v>
       </c>
       <c r="O149" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P149" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="R149" t="n">
-        <v>735</v>
+        <v>821</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -11507,13 +11507,13 @@
         <v>51</v>
       </c>
       <c r="J150" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K150" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L150" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -11529,11 +11529,11 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R150" t="n">
-        <v>628</v>
+        <v>725</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J151" t="n">
         <v>93</v>
@@ -11590,27 +11590,27 @@
         <v>30</v>
       </c>
       <c r="M151" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N151" t="n">
         <v>19</v>
       </c>
       <c r="O151" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P151" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R151" t="n">
-        <v>703</v>
+        <v>803</v>
       </c>
       <c r="S151" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>18</v>
       </c>
       <c r="L152" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M152" t="n">
         <v>2</v>
@@ -11670,18 +11670,18 @@
         <v>11</v>
       </c>
       <c r="O152" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P152" t="n">
         <v>25</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R152" t="n">
-        <v>840</v>
+        <v>901</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -11735,27 +11735,27 @@
         <v>17</v>
       </c>
       <c r="L153" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M153" t="n">
+        <v>2</v>
+      </c>
+      <c r="N153" t="n">
+        <v>8</v>
+      </c>
+      <c r="O153" t="n">
         <v>3</v>
       </c>
-      <c r="N153" t="n">
-        <v>7</v>
-      </c>
-      <c r="O153" t="n">
-        <v>5</v>
-      </c>
       <c r="P153" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R153" t="n">
-        <v>699</v>
+        <v>812</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -11803,25 +11803,25 @@
         <v>57</v>
       </c>
       <c r="J154" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K154" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L154" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M154" t="n">
         <v>5</v>
       </c>
       <c r="N154" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O154" t="n">
         <v>6</v>
       </c>
       <c r="P154" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         </is>
       </c>
       <c r="R154" t="n">
-        <v>692</v>
+        <v>831</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -11874,28 +11874,28 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J155" t="n">
         <v>77</v>
       </c>
       <c r="K155" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L155" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M155" t="n">
         <v>3</v>
       </c>
       <c r="N155" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O155" t="n">
         <v>5</v>
       </c>
       <c r="P155" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="R155" t="n">
-        <v>692</v>
+        <v>676</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -11957,30 +11957,30 @@
         <v>19</v>
       </c>
       <c r="L156" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M156" t="n">
         <v>2</v>
       </c>
       <c r="N156" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O156" t="n">
         <v>3</v>
       </c>
       <c r="P156" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R156" t="n">
-        <v>753</v>
+        <v>881</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -12022,16 +12022,16 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J157" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K157" t="n">
         <v>21</v>
       </c>
       <c r="L157" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M157" t="n">
         <v>2</v>
@@ -12040,21 +12040,21 @@
         <v>7</v>
       </c>
       <c r="O157" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P157" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R157" t="n">
-        <v>678</v>
+        <v>814</v>
       </c>
       <c r="S157" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -12096,36 +12096,36 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J158" t="n">
         <v>92</v>
       </c>
       <c r="K158" t="n">
+        <v>18</v>
+      </c>
+      <c r="L158" t="n">
+        <v>60</v>
+      </c>
+      <c r="M158" t="n">
+        <v>3</v>
+      </c>
+      <c r="N158" t="n">
         <v>16</v>
       </c>
-      <c r="L158" t="n">
-        <v>58</v>
-      </c>
-      <c r="M158" t="n">
+      <c r="O158" t="n">
         <v>5</v>
       </c>
-      <c r="N158" t="n">
-        <v>8</v>
-      </c>
-      <c r="O158" t="n">
-        <v>7</v>
-      </c>
       <c r="P158" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R158" t="n">
-        <v>775</v>
+        <v>866</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>

--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -552,36 +552,36 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J2" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L2" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>948</v>
+        <v>795</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -617,7 +617,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -629,25 +629,25 @@
         <v>87</v>
       </c>
       <c r="J3" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>905</v>
+        <v>862</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -691,7 +691,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -700,39 +700,39 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J4" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L4" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O4" t="n">
         <v>7</v>
       </c>
       <c r="P4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>809</v>
+        <v>737</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -774,36 +774,36 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J5" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K5" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L5" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" t="n">
-        <v>9</v>
-      </c>
-      <c r="O5" t="n">
-        <v>5</v>
-      </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="S5" t="n">
         <v>0.1</v>
@@ -839,7 +839,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -851,25 +851,25 @@
         <v>85</v>
       </c>
       <c r="J6" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>922</v>
+        <v>872</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -922,28 +922,28 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J7" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L7" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>775</v>
+        <v>532</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -996,28 +996,28 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J8" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L8" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N8" t="n">
         <v>13</v>
       </c>
       <c r="O8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>928</v>
+        <v>859</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1070,39 +1070,39 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J9" t="n">
+        <v>87</v>
+      </c>
+      <c r="K9" t="n">
+        <v>27</v>
+      </c>
+      <c r="L9" t="n">
         <v>89</v>
-      </c>
-      <c r="K9" t="n">
-        <v>25</v>
-      </c>
-      <c r="L9" t="n">
-        <v>80</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R9" t="n">
         <v>771</v>
       </c>
       <c r="S9" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1144,39 +1144,39 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J10" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="M10" t="n">
         <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>909</v>
+        <v>820</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1218,39 +1218,39 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J11" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K11" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L11" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="S11" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1292,36 +1292,36 @@
         </is>
       </c>
       <c r="I12" t="n">
+        <v>62</v>
+      </c>
+      <c r="J12" t="n">
+        <v>92</v>
+      </c>
+      <c r="K12" t="n">
+        <v>22</v>
+      </c>
+      <c r="L12" t="n">
         <v>60</v>
-      </c>
-      <c r="J12" t="n">
-        <v>93</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L12" t="n">
-        <v>64</v>
       </c>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
         <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>926</v>
+        <v>771</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1366,36 +1366,36 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J13" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K13" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L13" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>775</v>
+        <v>852</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1443,36 +1443,36 @@
         <v>58</v>
       </c>
       <c r="J14" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K14" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L14" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>734</v>
+        <v>714</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1514,36 +1514,36 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J15" t="n">
         <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L15" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>945</v>
+        <v>855</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1588,39 +1588,39 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J16" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="K16" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="L16" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>791</v>
+        <v>709</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1665,36 +1665,36 @@
         <v>59</v>
       </c>
       <c r="J17" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K17" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L17" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>782</v>
+        <v>711</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1736,39 +1736,39 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J18" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="K18" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L18" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="M18" t="n">
         <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P18" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>730</v>
+        <v>668</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1810,39 +1810,39 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J19" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L19" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M19" t="n">
         <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P19" t="n">
         <v>19</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>886</v>
+        <v>717</v>
       </c>
       <c r="S19" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1884,39 +1884,39 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J20" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K20" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L20" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>929</v>
+        <v>793</v>
       </c>
       <c r="S20" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1958,36 +1958,36 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J21" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K21" t="n">
+        <v>22</v>
+      </c>
+      <c r="L21" t="n">
+        <v>61</v>
+      </c>
+      <c r="M21" t="n">
+        <v>10</v>
+      </c>
+      <c r="N21" t="n">
+        <v>15</v>
+      </c>
+      <c r="O21" t="n">
+        <v>15</v>
+      </c>
+      <c r="P21" t="n">
         <v>23</v>
       </c>
-      <c r="L21" t="n">
-        <v>71</v>
-      </c>
-      <c r="M21" t="n">
-        <v>8</v>
-      </c>
-      <c r="N21" t="n">
-        <v>13</v>
-      </c>
-      <c r="O21" t="n">
-        <v>10</v>
-      </c>
-      <c r="P21" t="n">
-        <v>19</v>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>920</v>
+        <v>825</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2032,39 +2032,39 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J22" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K22" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L22" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
         <v>6</v>
       </c>
       <c r="P22" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>966</v>
+        <v>784</v>
       </c>
       <c r="S22" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2109,36 +2109,36 @@
         <v>84</v>
       </c>
       <c r="J23" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K23" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L23" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
         <v>6</v>
       </c>
       <c r="P23" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>924</v>
+        <v>816</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2180,22 +2180,22 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J24" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K24" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L24" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
         <v>6</v>
@@ -2205,11 +2205,11 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2254,36 +2254,36 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J25" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
+        <v>9</v>
+      </c>
+      <c r="O25" t="n">
         <v>8</v>
       </c>
-      <c r="O25" t="n">
-        <v>10</v>
-      </c>
       <c r="P25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>924</v>
+        <v>768</v>
       </c>
       <c r="S25" t="n">
         <v>0.11</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2328,39 +2328,39 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J26" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K26" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L26" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="M26" t="n">
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>794</v>
+        <v>833</v>
       </c>
       <c r="S26" t="n">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2402,39 +2402,39 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J27" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K27" t="n">
         <v>21</v>
       </c>
       <c r="L27" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>956</v>
+        <v>842</v>
       </c>
       <c r="S27" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2476,36 +2476,36 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J28" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L28" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O28" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P28" t="n">
         <v>22</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>917</v>
+        <v>870</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2550,36 +2550,36 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J29" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K29" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L29" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="M29" t="n">
         <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>781</v>
+        <v>597</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2624,36 +2624,36 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J30" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O30" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P30" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>920</v>
+        <v>876</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2698,39 +2698,39 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J31" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K31" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L31" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
       <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="n">
         <v>5</v>
       </c>
-      <c r="O31" t="n">
-        <v>6</v>
-      </c>
       <c r="P31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>812</v>
+        <v>729</v>
       </c>
       <c r="S31" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2772,39 +2772,39 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J32" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K32" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="L32" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M32" t="n">
         <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>810</v>
+        <v>711</v>
       </c>
       <c r="S32" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2846,39 +2846,39 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J33" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="M33" t="n">
         <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>676</v>
+        <v>698</v>
       </c>
       <c r="S33" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2923,36 +2923,36 @@
         <v>66</v>
       </c>
       <c r="J34" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K34" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L34" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M34" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" t="n">
         <v>3</v>
       </c>
-      <c r="N34" t="n">
-        <v>9</v>
-      </c>
-      <c r="O34" t="n">
-        <v>5</v>
-      </c>
       <c r="P34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>888</v>
+        <v>811</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2994,39 +2994,39 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J35" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K35" t="n">
+        <v>19</v>
+      </c>
+      <c r="L35" t="n">
+        <v>54</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>10</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P35" t="n">
         <v>15</v>
       </c>
-      <c r="L35" t="n">
-        <v>59</v>
-      </c>
-      <c r="M35" t="n">
-        <v>6</v>
-      </c>
-      <c r="N35" t="n">
-        <v>11</v>
-      </c>
-      <c r="O35" t="n">
-        <v>8</v>
-      </c>
-      <c r="P35" t="n">
-        <v>16</v>
-      </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>886</v>
+        <v>730</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3071,36 +3071,36 @@
         <v>58</v>
       </c>
       <c r="J36" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K36" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L36" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P36" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>773</v>
+        <v>651</v>
       </c>
       <c r="S36" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3142,39 +3142,39 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J37" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K37" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L37" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M37" t="n">
         <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O37" t="n">
         <v>5</v>
       </c>
       <c r="P37" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3219,33 +3219,33 @@
         <v>86</v>
       </c>
       <c r="J38" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K38" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L38" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>930</v>
+        <v>862</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3290,16 +3290,16 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J39" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K39" t="n">
         <v>23</v>
       </c>
       <c r="L39" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="M39" t="n">
         <v>5</v>
@@ -3311,15 +3311,15 @@
         <v>13</v>
       </c>
       <c r="P39" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>960</v>
+        <v>816</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3364,39 +3364,39 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J40" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K40" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L40" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="M40" t="n">
         <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P40" t="n">
         <v>15</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1/7/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>824</v>
+        <v>796</v>
       </c>
       <c r="S40" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3438,39 +3438,39 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J41" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K41" t="n">
+        <v>42</v>
+      </c>
+      <c r="L41" t="n">
+        <v>81</v>
+      </c>
+      <c r="M41" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" t="n">
+        <v>17</v>
+      </c>
+      <c r="O41" t="n">
+        <v>7</v>
+      </c>
+      <c r="P41" t="n">
         <v>28</v>
       </c>
-      <c r="L41" t="n">
-        <v>58</v>
-      </c>
-      <c r="M41" t="n">
-        <v>2</v>
-      </c>
-      <c r="N41" t="n">
-        <v>15</v>
-      </c>
-      <c r="O41" t="n">
-        <v>3</v>
-      </c>
-      <c r="P41" t="n">
-        <v>24</v>
-      </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>801</v>
+        <v>724</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3512,39 +3512,39 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J42" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K42" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L42" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="M42" t="n">
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>787</v>
+        <v>765</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3586,39 +3586,39 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J43" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K43" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L43" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P43" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1/7/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>934</v>
+        <v>824</v>
       </c>
       <c r="S43" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3660,39 +3660,39 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J44" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K44" t="n">
+        <v>33</v>
+      </c>
+      <c r="L44" t="n">
+        <v>86</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6</v>
+      </c>
+      <c r="N44" t="n">
+        <v>14</v>
+      </c>
+      <c r="O44" t="n">
+        <v>7</v>
+      </c>
+      <c r="P44" t="n">
         <v>22</v>
       </c>
-      <c r="L44" t="n">
-        <v>64</v>
-      </c>
-      <c r="M44" t="n">
-        <v>3</v>
-      </c>
-      <c r="N44" t="n">
-        <v>11</v>
-      </c>
-      <c r="O44" t="n">
-        <v>5</v>
-      </c>
-      <c r="P44" t="n">
-        <v>18</v>
-      </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>854</v>
+        <v>647</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3734,36 +3734,36 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J45" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L45" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N45" t="n">
+        <v>15</v>
+      </c>
+      <c r="O45" t="n">
         <v>11</v>
       </c>
-      <c r="O45" t="n">
-        <v>5</v>
-      </c>
       <c r="P45" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>931</v>
+        <v>841</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3808,39 +3808,39 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J46" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K46" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L46" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
         <v>6</v>
       </c>
       <c r="P46" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R46" t="n">
-        <v>927</v>
+        <v>777</v>
       </c>
       <c r="S46" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3882,36 +3882,36 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J47" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K47" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L47" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P47" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>744</v>
+        <v>719</v>
       </c>
       <c r="S47" t="n">
         <v>0.02</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3956,36 +3956,36 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J48" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K48" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L48" t="n">
         <v>55</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N48" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P48" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>923</v>
+        <v>862</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4030,28 +4030,28 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J49" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K49" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L49" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N49" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P49" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>784</v>
+        <v>643</v>
       </c>
       <c r="S49" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4104,36 +4104,36 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J50" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K50" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L50" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N50" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O50" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P50" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4181,25 +4181,25 @@
         <v>87</v>
       </c>
       <c r="J51" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K51" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L51" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="M51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N51" t="n">
+        <v>14</v>
+      </c>
+      <c r="O51" t="n">
         <v>11</v>
       </c>
-      <c r="O51" t="n">
-        <v>9</v>
-      </c>
       <c r="P51" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="R51" t="n">
-        <v>892</v>
+        <v>870</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4252,39 +4252,39 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J52" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K52" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L52" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>823</v>
+        <v>780</v>
       </c>
       <c r="S52" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4326,28 +4326,28 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J53" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K53" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L53" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="M53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O53" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P53" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -4355,10 +4355,10 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>875</v>
+        <v>825</v>
       </c>
       <c r="S53" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4400,36 +4400,36 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J54" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="K54" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L54" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="M54" t="n">
         <v>2</v>
       </c>
       <c r="N54" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O54" t="n">
         <v>5</v>
       </c>
       <c r="P54" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R54" t="n">
-        <v>894</v>
+        <v>806</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4474,39 +4474,39 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J55" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K55" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L55" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N55" t="n">
         <v>17</v>
       </c>
       <c r="O55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P55" t="n">
         <v>26</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>850</v>
+        <v>863</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4551,36 +4551,36 @@
         <v>55</v>
       </c>
       <c r="J56" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K56" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L56" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M56" t="n">
         <v>2</v>
       </c>
       <c r="N56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O56" t="n">
         <v>3</v>
       </c>
       <c r="P56" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>817</v>
+        <v>633</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4622,39 +4622,39 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J57" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K57" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="L57" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N57" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P57" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>782</v>
+        <v>661</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4696,39 +4696,39 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J58" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K58" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L58" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P58" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>696</v>
+        <v>526</v>
       </c>
       <c r="S58" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4770,39 +4770,39 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J59" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K59" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="L59" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N59" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O59" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P59" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R59" t="n">
-        <v>802</v>
+        <v>702</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4844,28 +4844,28 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J60" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K60" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L60" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="M60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N60" t="n">
+        <v>14</v>
+      </c>
+      <c r="O60" t="n">
         <v>13</v>
       </c>
-      <c r="O60" t="n">
-        <v>15</v>
-      </c>
       <c r="P60" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>885</v>
+        <v>835</v>
       </c>
       <c r="S60" t="n">
         <v>0.08</v>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4921,33 +4921,33 @@
         <v>72</v>
       </c>
       <c r="J61" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K61" t="n">
         <v>15</v>
       </c>
       <c r="L61" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M61" t="n">
+        <v>2</v>
+      </c>
+      <c r="N61" t="n">
+        <v>8</v>
+      </c>
+      <c r="O61" t="n">
         <v>3</v>
       </c>
-      <c r="N61" t="n">
-        <v>9</v>
-      </c>
-      <c r="O61" t="n">
-        <v>6</v>
-      </c>
       <c r="P61" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>951</v>
+        <v>860</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4992,39 +4992,39 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J62" t="n">
+        <v>83</v>
+      </c>
+      <c r="K62" t="n">
+        <v>33</v>
+      </c>
+      <c r="L62" t="n">
         <v>86</v>
-      </c>
-      <c r="K62" t="n">
-        <v>26</v>
-      </c>
-      <c r="L62" t="n">
-        <v>70</v>
       </c>
       <c r="M62" t="n">
         <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O62" t="n">
         <v>2</v>
       </c>
       <c r="P62" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R62" t="n">
-        <v>685</v>
+        <v>835</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5066,28 +5066,28 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J63" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K63" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L63" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="M63" t="n">
         <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O63" t="n">
         <v>6</v>
       </c>
       <c r="P63" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>889</v>
+        <v>857</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5140,39 +5140,39 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J64" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K64" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L64" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N64" t="n">
+        <v>5</v>
+      </c>
+      <c r="O64" t="n">
         <v>6</v>
       </c>
-      <c r="O64" t="n">
-        <v>7</v>
-      </c>
       <c r="P64" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R64" t="n">
-        <v>875</v>
+        <v>780</v>
       </c>
       <c r="S64" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5214,39 +5214,39 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J65" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K65" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L65" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="M65" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" t="n">
+        <v>11</v>
+      </c>
+      <c r="O65" t="n">
         <v>2</v>
       </c>
-      <c r="N65" t="n">
-        <v>9</v>
-      </c>
-      <c r="O65" t="n">
-        <v>3</v>
-      </c>
       <c r="P65" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R65" t="n">
-        <v>757</v>
+        <v>736</v>
       </c>
       <c r="S65" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5288,36 +5288,36 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J66" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K66" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="L66" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R66" t="n">
-        <v>875</v>
+        <v>846</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5362,39 +5362,39 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J67" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K67" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="L67" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P67" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R67" t="n">
-        <v>699</v>
+        <v>510</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5436,39 +5436,39 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J68" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K68" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L68" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="M68" t="n">
         <v>3</v>
       </c>
       <c r="N68" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O68" t="n">
         <v>8</v>
       </c>
       <c r="P68" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>1/5/1 17:00 LMT</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5510,39 +5510,39 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J69" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K69" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L69" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="M69" t="n">
         <v>5</v>
       </c>
       <c r="N69" t="n">
+        <v>11</v>
+      </c>
+      <c r="O69" t="n">
         <v>9</v>
       </c>
-      <c r="O69" t="n">
-        <v>10</v>
-      </c>
       <c r="P69" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>915</v>
+        <v>841</v>
       </c>
       <c r="S69" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5584,39 +5584,39 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J70" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K70" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="L70" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="M70" t="n">
         <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O70" t="n">
         <v>6</v>
       </c>
       <c r="P70" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R70" t="n">
-        <v>902</v>
+        <v>776</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5658,28 +5658,28 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J71" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K71" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="L71" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M71" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N71" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O71" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P71" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>824</v>
+        <v>847</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5732,39 +5732,39 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J72" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K72" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L72" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="M72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N72" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O72" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P72" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>890</v>
+        <v>863</v>
       </c>
       <c r="S72" t="n">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5806,39 +5806,39 @@
         </is>
       </c>
       <c r="I73" t="n">
+        <v>57</v>
+      </c>
+      <c r="J73" t="n">
+        <v>80</v>
+      </c>
+      <c r="K73" t="n">
+        <v>23</v>
+      </c>
+      <c r="L73" t="n">
         <v>55</v>
-      </c>
-      <c r="J73" t="n">
-        <v>81</v>
-      </c>
-      <c r="K73" t="n">
-        <v>21</v>
-      </c>
-      <c r="L73" t="n">
-        <v>64</v>
       </c>
       <c r="M73" t="n">
         <v>2</v>
       </c>
       <c r="N73" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O73" t="n">
         <v>3</v>
       </c>
       <c r="P73" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R73" t="n">
-        <v>735</v>
+        <v>765</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5880,39 +5880,39 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J74" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K74" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L74" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="M74" t="n">
         <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R74" t="n">
-        <v>795</v>
+        <v>753</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5954,39 +5954,39 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J75" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K75" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L75" t="n">
         <v>52</v>
       </c>
       <c r="M75" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O75" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P75" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R75" t="n">
-        <v>930</v>
+        <v>738</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6028,39 +6028,39 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J76" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K76" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L76" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="M76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N76" t="n">
         <v>9</v>
       </c>
       <c r="O76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P76" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R76" t="n">
-        <v>676</v>
+        <v>790</v>
       </c>
       <c r="S76" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6102,28 +6102,28 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="J77" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K77" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L77" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="M77" t="n">
+        <v>2</v>
+      </c>
+      <c r="N77" t="n">
+        <v>11</v>
+      </c>
+      <c r="O77" t="n">
         <v>3</v>
       </c>
-      <c r="N77" t="n">
-        <v>10</v>
-      </c>
-      <c r="O77" t="n">
-        <v>5</v>
-      </c>
       <c r="P77" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>785</v>
+        <v>813</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6176,39 +6176,39 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J78" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="K78" t="n">
+        <v>40</v>
+      </c>
+      <c r="L78" t="n">
+        <v>72</v>
+      </c>
+      <c r="M78" t="n">
+        <v>5</v>
+      </c>
+      <c r="N78" t="n">
+        <v>16</v>
+      </c>
+      <c r="O78" t="n">
+        <v>7</v>
+      </c>
+      <c r="P78" t="n">
         <v>26</v>
       </c>
-      <c r="L78" t="n">
-        <v>54</v>
-      </c>
-      <c r="M78" t="n">
-        <v>2</v>
-      </c>
-      <c r="N78" t="n">
-        <v>15</v>
-      </c>
-      <c r="O78" t="n">
-        <v>3</v>
-      </c>
-      <c r="P78" t="n">
-        <v>24</v>
-      </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R78" t="n">
-        <v>883</v>
+        <v>699</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6250,39 +6250,39 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J79" t="n">
+        <v>85</v>
+      </c>
+      <c r="K79" t="n">
+        <v>28</v>
+      </c>
+      <c r="L79" t="n">
         <v>87</v>
-      </c>
-      <c r="K79" t="n">
-        <v>23</v>
-      </c>
-      <c r="L79" t="n">
-        <v>74</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R79" t="n">
-        <v>743</v>
+        <v>760</v>
       </c>
       <c r="S79" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6327,36 +6327,36 @@
         <v>60</v>
       </c>
       <c r="J80" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K80" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L80" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M80" t="n">
         <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O80" t="n">
         <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R80" t="n">
-        <v>726</v>
+        <v>675</v>
       </c>
       <c r="S80" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6401,36 +6401,36 @@
         <v>57</v>
       </c>
       <c r="J81" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K81" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L81" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="M81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
+        <v>8</v>
+      </c>
+      <c r="O81" t="n">
+        <v>5</v>
+      </c>
+      <c r="P81" t="n">
         <v>11</v>
       </c>
-      <c r="O81" t="n">
-        <v>3</v>
-      </c>
-      <c r="P81" t="n">
-        <v>16</v>
-      </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R81" t="n">
-        <v>740</v>
+        <v>634</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6472,39 +6472,39 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J82" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K82" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L82" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M82" t="n">
         <v>2</v>
       </c>
       <c r="N82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R82" t="n">
-        <v>850</v>
+        <v>764</v>
       </c>
       <c r="S82" t="n">
-        <v>0.17</v>
+        <v>0.02</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6546,36 +6546,36 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J83" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K83" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L83" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="M83" t="n">
         <v>5</v>
       </c>
       <c r="N83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O83" t="n">
         <v>7</v>
       </c>
       <c r="P83" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R83" t="n">
-        <v>964</v>
+        <v>834</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6620,28 +6620,28 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J84" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K84" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L84" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="M84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N84" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O84" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="P84" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="R84" t="n">
-        <v>931</v>
+        <v>826</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6694,16 +6694,16 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J85" t="n">
         <v>84</v>
       </c>
       <c r="K85" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L85" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="M85" t="n">
         <v>3</v>
@@ -6719,14 +6719,14 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1/7/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R85" t="n">
-        <v>843</v>
+        <v>804</v>
       </c>
       <c r="S85" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6768,39 +6768,39 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J86" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K86" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L86" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M86" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O86" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P86" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1/7/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R86" t="n">
-        <v>814</v>
+        <v>677</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6842,36 +6842,36 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J87" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K87" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L87" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="M87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N87" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="O87" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P87" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R87" t="n">
-        <v>942</v>
+        <v>786</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6916,39 +6916,39 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J88" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K88" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L88" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M88" t="n">
         <v>1</v>
       </c>
       <c r="N88" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O88" t="n">
         <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R88" t="n">
-        <v>793</v>
+        <v>817</v>
       </c>
       <c r="S88" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6993,33 +6993,33 @@
         <v>86</v>
       </c>
       <c r="J89" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K89" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L89" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N89" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O89" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P89" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R89" t="n">
-        <v>921</v>
+        <v>860</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7064,39 +7064,39 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J90" t="n">
+        <v>81</v>
+      </c>
+      <c r="K90" t="n">
+        <v>34</v>
+      </c>
+      <c r="L90" t="n">
         <v>86</v>
-      </c>
-      <c r="K90" t="n">
-        <v>23</v>
-      </c>
-      <c r="L90" t="n">
-        <v>69</v>
       </c>
       <c r="M90" t="n">
         <v>2</v>
       </c>
       <c r="N90" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O90" t="n">
         <v>3</v>
       </c>
       <c r="P90" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R90" t="n">
-        <v>662</v>
+        <v>721</v>
       </c>
       <c r="S90" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7138,36 +7138,36 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J91" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K91" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L91" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="M91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N91" t="n">
+        <v>14</v>
+      </c>
+      <c r="O91" t="n">
         <v>13</v>
       </c>
-      <c r="O91" t="n">
-        <v>9</v>
-      </c>
       <c r="P91" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R91" t="n">
-        <v>852</v>
+        <v>840</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7212,36 +7212,36 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J92" t="n">
         <v>91</v>
       </c>
       <c r="K92" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L92" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="M92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N92" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P92" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1/7/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R92" t="n">
-        <v>919</v>
+        <v>855</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7286,39 +7286,39 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J93" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K93" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L93" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="M93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N93" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P93" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R93" t="n">
-        <v>709</v>
+        <v>637</v>
       </c>
       <c r="S93" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7360,36 +7360,36 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J94" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K94" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L94" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="M94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N94" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O94" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P94" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R94" t="n">
-        <v>835</v>
+        <v>795</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7434,39 +7434,39 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J95" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K95" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L95" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="M95" t="n">
         <v>2</v>
       </c>
       <c r="N95" t="n">
+        <v>7</v>
+      </c>
+      <c r="O95" t="n">
         <v>6</v>
       </c>
-      <c r="O95" t="n">
-        <v>7</v>
-      </c>
       <c r="P95" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R95" t="n">
-        <v>938</v>
+        <v>859</v>
       </c>
       <c r="S95" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7508,28 +7508,28 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J96" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K96" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="L96" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="M96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N96" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O96" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P96" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="R96" t="n">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7582,39 +7582,39 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J97" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="K97" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="L97" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="M97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N97" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P97" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R97" t="n">
-        <v>780</v>
+        <v>699</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7656,36 +7656,36 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J98" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K98" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L98" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="M98" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N98" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="O98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R98" t="n">
-        <v>842</v>
+        <v>790</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7730,39 +7730,39 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J99" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K99" t="n">
+        <v>34</v>
+      </c>
+      <c r="L99" t="n">
+        <v>67</v>
+      </c>
+      <c r="M99" t="n">
+        <v>3</v>
+      </c>
+      <c r="N99" t="n">
+        <v>9</v>
+      </c>
+      <c r="O99" t="n">
+        <v>7</v>
+      </c>
+      <c r="P99" t="n">
         <v>25</v>
       </c>
-      <c r="L99" t="n">
-        <v>51</v>
-      </c>
-      <c r="M99" t="n">
-        <v>2</v>
-      </c>
-      <c r="N99" t="n">
-        <v>8</v>
-      </c>
-      <c r="O99" t="n">
-        <v>5</v>
-      </c>
-      <c r="P99" t="n">
-        <v>22</v>
-      </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R99" t="n">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="S99" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7804,16 +7804,16 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J100" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K100" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L100" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M100" t="n">
         <v>3</v>
@@ -7825,18 +7825,18 @@
         <v>6</v>
       </c>
       <c r="P100" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R100" t="n">
-        <v>915</v>
+        <v>859</v>
       </c>
       <c r="S100" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7881,13 +7881,13 @@
         <v>69</v>
       </c>
       <c r="J101" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K101" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="L101" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="M101" t="n">
         <v>3</v>
@@ -7903,14 +7903,14 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R101" t="n">
-        <v>795</v>
+        <v>760</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7952,36 +7952,36 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J102" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K102" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L102" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="M102" t="n">
         <v>2</v>
       </c>
       <c r="N102" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O102" t="n">
         <v>3</v>
       </c>
       <c r="P102" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R102" t="n">
-        <v>924</v>
+        <v>856</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8026,36 +8026,36 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J103" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="K103" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L103" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="M103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N103" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P103" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R103" t="n">
-        <v>916</v>
+        <v>816</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8100,39 +8100,39 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J104" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K104" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L104" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="M104" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N104" t="n">
+        <v>18</v>
+      </c>
+      <c r="O104" t="n">
         <v>15</v>
       </c>
-      <c r="O104" t="n">
-        <v>13</v>
-      </c>
       <c r="P104" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R104" t="n">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="S104" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8174,36 +8174,36 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J105" t="n">
         <v>97</v>
       </c>
       <c r="K105" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L105" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="M105" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N105" t="n">
+        <v>14</v>
+      </c>
+      <c r="O105" t="n">
         <v>13</v>
       </c>
-      <c r="O105" t="n">
-        <v>9</v>
-      </c>
       <c r="P105" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R105" t="n">
-        <v>937</v>
+        <v>849</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8248,39 +8248,39 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J106" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="K106" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="L106" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="M106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N106" t="n">
+        <v>11</v>
+      </c>
+      <c r="O106" t="n">
         <v>8</v>
       </c>
-      <c r="O106" t="n">
-        <v>5</v>
-      </c>
       <c r="P106" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R106" t="n">
-        <v>781</v>
+        <v>690</v>
       </c>
       <c r="S106" t="n">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8322,39 +8322,39 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J107" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="K107" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L107" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="M107" t="n">
         <v>1</v>
       </c>
       <c r="N107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O107" t="n">
         <v>2</v>
       </c>
       <c r="P107" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R107" t="n">
-        <v>806</v>
+        <v>597</v>
       </c>
       <c r="S107" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8396,36 +8396,36 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J108" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K108" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L108" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="M108" t="n">
         <v>2</v>
       </c>
       <c r="N108" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O108" t="n">
         <v>3</v>
       </c>
       <c r="P108" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R108" t="n">
-        <v>891</v>
+        <v>802</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8473,36 +8473,36 @@
         <v>61</v>
       </c>
       <c r="J109" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K109" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L109" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M109" t="n">
         <v>5</v>
       </c>
       <c r="N109" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O109" t="n">
         <v>7</v>
       </c>
       <c r="P109" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R109" t="n">
-        <v>750</v>
+        <v>667</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8544,39 +8544,39 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J110" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="K110" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L110" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M110" t="n">
         <v>3</v>
       </c>
       <c r="N110" t="n">
+        <v>8</v>
+      </c>
+      <c r="O110" t="n">
         <v>7</v>
       </c>
-      <c r="O110" t="n">
-        <v>8</v>
-      </c>
       <c r="P110" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R110" t="n">
-        <v>924</v>
+        <v>854</v>
       </c>
       <c r="S110" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8618,39 +8618,39 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J111" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K111" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L111" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="M111" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" t="n">
+        <v>10</v>
+      </c>
+      <c r="O111" t="n">
         <v>2</v>
       </c>
-      <c r="N111" t="n">
-        <v>9</v>
-      </c>
-      <c r="O111" t="n">
-        <v>3</v>
-      </c>
       <c r="P111" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R111" t="n">
-        <v>781</v>
+        <v>847</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8692,39 +8692,39 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J112" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="K112" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L112" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="M112" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N112" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O112" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P112" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R112" t="n">
-        <v>765</v>
+        <v>786</v>
       </c>
       <c r="S112" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8769,25 +8769,25 @@
         <v>60</v>
       </c>
       <c r="J113" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K113" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L113" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="M113" t="n">
         <v>2</v>
       </c>
       <c r="N113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P113" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="R113" t="n">
-        <v>775</v>
+        <v>561</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8840,19 +8840,19 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J114" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K114" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L114" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="M114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N114" t="n">
         <v>9</v>
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="R114" t="n">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="S114" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8914,39 +8914,39 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J115" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K115" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L115" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="M115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N115" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O115" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P115" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R115" t="n">
-        <v>720</v>
+        <v>806</v>
       </c>
       <c r="S115" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8988,36 +8988,36 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J116" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K116" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L116" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N116" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O116" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P116" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R116" t="n">
-        <v>862</v>
+        <v>775</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9065,36 +9065,36 @@
         <v>57</v>
       </c>
       <c r="J117" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K117" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L117" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="M117" t="n">
         <v>3</v>
       </c>
       <c r="N117" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O117" t="n">
         <v>5</v>
       </c>
       <c r="P117" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R117" t="n">
-        <v>751</v>
+        <v>682</v>
       </c>
       <c r="S117" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9136,36 +9136,36 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J118" t="n">
         <v>81</v>
       </c>
       <c r="K118" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L118" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M118" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N118" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O118" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P118" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1/3/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R118" t="n">
-        <v>931</v>
+        <v>798</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9210,25 +9210,25 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J119" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K119" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L119" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="M119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N119" t="n">
         <v>8</v>
       </c>
       <c r="O119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P119" t="n">
         <v>14</v>
@@ -9239,10 +9239,10 @@
         </is>
       </c>
       <c r="R119" t="n">
-        <v>809</v>
+        <v>771</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9287,36 +9287,36 @@
         <v>59</v>
       </c>
       <c r="J120" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K120" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L120" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N120" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P120" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R120" t="n">
-        <v>821</v>
+        <v>730</v>
       </c>
       <c r="S120" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9358,39 +9358,39 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J121" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K121" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L121" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M121" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N121" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O121" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P121" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R121" t="n">
-        <v>958</v>
+        <v>774</v>
       </c>
       <c r="S121" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9432,39 +9432,39 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J122" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K122" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L122" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="M122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N122" t="n">
         <v>5</v>
       </c>
       <c r="O122" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P122" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R122" t="n">
-        <v>832</v>
+        <v>733</v>
       </c>
       <c r="S122" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9506,39 +9506,39 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J123" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K123" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L123" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="M123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N123" t="n">
+        <v>6</v>
+      </c>
+      <c r="O123" t="n">
         <v>5</v>
       </c>
-      <c r="O123" t="n">
-        <v>7</v>
-      </c>
       <c r="P123" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R123" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="S123" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9580,16 +9580,16 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J124" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K124" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L124" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M124" t="n">
         <v>3</v>
@@ -9605,14 +9605,14 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R124" t="n">
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="S124" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9654,28 +9654,28 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J125" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K125" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L125" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="M125" t="n">
         <v>2</v>
       </c>
       <c r="N125" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O125" t="n">
         <v>6</v>
       </c>
       <c r="P125" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="R125" t="n">
-        <v>892</v>
+        <v>862</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9728,36 +9728,36 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J126" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K126" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L126" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="M126" t="n">
+        <v>3</v>
+      </c>
+      <c r="N126" t="n">
+        <v>10</v>
+      </c>
+      <c r="O126" t="n">
         <v>5</v>
       </c>
-      <c r="N126" t="n">
-        <v>11</v>
-      </c>
-      <c r="O126" t="n">
-        <v>7</v>
-      </c>
       <c r="P126" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R126" t="n">
-        <v>944</v>
+        <v>850</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9802,28 +9802,28 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J127" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K127" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L127" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="M127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N127" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P127" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="R127" t="n">
-        <v>942</v>
+        <v>839</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9876,36 +9876,36 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J128" t="n">
         <v>84</v>
       </c>
       <c r="K128" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L128" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="M128" t="n">
         <v>2</v>
       </c>
       <c r="N128" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O128" t="n">
         <v>3</v>
       </c>
       <c r="P128" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R128" t="n">
-        <v>889</v>
+        <v>811</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9950,39 +9950,39 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J129" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K129" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L129" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="M129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N129" t="n">
+        <v>8</v>
+      </c>
+      <c r="O129" t="n">
         <v>6</v>
       </c>
-      <c r="O129" t="n">
-        <v>7</v>
-      </c>
       <c r="P129" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R129" t="n">
-        <v>838</v>
+        <v>877</v>
       </c>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10024,39 +10024,39 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J130" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K130" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L130" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="M130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N130" t="n">
         <v>8</v>
       </c>
       <c r="O130" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P130" t="n">
         <v>15</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>1/4/1 17:00 LMT</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R130" t="n">
-        <v>931</v>
+        <v>769</v>
       </c>
       <c r="S130" t="n">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -10101,36 +10101,36 @@
         <v>80</v>
       </c>
       <c r="J131" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K131" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L131" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="M131" t="n">
         <v>2</v>
       </c>
       <c r="N131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O131" t="n">
         <v>6</v>
       </c>
       <c r="P131" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R131" t="n">
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="S131" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -10172,36 +10172,36 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J132" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K132" t="n">
+        <v>20</v>
+      </c>
+      <c r="L132" t="n">
+        <v>57</v>
+      </c>
+      <c r="M132" t="n">
+        <v>3</v>
+      </c>
+      <c r="N132" t="n">
+        <v>13</v>
+      </c>
+      <c r="O132" t="n">
+        <v>5</v>
+      </c>
+      <c r="P132" t="n">
         <v>17</v>
       </c>
-      <c r="L132" t="n">
-        <v>61</v>
-      </c>
-      <c r="M132" t="n">
-        <v>6</v>
-      </c>
-      <c r="N132" t="n">
-        <v>10</v>
-      </c>
-      <c r="O132" t="n">
-        <v>8</v>
-      </c>
-      <c r="P132" t="n">
-        <v>15</v>
-      </c>
       <c r="Q132" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
       <c r="R132" t="n">
-        <v>950</v>
+        <v>832</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10246,28 +10246,28 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J133" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="K133" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L133" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="M133" t="n">
+        <v>1</v>
+      </c>
+      <c r="N133" t="n">
+        <v>9</v>
+      </c>
+      <c r="O133" t="n">
         <v>2</v>
       </c>
-      <c r="N133" t="n">
-        <v>8</v>
-      </c>
-      <c r="O133" t="n">
-        <v>3</v>
-      </c>
       <c r="P133" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -10275,10 +10275,10 @@
         </is>
       </c>
       <c r="R133" t="n">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="S133" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10320,39 +10320,39 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J134" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K134" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L134" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="M134" t="n">
         <v>1</v>
       </c>
       <c r="N134" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O134" t="n">
         <v>1</v>
       </c>
       <c r="P134" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R134" t="n">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="S134" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10394,39 +10394,39 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J135" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K135" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L135" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M135" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N135" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="O135" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P135" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R135" t="n">
-        <v>907</v>
+        <v>848</v>
       </c>
       <c r="S135" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J136" t="n">
         <v>86</v>
@@ -10477,30 +10477,30 @@
         <v>32</v>
       </c>
       <c r="L136" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="M136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N136" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P136" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1/5/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R136" t="n">
-        <v>827</v>
+        <v>777</v>
       </c>
       <c r="S136" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10542,39 +10542,39 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J137" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="K137" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L137" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="M137" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N137" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O137" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P137" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R137" t="n">
-        <v>828</v>
+        <v>698</v>
       </c>
       <c r="S137" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10616,39 +10616,39 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J138" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="K138" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L138" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M138" t="n">
         <v>5</v>
       </c>
       <c r="N138" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O138" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P138" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R138" t="n">
-        <v>903</v>
+        <v>710</v>
       </c>
       <c r="S138" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10690,39 +10690,39 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J139" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K139" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L139" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N139" t="n">
         <v>10</v>
       </c>
       <c r="O139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P139" t="n">
         <v>15</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R139" t="n">
-        <v>812</v>
+        <v>753</v>
       </c>
       <c r="S139" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10764,16 +10764,16 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J140" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K140" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L140" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M140" t="n">
         <v>3</v>
@@ -10782,21 +10782,21 @@
         <v>8</v>
       </c>
       <c r="O140" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P140" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R140" t="n">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="S140" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10838,16 +10838,16 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J141" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K141" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L141" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="M141" t="n">
         <v>3</v>
@@ -10856,10 +10856,10 @@
         <v>11</v>
       </c>
       <c r="O141" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P141" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="R141" t="n">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="S141" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -10912,36 +10912,36 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J142" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K142" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="L142" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="M142" t="n">
         <v>3</v>
       </c>
       <c r="N142" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O142" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P142" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R142" t="n">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10986,36 +10986,36 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J143" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K143" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L143" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="M143" t="n">
         <v>2</v>
       </c>
       <c r="N143" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O143" t="n">
         <v>3</v>
       </c>
       <c r="P143" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R143" t="n">
-        <v>927</v>
+        <v>810</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11060,39 +11060,39 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J144" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K144" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L144" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="M144" t="n">
         <v>1</v>
       </c>
       <c r="N144" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O144" t="n">
         <v>1</v>
       </c>
       <c r="P144" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R144" t="n">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="S144" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -11134,28 +11134,28 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J145" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K145" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L145" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="M145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N145" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O145" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P145" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -11163,10 +11163,10 @@
         </is>
       </c>
       <c r="R145" t="n">
-        <v>813</v>
+        <v>605</v>
       </c>
       <c r="S145" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11208,39 +11208,39 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J146" t="n">
         <v>90</v>
       </c>
       <c r="K146" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L146" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="M146" t="n">
         <v>3</v>
       </c>
       <c r="N146" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O146" t="n">
         <v>5</v>
       </c>
       <c r="P146" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R146" t="n">
-        <v>875</v>
+        <v>804</v>
       </c>
       <c r="S146" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11282,39 +11282,39 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J147" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K147" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L147" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M147" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N147" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O147" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P147" t="n">
         <v>15</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R147" t="n">
-        <v>834</v>
+        <v>845</v>
       </c>
       <c r="S147" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11356,36 +11356,36 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J148" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K148" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L148" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="M148" t="n">
         <v>2</v>
       </c>
       <c r="N148" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O148" t="n">
         <v>3</v>
       </c>
       <c r="P148" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R148" t="n">
-        <v>887</v>
+        <v>795</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11430,28 +11430,28 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J149" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K149" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="L149" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="M149" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N149" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O149" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P149" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="R149" t="n">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11504,39 +11504,39 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J150" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K150" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L150" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N150" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P150" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R150" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="S150" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11578,39 +11578,39 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J151" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="K151" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L151" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M151" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N151" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O151" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="P151" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R151" t="n">
-        <v>803</v>
+        <v>827</v>
       </c>
       <c r="S151" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11652,36 +11652,36 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="J152" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K152" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L152" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="M152" t="n">
         <v>2</v>
       </c>
       <c r="N152" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O152" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P152" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R152" t="n">
-        <v>901</v>
+        <v>867</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -11717,7 +11717,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11729,36 +11729,36 @@
         <v>72</v>
       </c>
       <c r="J153" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K153" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L153" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="M153" t="n">
         <v>2</v>
       </c>
       <c r="N153" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O153" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P153" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R153" t="n">
-        <v>812</v>
+        <v>772</v>
       </c>
       <c r="S153" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11803,36 +11803,36 @@
         <v>57</v>
       </c>
       <c r="J154" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="K154" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L154" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="M154" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N154" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O154" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P154" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R154" t="n">
-        <v>831</v>
+        <v>699</v>
       </c>
       <c r="S154" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11874,39 +11874,39 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J155" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K155" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L155" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="M155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N155" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O155" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P155" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R155" t="n">
-        <v>676</v>
+        <v>590</v>
       </c>
       <c r="S155" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11948,39 +11948,39 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J156" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K156" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L156" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="M156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N156" t="n">
         <v>14</v>
       </c>
       <c r="O156" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P156" t="n">
         <v>19</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R156" t="n">
-        <v>881</v>
+        <v>730</v>
       </c>
       <c r="S156" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12022,39 +12022,39 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J157" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K157" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L157" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="M157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N157" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O157" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P157" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R157" t="n">
-        <v>814</v>
+        <v>858</v>
       </c>
       <c r="S157" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>8/27/2026</t>
+          <t>8/28/2026</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12096,39 +12096,39 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J158" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K158" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L158" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M158" t="n">
         <v>3</v>
       </c>
       <c r="N158" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O158" t="n">
         <v>5</v>
       </c>
       <c r="P158" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R158" t="n">
-        <v>866</v>
+        <v>780</v>
       </c>
       <c r="S158" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>

--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -552,36 +552,36 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
       </c>
       <c r="K2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>795</v>
+        <v>863</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -626,16 +626,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J3" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M3" t="n">
         <v>3</v>
@@ -647,15 +647,15 @@
         <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -706,19 +706,19 @@
         <v>87</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>11</v>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
         <v>16</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>737</v>
+        <v>806</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -777,36 +777,36 @@
         <v>55</v>
       </c>
       <c r="J5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K5" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -851,33 +851,33 @@
         <v>85</v>
       </c>
       <c r="J6" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L6" t="n">
         <v>53</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
         <v>11</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
         <v>22</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>872</v>
+        <v>916</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -922,16 +922,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J7" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L7" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M7" t="n">
         <v>3</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>532</v>
+        <v>576</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -996,36 +996,36 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J8" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L8" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11</v>
+      </c>
+      <c r="O8" t="n">
         <v>6</v>
       </c>
-      <c r="N8" t="n">
-        <v>13</v>
-      </c>
-      <c r="O8" t="n">
-        <v>10</v>
-      </c>
       <c r="P8" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>859</v>
+        <v>935</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1070,16 +1070,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J9" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K9" t="n">
         <v>27</v>
       </c>
       <c r="L9" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>771</v>
+        <v>913</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1147,10 +1147,10 @@
         <v>84</v>
       </c>
       <c r="J10" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L10" t="n">
         <v>46</v>
@@ -1162,21 +1162,21 @@
         <v>9</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
         <v>21</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>820</v>
+        <v>888</v>
       </c>
       <c r="S10" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1221,25 +1221,25 @@
         <v>80</v>
       </c>
       <c r="J11" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L11" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
         <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>868</v>
+        <v>937</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1292,25 +1292,25 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J12" t="n">
         <v>92</v>
       </c>
       <c r="K12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L12" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
         <v>8</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>771</v>
+        <v>862</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1366,28 +1366,28 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J13" t="n">
         <v>80</v>
       </c>
       <c r="K13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L13" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P13" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>852</v>
+        <v>883</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1440,39 +1440,39 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J14" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L14" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>714</v>
+        <v>835</v>
       </c>
       <c r="S14" t="n">
-        <v>0.21</v>
+        <v>0.04</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J15" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L15" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="M15" t="n">
         <v>2</v>
@@ -1539,11 +1539,11 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>855</v>
+        <v>948</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1594,33 +1594,33 @@
         <v>78</v>
       </c>
       <c r="K16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L16" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="M16" t="n">
         <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O16" t="n">
         <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>709</v>
+        <v>862</v>
       </c>
       <c r="S16" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1662,28 +1662,28 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J17" t="n">
         <v>80</v>
       </c>
       <c r="K17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L17" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O17" t="n">
         <v>5</v>
       </c>
-      <c r="N17" t="n">
-        <v>7</v>
-      </c>
-      <c r="O17" t="n">
-        <v>7</v>
-      </c>
       <c r="P17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>711</v>
+        <v>763</v>
       </c>
       <c r="S17" t="n">
-        <v>0.13</v>
+        <v>0.02</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1736,39 +1736,39 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J18" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K18" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M18" t="n">
         <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>668</v>
+        <v>837</v>
       </c>
       <c r="S18" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1810,39 +1810,39 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J19" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L19" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M19" t="n">
         <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O19" t="n">
         <v>11</v>
       </c>
       <c r="P19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>717</v>
+        <v>846</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1884,22 +1884,22 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J20" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L20" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O20" t="n">
         <v>6</v>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>793</v>
+        <v>946</v>
       </c>
       <c r="S20" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1958,36 +1958,36 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J21" t="n">
         <v>96</v>
       </c>
       <c r="K21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L21" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M21" t="n">
+        <v>9</v>
+      </c>
+      <c r="N21" t="n">
+        <v>14</v>
+      </c>
+      <c r="O21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" t="n">
-        <v>15</v>
-      </c>
-      <c r="O21" t="n">
-        <v>15</v>
-      </c>
       <c r="P21" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1/7/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>825</v>
+        <v>946</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2035,19 +2035,19 @@
         <v>70</v>
       </c>
       <c r="J22" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L22" t="n">
         <v>64</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O22" t="n">
         <v>6</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>784</v>
+        <v>934</v>
       </c>
       <c r="S22" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2106,39 +2106,39 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J23" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L23" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
         <v>15</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>816</v>
+        <v>832</v>
       </c>
       <c r="S23" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2180,39 +2180,39 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J24" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L24" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
+        <v>13</v>
+      </c>
+      <c r="O24" t="n">
         <v>9</v>
       </c>
-      <c r="O24" t="n">
-        <v>6</v>
-      </c>
       <c r="P24" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>851</v>
+        <v>891</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2260,33 +2260,33 @@
         <v>96</v>
       </c>
       <c r="K25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L25" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>768</v>
+        <v>842</v>
       </c>
       <c r="S25" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2328,39 +2328,39 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J26" t="n">
         <v>92</v>
       </c>
       <c r="K26" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>833</v>
+        <v>866</v>
       </c>
       <c r="S26" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2402,36 +2402,36 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J27" t="n">
         <v>94</v>
       </c>
       <c r="K27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L27" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
         <v>11</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P27" t="n">
         <v>16</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1/8/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>842</v>
+        <v>957</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2476,36 +2476,36 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J28" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K28" t="n">
         <v>19</v>
       </c>
       <c r="L28" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
         <v>13</v>
       </c>
       <c r="O28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>870</v>
+        <v>895</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J29" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="M29" t="n">
         <v>2</v>
@@ -2575,11 +2575,11 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/6/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>597</v>
+        <v>857</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -2627,33 +2627,33 @@
         <v>86</v>
       </c>
       <c r="J30" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K30" t="n">
         <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O30" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>876</v>
+        <v>914</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2701,13 +2701,13 @@
         <v>54</v>
       </c>
       <c r="J31" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K31" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L31" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -2723,14 +2723,14 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="S31" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -2772,28 +2772,28 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J32" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K32" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L32" t="n">
         <v>62</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P32" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>711</v>
+        <v>845</v>
       </c>
       <c r="S32" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -2846,39 +2846,39 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J33" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K33" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L33" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M33" t="n">
         <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>698</v>
+        <v>791</v>
       </c>
       <c r="S33" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2926,33 +2926,33 @@
         <v>89</v>
       </c>
       <c r="K34" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L34" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N34" t="n">
+        <v>14</v>
+      </c>
+      <c r="O34" t="n">
         <v>10</v>
       </c>
-      <c r="O34" t="n">
-        <v>3</v>
-      </c>
       <c r="P34" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>811</v>
+        <v>897</v>
       </c>
       <c r="S34" t="n">
-        <v>0.19</v>
+        <v>0.08</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J35" t="n">
         <v>88</v>
@@ -3003,7 +3003,7 @@
         <v>19</v>
       </c>
       <c r="L35" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M35" t="n">
         <v>2</v>
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>730</v>
+        <v>866</v>
       </c>
       <c r="S35" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3068,39 +3068,39 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J36" t="n">
         <v>79</v>
       </c>
       <c r="K36" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M36" t="n">
+        <v>2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>5</v>
+      </c>
+      <c r="O36" t="n">
         <v>3</v>
       </c>
-      <c r="N36" t="n">
-        <v>6</v>
-      </c>
-      <c r="O36" t="n">
-        <v>5</v>
-      </c>
       <c r="P36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/8/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>651</v>
+        <v>788</v>
       </c>
       <c r="S36" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3142,39 +3142,39 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J37" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K37" t="n">
         <v>18</v>
       </c>
       <c r="L37" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M37" t="n">
         <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O37" t="n">
         <v>5</v>
       </c>
       <c r="P37" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>731</v>
+        <v>842</v>
       </c>
       <c r="S37" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3219,33 +3219,33 @@
         <v>86</v>
       </c>
       <c r="J38" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K38" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L38" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N38" t="n">
         <v>11</v>
       </c>
       <c r="O38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>862</v>
+        <v>916</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3293,22 +3293,22 @@
         <v>75</v>
       </c>
       <c r="J39" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K39" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L39" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O39" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P39" t="n">
         <v>19</v>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>816</v>
+        <v>912</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3367,13 +3367,13 @@
         <v>65</v>
       </c>
       <c r="J40" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K40" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L40" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M40" t="n">
         <v>3</v>
@@ -3382,10 +3382,10 @@
         <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>796</v>
+        <v>860</v>
       </c>
       <c r="S40" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -3438,39 +3438,39 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J41" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K41" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L41" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="M41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O41" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P41" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>724</v>
+        <v>846</v>
       </c>
       <c r="S41" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -3512,16 +3512,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J42" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K42" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L42" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="M42" t="n">
         <v>1</v>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="R42" t="n">
-        <v>765</v>
+        <v>801</v>
       </c>
       <c r="S42" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J43" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K43" t="n">
         <v>22</v>
@@ -3601,13 +3601,13 @@
         <v>6</v>
       </c>
       <c r="N43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O43" t="n">
         <v>8</v>
       </c>
       <c r="P43" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>824</v>
+        <v>936</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3660,39 +3660,39 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J44" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K44" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L44" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="M44" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N44" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O44" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P44" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>647</v>
+        <v>845</v>
       </c>
       <c r="S44" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -3734,36 +3734,36 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J45" t="n">
         <v>101</v>
       </c>
       <c r="K45" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L45" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N45" t="n">
         <v>15</v>
       </c>
       <c r="O45" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P45" t="n">
         <v>21</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>841</v>
+        <v>948</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J46" t="n">
         <v>94</v>
       </c>
       <c r="K46" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L46" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
@@ -3826,7 +3826,7 @@
         <v>6</v>
       </c>
       <c r="O46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P46" t="n">
         <v>16</v>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>777</v>
+        <v>950</v>
       </c>
       <c r="S46" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -3885,10 +3885,10 @@
         <v>55</v>
       </c>
       <c r="J47" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K47" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L47" t="n">
         <v>89</v>
@@ -3897,24 +3897,24 @@
         <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>719</v>
+        <v>808</v>
       </c>
       <c r="S47" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -3956,36 +3956,36 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J48" t="n">
         <v>110</v>
       </c>
       <c r="K48" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L48" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>862</v>
+        <v>879</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>82</v>
       </c>
       <c r="K49" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L49" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M49" t="n">
         <v>6</v>
       </c>
       <c r="N49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P49" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>643</v>
+        <v>814</v>
       </c>
       <c r="S49" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4104,39 +4104,39 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J50" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K50" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L50" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M50" t="n">
         <v>8</v>
       </c>
       <c r="N50" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P50" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>790</v>
+        <v>711</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4181,33 +4181,33 @@
         <v>87</v>
       </c>
       <c r="J51" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K51" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L51" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N51" t="n">
         <v>14</v>
       </c>
       <c r="O51" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R51" t="n">
-        <v>870</v>
+        <v>907</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -4255,33 +4255,33 @@
         <v>56</v>
       </c>
       <c r="J52" t="n">
+        <v>91</v>
+      </c>
+      <c r="K52" t="n">
+        <v>24</v>
+      </c>
+      <c r="L52" t="n">
         <v>93</v>
-      </c>
-      <c r="K52" t="n">
-        <v>23</v>
-      </c>
-      <c r="L52" t="n">
-        <v>96</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>780</v>
+        <v>925</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -4329,22 +4329,22 @@
         <v>78</v>
       </c>
       <c r="J53" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K53" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L53" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N53" t="n">
         <v>9</v>
       </c>
       <c r="O53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P53" t="n">
         <v>21</v>
@@ -4355,10 +4355,10 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>825</v>
+        <v>850</v>
       </c>
       <c r="S53" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         <v>86</v>
       </c>
       <c r="J54" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K54" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L54" t="n">
         <v>46</v>
@@ -4415,24 +4415,24 @@
         <v>2</v>
       </c>
       <c r="N54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O54" t="n">
         <v>5</v>
       </c>
       <c r="P54" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R54" t="n">
-        <v>806</v>
+        <v>891</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -4477,36 +4477,36 @@
         <v>73</v>
       </c>
       <c r="J55" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K55" t="n">
         <v>26</v>
       </c>
       <c r="L55" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="M55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O55" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P55" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>863</v>
+        <v>848</v>
       </c>
       <c r="S55" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -4554,10 +4554,10 @@
         <v>80</v>
       </c>
       <c r="K56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L56" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M56" t="n">
         <v>2</v>
@@ -4577,10 +4577,10 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>633</v>
+        <v>806</v>
       </c>
       <c r="S56" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -4622,39 +4622,39 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J57" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K57" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L57" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="M57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N57" t="n">
+        <v>15</v>
+      </c>
+      <c r="O57" t="n">
         <v>13</v>
       </c>
-      <c r="O57" t="n">
-        <v>7</v>
-      </c>
       <c r="P57" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>661</v>
+        <v>763</v>
       </c>
       <c r="S57" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -4696,16 +4696,16 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J58" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K58" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L58" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M58" t="n">
         <v>5</v>
@@ -4714,21 +4714,21 @@
         <v>9</v>
       </c>
       <c r="O58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P58" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1/3/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>526</v>
+        <v>699</v>
       </c>
       <c r="S58" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -4773,36 +4773,36 @@
         <v>66</v>
       </c>
       <c r="J59" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K59" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="L59" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N59" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O59" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P59" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R59" t="n">
-        <v>702</v>
+        <v>907</v>
       </c>
       <c r="S59" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -4847,13 +4847,13 @@
         <v>72</v>
       </c>
       <c r="J60" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K60" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L60" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M60" t="n">
         <v>5</v>
@@ -4862,10 +4862,10 @@
         <v>14</v>
       </c>
       <c r="O60" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P60" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>835</v>
+        <v>940</v>
       </c>
       <c r="S60" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -4918,16 +4918,16 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J61" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K61" t="n">
         <v>15</v>
       </c>
       <c r="L61" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M61" t="n">
         <v>2</v>
@@ -4943,11 +4943,11 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>860</v>
+        <v>961</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -4992,39 +4992,39 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J62" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K62" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L62" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N62" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O62" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P62" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R62" t="n">
-        <v>835</v>
+        <v>882</v>
       </c>
       <c r="S62" t="n">
-        <v>0.02</v>
+        <v>0.14</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5066,36 +5066,36 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J63" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K63" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L63" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M63" t="n">
         <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R63" t="n">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -5140,22 +5140,22 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J64" t="n">
         <v>93</v>
       </c>
       <c r="K64" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L64" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O64" t="n">
         <v>6</v>
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>780</v>
+        <v>809</v>
       </c>
       <c r="S64" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -5214,39 +5214,39 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J65" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K65" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L65" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N65" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O65" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P65" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R65" t="n">
-        <v>736</v>
+        <v>892</v>
       </c>
       <c r="S65" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -5291,22 +5291,22 @@
         <v>62</v>
       </c>
       <c r="J66" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K66" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L66" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P66" t="n">
         <v>14</v>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>846</v>
+        <v>835</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5368,22 +5368,22 @@
         <v>92</v>
       </c>
       <c r="K67" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L67" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N67" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O67" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="P67" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>510</v>
+        <v>898</v>
       </c>
       <c r="S67" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -5436,39 +5436,39 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J68" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K68" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L68" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M68" t="n">
         <v>3</v>
       </c>
       <c r="N68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O68" t="n">
         <v>8</v>
       </c>
       <c r="P68" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>755</v>
+        <v>768</v>
       </c>
       <c r="S68" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5513,36 +5513,36 @@
         <v>76</v>
       </c>
       <c r="J69" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K69" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L69" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N69" t="n">
         <v>11</v>
       </c>
       <c r="O69" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P69" t="n">
         <v>24</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>841</v>
+        <v>921</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -5584,39 +5584,39 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J70" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K70" t="n">
         <v>31</v>
       </c>
       <c r="L70" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N70" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O70" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P70" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R70" t="n">
-        <v>776</v>
+        <v>912</v>
       </c>
       <c r="S70" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -5658,28 +5658,28 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J71" t="n">
         <v>88</v>
       </c>
       <c r="K71" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L71" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M71" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N71" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O71" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P71" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>847</v>
+        <v>836</v>
       </c>
       <c r="S71" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -5735,36 +5735,36 @@
         <v>65</v>
       </c>
       <c r="J72" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K72" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L72" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N72" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O72" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P72" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="S72" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -5806,16 +5806,16 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J73" t="n">
         <v>80</v>
       </c>
       <c r="K73" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L73" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M73" t="n">
         <v>2</v>
@@ -5831,14 +5831,14 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R73" t="n">
-        <v>765</v>
+        <v>911</v>
       </c>
       <c r="S73" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5880,16 +5880,16 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J74" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K74" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L74" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M74" t="n">
         <v>1</v>
@@ -5905,14 +5905,14 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R74" t="n">
-        <v>753</v>
+        <v>781</v>
       </c>
       <c r="S74" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -5954,39 +5954,39 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J75" t="n">
         <v>92</v>
       </c>
       <c r="K75" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L75" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N75" t="n">
         <v>10</v>
       </c>
       <c r="O75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P75" t="n">
         <v>15</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R75" t="n">
-        <v>738</v>
+        <v>803</v>
       </c>
       <c r="S75" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -6031,36 +6031,36 @@
         <v>57</v>
       </c>
       <c r="J76" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K76" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L76" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="M76" t="n">
         <v>6</v>
       </c>
       <c r="N76" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R76" t="n">
-        <v>790</v>
+        <v>741</v>
       </c>
       <c r="S76" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -6102,39 +6102,39 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J77" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K77" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L77" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M77" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N77" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O77" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P77" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R77" t="n">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -6179,36 +6179,36 @@
         <v>55</v>
       </c>
       <c r="J78" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K78" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L78" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M78" t="n">
         <v>5</v>
       </c>
       <c r="N78" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O78" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P78" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R78" t="n">
-        <v>699</v>
+        <v>884</v>
       </c>
       <c r="S78" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -6250,28 +6250,28 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J79" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K79" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L79" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="R79" t="n">
-        <v>760</v>
+        <v>877</v>
       </c>
       <c r="S79" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -6324,16 +6324,16 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J80" t="n">
         <v>79</v>
       </c>
       <c r="K80" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L80" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M80" t="n">
         <v>1</v>
@@ -6349,14 +6349,14 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R80" t="n">
-        <v>675</v>
+        <v>859</v>
       </c>
       <c r="S80" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -6398,39 +6398,39 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J81" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K81" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L81" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M81" t="n">
+        <v>2</v>
+      </c>
+      <c r="N81" t="n">
+        <v>9</v>
+      </c>
+      <c r="O81" t="n">
         <v>3</v>
       </c>
-      <c r="N81" t="n">
-        <v>8</v>
-      </c>
-      <c r="O81" t="n">
-        <v>5</v>
-      </c>
       <c r="P81" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R81" t="n">
-        <v>634</v>
+        <v>718</v>
       </c>
       <c r="S81" t="n">
-        <v>0.3</v>
+        <v>0.04</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -6472,13 +6472,13 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J82" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K82" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L82" t="n">
         <v>72</v>
@@ -6490,7 +6490,7 @@
         <v>5</v>
       </c>
       <c r="O82" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P82" t="n">
         <v>14</v>
@@ -6501,10 +6501,10 @@
         </is>
       </c>
       <c r="R82" t="n">
-        <v>764</v>
+        <v>799</v>
       </c>
       <c r="S82" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -6546,16 +6546,16 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J83" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K83" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L83" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M83" t="n">
         <v>5</v>
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>834</v>
+        <v>954</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -6620,36 +6620,36 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J84" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K84" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L84" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M84" t="n">
         <v>10</v>
       </c>
       <c r="N84" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O84" t="n">
         <v>15</v>
       </c>
       <c r="P84" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1/8/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R84" t="n">
-        <v>826</v>
+        <v>946</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -6697,13 +6697,13 @@
         <v>57</v>
       </c>
       <c r="J85" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K85" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L85" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M85" t="n">
         <v>3</v>
@@ -6715,18 +6715,18 @@
         <v>6</v>
       </c>
       <c r="P85" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>1/7/1 17:00 LMT</t>
+          <t>1/8/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R85" t="n">
-        <v>804</v>
+        <v>951</v>
       </c>
       <c r="S85" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -6768,39 +6768,39 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J86" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K86" t="n">
         <v>28</v>
       </c>
       <c r="L86" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P86" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>1/7/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R86" t="n">
-        <v>677</v>
+        <v>873</v>
       </c>
       <c r="S86" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J87" t="n">
         <v>93</v>
@@ -6857,21 +6857,21 @@
         <v>5</v>
       </c>
       <c r="N87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O87" t="n">
         <v>7</v>
       </c>
       <c r="P87" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>01</t>
         </is>
       </c>
       <c r="R87" t="n">
-        <v>786</v>
+        <v>900</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -6916,39 +6916,39 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J88" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K88" t="n">
         <v>25</v>
       </c>
       <c r="L88" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N88" t="n">
         <v>6</v>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P88" t="n">
         <v>8</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R88" t="n">
-        <v>817</v>
+        <v>919</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -6990,16 +6990,16 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J89" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K89" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L89" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M89" t="n">
         <v>3</v>
@@ -7008,18 +7008,18 @@
         <v>11</v>
       </c>
       <c r="O89" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P89" t="n">
         <v>21</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R89" t="n">
-        <v>860</v>
+        <v>920</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -7064,28 +7064,28 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J90" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K90" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L90" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N90" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O90" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P90" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -7093,10 +7093,10 @@
         </is>
       </c>
       <c r="R90" t="n">
-        <v>721</v>
+        <v>887</v>
       </c>
       <c r="S90" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -7141,33 +7141,33 @@
         <v>66</v>
       </c>
       <c r="J91" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K91" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L91" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M91" t="n">
         <v>6</v>
       </c>
       <c r="N91" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O91" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P91" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R91" t="n">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -7212,36 +7212,36 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J92" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K92" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L92" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M92" t="n">
         <v>5</v>
       </c>
       <c r="N92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O92" t="n">
         <v>7</v>
       </c>
       <c r="P92" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>1/7/1 17:00 LMT</t>
+          <t>1/8/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R92" t="n">
-        <v>855</v>
+        <v>951</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -7286,28 +7286,28 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J93" t="n">
         <v>83</v>
       </c>
       <c r="K93" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L93" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O93" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="R93" t="n">
-        <v>637</v>
+        <v>731</v>
       </c>
       <c r="S93" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -7360,39 +7360,39 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J94" t="n">
         <v>77</v>
       </c>
       <c r="K94" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L94" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M94" t="n">
         <v>7</v>
       </c>
       <c r="N94" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O94" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P94" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R94" t="n">
-        <v>795</v>
+        <v>831</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -7437,13 +7437,13 @@
         <v>71</v>
       </c>
       <c r="J95" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K95" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L95" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="M95" t="n">
         <v>2</v>
@@ -7459,11 +7459,11 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R95" t="n">
-        <v>859</v>
+        <v>936</v>
       </c>
       <c r="S95" t="n">
         <v>0.01</v>
@@ -7514,22 +7514,22 @@
         <v>91</v>
       </c>
       <c r="K96" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L96" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M96" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N96" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O96" t="n">
         <v>14</v>
       </c>
       <c r="P96" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="R96" t="n">
-        <v>837</v>
+        <v>808</v>
       </c>
       <c r="S96" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -7582,39 +7582,39 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J97" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K97" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L97" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M97" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N97" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O97" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="P97" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R97" t="n">
-        <v>699</v>
+        <v>865</v>
       </c>
       <c r="S97" t="n">
-        <v>0.14</v>
+        <v>0.04</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -7656,36 +7656,36 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J98" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K98" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L98" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M98" t="n">
         <v>8</v>
       </c>
       <c r="N98" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R98" t="n">
-        <v>790</v>
+        <v>868</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -7730,36 +7730,36 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J99" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K99" t="n">
         <v>34</v>
       </c>
       <c r="L99" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="M99" t="n">
         <v>3</v>
       </c>
       <c r="N99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O99" t="n">
         <v>7</v>
       </c>
       <c r="P99" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R99" t="n">
-        <v>784</v>
+        <v>839</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -7804,16 +7804,16 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J100" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K100" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L100" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="M100" t="n">
         <v>3</v>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="R100" t="n">
-        <v>859</v>
+        <v>883</v>
       </c>
       <c r="S100" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -7881,36 +7881,36 @@
         <v>69</v>
       </c>
       <c r="J101" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K101" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L101" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N101" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P101" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R101" t="n">
-        <v>760</v>
+        <v>806</v>
       </c>
       <c r="S101" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -7952,36 +7952,36 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J102" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K102" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L102" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M102" t="n">
         <v>2</v>
       </c>
       <c r="N102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O102" t="n">
         <v>3</v>
       </c>
       <c r="P102" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/8/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R102" t="n">
-        <v>856</v>
+        <v>879</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -8029,10 +8029,10 @@
         <v>87</v>
       </c>
       <c r="J103" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K103" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L103" t="n">
         <v>46</v>
@@ -8044,18 +8044,18 @@
         <v>11</v>
       </c>
       <c r="O103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P103" t="n">
         <v>21</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R103" t="n">
-        <v>816</v>
+        <v>906</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -8106,22 +8106,22 @@
         <v>101</v>
       </c>
       <c r="K104" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L104" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M104" t="n">
         <v>8</v>
       </c>
       <c r="N104" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O104" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P104" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="R104" t="n">
-        <v>827</v>
+        <v>872</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -8174,36 +8174,36 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J105" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K105" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L105" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M105" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N105" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O105" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P105" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R105" t="n">
-        <v>849</v>
+        <v>896</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -8248,36 +8248,36 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J106" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K106" t="n">
+        <v>32</v>
+      </c>
+      <c r="L106" t="n">
+        <v>60</v>
+      </c>
+      <c r="M106" t="n">
+        <v>7</v>
+      </c>
+      <c r="N106" t="n">
+        <v>17</v>
+      </c>
+      <c r="O106" t="n">
+        <v>13</v>
+      </c>
+      <c r="P106" t="n">
         <v>31</v>
       </c>
-      <c r="L106" t="n">
-        <v>61</v>
-      </c>
-      <c r="M106" t="n">
-        <v>6</v>
-      </c>
-      <c r="N106" t="n">
-        <v>11</v>
-      </c>
-      <c r="O106" t="n">
-        <v>8</v>
-      </c>
-      <c r="P106" t="n">
-        <v>19</v>
-      </c>
       <c r="Q106" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
       <c r="R106" t="n">
-        <v>690</v>
+        <v>823</v>
       </c>
       <c r="S106" t="n">
         <v>0.16</v>
@@ -8322,39 +8322,39 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J107" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K107" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L107" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N107" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O107" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P107" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R107" t="n">
-        <v>597</v>
+        <v>879</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J108" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K108" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L108" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M108" t="n">
         <v>2</v>
@@ -8421,11 +8421,11 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>1/8/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R108" t="n">
-        <v>802</v>
+        <v>867</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -8470,16 +8470,16 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J109" t="n">
         <v>81</v>
       </c>
       <c r="K109" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L109" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M109" t="n">
         <v>5</v>
@@ -8499,10 +8499,10 @@
         </is>
       </c>
       <c r="R109" t="n">
-        <v>667</v>
+        <v>832</v>
       </c>
       <c r="S109" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -8547,10 +8547,10 @@
         <v>81</v>
       </c>
       <c r="J110" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K110" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L110" t="n">
         <v>54</v>
@@ -8559,21 +8559,21 @@
         <v>3</v>
       </c>
       <c r="N110" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O110" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P110" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R110" t="n">
-        <v>854</v>
+        <v>824</v>
       </c>
       <c r="S110" t="n">
         <v>0.06</v>
@@ -8618,39 +8618,39 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J111" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K111" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L111" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N111" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O111" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P111" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R111" t="n">
-        <v>847</v>
+        <v>833</v>
       </c>
       <c r="S111" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -8692,39 +8692,39 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J112" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K112" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L112" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M112" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N112" t="n">
+        <v>15</v>
+      </c>
+      <c r="O112" t="n">
         <v>11</v>
       </c>
-      <c r="O112" t="n">
-        <v>3</v>
-      </c>
       <c r="P112" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R112" t="n">
-        <v>786</v>
+        <v>810</v>
       </c>
       <c r="S112" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -8766,39 +8766,39 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J113" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K113" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L113" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="M113" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N113" t="n">
+        <v>14</v>
+      </c>
+      <c r="O113" t="n">
         <v>10</v>
       </c>
-      <c r="O113" t="n">
-        <v>6</v>
-      </c>
       <c r="P113" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R113" t="n">
-        <v>561</v>
+        <v>820</v>
       </c>
       <c r="S113" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -8843,36 +8843,36 @@
         <v>64</v>
       </c>
       <c r="J114" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K114" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L114" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N114" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O114" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P114" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R114" t="n">
-        <v>782</v>
+        <v>901</v>
       </c>
       <c r="S114" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -8914,39 +8914,39 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J115" t="n">
         <v>80</v>
       </c>
       <c r="K115" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L115" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="M115" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N115" t="n">
+        <v>14</v>
+      </c>
+      <c r="O115" t="n">
         <v>10</v>
       </c>
-      <c r="O115" t="n">
-        <v>5</v>
-      </c>
       <c r="P115" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R115" t="n">
-        <v>806</v>
+        <v>848</v>
       </c>
       <c r="S115" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -8988,36 +8988,36 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J116" t="n">
         <v>91</v>
       </c>
       <c r="K116" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L116" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M116" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N116" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O116" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P116" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R116" t="n">
-        <v>775</v>
+        <v>838</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J117" t="n">
         <v>83</v>
@@ -9071,30 +9071,30 @@
         <v>27</v>
       </c>
       <c r="L117" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M117" t="n">
+        <v>2</v>
+      </c>
+      <c r="N117" t="n">
+        <v>11</v>
+      </c>
+      <c r="O117" t="n">
         <v>3</v>
       </c>
-      <c r="N117" t="n">
-        <v>9</v>
-      </c>
-      <c r="O117" t="n">
-        <v>5</v>
-      </c>
       <c r="P117" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R117" t="n">
-        <v>682</v>
+        <v>775</v>
       </c>
       <c r="S117" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -9136,36 +9136,36 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J118" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K118" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L118" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M118" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N118" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O118" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P118" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>1/1/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R118" t="n">
-        <v>798</v>
+        <v>954</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -9210,39 +9210,39 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J119" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K119" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L119" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="M119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O119" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P119" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R119" t="n">
-        <v>771</v>
+        <v>864</v>
       </c>
       <c r="S119" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -9284,39 +9284,39 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J120" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K120" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L120" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M120" t="n">
         <v>1</v>
       </c>
       <c r="N120" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O120" t="n">
         <v>1</v>
       </c>
       <c r="P120" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R120" t="n">
-        <v>730</v>
+        <v>936</v>
       </c>
       <c r="S120" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -9358,39 +9358,39 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J121" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K121" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L121" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M121" t="n">
         <v>3</v>
       </c>
       <c r="N121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O121" t="n">
         <v>8</v>
       </c>
       <c r="P121" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>1/1/1 17:00 LMT</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R121" t="n">
-        <v>774</v>
+        <v>756</v>
       </c>
       <c r="S121" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -9432,36 +9432,36 @@
         </is>
       </c>
       <c r="I122" t="n">
+        <v>63</v>
+      </c>
+      <c r="J122" t="n">
+        <v>91</v>
+      </c>
+      <c r="K122" t="n">
+        <v>25</v>
+      </c>
+      <c r="L122" t="n">
         <v>61</v>
       </c>
-      <c r="J122" t="n">
-        <v>89</v>
-      </c>
-      <c r="K122" t="n">
-        <v>30</v>
-      </c>
-      <c r="L122" t="n">
-        <v>67</v>
-      </c>
       <c r="M122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N122" t="n">
         <v>5</v>
       </c>
       <c r="O122" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P122" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R122" t="n">
-        <v>733</v>
+        <v>907</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -9515,10 +9515,10 @@
         <v>22</v>
       </c>
       <c r="L123" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N123" t="n">
         <v>6</v>
@@ -9535,10 +9535,10 @@
         </is>
       </c>
       <c r="R123" t="n">
-        <v>830</v>
+        <v>911</v>
       </c>
       <c r="S123" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -9580,16 +9580,16 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J124" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="K124" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L124" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M124" t="n">
         <v>3</v>
@@ -9609,10 +9609,10 @@
         </is>
       </c>
       <c r="R124" t="n">
-        <v>800</v>
+        <v>872</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -9657,25 +9657,25 @@
         <v>79</v>
       </c>
       <c r="J125" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K125" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L125" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O125" t="n">
         <v>6</v>
       </c>
       <c r="P125" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -9683,10 +9683,10 @@
         </is>
       </c>
       <c r="R125" t="n">
-        <v>862</v>
+        <v>851</v>
       </c>
       <c r="S125" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -9728,16 +9728,16 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J126" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K126" t="n">
         <v>22</v>
       </c>
       <c r="L126" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M126" t="n">
         <v>3</v>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="R126" t="n">
-        <v>850</v>
+        <v>882</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -9802,28 +9802,28 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J127" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K127" t="n">
         <v>20</v>
       </c>
       <c r="L127" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N127" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O127" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P127" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="R127" t="n">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -9876,13 +9876,13 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J128" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K128" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L128" t="n">
         <v>66</v>
@@ -9901,11 +9901,11 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R128" t="n">
-        <v>811</v>
+        <v>836</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>76</v>
       </c>
       <c r="M129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N129" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O129" t="n">
         <v>6</v>
@@ -9979,10 +9979,10 @@
         </is>
       </c>
       <c r="R129" t="n">
-        <v>877</v>
+        <v>906</v>
       </c>
       <c r="S129" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -10030,22 +10030,22 @@
         <v>82</v>
       </c>
       <c r="K130" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L130" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N130" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O130" t="n">
         <v>8</v>
       </c>
       <c r="P130" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -10053,10 +10053,10 @@
         </is>
       </c>
       <c r="R130" t="n">
-        <v>769</v>
+        <v>823</v>
       </c>
       <c r="S130" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -10101,10 +10101,10 @@
         <v>80</v>
       </c>
       <c r="J131" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K131" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L131" t="n">
         <v>60</v>
@@ -10113,13 +10113,13 @@
         <v>2</v>
       </c>
       <c r="N131" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O131" t="n">
         <v>6</v>
       </c>
       <c r="P131" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         </is>
       </c>
       <c r="R131" t="n">
-        <v>864</v>
+        <v>885</v>
       </c>
       <c r="S131" t="n">
         <v>0.11</v>
@@ -10172,25 +10172,25 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J132" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K132" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L132" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N132" t="n">
         <v>13</v>
       </c>
       <c r="O132" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P132" t="n">
         <v>17</v>
@@ -10201,7 +10201,7 @@
         </is>
       </c>
       <c r="R132" t="n">
-        <v>832</v>
+        <v>942</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -10246,28 +10246,28 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J133" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K133" t="n">
         <v>26</v>
       </c>
       <c r="L133" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N133" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O133" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P133" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -10275,10 +10275,10 @@
         </is>
       </c>
       <c r="R133" t="n">
-        <v>821</v>
+        <v>865</v>
       </c>
       <c r="S133" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -10320,39 +10320,39 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J134" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K134" t="n">
         <v>33</v>
       </c>
       <c r="L134" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M134" t="n">
         <v>1</v>
       </c>
       <c r="N134" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O134" t="n">
         <v>1</v>
       </c>
       <c r="P134" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R134" t="n">
-        <v>678</v>
+        <v>812</v>
       </c>
       <c r="S134" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -10397,13 +10397,13 @@
         <v>86</v>
       </c>
       <c r="J135" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K135" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L135" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M135" t="n">
         <v>5</v>
@@ -10423,10 +10423,10 @@
         </is>
       </c>
       <c r="R135" t="n">
-        <v>848</v>
+        <v>889</v>
       </c>
       <c r="S135" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -10468,28 +10468,28 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J136" t="n">
         <v>86</v>
       </c>
       <c r="K136" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L136" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M136" t="n">
         <v>3</v>
       </c>
       <c r="N136" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O136" t="n">
         <v>5</v>
       </c>
       <c r="P136" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -10497,10 +10497,10 @@
         </is>
       </c>
       <c r="R136" t="n">
-        <v>777</v>
+        <v>906</v>
       </c>
       <c r="S136" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J137" t="n">
         <v>81</v>
@@ -10551,30 +10551,30 @@
         <v>35</v>
       </c>
       <c r="L137" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M137" t="n">
         <v>6</v>
       </c>
       <c r="N137" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O137" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P137" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R137" t="n">
-        <v>698</v>
+        <v>760</v>
       </c>
       <c r="S137" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -10619,36 +10619,36 @@
         <v>82</v>
       </c>
       <c r="J138" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K138" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L138" t="n">
         <v>42</v>
       </c>
       <c r="M138" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N138" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O138" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P138" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R138" t="n">
-        <v>710</v>
+        <v>894</v>
       </c>
       <c r="S138" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -10690,16 +10690,16 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J139" t="n">
         <v>86</v>
       </c>
       <c r="K139" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L139" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M139" t="n">
         <v>1</v>
@@ -10719,10 +10719,10 @@
         </is>
       </c>
       <c r="R139" t="n">
-        <v>753</v>
+        <v>850</v>
       </c>
       <c r="S139" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -10767,25 +10767,25 @@
         <v>63</v>
       </c>
       <c r="J140" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K140" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L140" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M140" t="n">
         <v>3</v>
       </c>
       <c r="N140" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O140" t="n">
         <v>8</v>
       </c>
       <c r="P140" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="R140" t="n">
-        <v>763</v>
+        <v>822</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J141" t="n">
         <v>101</v>
@@ -10850,16 +10850,16 @@
         <v>52</v>
       </c>
       <c r="M141" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N141" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O141" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P141" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="R141" t="n">
-        <v>838</v>
+        <v>895</v>
       </c>
       <c r="S141" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -10912,13 +10912,13 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J142" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K142" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L142" t="n">
         <v>70</v>
@@ -10927,21 +10927,21 @@
         <v>3</v>
       </c>
       <c r="N142" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O142" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P142" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R142" t="n">
-        <v>836</v>
+        <v>742</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -10986,28 +10986,28 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J143" t="n">
         <v>88</v>
       </c>
       <c r="K143" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L143" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="M143" t="n">
         <v>2</v>
       </c>
       <c r="N143" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O143" t="n">
         <v>3</v>
       </c>
       <c r="P143" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="R143" t="n">
-        <v>810</v>
+        <v>891</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -11066,10 +11066,10 @@
         <v>79</v>
       </c>
       <c r="K144" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L144" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="M144" t="n">
         <v>1</v>
@@ -11085,14 +11085,14 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R144" t="n">
-        <v>704</v>
+        <v>819</v>
       </c>
       <c r="S144" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -11134,16 +11134,16 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J145" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K145" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L145" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M145" t="n">
         <v>3</v>
@@ -11152,21 +11152,21 @@
         <v>10</v>
       </c>
       <c r="O145" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P145" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R145" t="n">
-        <v>605</v>
+        <v>911</v>
       </c>
       <c r="S145" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -11211,13 +11211,13 @@
         <v>63</v>
       </c>
       <c r="J146" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K146" t="n">
         <v>22</v>
       </c>
       <c r="L146" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M146" t="n">
         <v>3</v>
@@ -11233,11 +11233,11 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R146" t="n">
-        <v>804</v>
+        <v>820</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -11291,7 +11291,7 @@
         <v>22</v>
       </c>
       <c r="L147" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M147" t="n">
         <v>5</v>
@@ -11307,11 +11307,11 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R147" t="n">
-        <v>845</v>
+        <v>789</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -11356,16 +11356,16 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J148" t="n">
         <v>81</v>
       </c>
       <c r="K148" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L148" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M148" t="n">
         <v>2</v>
@@ -11385,7 +11385,7 @@
         </is>
       </c>
       <c r="R148" t="n">
-        <v>795</v>
+        <v>886</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -11433,25 +11433,25 @@
         <v>74</v>
       </c>
       <c r="J149" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K149" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L149" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M149" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N149" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O149" t="n">
         <v>13</v>
       </c>
       <c r="P149" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="R149" t="n">
-        <v>824</v>
+        <v>784</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -11504,39 +11504,39 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J150" t="n">
         <v>85</v>
       </c>
       <c r="K150" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L150" t="n">
         <v>89</v>
       </c>
       <c r="M150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N150" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O150" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P150" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R150" t="n">
-        <v>726</v>
+        <v>766</v>
       </c>
       <c r="S150" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -11578,36 +11578,36 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J151" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K151" t="n">
+        <v>24</v>
+      </c>
+      <c r="L151" t="n">
+        <v>41</v>
+      </c>
+      <c r="M151" t="n">
+        <v>10</v>
+      </c>
+      <c r="N151" t="n">
         <v>26</v>
       </c>
-      <c r="L151" t="n">
-        <v>40</v>
-      </c>
-      <c r="M151" t="n">
-        <v>11</v>
-      </c>
-      <c r="N151" t="n">
-        <v>24</v>
-      </c>
       <c r="O151" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P151" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R151" t="n">
-        <v>827</v>
+        <v>880</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -11655,33 +11655,33 @@
         <v>82</v>
       </c>
       <c r="J152" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K152" t="n">
         <v>21</v>
       </c>
       <c r="L152" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M152" t="n">
         <v>2</v>
       </c>
       <c r="N152" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O152" t="n">
         <v>6</v>
       </c>
       <c r="P152" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R152" t="n">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -11726,39 +11726,39 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J153" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K153" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L153" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M153" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N153" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O153" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P153" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R153" t="n">
-        <v>772</v>
+        <v>875</v>
       </c>
       <c r="S153" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -11803,36 +11803,36 @@
         <v>57</v>
       </c>
       <c r="J154" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K154" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L154" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="M154" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N154" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O154" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="P154" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R154" t="n">
-        <v>699</v>
+        <v>850</v>
       </c>
       <c r="S154" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -11874,28 +11874,28 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J155" t="n">
         <v>74</v>
       </c>
       <c r="K155" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L155" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N155" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O155" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P155" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -11903,10 +11903,10 @@
         </is>
       </c>
       <c r="R155" t="n">
-        <v>590</v>
+        <v>886</v>
       </c>
       <c r="S155" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -11948,16 +11948,16 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J156" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K156" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L156" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M156" t="n">
         <v>3</v>
@@ -11977,10 +11977,10 @@
         </is>
       </c>
       <c r="R156" t="n">
-        <v>730</v>
+        <v>823</v>
       </c>
       <c r="S156" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -12022,36 +12022,36 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J157" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K157" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L157" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="M157" t="n">
         <v>3</v>
       </c>
       <c r="N157" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O157" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P157" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R157" t="n">
-        <v>858</v>
+        <v>764</v>
       </c>
       <c r="S157" t="n">
         <v>0.01</v>
@@ -12096,7 +12096,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J158" t="n">
         <v>89</v>
@@ -12105,19 +12105,19 @@
         <v>23</v>
       </c>
       <c r="L158" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M158" t="n">
         <v>3</v>
       </c>
       <c r="N158" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O158" t="n">
         <v>5</v>
       </c>
       <c r="P158" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -12125,10 +12125,10 @@
         </is>
       </c>
       <c r="R158" t="n">
-        <v>780</v>
+        <v>839</v>
       </c>
       <c r="S158" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>

--- a/data/fems_latest_wxMinMax.xlsx
+++ b/data/fems_latest_wxMinMax.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -552,36 +552,36 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J2" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L2" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>11</v>
       </c>
-      <c r="O2" t="n">
-        <v>7</v>
-      </c>
-      <c r="P2" t="n">
-        <v>16</v>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>863</v>
+        <v>842</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -617,7 +617,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -626,36 +626,36 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J3" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O3" t="n">
         <v>14</v>
-      </c>
-      <c r="O3" t="n">
-        <v>8</v>
       </c>
       <c r="P3" t="n">
         <v>28</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -691,7 +691,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -700,28 +700,28 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J4" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="K4" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>806</v>
+        <v>655</v>
       </c>
       <c r="S4" t="n">
         <v>0.02</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -774,39 +774,39 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J5" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L5" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
         <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>695</v>
+        <v>649</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -848,36 +848,36 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J6" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
         <v>11</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>916</v>
+        <v>875</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -925,33 +925,33 @@
         <v>59</v>
       </c>
       <c r="J7" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K7" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
         <v>8</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
         <v>11</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>576</v>
+        <v>730</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J8" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L8" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M8" t="n">
         <v>5</v>
@@ -1017,15 +1017,15 @@
         <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>935</v>
+        <v>821</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1073,10 +1073,10 @@
         <v>53</v>
       </c>
       <c r="J9" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
         <v>93</v>
@@ -1095,14 +1095,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>913</v>
+        <v>775</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1144,25 +1144,25 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J10" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
         <v>9</v>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P10" t="n">
         <v>21</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>888</v>
+        <v>837</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1218,39 +1218,39 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J11" t="n">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="K11" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" t="n">
         <v>7</v>
       </c>
-      <c r="O11" t="n">
-        <v>6</v>
-      </c>
       <c r="P11" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>937</v>
+        <v>840</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1292,36 +1292,36 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J12" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L12" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>862</v>
+        <v>779</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1366,28 +1366,28 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J13" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K13" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L13" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P13" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>883</v>
+        <v>813</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1440,25 +1440,25 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J14" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="K14" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="L14" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
         <v>8</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>835</v>
+        <v>653</v>
       </c>
       <c r="S14" t="n">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J15" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L15" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="M15" t="n">
         <v>2</v>
@@ -1539,11 +1539,11 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>948</v>
+        <v>844</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1588,39 +1588,39 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J16" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K16" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L16" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>862</v>
+        <v>639</v>
       </c>
       <c r="S16" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J17" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="K17" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L17" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="M17" t="n">
         <v>3</v>
@@ -1687,14 +1687,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>763</v>
+        <v>740</v>
       </c>
       <c r="S17" t="n">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1736,39 +1736,39 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J18" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K18" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L18" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P18" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>837</v>
+        <v>652</v>
       </c>
       <c r="S18" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1810,39 +1810,39 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J19" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K19" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L19" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M19" t="n">
         <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>846</v>
+        <v>781</v>
       </c>
       <c r="S19" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1884,39 +1884,39 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J20" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K20" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="L20" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>946</v>
+        <v>878</v>
       </c>
       <c r="S20" t="n">
-        <v>0.09</v>
+        <v>0.79</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1961,33 +1961,33 @@
         <v>70</v>
       </c>
       <c r="J21" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L21" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O21" t="n">
         <v>10</v>
       </c>
       <c r="P21" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1/7/1 17:00 LMT</t>
+          <t>1/6/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>946</v>
+        <v>834</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2032,28 +2032,28 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J22" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="K22" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="L22" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
+        <v>5</v>
+      </c>
+      <c r="O22" t="n">
         <v>7</v>
       </c>
-      <c r="O22" t="n">
-        <v>6</v>
-      </c>
       <c r="P22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>934</v>
+        <v>807</v>
       </c>
       <c r="S22" t="n">
-        <v>0.02</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2106,39 +2106,39 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J23" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="K23" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L23" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
         <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>832</v>
+        <v>847</v>
       </c>
       <c r="S23" t="n">
-        <v>0.03</v>
+        <v>0.19</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2180,39 +2180,39 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J24" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="K24" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L24" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
         <v>13</v>
       </c>
       <c r="O24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P24" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>891</v>
+        <v>776</v>
       </c>
       <c r="S24" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2254,39 +2254,39 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J25" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="K25" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L25" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>842</v>
+        <v>805</v>
       </c>
       <c r="S25" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2328,39 +2328,39 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J26" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="K26" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="L26" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>866</v>
+        <v>755</v>
       </c>
       <c r="S26" t="n">
-        <v>0.06</v>
+        <v>0.42</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2402,36 +2402,36 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J27" t="n">
         <v>94</v>
       </c>
       <c r="K27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L27" t="n">
         <v>58</v>
       </c>
       <c r="M27" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>9</v>
+      </c>
+      <c r="O27" t="n">
         <v>5</v>
       </c>
-      <c r="N27" t="n">
-        <v>11</v>
-      </c>
-      <c r="O27" t="n">
-        <v>7</v>
-      </c>
       <c r="P27" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1/8/1 17:00 LMT</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>957</v>
+        <v>825</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2476,36 +2476,36 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J28" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K28" t="n">
         <v>19</v>
       </c>
       <c r="L28" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N28" t="n">
         <v>13</v>
       </c>
       <c r="O28" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="P28" t="n">
         <v>23</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>895</v>
+        <v>882</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2550,36 +2550,36 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J29" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L29" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
         <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P29" t="n">
         <v>7</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1/6/1 17:00 LMT</t>
+          <t>1/7/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>857</v>
+        <v>779</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2624,36 +2624,36 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J30" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K30" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L30" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>914</v>
+        <v>881</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2698,16 +2698,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J31" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K31" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="L31" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -2716,21 +2716,21 @@
         <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P31" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>756</v>
+        <v>797</v>
       </c>
       <c r="S31" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2772,36 +2772,36 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J32" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K32" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L32" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
         <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P32" t="n">
         <v>15</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>845</v>
+        <v>765</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J33" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K33" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L33" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="M33" t="n">
         <v>2</v>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>791</v>
+        <v>713</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2920,39 +2920,39 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J34" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K34" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="L34" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="M34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N34" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>897</v>
+        <v>676</v>
       </c>
       <c r="S34" t="n">
-        <v>0.08</v>
+        <v>0.22</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2994,25 +2994,25 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J35" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="K35" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L35" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>10</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P35" t="n">
         <v>15</v>
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>866</v>
+        <v>736</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3068,16 +3068,16 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J36" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L36" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M36" t="n">
         <v>2</v>
@@ -3093,14 +3093,14 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1/8/1 17:00 LMT</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>788</v>
+        <v>578</v>
       </c>
       <c r="S36" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3142,39 +3142,39 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J37" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K37" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L37" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="M37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N37" t="n">
         <v>8</v>
       </c>
       <c r="O37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
         <v>11</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>842</v>
+        <v>733</v>
       </c>
       <c r="S37" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3216,36 +3216,36 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J38" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K38" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L38" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="M38" t="n">
         <v>5</v>
       </c>
       <c r="N38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>916</v>
+        <v>876</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3293,36 +3293,36 @@
         <v>75</v>
       </c>
       <c r="J39" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K39" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L39" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M39" t="n">
         <v>3</v>
       </c>
       <c r="N39" t="n">
+        <v>7</v>
+      </c>
+      <c r="O39" t="n">
         <v>9</v>
       </c>
-      <c r="O39" t="n">
-        <v>11</v>
-      </c>
       <c r="P39" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>912</v>
+        <v>820</v>
       </c>
       <c r="S39" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3364,39 +3364,39 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J40" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K40" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="L40" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="M40" t="n">
         <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P40" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>860</v>
+        <v>740</v>
       </c>
       <c r="S40" t="n">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3438,39 +3438,39 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J41" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K41" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="L41" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="M41" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N41" t="n">
         <v>16</v>
       </c>
       <c r="O41" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="P41" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>846</v>
+        <v>695</v>
       </c>
       <c r="S41" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3512,28 +3512,28 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J42" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K42" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="L42" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="R42" t="n">
-        <v>801</v>
+        <v>728</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3586,36 +3586,36 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J43" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K43" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L43" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N43" t="n">
         <v>10</v>
       </c>
       <c r="O43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P43" t="n">
         <v>15</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1/7/1 17:00 LMT</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>936</v>
+        <v>815</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3660,39 +3660,39 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J44" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="K44" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="L44" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="M44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N44" t="n">
+        <v>14</v>
+      </c>
+      <c r="O44" t="n">
         <v>16</v>
       </c>
-      <c r="O44" t="n">
-        <v>13</v>
-      </c>
       <c r="P44" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>845</v>
+        <v>613</v>
       </c>
       <c r="S44" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3734,36 +3734,36 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J45" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K45" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L45" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N45" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O45" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P45" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>948</v>
+        <v>822</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3808,39 +3808,39 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J46" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="K46" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="L46" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="M46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
         <v>6</v>
       </c>
       <c r="O46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P46" t="n">
         <v>16</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R46" t="n">
-        <v>950</v>
+        <v>788</v>
       </c>
       <c r="S46" t="n">
-        <v>0.19</v>
+        <v>0.46</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3882,39 +3882,39 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J47" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K47" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="L47" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N47" t="n">
         <v>15</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P47" t="n">
         <v>28</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>808</v>
+        <v>797</v>
       </c>
       <c r="S47" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3956,36 +3956,36 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J48" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K48" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L48" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M48" t="n">
         <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O48" t="n">
         <v>7</v>
       </c>
       <c r="P48" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4030,28 +4030,28 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J49" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K49" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L49" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="M49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N49" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O49" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P49" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>814</v>
+        <v>777</v>
       </c>
       <c r="S49" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4104,39 +4104,39 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J50" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K50" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L50" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="M50" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N50" t="n">
         <v>21</v>
       </c>
       <c r="O50" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="P50" t="n">
         <v>38</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>711</v>
+        <v>757</v>
       </c>
       <c r="S50" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4178,36 +4178,36 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J51" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="K51" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L51" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="M51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N51" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P51" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R51" t="n">
-        <v>907</v>
+        <v>879</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4255,36 +4255,36 @@
         <v>56</v>
       </c>
       <c r="J52" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K52" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L52" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>925</v>
+        <v>750</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4326,25 +4326,25 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J53" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="K53" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="L53" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="M53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
         <v>9</v>
       </c>
       <c r="O53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P53" t="n">
         <v>21</v>
@@ -4355,10 +4355,10 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>850</v>
+        <v>751</v>
       </c>
       <c r="S53" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4400,16 +4400,16 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="J54" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K54" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="L54" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="M54" t="n">
         <v>2</v>
@@ -4425,14 +4425,14 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R54" t="n">
-        <v>891</v>
+        <v>831</v>
       </c>
       <c r="S54" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4474,39 +4474,39 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J55" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="K55" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L55" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="M55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N55" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O55" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P55" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>848</v>
+        <v>859</v>
       </c>
       <c r="S55" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4548,25 +4548,25 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J56" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="K56" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L56" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="M56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
         <v>6</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P56" t="n">
         <v>8</v>
@@ -4577,10 +4577,10 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>806</v>
+        <v>732</v>
       </c>
       <c r="S56" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4622,39 +4622,39 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J57" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="K57" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="L57" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="M57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N57" t="n">
         <v>15</v>
       </c>
       <c r="O57" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>763</v>
+        <v>746</v>
       </c>
       <c r="S57" t="n">
-        <v>0.06</v>
+        <v>0.42</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4699,36 +4699,36 @@
         <v>54</v>
       </c>
       <c r="J58" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K58" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="L58" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="M58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
         <v>9</v>
       </c>
       <c r="O58" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>1/3/1 17:00 LMT</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>699</v>
+        <v>603</v>
       </c>
       <c r="S58" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4770,39 +4770,39 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J59" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K59" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L59" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="M59" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N59" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O59" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="P59" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R59" t="n">
-        <v>907</v>
+        <v>810</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4844,39 +4844,39 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J60" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="K60" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L60" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N60" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O60" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P60" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R60" t="n">
-        <v>940</v>
+        <v>835</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4921,33 +4921,33 @@
         <v>70</v>
       </c>
       <c r="J61" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L61" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="M61" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N61" t="n">
+        <v>14</v>
+      </c>
+      <c r="O61" t="n">
         <v>8</v>
       </c>
-      <c r="O61" t="n">
-        <v>3</v>
-      </c>
       <c r="P61" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>961</v>
+        <v>793</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4992,28 +4992,28 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J62" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="K62" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="L62" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N62" t="n">
         <v>15</v>
       </c>
       <c r="O62" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P62" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>882</v>
+        <v>756</v>
       </c>
       <c r="S62" t="n">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5066,36 +5066,36 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="J63" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="K63" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L63" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O63" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P63" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R63" t="n">
-        <v>869</v>
+        <v>843</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5140,39 +5140,39 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J64" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="K64" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L64" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O64" t="n">
         <v>6</v>
       </c>
       <c r="P64" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R64" t="n">
-        <v>809</v>
+        <v>788</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5214,28 +5214,28 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J65" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="K65" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L65" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="M65" t="n">
         <v>5</v>
       </c>
       <c r="N65" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O65" t="n">
         <v>9</v>
       </c>
       <c r="P65" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>892</v>
+        <v>645</v>
       </c>
       <c r="S65" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5288,25 +5288,25 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J66" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="K66" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="L66" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
         <v>6</v>
       </c>
       <c r="O66" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P66" t="n">
         <v>14</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>835</v>
+        <v>755</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5362,28 +5362,28 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J67" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="K67" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="L67" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="M67" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O67" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P67" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>898</v>
+        <v>708</v>
       </c>
       <c r="S67" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5436,39 +5436,39 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J68" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K68" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="L68" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N68" t="n">
         <v>9</v>
       </c>
       <c r="O68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1/6/1 17:00 LMT</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>768</v>
+        <v>618</v>
       </c>
       <c r="S68" t="n">
-        <v>0.18</v>
+        <v>0.58</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5510,19 +5510,19 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J69" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="K69" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L69" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N69" t="n">
         <v>11</v>
@@ -5535,14 +5535,14 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>921</v>
+        <v>724</v>
       </c>
       <c r="S69" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5584,39 +5584,39 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J70" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K70" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="L70" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="M70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P70" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R70" t="n">
-        <v>912</v>
+        <v>699</v>
       </c>
       <c r="S70" t="n">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5658,28 +5658,28 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J71" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="K71" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L71" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="M71" t="n">
         <v>10</v>
       </c>
       <c r="N71" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="O71" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P71" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5732,39 +5732,39 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J72" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K72" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="L72" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="M72" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N72" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O72" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="P72" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="S72" t="n">
-        <v>0.08</v>
+        <v>0.27</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5806,16 +5806,16 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J73" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L73" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="M73" t="n">
         <v>2</v>
@@ -5831,14 +5831,14 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R73" t="n">
-        <v>911</v>
+        <v>761</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5880,16 +5880,16 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J74" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K74" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L74" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="M74" t="n">
         <v>1</v>
@@ -5909,10 +5909,10 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5954,39 +5954,39 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J75" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="K75" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L75" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="M75" t="n">
         <v>5</v>
       </c>
       <c r="N75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O75" t="n">
         <v>7</v>
       </c>
       <c r="P75" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R75" t="n">
-        <v>803</v>
+        <v>777</v>
       </c>
       <c r="S75" t="n">
-        <v>0.01</v>
+        <v>0.11</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6028,28 +6028,28 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J76" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K76" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L76" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="M76" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N76" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P76" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="R76" t="n">
-        <v>741</v>
+        <v>673</v>
       </c>
       <c r="S76" t="n">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>8/28/2026</t>
+          <t>8/29/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6102,28 +6102,28 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J77" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K77" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L77" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="M77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N77" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>806</v>
+        <v>652</v>
       </c>
       <c r="S77" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
